--- a/030_設計ドキュメント/Nablarch開発標準設計書一覧.xlsx
+++ b/030_設計ドキュメント/Nablarch開発標準設計書一覧.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24931"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24326"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C22ED196-2359-4B51-8C16-4BE44E4A5F7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87493DE4-ED9D-4F1C-A3D6-399A1B9AA9EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2100" yWindow="1770" windowWidth="33090" windowHeight="18225" tabRatio="822" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21390" tabRatio="822" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="34" r:id="rId1"/>
@@ -17,13 +17,13 @@
     <sheet name="3. 設計書とソースコードの対応" sheetId="43" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'1. 概要'!$A$1:$AI$12</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'1. 概要'!$A$1:$AI$36</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'2.1. 設計書体系図'!$A$1:$BA$72</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'2.2. 設計書一覧'!$A$1:$AQ$75</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">'3. 設計書とソースコードの対応'!$A$1:$AI$125</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">表紙!$A$1:$S$39</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">変更履歴!$A$1:$AI$39</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">目次!$A$1:$AI$35</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">目次!$A$1:$AI$36</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'1. 概要'!$1:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'2.1. 設計書体系図'!$1:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'2.2. 設計書一覧'!$1:$11</definedName>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="251">
   <si>
     <t>PJ名</t>
   </si>
@@ -1351,6 +1351,175 @@
     <rPh sb="33" eb="35">
       <t>ヘンコウ</t>
     </rPh>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>特に断りがない限り、以下の表記はJakarta EEの仕様を指すものとする。</t>
+    <rPh sb="10" eb="12">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ヒョウキ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>サ</t>
+    </rPh>
+    <phoneticPr fontId="30"/>
+  </si>
+  <si>
+    <t>No.</t>
+    <phoneticPr fontId="30"/>
+  </si>
+  <si>
+    <t>表記</t>
+    <rPh sb="0" eb="2">
+      <t>ヒョウキ</t>
+    </rPh>
+    <phoneticPr fontId="30"/>
+  </si>
+  <si>
+    <t>Jakarta EE仕様</t>
+    <rPh sb="10" eb="12">
+      <t>シヨウ</t>
+    </rPh>
+    <phoneticPr fontId="30"/>
+  </si>
+  <si>
+    <t>JSF</t>
+  </si>
+  <si>
+    <t>Jakarta Faces</t>
+  </si>
+  <si>
+    <t>JASPIC</t>
+  </si>
+  <si>
+    <t>Jakarta Authentication</t>
+  </si>
+  <si>
+    <t>JACC</t>
+  </si>
+  <si>
+    <t>Jakarta Authorization</t>
+  </si>
+  <si>
+    <t>JMS</t>
+  </si>
+  <si>
+    <t>Jakarta Messaging</t>
+  </si>
+  <si>
+    <t>JPA</t>
+  </si>
+  <si>
+    <t>Jakarta Persistence</t>
+  </si>
+  <si>
+    <t>JTA</t>
+  </si>
+  <si>
+    <t>Jakarta Transactions</t>
+  </si>
+  <si>
+    <t>JBatch / JSR352</t>
+    <phoneticPr fontId="30"/>
+  </si>
+  <si>
+    <t>Jakarta Batch</t>
+  </si>
+  <si>
+    <t>JCA</t>
+  </si>
+  <si>
+    <t>Jakarta Connectors</t>
+  </si>
+  <si>
+    <t>JAF</t>
+  </si>
+  <si>
+    <t>Jakarta Activation</t>
+  </si>
+  <si>
+    <t>EL</t>
+  </si>
+  <si>
+    <t>Jakarta Expression Language</t>
+  </si>
+  <si>
+    <t>EJB</t>
+  </si>
+  <si>
+    <t>Jakarta Enterprise Beans</t>
+  </si>
+  <si>
+    <t>JAXB</t>
+  </si>
+  <si>
+    <t>Jakarta XML Binding</t>
+  </si>
+  <si>
+    <t>JSON-B</t>
+  </si>
+  <si>
+    <t>Jakarta JSON Binding</t>
+  </si>
+  <si>
+    <t>JSON-P</t>
+  </si>
+  <si>
+    <t>Jakarta JSON Processing</t>
+  </si>
+  <si>
+    <t>JSP</t>
+  </si>
+  <si>
+    <t>Jakarta Server Pages</t>
+  </si>
+  <si>
+    <t>JAX-WS</t>
+  </si>
+  <si>
+    <t>Jakarta XML Web Services</t>
+  </si>
+  <si>
+    <t>JAX-RS</t>
+  </si>
+  <si>
+    <t>Jakarta RESTful Web Services</t>
+  </si>
+  <si>
+    <t>JSTL</t>
+  </si>
+  <si>
+    <t>Jakarta Standard Tag Library</t>
+  </si>
+  <si>
+    <t>CDI</t>
+  </si>
+  <si>
+    <t>Jakarta Contexts and Dependency Injection</t>
+  </si>
+  <si>
+    <t>1.2. 本書におけるJakartaEE仕様への読み替えについて</t>
+    <rPh sb="5" eb="7">
+      <t>ホンショ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="30"/>
+  </si>
+  <si>
+    <t>1.2. 本書におけるJakartaEE仕様への読み替えについて</t>
     <phoneticPr fontId="10"/>
   </si>
 </sst>
@@ -1645,7 +1814,7 @@
       <charset val="128"/>
     </font>
   </fonts>
-  <fills count="26">
+  <fills count="27">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1771,6 +1940,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.34998626667073579"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2242,7 +2417,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="172">
+  <cellXfs count="183">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="41"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="41" applyAlignment="1">
@@ -2403,8 +2578,102 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="31" fontId="7" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="23" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="22" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="177" fontId="2" fillId="0" borderId="10" xfId="45" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
@@ -2523,98 +2792,14 @@
     <xf numFmtId="14" fontId="2" fillId="0" borderId="12" xfId="41" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="41" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="10" xfId="41" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="23" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="22" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="12" xfId="41" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="177" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
@@ -2625,13 +2810,31 @@
     <xf numFmtId="177" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="10" xfId="41" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="33" fillId="24" borderId="13" xfId="41" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="12" xfId="41" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="33" fillId="24" borderId="14" xfId="41" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="41" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="24" borderId="15" xfId="41" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="24" borderId="24" xfId="41" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="24" borderId="0" xfId="41" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="24" borderId="25" xfId="41" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="24" borderId="16" xfId="41" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="24" borderId="17" xfId="41" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="24" borderId="18" xfId="41" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="41" applyBorder="1" applyAlignment="1">
@@ -2661,34 +2864,19 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="41" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="24" borderId="13" xfId="41" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="44"/>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="20" xfId="44" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="10" xfId="44" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="11" xfId="44" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="12" xfId="44" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="44" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="44" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="44" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="24" borderId="14" xfId="41" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="24" borderId="15" xfId="41" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="24" borderId="24" xfId="41" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="24" borderId="0" xfId="41" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="24" borderId="25" xfId="41" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="24" borderId="16" xfId="41" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="24" borderId="17" xfId="41" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="24" borderId="18" xfId="41" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="44" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="44" applyFont="1"/>
   </cellXfs>
   <cellStyles count="52">
     <cellStyle name="20% - アクセント 1" xfId="1" builtinId="30" customBuiltin="1"/>
@@ -13611,12 +13799,12 @@
       <c r="F25" s="22"/>
       <c r="G25" s="22"/>
       <c r="H25" s="22"/>
-      <c r="I25" s="76">
+      <c r="I25" s="77">
         <f ca="1">IF(INDIRECT("変更履歴!D8")="","",MAX(INDIRECT("変更履歴!D8"):INDIRECT("変更履歴!F33")))</f>
         <v>44848</v>
       </c>
-      <c r="J25" s="76"/>
-      <c r="K25" s="76"/>
+      <c r="J25" s="77"/>
+      <c r="K25" s="77"/>
     </row>
     <row r="26" spans="6:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F26" s="22"/>
@@ -14210,55 +14398,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="93" t="s">
+      <c r="A1" s="125" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="85"/>
-      <c r="D1" s="86"/>
-      <c r="E1" s="94"/>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
-      <c r="H1" s="88"/>
-      <c r="I1" s="88"/>
-      <c r="J1" s="88"/>
-      <c r="K1" s="88"/>
-      <c r="L1" s="88"/>
-      <c r="M1" s="88"/>
-      <c r="N1" s="89"/>
-      <c r="O1" s="95" t="s">
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="118"/>
+      <c r="E1" s="126"/>
+      <c r="F1" s="120"/>
+      <c r="G1" s="120"/>
+      <c r="H1" s="120"/>
+      <c r="I1" s="120"/>
+      <c r="J1" s="120"/>
+      <c r="K1" s="120"/>
+      <c r="L1" s="120"/>
+      <c r="M1" s="120"/>
+      <c r="N1" s="121"/>
+      <c r="O1" s="127" t="s">
         <v>11</v>
       </c>
-      <c r="P1" s="96"/>
-      <c r="Q1" s="96"/>
-      <c r="R1" s="97"/>
-      <c r="S1" s="104" t="s">
+      <c r="P1" s="128"/>
+      <c r="Q1" s="128"/>
+      <c r="R1" s="129"/>
+      <c r="S1" s="136" t="s">
         <v>44</v>
       </c>
-      <c r="T1" s="105"/>
-      <c r="U1" s="105"/>
-      <c r="V1" s="105"/>
-      <c r="W1" s="105"/>
-      <c r="X1" s="105"/>
-      <c r="Y1" s="105"/>
-      <c r="Z1" s="106"/>
-      <c r="AA1" s="84" t="s">
+      <c r="T1" s="137"/>
+      <c r="U1" s="137"/>
+      <c r="V1" s="137"/>
+      <c r="W1" s="137"/>
+      <c r="X1" s="137"/>
+      <c r="Y1" s="137"/>
+      <c r="Z1" s="138"/>
+      <c r="AA1" s="116" t="s">
         <v>12</v>
       </c>
-      <c r="AB1" s="86"/>
-      <c r="AC1" s="113" t="str">
+      <c r="AB1" s="118"/>
+      <c r="AC1" s="145" t="str">
         <f>IF(AF8="","",AF8)</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="114"/>
-      <c r="AE1" s="114"/>
-      <c r="AF1" s="115"/>
-      <c r="AG1" s="77">
+      <c r="AD1" s="146"/>
+      <c r="AE1" s="146"/>
+      <c r="AF1" s="147"/>
+      <c r="AG1" s="109">
         <f>IF(D8="","",D8)</f>
         <v>43336</v>
       </c>
-      <c r="AH1" s="78"/>
-      <c r="AI1" s="79"/>
+      <c r="AH1" s="110"/>
+      <c r="AI1" s="111"/>
       <c r="AJ1" s="1"/>
       <c r="AK1" s="1"/>
       <c r="AL1" s="1"/>
@@ -14266,51 +14454,51 @@
       <c r="AN1" s="2"/>
     </row>
     <row r="2" spans="1:40" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="84" t="s">
+      <c r="A2" s="116" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="85"/>
-      <c r="C2" s="85"/>
-      <c r="D2" s="86"/>
-      <c r="E2" s="87"/>
-      <c r="F2" s="88"/>
-      <c r="G2" s="88"/>
-      <c r="H2" s="88"/>
-      <c r="I2" s="88"/>
-      <c r="J2" s="88"/>
-      <c r="K2" s="88"/>
-      <c r="L2" s="88"/>
-      <c r="M2" s="88"/>
-      <c r="N2" s="89"/>
-      <c r="O2" s="98"/>
-      <c r="P2" s="99"/>
-      <c r="Q2" s="99"/>
-      <c r="R2" s="100"/>
-      <c r="S2" s="107"/>
-      <c r="T2" s="108"/>
-      <c r="U2" s="108"/>
-      <c r="V2" s="108"/>
-      <c r="W2" s="108"/>
-      <c r="X2" s="108"/>
-      <c r="Y2" s="108"/>
-      <c r="Z2" s="109"/>
-      <c r="AA2" s="84" t="s">
+      <c r="B2" s="117"/>
+      <c r="C2" s="117"/>
+      <c r="D2" s="118"/>
+      <c r="E2" s="119"/>
+      <c r="F2" s="120"/>
+      <c r="G2" s="120"/>
+      <c r="H2" s="120"/>
+      <c r="I2" s="120"/>
+      <c r="J2" s="120"/>
+      <c r="K2" s="120"/>
+      <c r="L2" s="120"/>
+      <c r="M2" s="120"/>
+      <c r="N2" s="121"/>
+      <c r="O2" s="130"/>
+      <c r="P2" s="131"/>
+      <c r="Q2" s="131"/>
+      <c r="R2" s="132"/>
+      <c r="S2" s="139"/>
+      <c r="T2" s="140"/>
+      <c r="U2" s="140"/>
+      <c r="V2" s="140"/>
+      <c r="W2" s="140"/>
+      <c r="X2" s="140"/>
+      <c r="Y2" s="140"/>
+      <c r="Z2" s="141"/>
+      <c r="AA2" s="116" t="s">
         <v>13</v>
       </c>
-      <c r="AB2" s="86"/>
-      <c r="AC2" s="90" t="str">
+      <c r="AB2" s="118"/>
+      <c r="AC2" s="122" t="str">
         <f ca="1">IF(COUNTA(AF9:AF33)&lt;&gt;0,INDIRECT("AF"&amp;(COUNTA(AF9:AF33)+8)),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD2" s="91"/>
-      <c r="AE2" s="91"/>
-      <c r="AF2" s="92"/>
-      <c r="AG2" s="77">
+      <c r="AD2" s="123"/>
+      <c r="AE2" s="123"/>
+      <c r="AF2" s="124"/>
+      <c r="AG2" s="109">
         <f>IF(D9="","",MAX(D9:F33))</f>
         <v>44848</v>
       </c>
-      <c r="AH2" s="78"/>
-      <c r="AI2" s="79"/>
+      <c r="AH2" s="110"/>
+      <c r="AI2" s="111"/>
       <c r="AJ2" s="1"/>
       <c r="AK2" s="1"/>
       <c r="AL2" s="1"/>
@@ -14318,43 +14506,43 @@
       <c r="AN2" s="1"/>
     </row>
     <row r="3" spans="1:40" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="84" t="s">
+      <c r="A3" s="116" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="85"/>
-      <c r="C3" s="85"/>
-      <c r="D3" s="86"/>
-      <c r="E3" s="87"/>
-      <c r="F3" s="88"/>
-      <c r="G3" s="88"/>
-      <c r="H3" s="88"/>
-      <c r="I3" s="88"/>
-      <c r="J3" s="88"/>
-      <c r="K3" s="88"/>
-      <c r="L3" s="88"/>
-      <c r="M3" s="88"/>
-      <c r="N3" s="89"/>
-      <c r="O3" s="101"/>
-      <c r="P3" s="102"/>
-      <c r="Q3" s="102"/>
-      <c r="R3" s="103"/>
-      <c r="S3" s="110"/>
-      <c r="T3" s="111"/>
-      <c r="U3" s="111"/>
-      <c r="V3" s="111"/>
-      <c r="W3" s="111"/>
-      <c r="X3" s="111"/>
-      <c r="Y3" s="111"/>
-      <c r="Z3" s="112"/>
-      <c r="AA3" s="84"/>
-      <c r="AB3" s="86"/>
-      <c r="AC3" s="113"/>
-      <c r="AD3" s="114"/>
-      <c r="AE3" s="114"/>
-      <c r="AF3" s="115"/>
-      <c r="AG3" s="77"/>
-      <c r="AH3" s="78"/>
-      <c r="AI3" s="79"/>
+      <c r="B3" s="117"/>
+      <c r="C3" s="117"/>
+      <c r="D3" s="118"/>
+      <c r="E3" s="119"/>
+      <c r="F3" s="120"/>
+      <c r="G3" s="120"/>
+      <c r="H3" s="120"/>
+      <c r="I3" s="120"/>
+      <c r="J3" s="120"/>
+      <c r="K3" s="120"/>
+      <c r="L3" s="120"/>
+      <c r="M3" s="120"/>
+      <c r="N3" s="121"/>
+      <c r="O3" s="133"/>
+      <c r="P3" s="134"/>
+      <c r="Q3" s="134"/>
+      <c r="R3" s="135"/>
+      <c r="S3" s="142"/>
+      <c r="T3" s="143"/>
+      <c r="U3" s="143"/>
+      <c r="V3" s="143"/>
+      <c r="W3" s="143"/>
+      <c r="X3" s="143"/>
+      <c r="Y3" s="143"/>
+      <c r="Z3" s="144"/>
+      <c r="AA3" s="116"/>
+      <c r="AB3" s="118"/>
+      <c r="AC3" s="145"/>
+      <c r="AD3" s="146"/>
+      <c r="AE3" s="146"/>
+      <c r="AF3" s="147"/>
+      <c r="AG3" s="109"/>
+      <c r="AH3" s="110"/>
+      <c r="AI3" s="111"/>
       <c r="AJ3" s="1"/>
       <c r="AK3" s="1"/>
       <c r="AL3" s="1"/>
@@ -14391,1204 +14579,1048 @@
       <c r="A7" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="80" t="s">
+      <c r="B7" s="112" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="81"/>
-      <c r="D7" s="80" t="s">
+      <c r="C7" s="113"/>
+      <c r="D7" s="112" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="82"/>
-      <c r="F7" s="81"/>
-      <c r="G7" s="80" t="s">
+      <c r="E7" s="114"/>
+      <c r="F7" s="113"/>
+      <c r="G7" s="112" t="s">
         <v>8</v>
       </c>
-      <c r="H7" s="82"/>
-      <c r="I7" s="81"/>
-      <c r="J7" s="83" t="s">
+      <c r="H7" s="114"/>
+      <c r="I7" s="113"/>
+      <c r="J7" s="115" t="s">
         <v>23</v>
       </c>
-      <c r="K7" s="82"/>
-      <c r="L7" s="82"/>
-      <c r="M7" s="82"/>
-      <c r="N7" s="82"/>
-      <c r="O7" s="82"/>
-      <c r="P7" s="81"/>
-      <c r="Q7" s="80" t="s">
+      <c r="K7" s="114"/>
+      <c r="L7" s="114"/>
+      <c r="M7" s="114"/>
+      <c r="N7" s="114"/>
+      <c r="O7" s="114"/>
+      <c r="P7" s="113"/>
+      <c r="Q7" s="112" t="s">
         <v>9</v>
       </c>
-      <c r="R7" s="82"/>
-      <c r="S7" s="82"/>
-      <c r="T7" s="82"/>
-      <c r="U7" s="82"/>
-      <c r="V7" s="82"/>
-      <c r="W7" s="82"/>
-      <c r="X7" s="82"/>
-      <c r="Y7" s="82"/>
-      <c r="Z7" s="82"/>
-      <c r="AA7" s="82"/>
-      <c r="AB7" s="82"/>
-      <c r="AC7" s="82"/>
-      <c r="AD7" s="82"/>
-      <c r="AE7" s="81"/>
-      <c r="AF7" s="80" t="s">
+      <c r="R7" s="114"/>
+      <c r="S7" s="114"/>
+      <c r="T7" s="114"/>
+      <c r="U7" s="114"/>
+      <c r="V7" s="114"/>
+      <c r="W7" s="114"/>
+      <c r="X7" s="114"/>
+      <c r="Y7" s="114"/>
+      <c r="Z7" s="114"/>
+      <c r="AA7" s="114"/>
+      <c r="AB7" s="114"/>
+      <c r="AC7" s="114"/>
+      <c r="AD7" s="114"/>
+      <c r="AE7" s="113"/>
+      <c r="AF7" s="112" t="s">
         <v>10</v>
       </c>
-      <c r="AG7" s="82"/>
-      <c r="AH7" s="82"/>
-      <c r="AI7" s="81"/>
+      <c r="AG7" s="114"/>
+      <c r="AH7" s="114"/>
+      <c r="AI7" s="113"/>
     </row>
     <row r="8" spans="1:40" s="12" customFormat="1" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
       <c r="A8" s="16">
         <v>1</v>
       </c>
-      <c r="B8" s="129" t="s">
+      <c r="B8" s="95" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="130"/>
-      <c r="D8" s="131">
+      <c r="C8" s="96"/>
+      <c r="D8" s="97">
         <v>43336</v>
       </c>
-      <c r="E8" s="132"/>
-      <c r="F8" s="133"/>
-      <c r="G8" s="134" t="s">
+      <c r="E8" s="98"/>
+      <c r="F8" s="99"/>
+      <c r="G8" s="100" t="s">
         <v>18</v>
       </c>
-      <c r="H8" s="135"/>
-      <c r="I8" s="136"/>
-      <c r="J8" s="137" t="s">
+      <c r="H8" s="101"/>
+      <c r="I8" s="102"/>
+      <c r="J8" s="103" t="s">
         <v>19</v>
       </c>
-      <c r="K8" s="138"/>
-      <c r="L8" s="138"/>
-      <c r="M8" s="138"/>
-      <c r="N8" s="138"/>
-      <c r="O8" s="138"/>
-      <c r="P8" s="139"/>
-      <c r="Q8" s="140" t="s">
+      <c r="K8" s="104"/>
+      <c r="L8" s="104"/>
+      <c r="M8" s="104"/>
+      <c r="N8" s="104"/>
+      <c r="O8" s="104"/>
+      <c r="P8" s="105"/>
+      <c r="Q8" s="106" t="s">
         <v>20</v>
       </c>
-      <c r="R8" s="141"/>
-      <c r="S8" s="141"/>
-      <c r="T8" s="141"/>
-      <c r="U8" s="141"/>
-      <c r="V8" s="141"/>
-      <c r="W8" s="141"/>
-      <c r="X8" s="141"/>
-      <c r="Y8" s="141"/>
-      <c r="Z8" s="141"/>
-      <c r="AA8" s="141"/>
-      <c r="AB8" s="141"/>
-      <c r="AC8" s="141"/>
-      <c r="AD8" s="141"/>
-      <c r="AE8" s="142"/>
-      <c r="AF8" s="137" t="s">
+      <c r="R8" s="107"/>
+      <c r="S8" s="107"/>
+      <c r="T8" s="107"/>
+      <c r="U8" s="107"/>
+      <c r="V8" s="107"/>
+      <c r="W8" s="107"/>
+      <c r="X8" s="107"/>
+      <c r="Y8" s="107"/>
+      <c r="Z8" s="107"/>
+      <c r="AA8" s="107"/>
+      <c r="AB8" s="107"/>
+      <c r="AC8" s="107"/>
+      <c r="AD8" s="107"/>
+      <c r="AE8" s="108"/>
+      <c r="AF8" s="103" t="s">
         <v>21</v>
       </c>
-      <c r="AG8" s="138"/>
-      <c r="AH8" s="138"/>
-      <c r="AI8" s="139"/>
+      <c r="AG8" s="104"/>
+      <c r="AH8" s="104"/>
+      <c r="AI8" s="105"/>
     </row>
     <row r="9" spans="1:40" s="12" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="13">
         <v>2</v>
       </c>
-      <c r="B9" s="116" t="s">
+      <c r="B9" s="91" t="s">
         <v>199</v>
       </c>
-      <c r="C9" s="117"/>
-      <c r="D9" s="118">
+      <c r="C9" s="79"/>
+      <c r="D9" s="80">
         <v>44848</v>
       </c>
-      <c r="E9" s="119"/>
-      <c r="F9" s="120"/>
-      <c r="G9" s="121" t="s">
+      <c r="E9" s="81"/>
+      <c r="F9" s="82"/>
+      <c r="G9" s="92" t="s">
         <v>4</v>
       </c>
-      <c r="H9" s="122"/>
-      <c r="I9" s="117"/>
-      <c r="J9" s="123" t="s">
+      <c r="H9" s="83"/>
+      <c r="I9" s="79"/>
+      <c r="J9" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="K9" s="124"/>
-      <c r="L9" s="124"/>
-      <c r="M9" s="124"/>
-      <c r="N9" s="124"/>
-      <c r="O9" s="124"/>
-      <c r="P9" s="125"/>
-      <c r="Q9" s="126" t="s">
+      <c r="K9" s="85"/>
+      <c r="L9" s="85"/>
+      <c r="M9" s="85"/>
+      <c r="N9" s="85"/>
+      <c r="O9" s="85"/>
+      <c r="P9" s="86"/>
+      <c r="Q9" s="94" t="s">
         <v>206</v>
       </c>
-      <c r="R9" s="127"/>
-      <c r="S9" s="127"/>
-      <c r="T9" s="127"/>
-      <c r="U9" s="127"/>
-      <c r="V9" s="127"/>
-      <c r="W9" s="127"/>
-      <c r="X9" s="127"/>
-      <c r="Y9" s="127"/>
-      <c r="Z9" s="127"/>
-      <c r="AA9" s="127"/>
-      <c r="AB9" s="127"/>
-      <c r="AC9" s="127"/>
-      <c r="AD9" s="127"/>
-      <c r="AE9" s="128"/>
-      <c r="AF9" s="123" t="s">
+      <c r="R9" s="88"/>
+      <c r="S9" s="88"/>
+      <c r="T9" s="88"/>
+      <c r="U9" s="88"/>
+      <c r="V9" s="88"/>
+      <c r="W9" s="88"/>
+      <c r="X9" s="88"/>
+      <c r="Y9" s="88"/>
+      <c r="Z9" s="88"/>
+      <c r="AA9" s="88"/>
+      <c r="AB9" s="88"/>
+      <c r="AC9" s="88"/>
+      <c r="AD9" s="88"/>
+      <c r="AE9" s="89"/>
+      <c r="AF9" s="93" t="s">
         <v>21</v>
       </c>
-      <c r="AG9" s="124"/>
-      <c r="AH9" s="124"/>
-      <c r="AI9" s="125"/>
+      <c r="AG9" s="85"/>
+      <c r="AH9" s="85"/>
+      <c r="AI9" s="86"/>
     </row>
     <row r="10" spans="1:40" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="13"/>
-      <c r="B10" s="143"/>
-      <c r="C10" s="117"/>
-      <c r="D10" s="118"/>
-      <c r="E10" s="119"/>
-      <c r="F10" s="120"/>
-      <c r="G10" s="143"/>
-      <c r="H10" s="122"/>
-      <c r="I10" s="117"/>
-      <c r="J10" s="144"/>
-      <c r="K10" s="124"/>
-      <c r="L10" s="124"/>
-      <c r="M10" s="124"/>
-      <c r="N10" s="124"/>
-      <c r="O10" s="124"/>
-      <c r="P10" s="125"/>
-      <c r="Q10" s="145"/>
-      <c r="R10" s="127"/>
-      <c r="S10" s="127"/>
-      <c r="T10" s="127"/>
-      <c r="U10" s="127"/>
-      <c r="V10" s="127"/>
-      <c r="W10" s="127"/>
-      <c r="X10" s="127"/>
-      <c r="Y10" s="127"/>
-      <c r="Z10" s="127"/>
-      <c r="AA10" s="127"/>
-      <c r="AB10" s="127"/>
-      <c r="AC10" s="127"/>
-      <c r="AD10" s="127"/>
-      <c r="AE10" s="128"/>
-      <c r="AF10" s="144"/>
-      <c r="AG10" s="124"/>
-      <c r="AH10" s="124"/>
-      <c r="AI10" s="125"/>
+      <c r="B10" s="78"/>
+      <c r="C10" s="79"/>
+      <c r="D10" s="80"/>
+      <c r="E10" s="81"/>
+      <c r="F10" s="82"/>
+      <c r="G10" s="78"/>
+      <c r="H10" s="83"/>
+      <c r="I10" s="79"/>
+      <c r="J10" s="84"/>
+      <c r="K10" s="85"/>
+      <c r="L10" s="85"/>
+      <c r="M10" s="85"/>
+      <c r="N10" s="85"/>
+      <c r="O10" s="85"/>
+      <c r="P10" s="86"/>
+      <c r="Q10" s="87"/>
+      <c r="R10" s="88"/>
+      <c r="S10" s="88"/>
+      <c r="T10" s="88"/>
+      <c r="U10" s="88"/>
+      <c r="V10" s="88"/>
+      <c r="W10" s="88"/>
+      <c r="X10" s="88"/>
+      <c r="Y10" s="88"/>
+      <c r="Z10" s="88"/>
+      <c r="AA10" s="88"/>
+      <c r="AB10" s="88"/>
+      <c r="AC10" s="88"/>
+      <c r="AD10" s="88"/>
+      <c r="AE10" s="89"/>
+      <c r="AF10" s="84"/>
+      <c r="AG10" s="85"/>
+      <c r="AH10" s="85"/>
+      <c r="AI10" s="86"/>
     </row>
     <row r="11" spans="1:40" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="13"/>
-      <c r="B11" s="143"/>
-      <c r="C11" s="117"/>
-      <c r="D11" s="118"/>
-      <c r="E11" s="119"/>
-      <c r="F11" s="120"/>
-      <c r="G11" s="143"/>
-      <c r="H11" s="122"/>
-      <c r="I11" s="117"/>
-      <c r="J11" s="144"/>
-      <c r="K11" s="124"/>
-      <c r="L11" s="124"/>
-      <c r="M11" s="124"/>
-      <c r="N11" s="124"/>
-      <c r="O11" s="124"/>
-      <c r="P11" s="125"/>
-      <c r="Q11" s="145"/>
-      <c r="R11" s="127"/>
-      <c r="S11" s="127"/>
-      <c r="T11" s="127"/>
-      <c r="U11" s="127"/>
-      <c r="V11" s="127"/>
-      <c r="W11" s="127"/>
-      <c r="X11" s="127"/>
-      <c r="Y11" s="127"/>
-      <c r="Z11" s="127"/>
-      <c r="AA11" s="127"/>
-      <c r="AB11" s="127"/>
-      <c r="AC11" s="127"/>
-      <c r="AD11" s="127"/>
-      <c r="AE11" s="128"/>
-      <c r="AF11" s="144"/>
-      <c r="AG11" s="124"/>
-      <c r="AH11" s="124"/>
-      <c r="AI11" s="125"/>
+      <c r="B11" s="78"/>
+      <c r="C11" s="79"/>
+      <c r="D11" s="80"/>
+      <c r="E11" s="81"/>
+      <c r="F11" s="82"/>
+      <c r="G11" s="78"/>
+      <c r="H11" s="83"/>
+      <c r="I11" s="79"/>
+      <c r="J11" s="84"/>
+      <c r="K11" s="85"/>
+      <c r="L11" s="85"/>
+      <c r="M11" s="85"/>
+      <c r="N11" s="85"/>
+      <c r="O11" s="85"/>
+      <c r="P11" s="86"/>
+      <c r="Q11" s="87"/>
+      <c r="R11" s="88"/>
+      <c r="S11" s="88"/>
+      <c r="T11" s="88"/>
+      <c r="U11" s="88"/>
+      <c r="V11" s="88"/>
+      <c r="W11" s="88"/>
+      <c r="X11" s="88"/>
+      <c r="Y11" s="88"/>
+      <c r="Z11" s="88"/>
+      <c r="AA11" s="88"/>
+      <c r="AB11" s="88"/>
+      <c r="AC11" s="88"/>
+      <c r="AD11" s="88"/>
+      <c r="AE11" s="89"/>
+      <c r="AF11" s="84"/>
+      <c r="AG11" s="85"/>
+      <c r="AH11" s="85"/>
+      <c r="AI11" s="86"/>
     </row>
     <row r="12" spans="1:40" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="13"/>
-      <c r="B12" s="143"/>
-      <c r="C12" s="117"/>
-      <c r="D12" s="118"/>
-      <c r="E12" s="119"/>
-      <c r="F12" s="120"/>
-      <c r="G12" s="143"/>
-      <c r="H12" s="122"/>
-      <c r="I12" s="117"/>
-      <c r="J12" s="144"/>
-      <c r="K12" s="124"/>
-      <c r="L12" s="124"/>
-      <c r="M12" s="124"/>
-      <c r="N12" s="124"/>
-      <c r="O12" s="124"/>
-      <c r="P12" s="125"/>
-      <c r="Q12" s="145"/>
-      <c r="R12" s="127"/>
-      <c r="S12" s="127"/>
-      <c r="T12" s="127"/>
-      <c r="U12" s="127"/>
-      <c r="V12" s="127"/>
-      <c r="W12" s="127"/>
-      <c r="X12" s="127"/>
-      <c r="Y12" s="127"/>
-      <c r="Z12" s="127"/>
-      <c r="AA12" s="127"/>
-      <c r="AB12" s="127"/>
-      <c r="AC12" s="127"/>
-      <c r="AD12" s="127"/>
-      <c r="AE12" s="128"/>
-      <c r="AF12" s="144"/>
-      <c r="AG12" s="124"/>
-      <c r="AH12" s="124"/>
-      <c r="AI12" s="125"/>
+      <c r="B12" s="78"/>
+      <c r="C12" s="79"/>
+      <c r="D12" s="80"/>
+      <c r="E12" s="81"/>
+      <c r="F12" s="82"/>
+      <c r="G12" s="78"/>
+      <c r="H12" s="83"/>
+      <c r="I12" s="79"/>
+      <c r="J12" s="84"/>
+      <c r="K12" s="85"/>
+      <c r="L12" s="85"/>
+      <c r="M12" s="85"/>
+      <c r="N12" s="85"/>
+      <c r="O12" s="85"/>
+      <c r="P12" s="86"/>
+      <c r="Q12" s="87"/>
+      <c r="R12" s="88"/>
+      <c r="S12" s="88"/>
+      <c r="T12" s="88"/>
+      <c r="U12" s="88"/>
+      <c r="V12" s="88"/>
+      <c r="W12" s="88"/>
+      <c r="X12" s="88"/>
+      <c r="Y12" s="88"/>
+      <c r="Z12" s="88"/>
+      <c r="AA12" s="88"/>
+      <c r="AB12" s="88"/>
+      <c r="AC12" s="88"/>
+      <c r="AD12" s="88"/>
+      <c r="AE12" s="89"/>
+      <c r="AF12" s="84"/>
+      <c r="AG12" s="85"/>
+      <c r="AH12" s="85"/>
+      <c r="AI12" s="86"/>
     </row>
     <row r="13" spans="1:40" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="13"/>
-      <c r="B13" s="143"/>
-      <c r="C13" s="117"/>
-      <c r="D13" s="118"/>
-      <c r="E13" s="119"/>
-      <c r="F13" s="120"/>
-      <c r="G13" s="143"/>
-      <c r="H13" s="122"/>
-      <c r="I13" s="117"/>
-      <c r="J13" s="144"/>
-      <c r="K13" s="124"/>
-      <c r="L13" s="124"/>
-      <c r="M13" s="124"/>
-      <c r="N13" s="124"/>
-      <c r="O13" s="124"/>
-      <c r="P13" s="125"/>
-      <c r="Q13" s="145"/>
-      <c r="R13" s="127"/>
-      <c r="S13" s="127"/>
-      <c r="T13" s="127"/>
-      <c r="U13" s="127"/>
-      <c r="V13" s="127"/>
-      <c r="W13" s="127"/>
-      <c r="X13" s="127"/>
-      <c r="Y13" s="127"/>
-      <c r="Z13" s="127"/>
-      <c r="AA13" s="127"/>
-      <c r="AB13" s="127"/>
-      <c r="AC13" s="127"/>
-      <c r="AD13" s="127"/>
-      <c r="AE13" s="128"/>
-      <c r="AF13" s="144"/>
-      <c r="AG13" s="124"/>
-      <c r="AH13" s="124"/>
-      <c r="AI13" s="125"/>
+      <c r="B13" s="78"/>
+      <c r="C13" s="79"/>
+      <c r="D13" s="80"/>
+      <c r="E13" s="81"/>
+      <c r="F13" s="82"/>
+      <c r="G13" s="78"/>
+      <c r="H13" s="83"/>
+      <c r="I13" s="79"/>
+      <c r="J13" s="84"/>
+      <c r="K13" s="85"/>
+      <c r="L13" s="85"/>
+      <c r="M13" s="85"/>
+      <c r="N13" s="85"/>
+      <c r="O13" s="85"/>
+      <c r="P13" s="86"/>
+      <c r="Q13" s="87"/>
+      <c r="R13" s="88"/>
+      <c r="S13" s="88"/>
+      <c r="T13" s="88"/>
+      <c r="U13" s="88"/>
+      <c r="V13" s="88"/>
+      <c r="W13" s="88"/>
+      <c r="X13" s="88"/>
+      <c r="Y13" s="88"/>
+      <c r="Z13" s="88"/>
+      <c r="AA13" s="88"/>
+      <c r="AB13" s="88"/>
+      <c r="AC13" s="88"/>
+      <c r="AD13" s="88"/>
+      <c r="AE13" s="89"/>
+      <c r="AF13" s="84"/>
+      <c r="AG13" s="85"/>
+      <c r="AH13" s="85"/>
+      <c r="AI13" s="86"/>
     </row>
     <row r="14" spans="1:40" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="13"/>
-      <c r="B14" s="143"/>
-      <c r="C14" s="117"/>
-      <c r="D14" s="118"/>
-      <c r="E14" s="119"/>
-      <c r="F14" s="120"/>
-      <c r="G14" s="143"/>
-      <c r="H14" s="122"/>
-      <c r="I14" s="117"/>
-      <c r="J14" s="144"/>
-      <c r="K14" s="124"/>
-      <c r="L14" s="124"/>
-      <c r="M14" s="124"/>
-      <c r="N14" s="124"/>
-      <c r="O14" s="124"/>
-      <c r="P14" s="125"/>
-      <c r="Q14" s="145"/>
-      <c r="R14" s="127"/>
-      <c r="S14" s="127"/>
-      <c r="T14" s="127"/>
-      <c r="U14" s="127"/>
-      <c r="V14" s="127"/>
-      <c r="W14" s="127"/>
-      <c r="X14" s="127"/>
-      <c r="Y14" s="127"/>
-      <c r="Z14" s="127"/>
-      <c r="AA14" s="127"/>
-      <c r="AB14" s="127"/>
-      <c r="AC14" s="127"/>
-      <c r="AD14" s="127"/>
-      <c r="AE14" s="128"/>
-      <c r="AF14" s="144"/>
-      <c r="AG14" s="124"/>
-      <c r="AH14" s="124"/>
-      <c r="AI14" s="125"/>
+      <c r="B14" s="78"/>
+      <c r="C14" s="79"/>
+      <c r="D14" s="80"/>
+      <c r="E14" s="81"/>
+      <c r="F14" s="82"/>
+      <c r="G14" s="78"/>
+      <c r="H14" s="83"/>
+      <c r="I14" s="79"/>
+      <c r="J14" s="84"/>
+      <c r="K14" s="85"/>
+      <c r="L14" s="85"/>
+      <c r="M14" s="85"/>
+      <c r="N14" s="85"/>
+      <c r="O14" s="85"/>
+      <c r="P14" s="86"/>
+      <c r="Q14" s="87"/>
+      <c r="R14" s="88"/>
+      <c r="S14" s="88"/>
+      <c r="T14" s="88"/>
+      <c r="U14" s="88"/>
+      <c r="V14" s="88"/>
+      <c r="W14" s="88"/>
+      <c r="X14" s="88"/>
+      <c r="Y14" s="88"/>
+      <c r="Z14" s="88"/>
+      <c r="AA14" s="88"/>
+      <c r="AB14" s="88"/>
+      <c r="AC14" s="88"/>
+      <c r="AD14" s="88"/>
+      <c r="AE14" s="89"/>
+      <c r="AF14" s="84"/>
+      <c r="AG14" s="85"/>
+      <c r="AH14" s="85"/>
+      <c r="AI14" s="86"/>
     </row>
     <row r="15" spans="1:40" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="13"/>
-      <c r="B15" s="143"/>
-      <c r="C15" s="117"/>
-      <c r="D15" s="118"/>
-      <c r="E15" s="119"/>
-      <c r="F15" s="120"/>
-      <c r="G15" s="143"/>
-      <c r="H15" s="122"/>
-      <c r="I15" s="117"/>
-      <c r="J15" s="144"/>
-      <c r="K15" s="124"/>
-      <c r="L15" s="124"/>
-      <c r="M15" s="124"/>
-      <c r="N15" s="124"/>
-      <c r="O15" s="124"/>
-      <c r="P15" s="125"/>
-      <c r="Q15" s="145"/>
-      <c r="R15" s="127"/>
-      <c r="S15" s="127"/>
-      <c r="T15" s="127"/>
-      <c r="U15" s="127"/>
-      <c r="V15" s="127"/>
-      <c r="W15" s="127"/>
-      <c r="X15" s="127"/>
-      <c r="Y15" s="127"/>
-      <c r="Z15" s="127"/>
-      <c r="AA15" s="127"/>
-      <c r="AB15" s="127"/>
-      <c r="AC15" s="127"/>
-      <c r="AD15" s="127"/>
-      <c r="AE15" s="128"/>
-      <c r="AF15" s="144"/>
-      <c r="AG15" s="124"/>
-      <c r="AH15" s="124"/>
-      <c r="AI15" s="125"/>
+      <c r="B15" s="78"/>
+      <c r="C15" s="79"/>
+      <c r="D15" s="80"/>
+      <c r="E15" s="81"/>
+      <c r="F15" s="82"/>
+      <c r="G15" s="78"/>
+      <c r="H15" s="83"/>
+      <c r="I15" s="79"/>
+      <c r="J15" s="84"/>
+      <c r="K15" s="85"/>
+      <c r="L15" s="85"/>
+      <c r="M15" s="85"/>
+      <c r="N15" s="85"/>
+      <c r="O15" s="85"/>
+      <c r="P15" s="86"/>
+      <c r="Q15" s="87"/>
+      <c r="R15" s="88"/>
+      <c r="S15" s="88"/>
+      <c r="T15" s="88"/>
+      <c r="U15" s="88"/>
+      <c r="V15" s="88"/>
+      <c r="W15" s="88"/>
+      <c r="X15" s="88"/>
+      <c r="Y15" s="88"/>
+      <c r="Z15" s="88"/>
+      <c r="AA15" s="88"/>
+      <c r="AB15" s="88"/>
+      <c r="AC15" s="88"/>
+      <c r="AD15" s="88"/>
+      <c r="AE15" s="89"/>
+      <c r="AF15" s="84"/>
+      <c r="AG15" s="85"/>
+      <c r="AH15" s="85"/>
+      <c r="AI15" s="86"/>
     </row>
     <row r="16" spans="1:40" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="13"/>
-      <c r="B16" s="143"/>
-      <c r="C16" s="117"/>
-      <c r="D16" s="118"/>
-      <c r="E16" s="119"/>
-      <c r="F16" s="120"/>
-      <c r="G16" s="143"/>
-      <c r="H16" s="122"/>
-      <c r="I16" s="117"/>
-      <c r="J16" s="144"/>
-      <c r="K16" s="124"/>
-      <c r="L16" s="124"/>
-      <c r="M16" s="124"/>
-      <c r="N16" s="124"/>
-      <c r="O16" s="124"/>
-      <c r="P16" s="125"/>
-      <c r="Q16" s="145"/>
-      <c r="R16" s="127"/>
-      <c r="S16" s="127"/>
-      <c r="T16" s="127"/>
-      <c r="U16" s="127"/>
-      <c r="V16" s="127"/>
-      <c r="W16" s="127"/>
-      <c r="X16" s="127"/>
-      <c r="Y16" s="127"/>
-      <c r="Z16" s="127"/>
-      <c r="AA16" s="127"/>
-      <c r="AB16" s="127"/>
-      <c r="AC16" s="127"/>
-      <c r="AD16" s="127"/>
-      <c r="AE16" s="128"/>
-      <c r="AF16" s="144"/>
-      <c r="AG16" s="124"/>
-      <c r="AH16" s="124"/>
-      <c r="AI16" s="125"/>
+      <c r="B16" s="78"/>
+      <c r="C16" s="79"/>
+      <c r="D16" s="80"/>
+      <c r="E16" s="81"/>
+      <c r="F16" s="82"/>
+      <c r="G16" s="78"/>
+      <c r="H16" s="83"/>
+      <c r="I16" s="79"/>
+      <c r="J16" s="84"/>
+      <c r="K16" s="85"/>
+      <c r="L16" s="85"/>
+      <c r="M16" s="85"/>
+      <c r="N16" s="85"/>
+      <c r="O16" s="85"/>
+      <c r="P16" s="86"/>
+      <c r="Q16" s="87"/>
+      <c r="R16" s="88"/>
+      <c r="S16" s="88"/>
+      <c r="T16" s="88"/>
+      <c r="U16" s="88"/>
+      <c r="V16" s="88"/>
+      <c r="W16" s="88"/>
+      <c r="X16" s="88"/>
+      <c r="Y16" s="88"/>
+      <c r="Z16" s="88"/>
+      <c r="AA16" s="88"/>
+      <c r="AB16" s="88"/>
+      <c r="AC16" s="88"/>
+      <c r="AD16" s="88"/>
+      <c r="AE16" s="89"/>
+      <c r="AF16" s="84"/>
+      <c r="AG16" s="85"/>
+      <c r="AH16" s="85"/>
+      <c r="AI16" s="86"/>
     </row>
     <row r="17" spans="1:35" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="13"/>
-      <c r="B17" s="143"/>
-      <c r="C17" s="117"/>
-      <c r="D17" s="118"/>
-      <c r="E17" s="119"/>
-      <c r="F17" s="120"/>
-      <c r="G17" s="143"/>
-      <c r="H17" s="122"/>
-      <c r="I17" s="117"/>
-      <c r="J17" s="144"/>
-      <c r="K17" s="124"/>
-      <c r="L17" s="124"/>
-      <c r="M17" s="124"/>
-      <c r="N17" s="124"/>
-      <c r="O17" s="124"/>
-      <c r="P17" s="125"/>
-      <c r="Q17" s="145"/>
-      <c r="R17" s="127"/>
-      <c r="S17" s="127"/>
-      <c r="T17" s="127"/>
-      <c r="U17" s="127"/>
-      <c r="V17" s="127"/>
-      <c r="W17" s="127"/>
-      <c r="X17" s="127"/>
-      <c r="Y17" s="127"/>
-      <c r="Z17" s="127"/>
-      <c r="AA17" s="127"/>
-      <c r="AB17" s="127"/>
-      <c r="AC17" s="127"/>
-      <c r="AD17" s="127"/>
-      <c r="AE17" s="128"/>
-      <c r="AF17" s="144"/>
-      <c r="AG17" s="124"/>
-      <c r="AH17" s="124"/>
-      <c r="AI17" s="125"/>
+      <c r="B17" s="78"/>
+      <c r="C17" s="79"/>
+      <c r="D17" s="80"/>
+      <c r="E17" s="81"/>
+      <c r="F17" s="82"/>
+      <c r="G17" s="78"/>
+      <c r="H17" s="83"/>
+      <c r="I17" s="79"/>
+      <c r="J17" s="84"/>
+      <c r="K17" s="85"/>
+      <c r="L17" s="85"/>
+      <c r="M17" s="85"/>
+      <c r="N17" s="85"/>
+      <c r="O17" s="85"/>
+      <c r="P17" s="86"/>
+      <c r="Q17" s="87"/>
+      <c r="R17" s="88"/>
+      <c r="S17" s="88"/>
+      <c r="T17" s="88"/>
+      <c r="U17" s="88"/>
+      <c r="V17" s="88"/>
+      <c r="W17" s="88"/>
+      <c r="X17" s="88"/>
+      <c r="Y17" s="88"/>
+      <c r="Z17" s="88"/>
+      <c r="AA17" s="88"/>
+      <c r="AB17" s="88"/>
+      <c r="AC17" s="88"/>
+      <c r="AD17" s="88"/>
+      <c r="AE17" s="89"/>
+      <c r="AF17" s="84"/>
+      <c r="AG17" s="85"/>
+      <c r="AH17" s="85"/>
+      <c r="AI17" s="86"/>
     </row>
     <row r="18" spans="1:35" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="13"/>
-      <c r="B18" s="143"/>
-      <c r="C18" s="117"/>
-      <c r="D18" s="118"/>
-      <c r="E18" s="119"/>
-      <c r="F18" s="120"/>
-      <c r="G18" s="143"/>
-      <c r="H18" s="122"/>
-      <c r="I18" s="117"/>
-      <c r="J18" s="144"/>
-      <c r="K18" s="124"/>
-      <c r="L18" s="124"/>
-      <c r="M18" s="124"/>
-      <c r="N18" s="124"/>
-      <c r="O18" s="124"/>
-      <c r="P18" s="125"/>
-      <c r="Q18" s="145"/>
-      <c r="R18" s="127"/>
-      <c r="S18" s="127"/>
-      <c r="T18" s="127"/>
-      <c r="U18" s="127"/>
-      <c r="V18" s="127"/>
-      <c r="W18" s="127"/>
-      <c r="X18" s="127"/>
-      <c r="Y18" s="127"/>
-      <c r="Z18" s="127"/>
-      <c r="AA18" s="127"/>
-      <c r="AB18" s="127"/>
-      <c r="AC18" s="127"/>
-      <c r="AD18" s="127"/>
-      <c r="AE18" s="128"/>
-      <c r="AF18" s="144"/>
-      <c r="AG18" s="124"/>
-      <c r="AH18" s="124"/>
-      <c r="AI18" s="125"/>
+      <c r="B18" s="78"/>
+      <c r="C18" s="79"/>
+      <c r="D18" s="80"/>
+      <c r="E18" s="81"/>
+      <c r="F18" s="82"/>
+      <c r="G18" s="78"/>
+      <c r="H18" s="83"/>
+      <c r="I18" s="79"/>
+      <c r="J18" s="84"/>
+      <c r="K18" s="85"/>
+      <c r="L18" s="85"/>
+      <c r="M18" s="85"/>
+      <c r="N18" s="85"/>
+      <c r="O18" s="85"/>
+      <c r="P18" s="86"/>
+      <c r="Q18" s="87"/>
+      <c r="R18" s="88"/>
+      <c r="S18" s="88"/>
+      <c r="T18" s="88"/>
+      <c r="U18" s="88"/>
+      <c r="V18" s="88"/>
+      <c r="W18" s="88"/>
+      <c r="X18" s="88"/>
+      <c r="Y18" s="88"/>
+      <c r="Z18" s="88"/>
+      <c r="AA18" s="88"/>
+      <c r="AB18" s="88"/>
+      <c r="AC18" s="88"/>
+      <c r="AD18" s="88"/>
+      <c r="AE18" s="89"/>
+      <c r="AF18" s="84"/>
+      <c r="AG18" s="85"/>
+      <c r="AH18" s="85"/>
+      <c r="AI18" s="86"/>
     </row>
     <row r="19" spans="1:35" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="13"/>
-      <c r="B19" s="143"/>
-      <c r="C19" s="117"/>
-      <c r="D19" s="118"/>
-      <c r="E19" s="119"/>
-      <c r="F19" s="120"/>
-      <c r="G19" s="143"/>
-      <c r="H19" s="122"/>
-      <c r="I19" s="117"/>
-      <c r="J19" s="144"/>
-      <c r="K19" s="124"/>
-      <c r="L19" s="124"/>
-      <c r="M19" s="124"/>
-      <c r="N19" s="124"/>
-      <c r="O19" s="124"/>
-      <c r="P19" s="125"/>
-      <c r="Q19" s="145"/>
-      <c r="R19" s="127"/>
-      <c r="S19" s="127"/>
-      <c r="T19" s="127"/>
-      <c r="U19" s="127"/>
-      <c r="V19" s="127"/>
-      <c r="W19" s="127"/>
-      <c r="X19" s="127"/>
-      <c r="Y19" s="127"/>
-      <c r="Z19" s="127"/>
-      <c r="AA19" s="127"/>
-      <c r="AB19" s="127"/>
-      <c r="AC19" s="127"/>
-      <c r="AD19" s="127"/>
-      <c r="AE19" s="128"/>
-      <c r="AF19" s="144"/>
-      <c r="AG19" s="124"/>
-      <c r="AH19" s="124"/>
-      <c r="AI19" s="125"/>
+      <c r="B19" s="78"/>
+      <c r="C19" s="79"/>
+      <c r="D19" s="80"/>
+      <c r="E19" s="81"/>
+      <c r="F19" s="82"/>
+      <c r="G19" s="78"/>
+      <c r="H19" s="83"/>
+      <c r="I19" s="79"/>
+      <c r="J19" s="84"/>
+      <c r="K19" s="85"/>
+      <c r="L19" s="85"/>
+      <c r="M19" s="85"/>
+      <c r="N19" s="85"/>
+      <c r="O19" s="85"/>
+      <c r="P19" s="86"/>
+      <c r="Q19" s="87"/>
+      <c r="R19" s="88"/>
+      <c r="S19" s="88"/>
+      <c r="T19" s="88"/>
+      <c r="U19" s="88"/>
+      <c r="V19" s="88"/>
+      <c r="W19" s="88"/>
+      <c r="X19" s="88"/>
+      <c r="Y19" s="88"/>
+      <c r="Z19" s="88"/>
+      <c r="AA19" s="88"/>
+      <c r="AB19" s="88"/>
+      <c r="AC19" s="88"/>
+      <c r="AD19" s="88"/>
+      <c r="AE19" s="89"/>
+      <c r="AF19" s="84"/>
+      <c r="AG19" s="85"/>
+      <c r="AH19" s="85"/>
+      <c r="AI19" s="86"/>
     </row>
     <row r="20" spans="1:35" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="13"/>
-      <c r="B20" s="143"/>
-      <c r="C20" s="117"/>
-      <c r="D20" s="118"/>
-      <c r="E20" s="119"/>
-      <c r="F20" s="120"/>
-      <c r="G20" s="143"/>
-      <c r="H20" s="122"/>
-      <c r="I20" s="117"/>
-      <c r="J20" s="144"/>
-      <c r="K20" s="124"/>
-      <c r="L20" s="124"/>
-      <c r="M20" s="124"/>
-      <c r="N20" s="124"/>
-      <c r="O20" s="124"/>
-      <c r="P20" s="125"/>
-      <c r="Q20" s="145"/>
-      <c r="R20" s="127"/>
-      <c r="S20" s="127"/>
-      <c r="T20" s="127"/>
-      <c r="U20" s="127"/>
-      <c r="V20" s="127"/>
-      <c r="W20" s="127"/>
-      <c r="X20" s="127"/>
-      <c r="Y20" s="127"/>
-      <c r="Z20" s="127"/>
-      <c r="AA20" s="127"/>
-      <c r="AB20" s="127"/>
-      <c r="AC20" s="127"/>
-      <c r="AD20" s="127"/>
-      <c r="AE20" s="128"/>
-      <c r="AF20" s="144"/>
-      <c r="AG20" s="124"/>
-      <c r="AH20" s="124"/>
-      <c r="AI20" s="125"/>
+      <c r="B20" s="78"/>
+      <c r="C20" s="79"/>
+      <c r="D20" s="80"/>
+      <c r="E20" s="81"/>
+      <c r="F20" s="82"/>
+      <c r="G20" s="78"/>
+      <c r="H20" s="83"/>
+      <c r="I20" s="79"/>
+      <c r="J20" s="84"/>
+      <c r="K20" s="85"/>
+      <c r="L20" s="85"/>
+      <c r="M20" s="85"/>
+      <c r="N20" s="85"/>
+      <c r="O20" s="85"/>
+      <c r="P20" s="86"/>
+      <c r="Q20" s="87"/>
+      <c r="R20" s="88"/>
+      <c r="S20" s="88"/>
+      <c r="T20" s="88"/>
+      <c r="U20" s="88"/>
+      <c r="V20" s="88"/>
+      <c r="W20" s="88"/>
+      <c r="X20" s="88"/>
+      <c r="Y20" s="88"/>
+      <c r="Z20" s="88"/>
+      <c r="AA20" s="88"/>
+      <c r="AB20" s="88"/>
+      <c r="AC20" s="88"/>
+      <c r="AD20" s="88"/>
+      <c r="AE20" s="89"/>
+      <c r="AF20" s="84"/>
+      <c r="AG20" s="85"/>
+      <c r="AH20" s="85"/>
+      <c r="AI20" s="86"/>
     </row>
     <row r="21" spans="1:35" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="13"/>
-      <c r="B21" s="143"/>
-      <c r="C21" s="117"/>
-      <c r="D21" s="118"/>
-      <c r="E21" s="119"/>
-      <c r="F21" s="120"/>
-      <c r="G21" s="143"/>
-      <c r="H21" s="122"/>
-      <c r="I21" s="117"/>
-      <c r="J21" s="144"/>
-      <c r="K21" s="124"/>
-      <c r="L21" s="124"/>
-      <c r="M21" s="124"/>
-      <c r="N21" s="124"/>
-      <c r="O21" s="124"/>
-      <c r="P21" s="125"/>
-      <c r="Q21" s="145"/>
-      <c r="R21" s="127"/>
-      <c r="S21" s="127"/>
-      <c r="T21" s="127"/>
-      <c r="U21" s="127"/>
-      <c r="V21" s="127"/>
-      <c r="W21" s="127"/>
-      <c r="X21" s="127"/>
-      <c r="Y21" s="127"/>
-      <c r="Z21" s="127"/>
-      <c r="AA21" s="127"/>
-      <c r="AB21" s="127"/>
-      <c r="AC21" s="127"/>
-      <c r="AD21" s="127"/>
-      <c r="AE21" s="128"/>
-      <c r="AF21" s="144"/>
-      <c r="AG21" s="124"/>
-      <c r="AH21" s="124"/>
-      <c r="AI21" s="125"/>
+      <c r="B21" s="78"/>
+      <c r="C21" s="79"/>
+      <c r="D21" s="80"/>
+      <c r="E21" s="81"/>
+      <c r="F21" s="82"/>
+      <c r="G21" s="78"/>
+      <c r="H21" s="83"/>
+      <c r="I21" s="79"/>
+      <c r="J21" s="84"/>
+      <c r="K21" s="85"/>
+      <c r="L21" s="85"/>
+      <c r="M21" s="85"/>
+      <c r="N21" s="85"/>
+      <c r="O21" s="85"/>
+      <c r="P21" s="86"/>
+      <c r="Q21" s="87"/>
+      <c r="R21" s="88"/>
+      <c r="S21" s="88"/>
+      <c r="T21" s="88"/>
+      <c r="U21" s="88"/>
+      <c r="V21" s="88"/>
+      <c r="W21" s="88"/>
+      <c r="X21" s="88"/>
+      <c r="Y21" s="88"/>
+      <c r="Z21" s="88"/>
+      <c r="AA21" s="88"/>
+      <c r="AB21" s="88"/>
+      <c r="AC21" s="88"/>
+      <c r="AD21" s="88"/>
+      <c r="AE21" s="89"/>
+      <c r="AF21" s="84"/>
+      <c r="AG21" s="85"/>
+      <c r="AH21" s="85"/>
+      <c r="AI21" s="86"/>
     </row>
     <row r="22" spans="1:35" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="13"/>
-      <c r="B22" s="143"/>
-      <c r="C22" s="117"/>
-      <c r="D22" s="118"/>
-      <c r="E22" s="119"/>
-      <c r="F22" s="120"/>
-      <c r="G22" s="143"/>
-      <c r="H22" s="122"/>
-      <c r="I22" s="117"/>
-      <c r="J22" s="144"/>
-      <c r="K22" s="124"/>
-      <c r="L22" s="124"/>
-      <c r="M22" s="124"/>
-      <c r="N22" s="124"/>
-      <c r="O22" s="124"/>
-      <c r="P22" s="125"/>
-      <c r="Q22" s="145"/>
-      <c r="R22" s="127"/>
-      <c r="S22" s="127"/>
-      <c r="T22" s="127"/>
-      <c r="U22" s="127"/>
-      <c r="V22" s="127"/>
-      <c r="W22" s="127"/>
-      <c r="X22" s="127"/>
-      <c r="Y22" s="127"/>
-      <c r="Z22" s="127"/>
-      <c r="AA22" s="127"/>
-      <c r="AB22" s="127"/>
-      <c r="AC22" s="127"/>
-      <c r="AD22" s="127"/>
-      <c r="AE22" s="128"/>
-      <c r="AF22" s="144"/>
-      <c r="AG22" s="124"/>
-      <c r="AH22" s="124"/>
-      <c r="AI22" s="125"/>
+      <c r="B22" s="78"/>
+      <c r="C22" s="79"/>
+      <c r="D22" s="80"/>
+      <c r="E22" s="81"/>
+      <c r="F22" s="82"/>
+      <c r="G22" s="78"/>
+      <c r="H22" s="83"/>
+      <c r="I22" s="79"/>
+      <c r="J22" s="84"/>
+      <c r="K22" s="85"/>
+      <c r="L22" s="85"/>
+      <c r="M22" s="85"/>
+      <c r="N22" s="85"/>
+      <c r="O22" s="85"/>
+      <c r="P22" s="86"/>
+      <c r="Q22" s="87"/>
+      <c r="R22" s="88"/>
+      <c r="S22" s="88"/>
+      <c r="T22" s="88"/>
+      <c r="U22" s="88"/>
+      <c r="V22" s="88"/>
+      <c r="W22" s="88"/>
+      <c r="X22" s="88"/>
+      <c r="Y22" s="88"/>
+      <c r="Z22" s="88"/>
+      <c r="AA22" s="88"/>
+      <c r="AB22" s="88"/>
+      <c r="AC22" s="88"/>
+      <c r="AD22" s="88"/>
+      <c r="AE22" s="89"/>
+      <c r="AF22" s="84"/>
+      <c r="AG22" s="85"/>
+      <c r="AH22" s="85"/>
+      <c r="AI22" s="86"/>
     </row>
     <row r="23" spans="1:35" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="13"/>
-      <c r="B23" s="143"/>
-      <c r="C23" s="117"/>
-      <c r="D23" s="118"/>
-      <c r="E23" s="119"/>
-      <c r="F23" s="120"/>
-      <c r="G23" s="143"/>
-      <c r="H23" s="122"/>
-      <c r="I23" s="117"/>
-      <c r="J23" s="144"/>
-      <c r="K23" s="124"/>
-      <c r="L23" s="124"/>
-      <c r="M23" s="124"/>
-      <c r="N23" s="124"/>
-      <c r="O23" s="124"/>
-      <c r="P23" s="125"/>
-      <c r="Q23" s="145"/>
-      <c r="R23" s="127"/>
-      <c r="S23" s="127"/>
-      <c r="T23" s="127"/>
-      <c r="U23" s="127"/>
-      <c r="V23" s="127"/>
-      <c r="W23" s="127"/>
-      <c r="X23" s="127"/>
-      <c r="Y23" s="127"/>
-      <c r="Z23" s="127"/>
-      <c r="AA23" s="127"/>
-      <c r="AB23" s="127"/>
-      <c r="AC23" s="127"/>
-      <c r="AD23" s="127"/>
-      <c r="AE23" s="128"/>
-      <c r="AF23" s="144"/>
-      <c r="AG23" s="124"/>
-      <c r="AH23" s="124"/>
-      <c r="AI23" s="125"/>
+      <c r="B23" s="78"/>
+      <c r="C23" s="79"/>
+      <c r="D23" s="80"/>
+      <c r="E23" s="81"/>
+      <c r="F23" s="82"/>
+      <c r="G23" s="78"/>
+      <c r="H23" s="83"/>
+      <c r="I23" s="79"/>
+      <c r="J23" s="84"/>
+      <c r="K23" s="85"/>
+      <c r="L23" s="85"/>
+      <c r="M23" s="85"/>
+      <c r="N23" s="85"/>
+      <c r="O23" s="85"/>
+      <c r="P23" s="86"/>
+      <c r="Q23" s="87"/>
+      <c r="R23" s="88"/>
+      <c r="S23" s="88"/>
+      <c r="T23" s="88"/>
+      <c r="U23" s="88"/>
+      <c r="V23" s="88"/>
+      <c r="W23" s="88"/>
+      <c r="X23" s="88"/>
+      <c r="Y23" s="88"/>
+      <c r="Z23" s="88"/>
+      <c r="AA23" s="88"/>
+      <c r="AB23" s="88"/>
+      <c r="AC23" s="88"/>
+      <c r="AD23" s="88"/>
+      <c r="AE23" s="89"/>
+      <c r="AF23" s="84"/>
+      <c r="AG23" s="85"/>
+      <c r="AH23" s="85"/>
+      <c r="AI23" s="86"/>
     </row>
     <row r="24" spans="1:35" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="13"/>
-      <c r="B24" s="143"/>
-      <c r="C24" s="117"/>
-      <c r="D24" s="118"/>
-      <c r="E24" s="119"/>
-      <c r="F24" s="120"/>
-      <c r="G24" s="143"/>
-      <c r="H24" s="122"/>
-      <c r="I24" s="117"/>
-      <c r="J24" s="144"/>
-      <c r="K24" s="124"/>
-      <c r="L24" s="124"/>
-      <c r="M24" s="124"/>
-      <c r="N24" s="124"/>
-      <c r="O24" s="124"/>
-      <c r="P24" s="125"/>
-      <c r="Q24" s="145"/>
-      <c r="R24" s="127"/>
-      <c r="S24" s="127"/>
-      <c r="T24" s="127"/>
-      <c r="U24" s="127"/>
-      <c r="V24" s="127"/>
-      <c r="W24" s="127"/>
-      <c r="X24" s="127"/>
-      <c r="Y24" s="127"/>
-      <c r="Z24" s="127"/>
-      <c r="AA24" s="127"/>
-      <c r="AB24" s="127"/>
-      <c r="AC24" s="127"/>
-      <c r="AD24" s="127"/>
-      <c r="AE24" s="128"/>
-      <c r="AF24" s="144"/>
-      <c r="AG24" s="124"/>
-      <c r="AH24" s="124"/>
-      <c r="AI24" s="125"/>
+      <c r="B24" s="78"/>
+      <c r="C24" s="79"/>
+      <c r="D24" s="80"/>
+      <c r="E24" s="81"/>
+      <c r="F24" s="82"/>
+      <c r="G24" s="78"/>
+      <c r="H24" s="83"/>
+      <c r="I24" s="79"/>
+      <c r="J24" s="84"/>
+      <c r="K24" s="85"/>
+      <c r="L24" s="85"/>
+      <c r="M24" s="85"/>
+      <c r="N24" s="85"/>
+      <c r="O24" s="85"/>
+      <c r="P24" s="86"/>
+      <c r="Q24" s="87"/>
+      <c r="R24" s="88"/>
+      <c r="S24" s="88"/>
+      <c r="T24" s="88"/>
+      <c r="U24" s="88"/>
+      <c r="V24" s="88"/>
+      <c r="W24" s="88"/>
+      <c r="X24" s="88"/>
+      <c r="Y24" s="88"/>
+      <c r="Z24" s="88"/>
+      <c r="AA24" s="88"/>
+      <c r="AB24" s="88"/>
+      <c r="AC24" s="88"/>
+      <c r="AD24" s="88"/>
+      <c r="AE24" s="89"/>
+      <c r="AF24" s="84"/>
+      <c r="AG24" s="85"/>
+      <c r="AH24" s="85"/>
+      <c r="AI24" s="86"/>
     </row>
     <row r="25" spans="1:35" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="13"/>
-      <c r="B25" s="143"/>
-      <c r="C25" s="117"/>
-      <c r="D25" s="118"/>
-      <c r="E25" s="119"/>
-      <c r="F25" s="120"/>
-      <c r="G25" s="143"/>
-      <c r="H25" s="122"/>
-      <c r="I25" s="117"/>
-      <c r="J25" s="144"/>
-      <c r="K25" s="124"/>
-      <c r="L25" s="124"/>
-      <c r="M25" s="124"/>
-      <c r="N25" s="124"/>
-      <c r="O25" s="124"/>
-      <c r="P25" s="125"/>
-      <c r="Q25" s="145"/>
-      <c r="R25" s="127"/>
-      <c r="S25" s="127"/>
-      <c r="T25" s="127"/>
-      <c r="U25" s="127"/>
-      <c r="V25" s="127"/>
-      <c r="W25" s="127"/>
-      <c r="X25" s="127"/>
-      <c r="Y25" s="127"/>
-      <c r="Z25" s="127"/>
-      <c r="AA25" s="127"/>
-      <c r="AB25" s="127"/>
-      <c r="AC25" s="127"/>
-      <c r="AD25" s="127"/>
-      <c r="AE25" s="128"/>
-      <c r="AF25" s="144"/>
-      <c r="AG25" s="124"/>
-      <c r="AH25" s="124"/>
-      <c r="AI25" s="125"/>
+      <c r="B25" s="78"/>
+      <c r="C25" s="79"/>
+      <c r="D25" s="80"/>
+      <c r="E25" s="81"/>
+      <c r="F25" s="82"/>
+      <c r="G25" s="78"/>
+      <c r="H25" s="83"/>
+      <c r="I25" s="79"/>
+      <c r="J25" s="84"/>
+      <c r="K25" s="85"/>
+      <c r="L25" s="85"/>
+      <c r="M25" s="85"/>
+      <c r="N25" s="85"/>
+      <c r="O25" s="85"/>
+      <c r="P25" s="86"/>
+      <c r="Q25" s="87"/>
+      <c r="R25" s="88"/>
+      <c r="S25" s="88"/>
+      <c r="T25" s="88"/>
+      <c r="U25" s="88"/>
+      <c r="V25" s="88"/>
+      <c r="W25" s="88"/>
+      <c r="X25" s="88"/>
+      <c r="Y25" s="88"/>
+      <c r="Z25" s="88"/>
+      <c r="AA25" s="88"/>
+      <c r="AB25" s="88"/>
+      <c r="AC25" s="88"/>
+      <c r="AD25" s="88"/>
+      <c r="AE25" s="89"/>
+      <c r="AF25" s="84"/>
+      <c r="AG25" s="85"/>
+      <c r="AH25" s="85"/>
+      <c r="AI25" s="86"/>
     </row>
     <row r="26" spans="1:35" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="13"/>
-      <c r="B26" s="143"/>
-      <c r="C26" s="117"/>
-      <c r="D26" s="118"/>
-      <c r="E26" s="119"/>
-      <c r="F26" s="120"/>
-      <c r="G26" s="143"/>
-      <c r="H26" s="122"/>
-      <c r="I26" s="117"/>
-      <c r="J26" s="144"/>
-      <c r="K26" s="124"/>
-      <c r="L26" s="124"/>
-      <c r="M26" s="124"/>
-      <c r="N26" s="124"/>
-      <c r="O26" s="124"/>
-      <c r="P26" s="125"/>
-      <c r="Q26" s="145"/>
-      <c r="R26" s="127"/>
-      <c r="S26" s="127"/>
-      <c r="T26" s="127"/>
-      <c r="U26" s="127"/>
-      <c r="V26" s="127"/>
-      <c r="W26" s="127"/>
-      <c r="X26" s="127"/>
-      <c r="Y26" s="127"/>
-      <c r="Z26" s="127"/>
-      <c r="AA26" s="127"/>
-      <c r="AB26" s="127"/>
-      <c r="AC26" s="127"/>
-      <c r="AD26" s="127"/>
-      <c r="AE26" s="128"/>
-      <c r="AF26" s="144"/>
-      <c r="AG26" s="124"/>
-      <c r="AH26" s="124"/>
-      <c r="AI26" s="125"/>
+      <c r="B26" s="78"/>
+      <c r="C26" s="79"/>
+      <c r="D26" s="80"/>
+      <c r="E26" s="81"/>
+      <c r="F26" s="82"/>
+      <c r="G26" s="78"/>
+      <c r="H26" s="83"/>
+      <c r="I26" s="79"/>
+      <c r="J26" s="84"/>
+      <c r="K26" s="85"/>
+      <c r="L26" s="85"/>
+      <c r="M26" s="85"/>
+      <c r="N26" s="85"/>
+      <c r="O26" s="85"/>
+      <c r="P26" s="86"/>
+      <c r="Q26" s="87"/>
+      <c r="R26" s="88"/>
+      <c r="S26" s="88"/>
+      <c r="T26" s="88"/>
+      <c r="U26" s="88"/>
+      <c r="V26" s="88"/>
+      <c r="W26" s="88"/>
+      <c r="X26" s="88"/>
+      <c r="Y26" s="88"/>
+      <c r="Z26" s="88"/>
+      <c r="AA26" s="88"/>
+      <c r="AB26" s="88"/>
+      <c r="AC26" s="88"/>
+      <c r="AD26" s="88"/>
+      <c r="AE26" s="89"/>
+      <c r="AF26" s="84"/>
+      <c r="AG26" s="85"/>
+      <c r="AH26" s="85"/>
+      <c r="AI26" s="86"/>
     </row>
     <row r="27" spans="1:35" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="13"/>
-      <c r="B27" s="143"/>
-      <c r="C27" s="117"/>
-      <c r="D27" s="118"/>
-      <c r="E27" s="119"/>
-      <c r="F27" s="120"/>
-      <c r="G27" s="143"/>
-      <c r="H27" s="122"/>
-      <c r="I27" s="117"/>
-      <c r="J27" s="144"/>
-      <c r="K27" s="124"/>
-      <c r="L27" s="124"/>
-      <c r="M27" s="124"/>
-      <c r="N27" s="124"/>
-      <c r="O27" s="124"/>
-      <c r="P27" s="125"/>
-      <c r="Q27" s="145"/>
-      <c r="R27" s="127"/>
-      <c r="S27" s="127"/>
-      <c r="T27" s="127"/>
-      <c r="U27" s="127"/>
-      <c r="V27" s="127"/>
-      <c r="W27" s="127"/>
-      <c r="X27" s="127"/>
-      <c r="Y27" s="127"/>
-      <c r="Z27" s="127"/>
-      <c r="AA27" s="127"/>
-      <c r="AB27" s="127"/>
-      <c r="AC27" s="127"/>
-      <c r="AD27" s="127"/>
-      <c r="AE27" s="128"/>
-      <c r="AF27" s="144"/>
-      <c r="AG27" s="124"/>
-      <c r="AH27" s="124"/>
-      <c r="AI27" s="125"/>
+      <c r="B27" s="78"/>
+      <c r="C27" s="79"/>
+      <c r="D27" s="80"/>
+      <c r="E27" s="81"/>
+      <c r="F27" s="82"/>
+      <c r="G27" s="78"/>
+      <c r="H27" s="83"/>
+      <c r="I27" s="79"/>
+      <c r="J27" s="84"/>
+      <c r="K27" s="85"/>
+      <c r="L27" s="85"/>
+      <c r="M27" s="85"/>
+      <c r="N27" s="85"/>
+      <c r="O27" s="85"/>
+      <c r="P27" s="86"/>
+      <c r="Q27" s="87"/>
+      <c r="R27" s="88"/>
+      <c r="S27" s="88"/>
+      <c r="T27" s="88"/>
+      <c r="U27" s="88"/>
+      <c r="V27" s="88"/>
+      <c r="W27" s="88"/>
+      <c r="X27" s="88"/>
+      <c r="Y27" s="88"/>
+      <c r="Z27" s="88"/>
+      <c r="AA27" s="88"/>
+      <c r="AB27" s="88"/>
+      <c r="AC27" s="88"/>
+      <c r="AD27" s="88"/>
+      <c r="AE27" s="89"/>
+      <c r="AF27" s="84"/>
+      <c r="AG27" s="85"/>
+      <c r="AH27" s="85"/>
+      <c r="AI27" s="86"/>
     </row>
     <row r="28" spans="1:35" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="13"/>
-      <c r="B28" s="143"/>
-      <c r="C28" s="117"/>
-      <c r="D28" s="118"/>
-      <c r="E28" s="119"/>
-      <c r="F28" s="120"/>
-      <c r="G28" s="143"/>
-      <c r="H28" s="122"/>
-      <c r="I28" s="117"/>
-      <c r="J28" s="144"/>
-      <c r="K28" s="124"/>
-      <c r="L28" s="124"/>
-      <c r="M28" s="124"/>
-      <c r="N28" s="124"/>
-      <c r="O28" s="124"/>
-      <c r="P28" s="125"/>
-      <c r="Q28" s="145"/>
-      <c r="R28" s="127"/>
-      <c r="S28" s="127"/>
-      <c r="T28" s="127"/>
-      <c r="U28" s="127"/>
-      <c r="V28" s="127"/>
-      <c r="W28" s="127"/>
-      <c r="X28" s="127"/>
-      <c r="Y28" s="127"/>
-      <c r="Z28" s="127"/>
-      <c r="AA28" s="127"/>
-      <c r="AB28" s="127"/>
-      <c r="AC28" s="127"/>
-      <c r="AD28" s="127"/>
-      <c r="AE28" s="128"/>
-      <c r="AF28" s="144"/>
-      <c r="AG28" s="124"/>
-      <c r="AH28" s="124"/>
-      <c r="AI28" s="125"/>
+      <c r="B28" s="78"/>
+      <c r="C28" s="79"/>
+      <c r="D28" s="80"/>
+      <c r="E28" s="81"/>
+      <c r="F28" s="82"/>
+      <c r="G28" s="78"/>
+      <c r="H28" s="83"/>
+      <c r="I28" s="79"/>
+      <c r="J28" s="84"/>
+      <c r="K28" s="85"/>
+      <c r="L28" s="85"/>
+      <c r="M28" s="85"/>
+      <c r="N28" s="85"/>
+      <c r="O28" s="85"/>
+      <c r="P28" s="86"/>
+      <c r="Q28" s="87"/>
+      <c r="R28" s="88"/>
+      <c r="S28" s="88"/>
+      <c r="T28" s="88"/>
+      <c r="U28" s="88"/>
+      <c r="V28" s="88"/>
+      <c r="W28" s="88"/>
+      <c r="X28" s="88"/>
+      <c r="Y28" s="88"/>
+      <c r="Z28" s="88"/>
+      <c r="AA28" s="88"/>
+      <c r="AB28" s="88"/>
+      <c r="AC28" s="88"/>
+      <c r="AD28" s="88"/>
+      <c r="AE28" s="89"/>
+      <c r="AF28" s="84"/>
+      <c r="AG28" s="85"/>
+      <c r="AH28" s="85"/>
+      <c r="AI28" s="86"/>
     </row>
     <row r="29" spans="1:35" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="13"/>
-      <c r="B29" s="143"/>
-      <c r="C29" s="117"/>
-      <c r="D29" s="118"/>
-      <c r="E29" s="119"/>
-      <c r="F29" s="120"/>
-      <c r="G29" s="143"/>
-      <c r="H29" s="122"/>
-      <c r="I29" s="117"/>
-      <c r="J29" s="144"/>
-      <c r="K29" s="124"/>
-      <c r="L29" s="124"/>
-      <c r="M29" s="124"/>
-      <c r="N29" s="124"/>
-      <c r="O29" s="124"/>
-      <c r="P29" s="125"/>
-      <c r="Q29" s="145"/>
-      <c r="R29" s="127"/>
-      <c r="S29" s="127"/>
-      <c r="T29" s="127"/>
-      <c r="U29" s="127"/>
-      <c r="V29" s="127"/>
-      <c r="W29" s="127"/>
-      <c r="X29" s="127"/>
-      <c r="Y29" s="127"/>
-      <c r="Z29" s="127"/>
-      <c r="AA29" s="127"/>
-      <c r="AB29" s="127"/>
-      <c r="AC29" s="127"/>
-      <c r="AD29" s="127"/>
-      <c r="AE29" s="128"/>
-      <c r="AF29" s="144"/>
-      <c r="AG29" s="124"/>
-      <c r="AH29" s="124"/>
-      <c r="AI29" s="125"/>
+      <c r="B29" s="78"/>
+      <c r="C29" s="79"/>
+      <c r="D29" s="80"/>
+      <c r="E29" s="81"/>
+      <c r="F29" s="82"/>
+      <c r="G29" s="78"/>
+      <c r="H29" s="83"/>
+      <c r="I29" s="79"/>
+      <c r="J29" s="84"/>
+      <c r="K29" s="85"/>
+      <c r="L29" s="85"/>
+      <c r="M29" s="85"/>
+      <c r="N29" s="85"/>
+      <c r="O29" s="85"/>
+      <c r="P29" s="86"/>
+      <c r="Q29" s="87"/>
+      <c r="R29" s="88"/>
+      <c r="S29" s="88"/>
+      <c r="T29" s="88"/>
+      <c r="U29" s="88"/>
+      <c r="V29" s="88"/>
+      <c r="W29" s="88"/>
+      <c r="X29" s="88"/>
+      <c r="Y29" s="88"/>
+      <c r="Z29" s="88"/>
+      <c r="AA29" s="88"/>
+      <c r="AB29" s="88"/>
+      <c r="AC29" s="88"/>
+      <c r="AD29" s="88"/>
+      <c r="AE29" s="89"/>
+      <c r="AF29" s="84"/>
+      <c r="AG29" s="85"/>
+      <c r="AH29" s="85"/>
+      <c r="AI29" s="86"/>
     </row>
     <row r="30" spans="1:35" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="13"/>
-      <c r="B30" s="143"/>
-      <c r="C30" s="117"/>
-      <c r="D30" s="118"/>
-      <c r="E30" s="119"/>
-      <c r="F30" s="120"/>
-      <c r="G30" s="143"/>
-      <c r="H30" s="122"/>
-      <c r="I30" s="117"/>
-      <c r="J30" s="144"/>
-      <c r="K30" s="124"/>
-      <c r="L30" s="124"/>
-      <c r="M30" s="124"/>
-      <c r="N30" s="124"/>
-      <c r="O30" s="124"/>
-      <c r="P30" s="125"/>
-      <c r="Q30" s="145"/>
-      <c r="R30" s="127"/>
-      <c r="S30" s="127"/>
-      <c r="T30" s="127"/>
-      <c r="U30" s="127"/>
-      <c r="V30" s="127"/>
-      <c r="W30" s="127"/>
-      <c r="X30" s="127"/>
-      <c r="Y30" s="127"/>
-      <c r="Z30" s="127"/>
-      <c r="AA30" s="127"/>
-      <c r="AB30" s="127"/>
-      <c r="AC30" s="127"/>
-      <c r="AD30" s="127"/>
-      <c r="AE30" s="128"/>
-      <c r="AF30" s="144"/>
-      <c r="AG30" s="124"/>
-      <c r="AH30" s="124"/>
-      <c r="AI30" s="125"/>
+      <c r="B30" s="78"/>
+      <c r="C30" s="79"/>
+      <c r="D30" s="80"/>
+      <c r="E30" s="81"/>
+      <c r="F30" s="82"/>
+      <c r="G30" s="78"/>
+      <c r="H30" s="83"/>
+      <c r="I30" s="79"/>
+      <c r="J30" s="84"/>
+      <c r="K30" s="85"/>
+      <c r="L30" s="85"/>
+      <c r="M30" s="85"/>
+      <c r="N30" s="85"/>
+      <c r="O30" s="85"/>
+      <c r="P30" s="86"/>
+      <c r="Q30" s="87"/>
+      <c r="R30" s="88"/>
+      <c r="S30" s="88"/>
+      <c r="T30" s="88"/>
+      <c r="U30" s="88"/>
+      <c r="V30" s="88"/>
+      <c r="W30" s="88"/>
+      <c r="X30" s="88"/>
+      <c r="Y30" s="88"/>
+      <c r="Z30" s="88"/>
+      <c r="AA30" s="88"/>
+      <c r="AB30" s="88"/>
+      <c r="AC30" s="88"/>
+      <c r="AD30" s="88"/>
+      <c r="AE30" s="89"/>
+      <c r="AF30" s="84"/>
+      <c r="AG30" s="85"/>
+      <c r="AH30" s="85"/>
+      <c r="AI30" s="86"/>
     </row>
     <row r="31" spans="1:35" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="13"/>
-      <c r="B31" s="143"/>
-      <c r="C31" s="117"/>
-      <c r="D31" s="118"/>
-      <c r="E31" s="119"/>
-      <c r="F31" s="120"/>
-      <c r="G31" s="143"/>
-      <c r="H31" s="122"/>
-      <c r="I31" s="117"/>
-      <c r="J31" s="144"/>
-      <c r="K31" s="124"/>
-      <c r="L31" s="124"/>
-      <c r="M31" s="124"/>
-      <c r="N31" s="124"/>
-      <c r="O31" s="124"/>
-      <c r="P31" s="125"/>
-      <c r="Q31" s="145"/>
-      <c r="R31" s="127"/>
-      <c r="S31" s="127"/>
-      <c r="T31" s="127"/>
-      <c r="U31" s="127"/>
-      <c r="V31" s="127"/>
-      <c r="W31" s="127"/>
-      <c r="X31" s="127"/>
-      <c r="Y31" s="127"/>
-      <c r="Z31" s="127"/>
-      <c r="AA31" s="127"/>
-      <c r="AB31" s="127"/>
-      <c r="AC31" s="127"/>
-      <c r="AD31" s="127"/>
-      <c r="AE31" s="128"/>
-      <c r="AF31" s="144"/>
-      <c r="AG31" s="124"/>
-      <c r="AH31" s="124"/>
-      <c r="AI31" s="125"/>
+      <c r="B31" s="78"/>
+      <c r="C31" s="79"/>
+      <c r="D31" s="80"/>
+      <c r="E31" s="81"/>
+      <c r="F31" s="82"/>
+      <c r="G31" s="78"/>
+      <c r="H31" s="83"/>
+      <c r="I31" s="79"/>
+      <c r="J31" s="84"/>
+      <c r="K31" s="85"/>
+      <c r="L31" s="85"/>
+      <c r="M31" s="85"/>
+      <c r="N31" s="85"/>
+      <c r="O31" s="85"/>
+      <c r="P31" s="86"/>
+      <c r="Q31" s="87"/>
+      <c r="R31" s="88"/>
+      <c r="S31" s="88"/>
+      <c r="T31" s="88"/>
+      <c r="U31" s="88"/>
+      <c r="V31" s="88"/>
+      <c r="W31" s="88"/>
+      <c r="X31" s="88"/>
+      <c r="Y31" s="88"/>
+      <c r="Z31" s="88"/>
+      <c r="AA31" s="88"/>
+      <c r="AB31" s="88"/>
+      <c r="AC31" s="88"/>
+      <c r="AD31" s="88"/>
+      <c r="AE31" s="89"/>
+      <c r="AF31" s="84"/>
+      <c r="AG31" s="85"/>
+      <c r="AH31" s="85"/>
+      <c r="AI31" s="86"/>
     </row>
     <row r="32" spans="1:35" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="13"/>
-      <c r="B32" s="143"/>
-      <c r="C32" s="117"/>
-      <c r="D32" s="118"/>
-      <c r="E32" s="119"/>
-      <c r="F32" s="120"/>
-      <c r="G32" s="143"/>
-      <c r="H32" s="122"/>
-      <c r="I32" s="117"/>
-      <c r="J32" s="144"/>
-      <c r="K32" s="146"/>
-      <c r="L32" s="124"/>
-      <c r="M32" s="124"/>
-      <c r="N32" s="124"/>
-      <c r="O32" s="124"/>
-      <c r="P32" s="125"/>
-      <c r="Q32" s="145"/>
-      <c r="R32" s="127"/>
-      <c r="S32" s="127"/>
-      <c r="T32" s="127"/>
-      <c r="U32" s="127"/>
-      <c r="V32" s="127"/>
-      <c r="W32" s="127"/>
-      <c r="X32" s="127"/>
-      <c r="Y32" s="127"/>
-      <c r="Z32" s="127"/>
-      <c r="AA32" s="127"/>
-      <c r="AB32" s="127"/>
-      <c r="AC32" s="127"/>
-      <c r="AD32" s="127"/>
-      <c r="AE32" s="128"/>
-      <c r="AF32" s="144"/>
-      <c r="AG32" s="124"/>
-      <c r="AH32" s="124"/>
-      <c r="AI32" s="125"/>
+      <c r="B32" s="78"/>
+      <c r="C32" s="79"/>
+      <c r="D32" s="80"/>
+      <c r="E32" s="81"/>
+      <c r="F32" s="82"/>
+      <c r="G32" s="78"/>
+      <c r="H32" s="83"/>
+      <c r="I32" s="79"/>
+      <c r="J32" s="84"/>
+      <c r="K32" s="90"/>
+      <c r="L32" s="85"/>
+      <c r="M32" s="85"/>
+      <c r="N32" s="85"/>
+      <c r="O32" s="85"/>
+      <c r="P32" s="86"/>
+      <c r="Q32" s="87"/>
+      <c r="R32" s="88"/>
+      <c r="S32" s="88"/>
+      <c r="T32" s="88"/>
+      <c r="U32" s="88"/>
+      <c r="V32" s="88"/>
+      <c r="W32" s="88"/>
+      <c r="X32" s="88"/>
+      <c r="Y32" s="88"/>
+      <c r="Z32" s="88"/>
+      <c r="AA32" s="88"/>
+      <c r="AB32" s="88"/>
+      <c r="AC32" s="88"/>
+      <c r="AD32" s="88"/>
+      <c r="AE32" s="89"/>
+      <c r="AF32" s="84"/>
+      <c r="AG32" s="85"/>
+      <c r="AH32" s="85"/>
+      <c r="AI32" s="86"/>
     </row>
     <row r="33" spans="1:35" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="13"/>
-      <c r="B33" s="143"/>
-      <c r="C33" s="117"/>
-      <c r="D33" s="118"/>
-      <c r="E33" s="119"/>
-      <c r="F33" s="120"/>
-      <c r="G33" s="143"/>
-      <c r="H33" s="122"/>
-      <c r="I33" s="117"/>
-      <c r="J33" s="144"/>
-      <c r="K33" s="124"/>
-      <c r="L33" s="124"/>
-      <c r="M33" s="124"/>
-      <c r="N33" s="124"/>
-      <c r="O33" s="124"/>
-      <c r="P33" s="125"/>
-      <c r="Q33" s="145"/>
-      <c r="R33" s="127"/>
-      <c r="S33" s="127"/>
-      <c r="T33" s="127"/>
-      <c r="U33" s="127"/>
-      <c r="V33" s="127"/>
-      <c r="W33" s="127"/>
-      <c r="X33" s="127"/>
-      <c r="Y33" s="127"/>
-      <c r="Z33" s="127"/>
-      <c r="AA33" s="127"/>
-      <c r="AB33" s="127"/>
-      <c r="AC33" s="127"/>
-      <c r="AD33" s="127"/>
-      <c r="AE33" s="128"/>
-      <c r="AF33" s="144"/>
-      <c r="AG33" s="124"/>
-      <c r="AH33" s="124"/>
-      <c r="AI33" s="125"/>
+      <c r="B33" s="78"/>
+      <c r="C33" s="79"/>
+      <c r="D33" s="80"/>
+      <c r="E33" s="81"/>
+      <c r="F33" s="82"/>
+      <c r="G33" s="78"/>
+      <c r="H33" s="83"/>
+      <c r="I33" s="79"/>
+      <c r="J33" s="84"/>
+      <c r="K33" s="85"/>
+      <c r="L33" s="85"/>
+      <c r="M33" s="85"/>
+      <c r="N33" s="85"/>
+      <c r="O33" s="85"/>
+      <c r="P33" s="86"/>
+      <c r="Q33" s="87"/>
+      <c r="R33" s="88"/>
+      <c r="S33" s="88"/>
+      <c r="T33" s="88"/>
+      <c r="U33" s="88"/>
+      <c r="V33" s="88"/>
+      <c r="W33" s="88"/>
+      <c r="X33" s="88"/>
+      <c r="Y33" s="88"/>
+      <c r="Z33" s="88"/>
+      <c r="AA33" s="88"/>
+      <c r="AB33" s="88"/>
+      <c r="AC33" s="88"/>
+      <c r="AD33" s="88"/>
+      <c r="AE33" s="89"/>
+      <c r="AF33" s="84"/>
+      <c r="AG33" s="85"/>
+      <c r="AH33" s="85"/>
+      <c r="AI33" s="86"/>
     </row>
     <row r="34" spans="1:35" ht="14.25" x14ac:dyDescent="0.15">
       <c r="K34" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="179">
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="J33:P33"/>
-    <mergeCell ref="Q33:AE33"/>
-    <mergeCell ref="AF33:AI33"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="J32:P32"/>
-    <mergeCell ref="Q32:AE32"/>
-    <mergeCell ref="AF32:AI32"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:P31"/>
-    <mergeCell ref="Q31:AE31"/>
-    <mergeCell ref="AF31:AI31"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:P30"/>
-    <mergeCell ref="Q30:AE30"/>
-    <mergeCell ref="AF30:AI30"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:P29"/>
-    <mergeCell ref="Q29:AE29"/>
-    <mergeCell ref="AF29:AI29"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:P28"/>
-    <mergeCell ref="Q28:AE28"/>
-    <mergeCell ref="AF28:AI28"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:P27"/>
-    <mergeCell ref="Q27:AE27"/>
-    <mergeCell ref="AF27:AI27"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="J26:P26"/>
-    <mergeCell ref="Q26:AE26"/>
-    <mergeCell ref="AF26:AI26"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:P25"/>
-    <mergeCell ref="Q25:AE25"/>
-    <mergeCell ref="AF25:AI25"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:P24"/>
-    <mergeCell ref="Q24:AE24"/>
-    <mergeCell ref="AF24:AI24"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:P23"/>
-    <mergeCell ref="Q23:AE23"/>
-    <mergeCell ref="AF23:AI23"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:P22"/>
-    <mergeCell ref="Q22:AE22"/>
-    <mergeCell ref="AF22:AI22"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:P21"/>
-    <mergeCell ref="Q21:AE21"/>
-    <mergeCell ref="AF21:AI21"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:P20"/>
-    <mergeCell ref="Q20:AE20"/>
-    <mergeCell ref="AF20:AI20"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:P19"/>
-    <mergeCell ref="Q19:AE19"/>
-    <mergeCell ref="AF19:AI19"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="J18:P18"/>
-    <mergeCell ref="Q18:AE18"/>
-    <mergeCell ref="AF18:AI18"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:P17"/>
-    <mergeCell ref="Q17:AE17"/>
-    <mergeCell ref="AF17:AI17"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:P16"/>
-    <mergeCell ref="Q16:AE16"/>
-    <mergeCell ref="AF16:AI16"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:P15"/>
-    <mergeCell ref="Q15:AE15"/>
-    <mergeCell ref="AF15:AI15"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="J14:P14"/>
-    <mergeCell ref="Q14:AE14"/>
-    <mergeCell ref="AF14:AI14"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="J13:P13"/>
-    <mergeCell ref="Q13:AE13"/>
-    <mergeCell ref="AF13:AI13"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="J12:P12"/>
-    <mergeCell ref="Q12:AE12"/>
-    <mergeCell ref="AF12:AI12"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="J11:P11"/>
-    <mergeCell ref="Q11:AE11"/>
-    <mergeCell ref="AF11:AI11"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="J10:P10"/>
-    <mergeCell ref="Q10:AE10"/>
-    <mergeCell ref="AF10:AI10"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="J9:P9"/>
-    <mergeCell ref="Q9:AE9"/>
-    <mergeCell ref="AF9:AI9"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="J8:P8"/>
-    <mergeCell ref="Q8:AE8"/>
-    <mergeCell ref="AF8:AI8"/>
     <mergeCell ref="AG3:AI3"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="D7:F7"/>
@@ -15612,6 +15644,162 @@
     <mergeCell ref="E3:N3"/>
     <mergeCell ref="AA3:AB3"/>
     <mergeCell ref="AC3:AF3"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="J9:P9"/>
+    <mergeCell ref="Q9:AE9"/>
+    <mergeCell ref="AF9:AI9"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="J8:P8"/>
+    <mergeCell ref="Q8:AE8"/>
+    <mergeCell ref="AF8:AI8"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="J11:P11"/>
+    <mergeCell ref="Q11:AE11"/>
+    <mergeCell ref="AF11:AI11"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="J10:P10"/>
+    <mergeCell ref="Q10:AE10"/>
+    <mergeCell ref="AF10:AI10"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="J13:P13"/>
+    <mergeCell ref="Q13:AE13"/>
+    <mergeCell ref="AF13:AI13"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="J12:P12"/>
+    <mergeCell ref="Q12:AE12"/>
+    <mergeCell ref="AF12:AI12"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:P15"/>
+    <mergeCell ref="Q15:AE15"/>
+    <mergeCell ref="AF15:AI15"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="J14:P14"/>
+    <mergeCell ref="Q14:AE14"/>
+    <mergeCell ref="AF14:AI14"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:P17"/>
+    <mergeCell ref="Q17:AE17"/>
+    <mergeCell ref="AF17:AI17"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:P16"/>
+    <mergeCell ref="Q16:AE16"/>
+    <mergeCell ref="AF16:AI16"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:P19"/>
+    <mergeCell ref="Q19:AE19"/>
+    <mergeCell ref="AF19:AI19"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="J18:P18"/>
+    <mergeCell ref="Q18:AE18"/>
+    <mergeCell ref="AF18:AI18"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:P21"/>
+    <mergeCell ref="Q21:AE21"/>
+    <mergeCell ref="AF21:AI21"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:P20"/>
+    <mergeCell ref="Q20:AE20"/>
+    <mergeCell ref="AF20:AI20"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:P23"/>
+    <mergeCell ref="Q23:AE23"/>
+    <mergeCell ref="AF23:AI23"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:P22"/>
+    <mergeCell ref="Q22:AE22"/>
+    <mergeCell ref="AF22:AI22"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:P25"/>
+    <mergeCell ref="Q25:AE25"/>
+    <mergeCell ref="AF25:AI25"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:P24"/>
+    <mergeCell ref="Q24:AE24"/>
+    <mergeCell ref="AF24:AI24"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:P27"/>
+    <mergeCell ref="Q27:AE27"/>
+    <mergeCell ref="AF27:AI27"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="J26:P26"/>
+    <mergeCell ref="Q26:AE26"/>
+    <mergeCell ref="AF26:AI26"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:P29"/>
+    <mergeCell ref="Q29:AE29"/>
+    <mergeCell ref="AF29:AI29"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:P28"/>
+    <mergeCell ref="Q28:AE28"/>
+    <mergeCell ref="AF28:AI28"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:P31"/>
+    <mergeCell ref="Q31:AE31"/>
+    <mergeCell ref="AF31:AI31"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:P30"/>
+    <mergeCell ref="Q30:AE30"/>
+    <mergeCell ref="AF30:AI30"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="J33:P33"/>
+    <mergeCell ref="Q33:AE33"/>
+    <mergeCell ref="AF33:AI33"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="J32:P32"/>
+    <mergeCell ref="Q32:AE32"/>
+    <mergeCell ref="AF32:AI32"/>
   </mergeCells>
   <phoneticPr fontId="10"/>
   <printOptions horizontalCentered="1"/>
@@ -15626,7 +15814,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AL48"/>
+  <dimension ref="A1:AL49"/>
   <sheetFormatPr defaultColWidth="4.83203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="16" width="4.83203125" style="33" customWidth="1"/>
@@ -15763,163 +15951,163 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="84" t="s">
+      <c r="A1" s="116" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="85"/>
-      <c r="D1" s="86"/>
-      <c r="E1" s="87" t="str">
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="118"/>
+      <c r="E1" s="119" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E1")&lt;&gt;"",INDIRECT("変更履歴!E1"),"")</f>
         <v/>
       </c>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
-      <c r="H1" s="88"/>
-      <c r="I1" s="88"/>
-      <c r="J1" s="88"/>
-      <c r="K1" s="88"/>
-      <c r="L1" s="88"/>
-      <c r="M1" s="88"/>
-      <c r="N1" s="89"/>
-      <c r="O1" s="95" t="s">
+      <c r="F1" s="120"/>
+      <c r="G1" s="120"/>
+      <c r="H1" s="120"/>
+      <c r="I1" s="120"/>
+      <c r="J1" s="120"/>
+      <c r="K1" s="120"/>
+      <c r="L1" s="120"/>
+      <c r="M1" s="120"/>
+      <c r="N1" s="121"/>
+      <c r="O1" s="127" t="s">
         <v>11</v>
       </c>
-      <c r="P1" s="96"/>
-      <c r="Q1" s="96"/>
-      <c r="R1" s="97"/>
-      <c r="S1" s="152" t="str">
+      <c r="P1" s="128"/>
+      <c r="Q1" s="128"/>
+      <c r="R1" s="129"/>
+      <c r="S1" s="148" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!S1")&lt;&gt;"",INDIRECT("変更履歴!S1"),"")</f>
         <v>Nablarch開発標準設計書一覧</v>
       </c>
-      <c r="T1" s="105"/>
-      <c r="U1" s="105"/>
-      <c r="V1" s="105"/>
-      <c r="W1" s="105"/>
-      <c r="X1" s="105"/>
-      <c r="Y1" s="105"/>
-      <c r="Z1" s="106"/>
-      <c r="AA1" s="150" t="s">
+      <c r="T1" s="137"/>
+      <c r="U1" s="137"/>
+      <c r="V1" s="137"/>
+      <c r="W1" s="137"/>
+      <c r="X1" s="137"/>
+      <c r="Y1" s="137"/>
+      <c r="Z1" s="138"/>
+      <c r="AA1" s="149" t="s">
         <v>12</v>
       </c>
-      <c r="AB1" s="151"/>
-      <c r="AC1" s="113" t="str">
+      <c r="AB1" s="150"/>
+      <c r="AC1" s="145" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC1")&lt;&gt;"",INDIRECT("変更履歴!AC1"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="114"/>
-      <c r="AE1" s="114"/>
-      <c r="AF1" s="115"/>
-      <c r="AG1" s="147">
+      <c r="AD1" s="146"/>
+      <c r="AE1" s="146"/>
+      <c r="AF1" s="147"/>
+      <c r="AG1" s="151">
         <f ca="1">IF(INDIRECT("変更履歴!AG1")&lt;&gt;"",INDIRECT("変更履歴!AG1"),"")</f>
         <v>43336</v>
       </c>
-      <c r="AH1" s="148"/>
-      <c r="AI1" s="149"/>
+      <c r="AH1" s="152"/>
+      <c r="AI1" s="153"/>
       <c r="AJ1" s="1"/>
       <c r="AK1" s="1"/>
       <c r="AL1" s="2"/>
     </row>
     <row r="2" spans="1:38" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="84" t="s">
+      <c r="A2" s="116" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="85"/>
-      <c r="C2" s="85"/>
-      <c r="D2" s="86"/>
-      <c r="E2" s="87" t="str">
+      <c r="B2" s="117"/>
+      <c r="C2" s="117"/>
+      <c r="D2" s="118"/>
+      <c r="E2" s="119" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E2")&lt;&gt;"",INDIRECT("変更履歴!E2"),"")</f>
         <v/>
       </c>
-      <c r="F2" s="88"/>
-      <c r="G2" s="88"/>
-      <c r="H2" s="88"/>
-      <c r="I2" s="88"/>
-      <c r="J2" s="88"/>
-      <c r="K2" s="88"/>
-      <c r="L2" s="88"/>
-      <c r="M2" s="88"/>
-      <c r="N2" s="89"/>
-      <c r="O2" s="98"/>
-      <c r="P2" s="99"/>
-      <c r="Q2" s="99"/>
-      <c r="R2" s="100"/>
-      <c r="S2" s="107"/>
-      <c r="T2" s="108"/>
-      <c r="U2" s="108"/>
-      <c r="V2" s="108"/>
-      <c r="W2" s="108"/>
-      <c r="X2" s="108"/>
-      <c r="Y2" s="108"/>
-      <c r="Z2" s="109"/>
-      <c r="AA2" s="150" t="s">
+      <c r="F2" s="120"/>
+      <c r="G2" s="120"/>
+      <c r="H2" s="120"/>
+      <c r="I2" s="120"/>
+      <c r="J2" s="120"/>
+      <c r="K2" s="120"/>
+      <c r="L2" s="120"/>
+      <c r="M2" s="120"/>
+      <c r="N2" s="121"/>
+      <c r="O2" s="130"/>
+      <c r="P2" s="131"/>
+      <c r="Q2" s="131"/>
+      <c r="R2" s="132"/>
+      <c r="S2" s="139"/>
+      <c r="T2" s="140"/>
+      <c r="U2" s="140"/>
+      <c r="V2" s="140"/>
+      <c r="W2" s="140"/>
+      <c r="X2" s="140"/>
+      <c r="Y2" s="140"/>
+      <c r="Z2" s="141"/>
+      <c r="AA2" s="149" t="s">
         <v>13</v>
       </c>
-      <c r="AB2" s="151"/>
-      <c r="AC2" s="113" t="str">
+      <c r="AB2" s="150"/>
+      <c r="AC2" s="145" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC2")&lt;&gt;"",INDIRECT("変更履歴!AC2"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD2" s="114"/>
-      <c r="AE2" s="114"/>
-      <c r="AF2" s="115"/>
-      <c r="AG2" s="147">
+      <c r="AD2" s="146"/>
+      <c r="AE2" s="146"/>
+      <c r="AF2" s="147"/>
+      <c r="AG2" s="151">
         <f ca="1">IF(INDIRECT("変更履歴!AG2")&lt;&gt;"",INDIRECT("変更履歴!AG2"),"")</f>
         <v>44848</v>
       </c>
-      <c r="AH2" s="148"/>
-      <c r="AI2" s="149"/>
+      <c r="AH2" s="152"/>
+      <c r="AI2" s="153"/>
       <c r="AJ2" s="1"/>
       <c r="AK2" s="1"/>
       <c r="AL2" s="1"/>
     </row>
     <row r="3" spans="1:38" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="84" t="s">
+      <c r="A3" s="116" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="85"/>
-      <c r="C3" s="85"/>
-      <c r="D3" s="86"/>
-      <c r="E3" s="87" t="str">
+      <c r="B3" s="117"/>
+      <c r="C3" s="117"/>
+      <c r="D3" s="118"/>
+      <c r="E3" s="119" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E3")&lt;&gt;"",INDIRECT("変更履歴!E3"),"")</f>
         <v/>
       </c>
-      <c r="F3" s="88"/>
-      <c r="G3" s="88"/>
-      <c r="H3" s="88"/>
-      <c r="I3" s="88"/>
-      <c r="J3" s="88"/>
-      <c r="K3" s="88"/>
-      <c r="L3" s="88"/>
-      <c r="M3" s="88"/>
-      <c r="N3" s="89"/>
-      <c r="O3" s="101"/>
-      <c r="P3" s="102"/>
-      <c r="Q3" s="102"/>
-      <c r="R3" s="103"/>
-      <c r="S3" s="110"/>
-      <c r="T3" s="111"/>
-      <c r="U3" s="111"/>
-      <c r="V3" s="111"/>
-      <c r="W3" s="111"/>
-      <c r="X3" s="111"/>
-      <c r="Y3" s="111"/>
-      <c r="Z3" s="112"/>
-      <c r="AA3" s="150"/>
-      <c r="AB3" s="151"/>
-      <c r="AC3" s="113" t="str">
+      <c r="F3" s="120"/>
+      <c r="G3" s="120"/>
+      <c r="H3" s="120"/>
+      <c r="I3" s="120"/>
+      <c r="J3" s="120"/>
+      <c r="K3" s="120"/>
+      <c r="L3" s="120"/>
+      <c r="M3" s="120"/>
+      <c r="N3" s="121"/>
+      <c r="O3" s="133"/>
+      <c r="P3" s="134"/>
+      <c r="Q3" s="134"/>
+      <c r="R3" s="135"/>
+      <c r="S3" s="142"/>
+      <c r="T3" s="143"/>
+      <c r="U3" s="143"/>
+      <c r="V3" s="143"/>
+      <c r="W3" s="143"/>
+      <c r="X3" s="143"/>
+      <c r="Y3" s="143"/>
+      <c r="Z3" s="144"/>
+      <c r="AA3" s="149"/>
+      <c r="AB3" s="150"/>
+      <c r="AC3" s="145" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC3")&lt;&gt;"",INDIRECT("変更履歴!AC3"),"")</f>
         <v/>
       </c>
-      <c r="AD3" s="114"/>
-      <c r="AE3" s="114"/>
-      <c r="AF3" s="115"/>
-      <c r="AG3" s="147" t="str">
+      <c r="AD3" s="146"/>
+      <c r="AE3" s="146"/>
+      <c r="AF3" s="147"/>
+      <c r="AG3" s="151" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AG3")&lt;&gt;"",INDIRECT("変更履歴!AG3"),"")</f>
         <v/>
       </c>
-      <c r="AH3" s="148"/>
-      <c r="AI3" s="149"/>
+      <c r="AH3" s="152"/>
+      <c r="AI3" s="153"/>
       <c r="AJ3" s="1"/>
       <c r="AK3" s="1"/>
       <c r="AL3" s="1"/>
@@ -15959,33 +16147,32 @@
     </row>
     <row r="9" spans="1:38" s="39" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B9" s="38"/>
-      <c r="D9" s="38"/>
+      <c r="D9" s="38" t="s">
+        <v>250</v>
+      </c>
       <c r="P9" s="40"/>
       <c r="R9" s="40"/>
       <c r="AH9" s="42"/>
     </row>
     <row r="10" spans="1:38" s="39" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C10" s="38" t="s">
-        <v>41</v>
-      </c>
+      <c r="B10" s="38"/>
+      <c r="D10" s="38"/>
       <c r="P10" s="40"/>
       <c r="R10" s="40"/>
-      <c r="AG10" s="40"/>
       <c r="AH10" s="42"/>
     </row>
     <row r="11" spans="1:38" s="39" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D11" s="38" t="s">
-        <v>42</v>
+      <c r="C11" s="38" t="s">
+        <v>41</v>
       </c>
       <c r="P11" s="40"/>
       <c r="R11" s="40"/>
-      <c r="V11" s="38"/>
       <c r="AG11" s="40"/>
       <c r="AH11" s="42"/>
     </row>
     <row r="12" spans="1:38" s="39" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D12" s="38" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="P12" s="40"/>
       <c r="R12" s="40"/>
@@ -15994,8 +16181,9 @@
       <c r="AH12" s="42"/>
     </row>
     <row r="13" spans="1:38" s="39" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D13" s="38"/>
-      <c r="N13" s="38"/>
+      <c r="D13" s="38" t="s">
+        <v>43</v>
+      </c>
       <c r="P13" s="40"/>
       <c r="R13" s="40"/>
       <c r="V13" s="38"/>
@@ -16003,33 +16191,37 @@
       <c r="AH13" s="42"/>
     </row>
     <row r="14" spans="1:38" s="39" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C14" s="38" t="s">
-        <v>46</v>
-      </c>
       <c r="D14" s="38"/>
-      <c r="Q14" s="43"/>
+      <c r="N14" s="38"/>
+      <c r="P14" s="40"/>
+      <c r="R14" s="40"/>
+      <c r="V14" s="38"/>
       <c r="AG14" s="40"/>
       <c r="AH14" s="42"/>
     </row>
     <row r="15" spans="1:38" s="39" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C15" s="38" t="s">
+        <v>46</v>
+      </c>
+      <c r="D15" s="38"/>
       <c r="Q15" s="43"/>
-      <c r="V15" s="38"/>
       <c r="AG15" s="40"/>
       <c r="AH15" s="42"/>
     </row>
     <row r="16" spans="1:38" s="39" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B16" s="43"/>
-      <c r="P16" s="40"/>
+      <c r="Q16" s="43"/>
+      <c r="V16" s="38"/>
       <c r="AG16" s="40"/>
       <c r="AH16" s="42"/>
     </row>
     <row r="17" spans="2:34" s="39" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D17" s="38"/>
+      <c r="B17" s="43"/>
       <c r="P17" s="40"/>
       <c r="AG17" s="40"/>
       <c r="AH17" s="42"/>
     </row>
     <row r="18" spans="2:34" s="39" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D18" s="38"/>
       <c r="P18" s="40"/>
       <c r="AG18" s="40"/>
       <c r="AH18" s="42"/>
@@ -16050,12 +16242,12 @@
       <c r="AH21" s="42"/>
     </row>
     <row r="22" spans="2:34" s="39" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B22" s="43"/>
       <c r="P22" s="40"/>
       <c r="AG22" s="40"/>
       <c r="AH22" s="42"/>
     </row>
     <row r="23" spans="2:34" s="39" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B23" s="43"/>
       <c r="P23" s="40"/>
       <c r="AG23" s="40"/>
       <c r="AH23" s="42"/>
@@ -16091,95 +16283,108 @@
       <c r="AH29" s="42"/>
     </row>
     <row r="30" spans="2:34" s="39" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C30" s="40"/>
       <c r="P30" s="40"/>
-      <c r="Q30" s="42"/>
-      <c r="S30" s="44"/>
       <c r="AG30" s="40"/>
       <c r="AH30" s="42"/>
     </row>
     <row r="31" spans="2:34" s="39" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="K31" s="45"/>
-      <c r="P31" s="46"/>
+      <c r="C31" s="40"/>
+      <c r="P31" s="40"/>
       <c r="Q31" s="42"/>
       <c r="S31" s="44"/>
       <c r="AG31" s="40"/>
       <c r="AH31" s="42"/>
     </row>
     <row r="32" spans="2:34" s="39" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="K32" s="45"/>
       <c r="P32" s="46"/>
       <c r="Q32" s="42"/>
+      <c r="S32" s="44"/>
       <c r="AG32" s="40"/>
       <c r="AH32" s="42"/>
     </row>
     <row r="33" spans="11:34" s="39" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="K33" s="45"/>
       <c r="P33" s="46"/>
       <c r="Q33" s="42"/>
-      <c r="S33" s="44"/>
       <c r="AG33" s="40"/>
       <c r="AH33" s="42"/>
     </row>
     <row r="34" spans="11:34" s="39" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="K34" s="45"/>
       <c r="P34" s="46"/>
       <c r="Q34" s="42"/>
-      <c r="U34" s="47"/>
+      <c r="S34" s="44"/>
       <c r="AG34" s="40"/>
       <c r="AH34" s="42"/>
     </row>
     <row r="35" spans="11:34" s="39" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="P35" s="46"/>
       <c r="Q35" s="42"/>
+      <c r="U35" s="47"/>
+      <c r="AG35" s="40"/>
       <c r="AH35" s="42"/>
     </row>
-    <row r="36" spans="11:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="P36" s="34"/>
-      <c r="U36" s="36"/>
-      <c r="AG36" s="37"/>
+    <row r="36" spans="11:34" s="39" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P36" s="46"/>
+      <c r="Q36" s="42"/>
+      <c r="AH36" s="42"/>
     </row>
     <row r="37" spans="11:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P37" s="34"/>
       <c r="U37" s="36"/>
-      <c r="AF37" s="37"/>
-      <c r="AG37" s="34"/>
+      <c r="AG37" s="37"/>
     </row>
     <row r="38" spans="11:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="T38" s="36"/>
+      <c r="U38" s="36"/>
       <c r="AF38" s="37"/>
-      <c r="AG38" s="37"/>
+      <c r="AG38" s="34"/>
     </row>
     <row r="39" spans="11:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="AG39" s="34"/>
+      <c r="T39" s="36"/>
+      <c r="AF39" s="37"/>
+      <c r="AG39" s="37"/>
     </row>
     <row r="40" spans="11:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="AG40" s="34"/>
     </row>
     <row r="41" spans="11:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="AF41" s="37"/>
       <c r="AG41" s="34"/>
     </row>
     <row r="42" spans="11:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="AF42" s="37"/>
-      <c r="AG42" s="37"/>
+      <c r="AG42" s="34"/>
     </row>
     <row r="43" spans="11:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="AF43" s="37"/>
       <c r="AG43" s="37"/>
     </row>
     <row r="44" spans="11:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AF44" s="37"/>
       <c r="AG44" s="37"/>
     </row>
     <row r="45" spans="11:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="AF45" s="37"/>
       <c r="AG45" s="37"/>
     </row>
     <row r="46" spans="11:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AF46" s="37"/>
       <c r="AG46" s="37"/>
     </row>
-    <row r="48" spans="11:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="AG48" s="37"/>
+    <row r="47" spans="11:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AG47" s="37"/>
+    </row>
+    <row r="49" spans="33:33" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AG49" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="AG1:AI1"/>
+    <mergeCell ref="AC1:AF1"/>
+    <mergeCell ref="AC2:AF2"/>
+    <mergeCell ref="AG2:AI2"/>
+    <mergeCell ref="E3:N3"/>
+    <mergeCell ref="AA3:AB3"/>
+    <mergeCell ref="AC3:AF3"/>
+    <mergeCell ref="AG3:AI3"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="E1:N1"/>
     <mergeCell ref="O1:R3"/>
@@ -16189,14 +16394,6 @@
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="E2:N2"/>
     <mergeCell ref="AA2:AB2"/>
-    <mergeCell ref="AG1:AI1"/>
-    <mergeCell ref="AC1:AF1"/>
-    <mergeCell ref="AC2:AF2"/>
-    <mergeCell ref="AG2:AI2"/>
-    <mergeCell ref="E3:N3"/>
-    <mergeCell ref="AA3:AB3"/>
-    <mergeCell ref="AC3:AF3"/>
-    <mergeCell ref="AG3:AI3"/>
   </mergeCells>
   <phoneticPr fontId="10"/>
   <printOptions horizontalCentered="1"/>
@@ -16211,7 +16408,7 @@
   <sheetPr codeName="Sheet6">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AX11"/>
+  <dimension ref="A1:AX35"/>
   <sheetFormatPr defaultColWidth="4.83203125" defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="31" width="4.83203125" style="10" customWidth="1"/>
@@ -16219,59 +16416,59 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:50" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="84" t="s">
+      <c r="A1" s="116" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="85"/>
-      <c r="D1" s="86"/>
-      <c r="E1" s="87" t="str">
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="118"/>
+      <c r="E1" s="119" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E1")&lt;&gt;"",INDIRECT("変更履歴!E1"),"")</f>
         <v/>
       </c>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
-      <c r="H1" s="88"/>
-      <c r="I1" s="88"/>
-      <c r="J1" s="88"/>
-      <c r="K1" s="88"/>
-      <c r="L1" s="88"/>
-      <c r="M1" s="88"/>
-      <c r="N1" s="89"/>
-      <c r="O1" s="162" t="s">
+      <c r="F1" s="120"/>
+      <c r="G1" s="120"/>
+      <c r="H1" s="120"/>
+      <c r="I1" s="120"/>
+      <c r="J1" s="120"/>
+      <c r="K1" s="120"/>
+      <c r="L1" s="120"/>
+      <c r="M1" s="120"/>
+      <c r="N1" s="121"/>
+      <c r="O1" s="154" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="163"/>
-      <c r="Q1" s="163"/>
-      <c r="R1" s="164"/>
-      <c r="S1" s="153" t="str">
+      <c r="P1" s="155"/>
+      <c r="Q1" s="155"/>
+      <c r="R1" s="156"/>
+      <c r="S1" s="163" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!S1")&lt;&gt;"",INDIRECT("変更履歴!S1"),"")</f>
         <v>Nablarch開発標準設計書一覧</v>
       </c>
-      <c r="T1" s="154"/>
-      <c r="U1" s="154"/>
-      <c r="V1" s="154"/>
-      <c r="W1" s="154"/>
-      <c r="X1" s="154"/>
-      <c r="Y1" s="154"/>
-      <c r="Z1" s="155"/>
-      <c r="AA1" s="84" t="s">
+      <c r="T1" s="164"/>
+      <c r="U1" s="164"/>
+      <c r="V1" s="164"/>
+      <c r="W1" s="164"/>
+      <c r="X1" s="164"/>
+      <c r="Y1" s="164"/>
+      <c r="Z1" s="165"/>
+      <c r="AA1" s="116" t="s">
         <v>3</v>
       </c>
-      <c r="AB1" s="86"/>
-      <c r="AC1" s="113" t="str">
+      <c r="AB1" s="118"/>
+      <c r="AC1" s="145" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC1")&lt;&gt;"",INDIRECT("変更履歴!AC1"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="114"/>
-      <c r="AE1" s="114"/>
-      <c r="AF1" s="115"/>
-      <c r="AG1" s="147">
+      <c r="AD1" s="146"/>
+      <c r="AE1" s="146"/>
+      <c r="AF1" s="147"/>
+      <c r="AG1" s="151">
         <f ca="1">IF(INDIRECT("変更履歴!AG1")&lt;&gt;"",INDIRECT("変更履歴!AG1"),"")</f>
         <v>43336</v>
       </c>
-      <c r="AH1" s="148"/>
-      <c r="AI1" s="149"/>
+      <c r="AH1" s="152"/>
+      <c r="AI1" s="153"/>
       <c r="AJ1" s="6"/>
       <c r="AN1" s="7"/>
       <c r="AO1" s="6"/>
@@ -16285,54 +16482,54 @@
       <c r="AW1" s="6"/>
     </row>
     <row r="2" spans="1:50" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="84" t="s">
+      <c r="A2" s="116" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="85"/>
-      <c r="C2" s="85"/>
-      <c r="D2" s="86"/>
-      <c r="E2" s="87" t="str">
+      <c r="B2" s="117"/>
+      <c r="C2" s="117"/>
+      <c r="D2" s="118"/>
+      <c r="E2" s="119" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E2")&lt;&gt;"",INDIRECT("変更履歴!E2"),"")</f>
         <v/>
       </c>
-      <c r="F2" s="88"/>
-      <c r="G2" s="88"/>
-      <c r="H2" s="88"/>
-      <c r="I2" s="88"/>
-      <c r="J2" s="88"/>
-      <c r="K2" s="88"/>
-      <c r="L2" s="88"/>
-      <c r="M2" s="88"/>
-      <c r="N2" s="89"/>
-      <c r="O2" s="165"/>
-      <c r="P2" s="166"/>
-      <c r="Q2" s="166"/>
-      <c r="R2" s="167"/>
-      <c r="S2" s="156"/>
-      <c r="T2" s="157"/>
-      <c r="U2" s="157"/>
-      <c r="V2" s="157"/>
-      <c r="W2" s="157"/>
-      <c r="X2" s="157"/>
-      <c r="Y2" s="157"/>
-      <c r="Z2" s="158"/>
-      <c r="AA2" s="84" t="s">
+      <c r="F2" s="120"/>
+      <c r="G2" s="120"/>
+      <c r="H2" s="120"/>
+      <c r="I2" s="120"/>
+      <c r="J2" s="120"/>
+      <c r="K2" s="120"/>
+      <c r="L2" s="120"/>
+      <c r="M2" s="120"/>
+      <c r="N2" s="121"/>
+      <c r="O2" s="157"/>
+      <c r="P2" s="158"/>
+      <c r="Q2" s="158"/>
+      <c r="R2" s="159"/>
+      <c r="S2" s="166"/>
+      <c r="T2" s="167"/>
+      <c r="U2" s="167"/>
+      <c r="V2" s="167"/>
+      <c r="W2" s="167"/>
+      <c r="X2" s="167"/>
+      <c r="Y2" s="167"/>
+      <c r="Z2" s="168"/>
+      <c r="AA2" s="116" t="s">
         <v>4</v>
       </c>
-      <c r="AB2" s="86"/>
-      <c r="AC2" s="113" t="str">
+      <c r="AB2" s="118"/>
+      <c r="AC2" s="145" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC2")&lt;&gt;"",INDIRECT("変更履歴!AC2"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD2" s="114"/>
-      <c r="AE2" s="114"/>
-      <c r="AF2" s="115"/>
-      <c r="AG2" s="147">
+      <c r="AD2" s="146"/>
+      <c r="AE2" s="146"/>
+      <c r="AF2" s="147"/>
+      <c r="AG2" s="151">
         <f ca="1">IF(INDIRECT("変更履歴!AG2")&lt;&gt;"",INDIRECT("変更履歴!AG2"),"")</f>
         <v>44848</v>
       </c>
-      <c r="AH2" s="148"/>
-      <c r="AI2" s="149"/>
+      <c r="AH2" s="152"/>
+      <c r="AI2" s="153"/>
       <c r="AJ2" s="6"/>
       <c r="AN2" s="7"/>
       <c r="AO2" s="6"/>
@@ -16346,52 +16543,52 @@
       <c r="AW2" s="6"/>
     </row>
     <row r="3" spans="1:50" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="84" t="s">
+      <c r="A3" s="116" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="85"/>
-      <c r="C3" s="85"/>
-      <c r="D3" s="86"/>
-      <c r="E3" s="87" t="str">
+      <c r="B3" s="117"/>
+      <c r="C3" s="117"/>
+      <c r="D3" s="118"/>
+      <c r="E3" s="119" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E3")&lt;&gt;"",INDIRECT("変更履歴!E3"),"")</f>
         <v/>
       </c>
-      <c r="F3" s="88"/>
-      <c r="G3" s="88"/>
-      <c r="H3" s="88"/>
-      <c r="I3" s="88"/>
-      <c r="J3" s="88"/>
-      <c r="K3" s="88"/>
-      <c r="L3" s="88"/>
-      <c r="M3" s="88"/>
-      <c r="N3" s="89"/>
-      <c r="O3" s="168"/>
-      <c r="P3" s="169"/>
-      <c r="Q3" s="169"/>
-      <c r="R3" s="170"/>
-      <c r="S3" s="159"/>
-      <c r="T3" s="160"/>
-      <c r="U3" s="160"/>
-      <c r="V3" s="160"/>
-      <c r="W3" s="160"/>
-      <c r="X3" s="160"/>
-      <c r="Y3" s="160"/>
-      <c r="Z3" s="161"/>
-      <c r="AA3" s="84"/>
-      <c r="AB3" s="86"/>
-      <c r="AC3" s="113" t="str">
+      <c r="F3" s="120"/>
+      <c r="G3" s="120"/>
+      <c r="H3" s="120"/>
+      <c r="I3" s="120"/>
+      <c r="J3" s="120"/>
+      <c r="K3" s="120"/>
+      <c r="L3" s="120"/>
+      <c r="M3" s="120"/>
+      <c r="N3" s="121"/>
+      <c r="O3" s="160"/>
+      <c r="P3" s="161"/>
+      <c r="Q3" s="161"/>
+      <c r="R3" s="162"/>
+      <c r="S3" s="169"/>
+      <c r="T3" s="170"/>
+      <c r="U3" s="170"/>
+      <c r="V3" s="170"/>
+      <c r="W3" s="170"/>
+      <c r="X3" s="170"/>
+      <c r="Y3" s="170"/>
+      <c r="Z3" s="171"/>
+      <c r="AA3" s="116"/>
+      <c r="AB3" s="118"/>
+      <c r="AC3" s="145" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC3")&lt;&gt;"",INDIRECT("変更履歴!AC3"),"")</f>
         <v/>
       </c>
-      <c r="AD3" s="114"/>
-      <c r="AE3" s="114"/>
-      <c r="AF3" s="115"/>
-      <c r="AG3" s="147" t="str">
+      <c r="AD3" s="146"/>
+      <c r="AE3" s="146"/>
+      <c r="AF3" s="147"/>
+      <c r="AG3" s="151" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AG3")&lt;&gt;"",INDIRECT("変更履歴!AG3"),"")</f>
         <v/>
       </c>
-      <c r="AH3" s="148"/>
-      <c r="AI3" s="149"/>
+      <c r="AH3" s="152"/>
+      <c r="AI3" s="153"/>
       <c r="AJ3" s="9"/>
       <c r="AK3" s="1"/>
       <c r="AL3" s="1"/>
@@ -16473,22 +16670,547 @@
       <c r="AW9" s="6"/>
       <c r="AX9" s="6"/>
     </row>
-    <row r="10" spans="1:50" x14ac:dyDescent="0.15">
-      <c r="D10" s="38"/>
-    </row>
-    <row r="11" spans="1:50" x14ac:dyDescent="0.15">
-      <c r="C11" s="38"/>
-      <c r="D11"/>
+    <row r="10" spans="1:50" s="172" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C10" s="182" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="11" spans="1:50" s="172" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="12" spans="1:50" s="172" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="D12" s="172" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="13" spans="1:50" s="172" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="14" spans="1:50" s="172" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="D14" s="173" t="s">
+        <v>208</v>
+      </c>
+      <c r="E14" s="174" t="s">
+        <v>209</v>
+      </c>
+      <c r="F14" s="175"/>
+      <c r="G14" s="175"/>
+      <c r="H14" s="175"/>
+      <c r="I14" s="174" t="s">
+        <v>210</v>
+      </c>
+      <c r="J14" s="176"/>
+      <c r="K14" s="175"/>
+      <c r="L14" s="175"/>
+      <c r="M14" s="175"/>
+      <c r="N14" s="175"/>
+      <c r="O14" s="175"/>
+      <c r="P14" s="175"/>
+      <c r="Q14" s="175"/>
+      <c r="R14" s="175"/>
+      <c r="S14" s="175"/>
+      <c r="T14" s="176"/>
+      <c r="U14" s="177"/>
+    </row>
+    <row r="15" spans="1:50" s="172" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="D15" s="178">
+        <v>1</v>
+      </c>
+      <c r="E15" s="178" t="s">
+        <v>211</v>
+      </c>
+      <c r="F15" s="179"/>
+      <c r="G15" s="179"/>
+      <c r="H15" s="179"/>
+      <c r="I15" s="180" t="s">
+        <v>212</v>
+      </c>
+      <c r="J15" s="181"/>
+      <c r="K15" s="179"/>
+      <c r="L15" s="179"/>
+      <c r="M15" s="179"/>
+      <c r="N15" s="179"/>
+      <c r="O15" s="179"/>
+      <c r="P15" s="179"/>
+      <c r="Q15" s="179"/>
+      <c r="R15" s="179"/>
+      <c r="S15" s="179"/>
+      <c r="T15" s="181"/>
+      <c r="U15" s="177"/>
+    </row>
+    <row r="16" spans="1:50" s="172" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="D16" s="178">
+        <v>2</v>
+      </c>
+      <c r="E16" s="178" t="s">
+        <v>213</v>
+      </c>
+      <c r="F16" s="179"/>
+      <c r="G16" s="179"/>
+      <c r="H16" s="179"/>
+      <c r="I16" s="180" t="s">
+        <v>214</v>
+      </c>
+      <c r="J16" s="181"/>
+      <c r="K16" s="179"/>
+      <c r="L16" s="179"/>
+      <c r="M16" s="179"/>
+      <c r="N16" s="179"/>
+      <c r="O16" s="179"/>
+      <c r="P16" s="179"/>
+      <c r="Q16" s="179"/>
+      <c r="R16" s="179"/>
+      <c r="S16" s="179"/>
+      <c r="T16" s="181"/>
+      <c r="U16" s="177"/>
+    </row>
+    <row r="17" spans="4:21" s="172" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="D17" s="178">
+        <v>3</v>
+      </c>
+      <c r="E17" s="178" t="s">
+        <v>215</v>
+      </c>
+      <c r="F17" s="179"/>
+      <c r="G17" s="179"/>
+      <c r="H17" s="179"/>
+      <c r="I17" s="180" t="s">
+        <v>216</v>
+      </c>
+      <c r="J17" s="181"/>
+      <c r="K17" s="179"/>
+      <c r="L17" s="179"/>
+      <c r="M17" s="179"/>
+      <c r="N17" s="179"/>
+      <c r="O17" s="179"/>
+      <c r="P17" s="179"/>
+      <c r="Q17" s="179"/>
+      <c r="R17" s="179"/>
+      <c r="S17" s="179"/>
+      <c r="T17" s="181"/>
+      <c r="U17" s="177"/>
+    </row>
+    <row r="18" spans="4:21" s="172" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="D18" s="178">
+        <v>4</v>
+      </c>
+      <c r="E18" s="178" t="s">
+        <v>217</v>
+      </c>
+      <c r="F18" s="179"/>
+      <c r="G18" s="179"/>
+      <c r="H18" s="179"/>
+      <c r="I18" s="180" t="s">
+        <v>218</v>
+      </c>
+      <c r="J18" s="181"/>
+      <c r="K18" s="179"/>
+      <c r="L18" s="179"/>
+      <c r="M18" s="179"/>
+      <c r="N18" s="179"/>
+      <c r="O18" s="179"/>
+      <c r="P18" s="179"/>
+      <c r="Q18" s="179"/>
+      <c r="R18" s="179"/>
+      <c r="S18" s="179"/>
+      <c r="T18" s="181"/>
+      <c r="U18" s="177"/>
+    </row>
+    <row r="19" spans="4:21" s="172" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="D19" s="178">
+        <v>5</v>
+      </c>
+      <c r="E19" s="178" t="s">
+        <v>219</v>
+      </c>
+      <c r="F19" s="179"/>
+      <c r="G19" s="179"/>
+      <c r="H19" s="179"/>
+      <c r="I19" s="180" t="s">
+        <v>220</v>
+      </c>
+      <c r="J19" s="181"/>
+      <c r="K19" s="179"/>
+      <c r="L19" s="179"/>
+      <c r="M19" s="179"/>
+      <c r="N19" s="179"/>
+      <c r="O19" s="179"/>
+      <c r="P19" s="179"/>
+      <c r="Q19" s="179"/>
+      <c r="R19" s="179"/>
+      <c r="S19" s="179"/>
+      <c r="T19" s="181"/>
+      <c r="U19" s="177"/>
+    </row>
+    <row r="20" spans="4:21" s="172" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="D20" s="178">
+        <v>6</v>
+      </c>
+      <c r="E20" s="178" t="s">
+        <v>221</v>
+      </c>
+      <c r="F20" s="179"/>
+      <c r="G20" s="179"/>
+      <c r="H20" s="179"/>
+      <c r="I20" s="180" t="s">
+        <v>222</v>
+      </c>
+      <c r="J20" s="181"/>
+      <c r="K20" s="179"/>
+      <c r="L20" s="179"/>
+      <c r="M20" s="179"/>
+      <c r="N20" s="179"/>
+      <c r="O20" s="179"/>
+      <c r="P20" s="179"/>
+      <c r="Q20" s="179"/>
+      <c r="R20" s="179"/>
+      <c r="S20" s="179"/>
+      <c r="T20" s="181"/>
+      <c r="U20" s="177"/>
+    </row>
+    <row r="21" spans="4:21" s="172" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="D21" s="178">
+        <v>7</v>
+      </c>
+      <c r="E21" s="178" t="s">
+        <v>223</v>
+      </c>
+      <c r="F21" s="179"/>
+      <c r="G21" s="179"/>
+      <c r="H21" s="179"/>
+      <c r="I21" s="180" t="s">
+        <v>224</v>
+      </c>
+      <c r="J21" s="181"/>
+      <c r="K21" s="179"/>
+      <c r="L21" s="179"/>
+      <c r="M21" s="179"/>
+      <c r="N21" s="179"/>
+      <c r="O21" s="179"/>
+      <c r="P21" s="179"/>
+      <c r="Q21" s="179"/>
+      <c r="R21" s="179"/>
+      <c r="S21" s="179"/>
+      <c r="T21" s="181"/>
+      <c r="U21" s="177"/>
+    </row>
+    <row r="22" spans="4:21" s="172" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="D22" s="178">
+        <v>8</v>
+      </c>
+      <c r="E22" s="178" t="s">
+        <v>225</v>
+      </c>
+      <c r="F22" s="179"/>
+      <c r="G22" s="179"/>
+      <c r="H22" s="179"/>
+      <c r="I22" s="180" t="s">
+        <v>226</v>
+      </c>
+      <c r="J22" s="181"/>
+      <c r="K22" s="179"/>
+      <c r="L22" s="179"/>
+      <c r="M22" s="179"/>
+      <c r="N22" s="179"/>
+      <c r="O22" s="179"/>
+      <c r="P22" s="179"/>
+      <c r="Q22" s="179"/>
+      <c r="R22" s="179"/>
+      <c r="S22" s="179"/>
+      <c r="T22" s="181"/>
+      <c r="U22" s="177"/>
+    </row>
+    <row r="23" spans="4:21" s="172" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="D23" s="178">
+        <v>9</v>
+      </c>
+      <c r="E23" s="178" t="s">
+        <v>227</v>
+      </c>
+      <c r="F23" s="179"/>
+      <c r="G23" s="179"/>
+      <c r="H23" s="179"/>
+      <c r="I23" s="180" t="s">
+        <v>228</v>
+      </c>
+      <c r="J23" s="181"/>
+      <c r="K23" s="179"/>
+      <c r="L23" s="179"/>
+      <c r="M23" s="179"/>
+      <c r="N23" s="179"/>
+      <c r="O23" s="179"/>
+      <c r="P23" s="179"/>
+      <c r="Q23" s="179"/>
+      <c r="R23" s="179"/>
+      <c r="S23" s="179"/>
+      <c r="T23" s="181"/>
+      <c r="U23" s="177"/>
+    </row>
+    <row r="24" spans="4:21" s="172" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="D24" s="178">
+        <v>10</v>
+      </c>
+      <c r="E24" s="178" t="s">
+        <v>229</v>
+      </c>
+      <c r="F24" s="179"/>
+      <c r="G24" s="179"/>
+      <c r="H24" s="179"/>
+      <c r="I24" s="180" t="s">
+        <v>230</v>
+      </c>
+      <c r="J24" s="181"/>
+      <c r="K24" s="179"/>
+      <c r="L24" s="179"/>
+      <c r="M24" s="179"/>
+      <c r="N24" s="179"/>
+      <c r="O24" s="179"/>
+      <c r="P24" s="179"/>
+      <c r="Q24" s="179"/>
+      <c r="R24" s="179"/>
+      <c r="S24" s="179"/>
+      <c r="T24" s="181"/>
+      <c r="U24" s="177"/>
+    </row>
+    <row r="25" spans="4:21" s="172" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="D25" s="178">
+        <v>11</v>
+      </c>
+      <c r="E25" s="178" t="s">
+        <v>231</v>
+      </c>
+      <c r="F25" s="179"/>
+      <c r="G25" s="179"/>
+      <c r="H25" s="179"/>
+      <c r="I25" s="180" t="s">
+        <v>232</v>
+      </c>
+      <c r="J25" s="181"/>
+      <c r="K25" s="179"/>
+      <c r="L25" s="179"/>
+      <c r="M25" s="179"/>
+      <c r="N25" s="179"/>
+      <c r="O25" s="179"/>
+      <c r="P25" s="179"/>
+      <c r="Q25" s="179"/>
+      <c r="R25" s="179"/>
+      <c r="S25" s="179"/>
+      <c r="T25" s="181"/>
+      <c r="U25" s="177"/>
+    </row>
+    <row r="26" spans="4:21" s="172" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="D26" s="178">
+        <v>12</v>
+      </c>
+      <c r="E26" s="178" t="s">
+        <v>233</v>
+      </c>
+      <c r="F26" s="179"/>
+      <c r="G26" s="179"/>
+      <c r="H26" s="179"/>
+      <c r="I26" s="180" t="s">
+        <v>234</v>
+      </c>
+      <c r="J26" s="181"/>
+      <c r="K26" s="179"/>
+      <c r="L26" s="179"/>
+      <c r="M26" s="179"/>
+      <c r="N26" s="179"/>
+      <c r="O26" s="179"/>
+      <c r="P26" s="179"/>
+      <c r="Q26" s="179"/>
+      <c r="R26" s="179"/>
+      <c r="S26" s="179"/>
+      <c r="T26" s="181"/>
+      <c r="U26" s="177"/>
+    </row>
+    <row r="27" spans="4:21" s="172" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="D27" s="178">
+        <v>13</v>
+      </c>
+      <c r="E27" s="178" t="s">
+        <v>235</v>
+      </c>
+      <c r="F27" s="179"/>
+      <c r="G27" s="179"/>
+      <c r="H27" s="179"/>
+      <c r="I27" s="180" t="s">
+        <v>236</v>
+      </c>
+      <c r="J27" s="181"/>
+      <c r="K27" s="179"/>
+      <c r="L27" s="179"/>
+      <c r="M27" s="179"/>
+      <c r="N27" s="179"/>
+      <c r="O27" s="179"/>
+      <c r="P27" s="179"/>
+      <c r="Q27" s="179"/>
+      <c r="R27" s="179"/>
+      <c r="S27" s="179"/>
+      <c r="T27" s="181"/>
+      <c r="U27" s="177"/>
+    </row>
+    <row r="28" spans="4:21" s="172" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="D28" s="178">
+        <v>14</v>
+      </c>
+      <c r="E28" s="178" t="s">
+        <v>237</v>
+      </c>
+      <c r="F28" s="179"/>
+      <c r="G28" s="179"/>
+      <c r="H28" s="179"/>
+      <c r="I28" s="180" t="s">
+        <v>238</v>
+      </c>
+      <c r="J28" s="181"/>
+      <c r="K28" s="179"/>
+      <c r="L28" s="179"/>
+      <c r="M28" s="179"/>
+      <c r="N28" s="179"/>
+      <c r="O28" s="179"/>
+      <c r="P28" s="179"/>
+      <c r="Q28" s="179"/>
+      <c r="R28" s="179"/>
+      <c r="S28" s="179"/>
+      <c r="T28" s="181"/>
+      <c r="U28" s="177"/>
+    </row>
+    <row r="29" spans="4:21" s="172" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="D29" s="178">
+        <v>15</v>
+      </c>
+      <c r="E29" s="178" t="s">
+        <v>239</v>
+      </c>
+      <c r="F29" s="179"/>
+      <c r="G29" s="179"/>
+      <c r="H29" s="179"/>
+      <c r="I29" s="180" t="s">
+        <v>240</v>
+      </c>
+      <c r="J29" s="181"/>
+      <c r="K29" s="179"/>
+      <c r="L29" s="179"/>
+      <c r="M29" s="179"/>
+      <c r="N29" s="179"/>
+      <c r="O29" s="179"/>
+      <c r="P29" s="179"/>
+      <c r="Q29" s="179"/>
+      <c r="R29" s="179"/>
+      <c r="S29" s="179"/>
+      <c r="T29" s="181"/>
+      <c r="U29" s="177"/>
+    </row>
+    <row r="30" spans="4:21" s="172" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="D30" s="178">
+        <v>16</v>
+      </c>
+      <c r="E30" s="178" t="s">
+        <v>241</v>
+      </c>
+      <c r="F30" s="179"/>
+      <c r="G30" s="179"/>
+      <c r="H30" s="179"/>
+      <c r="I30" s="180" t="s">
+        <v>242</v>
+      </c>
+      <c r="J30" s="181"/>
+      <c r="K30" s="179"/>
+      <c r="L30" s="179"/>
+      <c r="M30" s="179"/>
+      <c r="N30" s="179"/>
+      <c r="O30" s="179"/>
+      <c r="P30" s="179"/>
+      <c r="Q30" s="179"/>
+      <c r="R30" s="179"/>
+      <c r="S30" s="179"/>
+      <c r="T30" s="181"/>
+      <c r="U30" s="177"/>
+    </row>
+    <row r="31" spans="4:21" s="172" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="D31" s="178">
+        <v>17</v>
+      </c>
+      <c r="E31" s="178" t="s">
+        <v>243</v>
+      </c>
+      <c r="F31" s="179"/>
+      <c r="G31" s="179"/>
+      <c r="H31" s="179"/>
+      <c r="I31" s="180" t="s">
+        <v>244</v>
+      </c>
+      <c r="J31" s="181"/>
+      <c r="K31" s="179"/>
+      <c r="L31" s="179"/>
+      <c r="M31" s="179"/>
+      <c r="N31" s="179"/>
+      <c r="O31" s="179"/>
+      <c r="P31" s="179"/>
+      <c r="Q31" s="179"/>
+      <c r="R31" s="179"/>
+      <c r="S31" s="179"/>
+      <c r="T31" s="181"/>
+      <c r="U31" s="177"/>
+    </row>
+    <row r="32" spans="4:21" s="172" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="D32" s="178">
+        <v>18</v>
+      </c>
+      <c r="E32" s="178" t="s">
+        <v>245</v>
+      </c>
+      <c r="F32" s="179"/>
+      <c r="G32" s="179"/>
+      <c r="H32" s="179"/>
+      <c r="I32" s="180" t="s">
+        <v>246</v>
+      </c>
+      <c r="J32" s="181"/>
+      <c r="K32" s="179"/>
+      <c r="L32" s="179"/>
+      <c r="M32" s="179"/>
+      <c r="N32" s="179"/>
+      <c r="O32" s="179"/>
+      <c r="P32" s="179"/>
+      <c r="Q32" s="179"/>
+      <c r="R32" s="179"/>
+      <c r="S32" s="179"/>
+      <c r="T32" s="181"/>
+      <c r="U32" s="177"/>
+    </row>
+    <row r="33" spans="3:21" s="172" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="D33" s="178">
+        <v>19</v>
+      </c>
+      <c r="E33" s="178" t="s">
+        <v>247</v>
+      </c>
+      <c r="F33" s="179"/>
+      <c r="G33" s="179"/>
+      <c r="H33" s="179"/>
+      <c r="I33" s="180" t="s">
+        <v>248</v>
+      </c>
+      <c r="J33" s="181"/>
+      <c r="K33" s="179"/>
+      <c r="L33" s="179"/>
+      <c r="M33" s="179"/>
+      <c r="N33" s="179"/>
+      <c r="O33" s="179"/>
+      <c r="P33" s="179"/>
+      <c r="Q33" s="179"/>
+      <c r="R33" s="179"/>
+      <c r="S33" s="179"/>
+      <c r="T33" s="181"/>
+      <c r="U33" s="177"/>
+    </row>
+    <row r="34" spans="3:21" x14ac:dyDescent="0.15">
+      <c r="D34" s="38"/>
+    </row>
+    <row r="35" spans="3:21" x14ac:dyDescent="0.15">
+      <c r="C35" s="38"/>
+      <c r="D35"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="O1:R3"/>
-    <mergeCell ref="AA1:AB1"/>
-    <mergeCell ref="AA2:AB2"/>
-    <mergeCell ref="AA3:AB3"/>
     <mergeCell ref="AC3:AF3"/>
     <mergeCell ref="AG3:AI3"/>
     <mergeCell ref="E1:N1"/>
@@ -16499,11 +17221,39 @@
     <mergeCell ref="AC2:AF2"/>
     <mergeCell ref="AG2:AI2"/>
     <mergeCell ref="S1:Z3"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="O1:R3"/>
+    <mergeCell ref="AA1:AB1"/>
+    <mergeCell ref="AA2:AB2"/>
+    <mergeCell ref="AA3:AB3"/>
   </mergeCells>
   <phoneticPr fontId="10"/>
+  <hyperlinks>
+    <hyperlink ref="AB15" r:id="rId1" display="https://jakarta.ee/specifications/faces/" xr:uid="{A1CDF289-622B-415E-8DD7-79777CFD0F39}"/>
+    <hyperlink ref="AB16" r:id="rId2" display="https://jakarta.ee/specifications/authentication/" xr:uid="{49DDB29E-F977-4C84-B300-6B23000B25EC}"/>
+    <hyperlink ref="AB17" r:id="rId3" display="https://jakarta.ee/specifications/authorization/" xr:uid="{DF7FB6E4-BF79-4A82-A090-FB95A4DAEAA6}"/>
+    <hyperlink ref="AB18" r:id="rId4" display="https://jakarta.ee/specifications/messaging/" xr:uid="{D0B46F37-30B7-4F77-B1AE-19183BF86502}"/>
+    <hyperlink ref="AB19" r:id="rId5" display="https://jakarta.ee/specifications/persistence/" xr:uid="{9952206C-D127-4359-8EE3-DF51D8556240}"/>
+    <hyperlink ref="AB20" r:id="rId6" display="https://jakarta.ee/specifications/transactions/" xr:uid="{B7B333C1-7295-4D94-AAF5-67C2325FECD9}"/>
+    <hyperlink ref="AB21" r:id="rId7" display="https://jakarta.ee/specifications/batch/" xr:uid="{991A5834-A442-48FE-81E7-507ECD0B0FB2}"/>
+    <hyperlink ref="AB22" r:id="rId8" display="https://jakarta.ee/specifications/connectors/" xr:uid="{7633A53E-0FD7-4BAF-BA63-F434475351EF}"/>
+    <hyperlink ref="AB23" r:id="rId9" display="https://jakarta.ee/specifications/activation/" xr:uid="{91D54A17-C7C5-463A-BBCC-358D190D657F}"/>
+    <hyperlink ref="AB24" r:id="rId10" display="https://jakarta.ee/specifications/expression-language/" xr:uid="{6BB03A96-1BD2-46EF-9371-967C104EE2D5}"/>
+    <hyperlink ref="AB25" r:id="rId11" display="https://jakarta.ee/specifications/enterprise-beans/" xr:uid="{9703855A-D5F6-432D-BDCC-3086906EDB56}"/>
+    <hyperlink ref="AB26" r:id="rId12" display="https://jakarta.ee/specifications/xml-binding/" xr:uid="{66461F33-B064-49A5-9DA7-59758E41EC0A}"/>
+    <hyperlink ref="AB27" r:id="rId13" display="https://jakarta.ee/specifications/jsonb/" xr:uid="{9F173BD6-5F61-42ED-A3CE-23E9E226803E}"/>
+    <hyperlink ref="AB28" r:id="rId14" display="https://jakarta.ee/specifications/jsonp/" xr:uid="{AE9A363A-7A11-42A7-9F11-2B6EBB5B6892}"/>
+    <hyperlink ref="AB29" r:id="rId15" display="https://jakarta.ee/specifications/pages/" xr:uid="{BE4F1F25-AA14-4A4B-8152-A5631DE0939B}"/>
+    <hyperlink ref="AB30" r:id="rId16" display="https://jakarta.ee/specifications/xml-web-services/" xr:uid="{BA5BD9E6-2B5C-44F6-9B0C-7F2C127128C4}"/>
+    <hyperlink ref="AB31" r:id="rId17" display="https://jakarta.ee/specifications/restful-ws/" xr:uid="{F1C36587-F45F-4061-8AE5-FE737F71444C}"/>
+    <hyperlink ref="AB32" r:id="rId18" display="https://jakarta.ee/specifications/tags/" xr:uid="{46186705-1011-4047-B8BB-9F40E9200823}"/>
+    <hyperlink ref="AB33" r:id="rId19" display="https://jakarta.ee/specifications/cdi/" xr:uid="{E0FD9CCA-67BD-49E1-B6F2-68A671C7ADD3}"/>
+  </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
-  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" useFirstPageNumber="1" r:id="rId1"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" useFirstPageNumber="1" r:id="rId20"/>
   <headerFooter alignWithMargins="0">
     <oddFooter>&amp;C- &amp;P -</oddFooter>
   </headerFooter>
@@ -16523,59 +17273,59 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:49" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="84" t="s">
+      <c r="A1" s="116" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="85"/>
-      <c r="D1" s="86"/>
-      <c r="E1" s="87" t="str">
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="118"/>
+      <c r="E1" s="119" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E1")&lt;&gt;"",INDIRECT("変更履歴!E1"),"")</f>
         <v/>
       </c>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
-      <c r="H1" s="88"/>
-      <c r="I1" s="88"/>
-      <c r="J1" s="88"/>
-      <c r="K1" s="88"/>
-      <c r="L1" s="88"/>
-      <c r="M1" s="88"/>
-      <c r="N1" s="89"/>
-      <c r="O1" s="162" t="s">
+      <c r="F1" s="120"/>
+      <c r="G1" s="120"/>
+      <c r="H1" s="120"/>
+      <c r="I1" s="120"/>
+      <c r="J1" s="120"/>
+      <c r="K1" s="120"/>
+      <c r="L1" s="120"/>
+      <c r="M1" s="120"/>
+      <c r="N1" s="121"/>
+      <c r="O1" s="154" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="163"/>
-      <c r="Q1" s="163"/>
-      <c r="R1" s="164"/>
-      <c r="S1" s="153" t="str">
+      <c r="P1" s="155"/>
+      <c r="Q1" s="155"/>
+      <c r="R1" s="156"/>
+      <c r="S1" s="163" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!S1")&lt;&gt;"",INDIRECT("変更履歴!S1"),"")</f>
         <v>Nablarch開発標準設計書一覧</v>
       </c>
-      <c r="T1" s="154"/>
-      <c r="U1" s="154"/>
-      <c r="V1" s="154"/>
-      <c r="W1" s="154"/>
-      <c r="X1" s="154"/>
-      <c r="Y1" s="154"/>
-      <c r="Z1" s="155"/>
-      <c r="AA1" s="84" t="s">
+      <c r="T1" s="164"/>
+      <c r="U1" s="164"/>
+      <c r="V1" s="164"/>
+      <c r="W1" s="164"/>
+      <c r="X1" s="164"/>
+      <c r="Y1" s="164"/>
+      <c r="Z1" s="165"/>
+      <c r="AA1" s="116" t="s">
         <v>3</v>
       </c>
-      <c r="AB1" s="86"/>
-      <c r="AC1" s="113" t="str">
+      <c r="AB1" s="118"/>
+      <c r="AC1" s="145" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC1")&lt;&gt;"",INDIRECT("変更履歴!AC1"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="114"/>
-      <c r="AE1" s="114"/>
-      <c r="AF1" s="115"/>
-      <c r="AG1" s="147">
+      <c r="AD1" s="146"/>
+      <c r="AE1" s="146"/>
+      <c r="AF1" s="147"/>
+      <c r="AG1" s="151">
         <f ca="1">IF(INDIRECT("変更履歴!AG1")&lt;&gt;"",INDIRECT("変更履歴!AG1"),"")</f>
         <v>43336</v>
       </c>
-      <c r="AH1" s="148"/>
-      <c r="AI1" s="149"/>
+      <c r="AH1" s="152"/>
+      <c r="AI1" s="153"/>
       <c r="AJ1" s="6"/>
       <c r="AN1" s="7"/>
       <c r="AO1" s="6"/>
@@ -16589,54 +17339,54 @@
       <c r="AW1" s="6"/>
     </row>
     <row r="2" spans="1:49" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="84" t="s">
+      <c r="A2" s="116" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="85"/>
-      <c r="C2" s="85"/>
-      <c r="D2" s="86"/>
-      <c r="E2" s="87" t="str">
+      <c r="B2" s="117"/>
+      <c r="C2" s="117"/>
+      <c r="D2" s="118"/>
+      <c r="E2" s="119" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E2")&lt;&gt;"",INDIRECT("変更履歴!E2"),"")</f>
         <v/>
       </c>
-      <c r="F2" s="88"/>
-      <c r="G2" s="88"/>
-      <c r="H2" s="88"/>
-      <c r="I2" s="88"/>
-      <c r="J2" s="88"/>
-      <c r="K2" s="88"/>
-      <c r="L2" s="88"/>
-      <c r="M2" s="88"/>
-      <c r="N2" s="89"/>
-      <c r="O2" s="165"/>
-      <c r="P2" s="166"/>
-      <c r="Q2" s="166"/>
-      <c r="R2" s="167"/>
-      <c r="S2" s="156"/>
-      <c r="T2" s="157"/>
-      <c r="U2" s="157"/>
-      <c r="V2" s="157"/>
-      <c r="W2" s="157"/>
-      <c r="X2" s="157"/>
-      <c r="Y2" s="157"/>
-      <c r="Z2" s="158"/>
-      <c r="AA2" s="84" t="s">
+      <c r="F2" s="120"/>
+      <c r="G2" s="120"/>
+      <c r="H2" s="120"/>
+      <c r="I2" s="120"/>
+      <c r="J2" s="120"/>
+      <c r="K2" s="120"/>
+      <c r="L2" s="120"/>
+      <c r="M2" s="120"/>
+      <c r="N2" s="121"/>
+      <c r="O2" s="157"/>
+      <c r="P2" s="158"/>
+      <c r="Q2" s="158"/>
+      <c r="R2" s="159"/>
+      <c r="S2" s="166"/>
+      <c r="T2" s="167"/>
+      <c r="U2" s="167"/>
+      <c r="V2" s="167"/>
+      <c r="W2" s="167"/>
+      <c r="X2" s="167"/>
+      <c r="Y2" s="167"/>
+      <c r="Z2" s="168"/>
+      <c r="AA2" s="116" t="s">
         <v>4</v>
       </c>
-      <c r="AB2" s="86"/>
-      <c r="AC2" s="113" t="str">
+      <c r="AB2" s="118"/>
+      <c r="AC2" s="145" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC2")&lt;&gt;"",INDIRECT("変更履歴!AC2"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD2" s="114"/>
-      <c r="AE2" s="114"/>
-      <c r="AF2" s="115"/>
-      <c r="AG2" s="147">
+      <c r="AD2" s="146"/>
+      <c r="AE2" s="146"/>
+      <c r="AF2" s="147"/>
+      <c r="AG2" s="151">
         <f ca="1">IF(INDIRECT("変更履歴!AG2")&lt;&gt;"",INDIRECT("変更履歴!AG2"),"")</f>
         <v>44848</v>
       </c>
-      <c r="AH2" s="148"/>
-      <c r="AI2" s="149"/>
+      <c r="AH2" s="152"/>
+      <c r="AI2" s="153"/>
       <c r="AJ2" s="6"/>
       <c r="AN2" s="7"/>
       <c r="AO2" s="6"/>
@@ -16650,52 +17400,52 @@
       <c r="AW2" s="6"/>
     </row>
     <row r="3" spans="1:49" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="84" t="s">
+      <c r="A3" s="116" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="85"/>
-      <c r="C3" s="85"/>
-      <c r="D3" s="86"/>
-      <c r="E3" s="87" t="str">
+      <c r="B3" s="117"/>
+      <c r="C3" s="117"/>
+      <c r="D3" s="118"/>
+      <c r="E3" s="119" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E3")&lt;&gt;"",INDIRECT("変更履歴!E3"),"")</f>
         <v/>
       </c>
-      <c r="F3" s="88"/>
-      <c r="G3" s="88"/>
-      <c r="H3" s="88"/>
-      <c r="I3" s="88"/>
-      <c r="J3" s="88"/>
-      <c r="K3" s="88"/>
-      <c r="L3" s="88"/>
-      <c r="M3" s="88"/>
-      <c r="N3" s="89"/>
-      <c r="O3" s="168"/>
-      <c r="P3" s="169"/>
-      <c r="Q3" s="169"/>
-      <c r="R3" s="170"/>
-      <c r="S3" s="159"/>
-      <c r="T3" s="160"/>
-      <c r="U3" s="160"/>
-      <c r="V3" s="160"/>
-      <c r="W3" s="160"/>
-      <c r="X3" s="160"/>
-      <c r="Y3" s="160"/>
-      <c r="Z3" s="161"/>
-      <c r="AA3" s="84"/>
-      <c r="AB3" s="86"/>
-      <c r="AC3" s="113" t="str">
+      <c r="F3" s="120"/>
+      <c r="G3" s="120"/>
+      <c r="H3" s="120"/>
+      <c r="I3" s="120"/>
+      <c r="J3" s="120"/>
+      <c r="K3" s="120"/>
+      <c r="L3" s="120"/>
+      <c r="M3" s="120"/>
+      <c r="N3" s="121"/>
+      <c r="O3" s="160"/>
+      <c r="P3" s="161"/>
+      <c r="Q3" s="161"/>
+      <c r="R3" s="162"/>
+      <c r="S3" s="169"/>
+      <c r="T3" s="170"/>
+      <c r="U3" s="170"/>
+      <c r="V3" s="170"/>
+      <c r="W3" s="170"/>
+      <c r="X3" s="170"/>
+      <c r="Y3" s="170"/>
+      <c r="Z3" s="171"/>
+      <c r="AA3" s="116"/>
+      <c r="AB3" s="118"/>
+      <c r="AC3" s="145" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC3")&lt;&gt;"",INDIRECT("変更履歴!AC3"),"")</f>
         <v/>
       </c>
-      <c r="AD3" s="114"/>
-      <c r="AE3" s="114"/>
-      <c r="AF3" s="115"/>
-      <c r="AG3" s="147" t="str">
+      <c r="AD3" s="146"/>
+      <c r="AE3" s="146"/>
+      <c r="AF3" s="147"/>
+      <c r="AG3" s="151" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AG3")&lt;&gt;"",INDIRECT("変更履歴!AG3"),"")</f>
         <v/>
       </c>
-      <c r="AH3" s="148"/>
-      <c r="AI3" s="149"/>
+      <c r="AH3" s="152"/>
+      <c r="AI3" s="153"/>
       <c r="AJ3" s="9"/>
       <c r="AK3" s="1"/>
       <c r="AL3" s="1"/>
@@ -16737,14 +17487,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="AG1:AI1"/>
-    <mergeCell ref="AC1:AF1"/>
-    <mergeCell ref="AC2:AF2"/>
-    <mergeCell ref="AG2:AI2"/>
-    <mergeCell ref="E3:N3"/>
-    <mergeCell ref="AA3:AB3"/>
-    <mergeCell ref="AC3:AF3"/>
-    <mergeCell ref="AG3:AI3"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="E1:N1"/>
     <mergeCell ref="O1:R3"/>
@@ -16754,6 +17496,14 @@
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="E2:N2"/>
     <mergeCell ref="AA2:AB2"/>
+    <mergeCell ref="AG1:AI1"/>
+    <mergeCell ref="AC1:AF1"/>
+    <mergeCell ref="AC2:AF2"/>
+    <mergeCell ref="AG2:AI2"/>
+    <mergeCell ref="E3:N3"/>
+    <mergeCell ref="AA3:AB3"/>
+    <mergeCell ref="AC3:AF3"/>
+    <mergeCell ref="AG3:AI3"/>
   </mergeCells>
   <phoneticPr fontId="10"/>
   <printOptions horizontalCentered="1"/>
@@ -16783,59 +17533,59 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="84" t="s">
+      <c r="A1" s="116" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="85"/>
-      <c r="D1" s="86"/>
-      <c r="E1" s="87" t="str">
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="118"/>
+      <c r="E1" s="119" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E1")&lt;&gt;"",INDIRECT("変更履歴!E1"),"")</f>
         <v/>
       </c>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
-      <c r="H1" s="88"/>
-      <c r="I1" s="88"/>
-      <c r="J1" s="88"/>
-      <c r="K1" s="88"/>
-      <c r="L1" s="88"/>
-      <c r="M1" s="88"/>
-      <c r="N1" s="89"/>
-      <c r="O1" s="162" t="s">
+      <c r="F1" s="120"/>
+      <c r="G1" s="120"/>
+      <c r="H1" s="120"/>
+      <c r="I1" s="120"/>
+      <c r="J1" s="120"/>
+      <c r="K1" s="120"/>
+      <c r="L1" s="120"/>
+      <c r="M1" s="120"/>
+      <c r="N1" s="121"/>
+      <c r="O1" s="154" t="s">
         <v>73</v>
       </c>
-      <c r="P1" s="163"/>
-      <c r="Q1" s="163"/>
-      <c r="R1" s="164"/>
-      <c r="S1" s="153" t="str">
+      <c r="P1" s="155"/>
+      <c r="Q1" s="155"/>
+      <c r="R1" s="156"/>
+      <c r="S1" s="163" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!S1")&lt;&gt;"",INDIRECT("変更履歴!S1"),"")</f>
         <v>Nablarch開発標準設計書一覧</v>
       </c>
-      <c r="T1" s="154"/>
-      <c r="U1" s="154"/>
-      <c r="V1" s="154"/>
-      <c r="W1" s="154"/>
-      <c r="X1" s="154"/>
-      <c r="Y1" s="154"/>
-      <c r="Z1" s="155"/>
-      <c r="AA1" s="84" t="s">
+      <c r="T1" s="164"/>
+      <c r="U1" s="164"/>
+      <c r="V1" s="164"/>
+      <c r="W1" s="164"/>
+      <c r="X1" s="164"/>
+      <c r="Y1" s="164"/>
+      <c r="Z1" s="165"/>
+      <c r="AA1" s="116" t="s">
         <v>3</v>
       </c>
-      <c r="AB1" s="86"/>
-      <c r="AC1" s="113" t="str">
+      <c r="AB1" s="118"/>
+      <c r="AC1" s="145" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC1")&lt;&gt;"",INDIRECT("変更履歴!AC1"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="114"/>
-      <c r="AE1" s="114"/>
-      <c r="AF1" s="115"/>
-      <c r="AG1" s="147">
+      <c r="AD1" s="146"/>
+      <c r="AE1" s="146"/>
+      <c r="AF1" s="147"/>
+      <c r="AG1" s="151">
         <f ca="1">IF(INDIRECT("変更履歴!AG1")&lt;&gt;"",INDIRECT("変更履歴!AG1"),"")</f>
         <v>43336</v>
       </c>
-      <c r="AH1" s="148"/>
-      <c r="AI1" s="149"/>
+      <c r="AH1" s="152"/>
+      <c r="AI1" s="153"/>
       <c r="AJ1" s="6"/>
       <c r="AM1" s="6"/>
       <c r="AN1" s="6"/>
@@ -16843,54 +17593,54 @@
       <c r="AP1" s="6"/>
     </row>
     <row r="2" spans="1:42" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="84" t="s">
+      <c r="A2" s="116" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="85"/>
-      <c r="C2" s="85"/>
-      <c r="D2" s="86"/>
-      <c r="E2" s="87" t="str">
+      <c r="B2" s="117"/>
+      <c r="C2" s="117"/>
+      <c r="D2" s="118"/>
+      <c r="E2" s="119" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E2")&lt;&gt;"",INDIRECT("変更履歴!E2"),"")</f>
         <v/>
       </c>
-      <c r="F2" s="88"/>
-      <c r="G2" s="88"/>
-      <c r="H2" s="88"/>
-      <c r="I2" s="88"/>
-      <c r="J2" s="88"/>
-      <c r="K2" s="88"/>
-      <c r="L2" s="88"/>
-      <c r="M2" s="88"/>
-      <c r="N2" s="89"/>
-      <c r="O2" s="165"/>
-      <c r="P2" s="166"/>
-      <c r="Q2" s="166"/>
-      <c r="R2" s="167"/>
-      <c r="S2" s="156"/>
-      <c r="T2" s="157"/>
-      <c r="U2" s="157"/>
-      <c r="V2" s="157"/>
-      <c r="W2" s="157"/>
-      <c r="X2" s="157"/>
-      <c r="Y2" s="157"/>
-      <c r="Z2" s="158"/>
-      <c r="AA2" s="84" t="s">
+      <c r="F2" s="120"/>
+      <c r="G2" s="120"/>
+      <c r="H2" s="120"/>
+      <c r="I2" s="120"/>
+      <c r="J2" s="120"/>
+      <c r="K2" s="120"/>
+      <c r="L2" s="120"/>
+      <c r="M2" s="120"/>
+      <c r="N2" s="121"/>
+      <c r="O2" s="157"/>
+      <c r="P2" s="158"/>
+      <c r="Q2" s="158"/>
+      <c r="R2" s="159"/>
+      <c r="S2" s="166"/>
+      <c r="T2" s="167"/>
+      <c r="U2" s="167"/>
+      <c r="V2" s="167"/>
+      <c r="W2" s="167"/>
+      <c r="X2" s="167"/>
+      <c r="Y2" s="167"/>
+      <c r="Z2" s="168"/>
+      <c r="AA2" s="116" t="s">
         <v>4</v>
       </c>
-      <c r="AB2" s="86"/>
-      <c r="AC2" s="113" t="str">
+      <c r="AB2" s="118"/>
+      <c r="AC2" s="145" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC2")&lt;&gt;"",INDIRECT("変更履歴!AC2"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD2" s="114"/>
-      <c r="AE2" s="114"/>
-      <c r="AF2" s="115"/>
-      <c r="AG2" s="147">
+      <c r="AD2" s="146"/>
+      <c r="AE2" s="146"/>
+      <c r="AF2" s="147"/>
+      <c r="AG2" s="151">
         <f ca="1">IF(INDIRECT("変更履歴!AG2")&lt;&gt;"",INDIRECT("変更履歴!AG2"),"")</f>
         <v>44848</v>
       </c>
-      <c r="AH2" s="148"/>
-      <c r="AI2" s="149"/>
+      <c r="AH2" s="152"/>
+      <c r="AI2" s="153"/>
       <c r="AJ2" s="6"/>
       <c r="AM2" s="6"/>
       <c r="AN2" s="6"/>
@@ -16898,52 +17648,52 @@
       <c r="AP2" s="6"/>
     </row>
     <row r="3" spans="1:42" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="84" t="s">
+      <c r="A3" s="116" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="85"/>
-      <c r="C3" s="85"/>
-      <c r="D3" s="86"/>
-      <c r="E3" s="87" t="str">
+      <c r="B3" s="117"/>
+      <c r="C3" s="117"/>
+      <c r="D3" s="118"/>
+      <c r="E3" s="119" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E3")&lt;&gt;"",INDIRECT("変更履歴!E3"),"")</f>
         <v/>
       </c>
-      <c r="F3" s="88"/>
-      <c r="G3" s="88"/>
-      <c r="H3" s="88"/>
-      <c r="I3" s="88"/>
-      <c r="J3" s="88"/>
-      <c r="K3" s="88"/>
-      <c r="L3" s="88"/>
-      <c r="M3" s="88"/>
-      <c r="N3" s="89"/>
-      <c r="O3" s="168"/>
-      <c r="P3" s="169"/>
-      <c r="Q3" s="169"/>
-      <c r="R3" s="170"/>
-      <c r="S3" s="159"/>
-      <c r="T3" s="160"/>
-      <c r="U3" s="160"/>
-      <c r="V3" s="160"/>
-      <c r="W3" s="160"/>
-      <c r="X3" s="160"/>
-      <c r="Y3" s="160"/>
-      <c r="Z3" s="161"/>
-      <c r="AA3" s="84"/>
-      <c r="AB3" s="86"/>
-      <c r="AC3" s="113" t="str">
+      <c r="F3" s="120"/>
+      <c r="G3" s="120"/>
+      <c r="H3" s="120"/>
+      <c r="I3" s="120"/>
+      <c r="J3" s="120"/>
+      <c r="K3" s="120"/>
+      <c r="L3" s="120"/>
+      <c r="M3" s="120"/>
+      <c r="N3" s="121"/>
+      <c r="O3" s="160"/>
+      <c r="P3" s="161"/>
+      <c r="Q3" s="161"/>
+      <c r="R3" s="162"/>
+      <c r="S3" s="169"/>
+      <c r="T3" s="170"/>
+      <c r="U3" s="170"/>
+      <c r="V3" s="170"/>
+      <c r="W3" s="170"/>
+      <c r="X3" s="170"/>
+      <c r="Y3" s="170"/>
+      <c r="Z3" s="171"/>
+      <c r="AA3" s="116"/>
+      <c r="AB3" s="118"/>
+      <c r="AC3" s="145" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC3")&lt;&gt;"",INDIRECT("変更履歴!AC3"),"")</f>
         <v/>
       </c>
-      <c r="AD3" s="114"/>
-      <c r="AE3" s="114"/>
-      <c r="AF3" s="115"/>
-      <c r="AG3" s="147" t="str">
+      <c r="AD3" s="146"/>
+      <c r="AE3" s="146"/>
+      <c r="AF3" s="147"/>
+      <c r="AG3" s="151" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AG3")&lt;&gt;"",INDIRECT("変更履歴!AG3"),"")</f>
         <v/>
       </c>
-      <c r="AH3" s="148"/>
-      <c r="AI3" s="149"/>
+      <c r="AH3" s="152"/>
+      <c r="AI3" s="153"/>
       <c r="AJ3" s="9"/>
       <c r="AK3" s="1"/>
       <c r="AL3" s="1"/>
@@ -20121,7 +20871,7 @@
     <row r="69" spans="2:42" x14ac:dyDescent="0.15">
       <c r="B69" s="71"/>
       <c r="C69" s="69"/>
-      <c r="D69" s="171" t="s">
+      <c r="D69" s="76" t="s">
         <v>202</v>
       </c>
       <c r="E69" s="67"/>
@@ -20176,7 +20926,7 @@
     <row r="70" spans="2:42" x14ac:dyDescent="0.15">
       <c r="B70" s="71"/>
       <c r="C70" s="69"/>
-      <c r="D70" s="171" t="s">
+      <c r="D70" s="76" t="s">
         <v>203</v>
       </c>
       <c r="E70" s="67"/>
@@ -20231,7 +20981,7 @@
     <row r="71" spans="2:42" x14ac:dyDescent="0.15">
       <c r="B71" s="71"/>
       <c r="C71" s="69"/>
-      <c r="D71" s="171" t="s">
+      <c r="D71" s="76" t="s">
         <v>204</v>
       </c>
       <c r="E71" s="67"/>
@@ -20286,7 +21036,7 @@
     <row r="72" spans="2:42" x14ac:dyDescent="0.15">
       <c r="B72" s="72"/>
       <c r="C72" s="65"/>
-      <c r="D72" s="171" t="s">
+      <c r="D72" s="76" t="s">
         <v>205</v>
       </c>
       <c r="E72" s="67"/>
@@ -20340,6 +21090,14 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="AG1:AI1"/>
+    <mergeCell ref="AC1:AF1"/>
+    <mergeCell ref="AC2:AF2"/>
+    <mergeCell ref="AG2:AI2"/>
+    <mergeCell ref="E3:N3"/>
+    <mergeCell ref="AA3:AB3"/>
+    <mergeCell ref="AC3:AF3"/>
+    <mergeCell ref="AG3:AI3"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="E1:N1"/>
     <mergeCell ref="O1:R3"/>
@@ -20349,14 +21107,6 @@
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="E2:N2"/>
     <mergeCell ref="AA2:AB2"/>
-    <mergeCell ref="AG1:AI1"/>
-    <mergeCell ref="AC1:AF1"/>
-    <mergeCell ref="AC2:AF2"/>
-    <mergeCell ref="AG2:AI2"/>
-    <mergeCell ref="E3:N3"/>
-    <mergeCell ref="AA3:AB3"/>
-    <mergeCell ref="AC3:AF3"/>
-    <mergeCell ref="AG3:AI3"/>
   </mergeCells>
   <phoneticPr fontId="10"/>
   <printOptions horizontalCentered="1"/>
@@ -20384,59 +21134,59 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:49" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="84" t="s">
+      <c r="A1" s="116" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="85"/>
-      <c r="D1" s="86"/>
-      <c r="E1" s="87" t="str">
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="118"/>
+      <c r="E1" s="119" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E1")&lt;&gt;"",INDIRECT("変更履歴!E1"),"")</f>
         <v/>
       </c>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
-      <c r="H1" s="88"/>
-      <c r="I1" s="88"/>
-      <c r="J1" s="88"/>
-      <c r="K1" s="88"/>
-      <c r="L1" s="88"/>
-      <c r="M1" s="88"/>
-      <c r="N1" s="89"/>
-      <c r="O1" s="162" t="s">
+      <c r="F1" s="120"/>
+      <c r="G1" s="120"/>
+      <c r="H1" s="120"/>
+      <c r="I1" s="120"/>
+      <c r="J1" s="120"/>
+      <c r="K1" s="120"/>
+      <c r="L1" s="120"/>
+      <c r="M1" s="120"/>
+      <c r="N1" s="121"/>
+      <c r="O1" s="154" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="163"/>
-      <c r="Q1" s="163"/>
-      <c r="R1" s="164"/>
-      <c r="S1" s="153" t="str">
+      <c r="P1" s="155"/>
+      <c r="Q1" s="155"/>
+      <c r="R1" s="156"/>
+      <c r="S1" s="163" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!S1")&lt;&gt;"",INDIRECT("変更履歴!S1"),"")</f>
         <v>Nablarch開発標準設計書一覧</v>
       </c>
-      <c r="T1" s="154"/>
-      <c r="U1" s="154"/>
-      <c r="V1" s="154"/>
-      <c r="W1" s="154"/>
-      <c r="X1" s="154"/>
-      <c r="Y1" s="154"/>
-      <c r="Z1" s="155"/>
-      <c r="AA1" s="84" t="s">
+      <c r="T1" s="164"/>
+      <c r="U1" s="164"/>
+      <c r="V1" s="164"/>
+      <c r="W1" s="164"/>
+      <c r="X1" s="164"/>
+      <c r="Y1" s="164"/>
+      <c r="Z1" s="165"/>
+      <c r="AA1" s="116" t="s">
         <v>3</v>
       </c>
-      <c r="AB1" s="86"/>
-      <c r="AC1" s="113" t="str">
+      <c r="AB1" s="118"/>
+      <c r="AC1" s="145" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC1")&lt;&gt;"",INDIRECT("変更履歴!AC1"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="114"/>
-      <c r="AE1" s="114"/>
-      <c r="AF1" s="115"/>
-      <c r="AG1" s="147">
+      <c r="AD1" s="146"/>
+      <c r="AE1" s="146"/>
+      <c r="AF1" s="147"/>
+      <c r="AG1" s="151">
         <f ca="1">IF(INDIRECT("変更履歴!AG1")&lt;&gt;"",INDIRECT("変更履歴!AG1"),"")</f>
         <v>43336</v>
       </c>
-      <c r="AH1" s="148"/>
-      <c r="AI1" s="149"/>
+      <c r="AH1" s="152"/>
+      <c r="AI1" s="153"/>
       <c r="AJ1" s="6"/>
       <c r="AN1" s="7"/>
       <c r="AO1" s="6"/>
@@ -20450,54 +21200,54 @@
       <c r="AW1" s="6"/>
     </row>
     <row r="2" spans="1:49" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="84" t="s">
+      <c r="A2" s="116" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="85"/>
-      <c r="C2" s="85"/>
-      <c r="D2" s="86"/>
-      <c r="E2" s="87" t="str">
+      <c r="B2" s="117"/>
+      <c r="C2" s="117"/>
+      <c r="D2" s="118"/>
+      <c r="E2" s="119" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E2")&lt;&gt;"",INDIRECT("変更履歴!E2"),"")</f>
         <v/>
       </c>
-      <c r="F2" s="88"/>
-      <c r="G2" s="88"/>
-      <c r="H2" s="88"/>
-      <c r="I2" s="88"/>
-      <c r="J2" s="88"/>
-      <c r="K2" s="88"/>
-      <c r="L2" s="88"/>
-      <c r="M2" s="88"/>
-      <c r="N2" s="89"/>
-      <c r="O2" s="165"/>
-      <c r="P2" s="166"/>
-      <c r="Q2" s="166"/>
-      <c r="R2" s="167"/>
-      <c r="S2" s="156"/>
-      <c r="T2" s="157"/>
-      <c r="U2" s="157"/>
-      <c r="V2" s="157"/>
-      <c r="W2" s="157"/>
-      <c r="X2" s="157"/>
-      <c r="Y2" s="157"/>
-      <c r="Z2" s="158"/>
-      <c r="AA2" s="84" t="s">
+      <c r="F2" s="120"/>
+      <c r="G2" s="120"/>
+      <c r="H2" s="120"/>
+      <c r="I2" s="120"/>
+      <c r="J2" s="120"/>
+      <c r="K2" s="120"/>
+      <c r="L2" s="120"/>
+      <c r="M2" s="120"/>
+      <c r="N2" s="121"/>
+      <c r="O2" s="157"/>
+      <c r="P2" s="158"/>
+      <c r="Q2" s="158"/>
+      <c r="R2" s="159"/>
+      <c r="S2" s="166"/>
+      <c r="T2" s="167"/>
+      <c r="U2" s="167"/>
+      <c r="V2" s="167"/>
+      <c r="W2" s="167"/>
+      <c r="X2" s="167"/>
+      <c r="Y2" s="167"/>
+      <c r="Z2" s="168"/>
+      <c r="AA2" s="116" t="s">
         <v>4</v>
       </c>
-      <c r="AB2" s="86"/>
-      <c r="AC2" s="113" t="str">
+      <c r="AB2" s="118"/>
+      <c r="AC2" s="145" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC2")&lt;&gt;"",INDIRECT("変更履歴!AC2"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD2" s="114"/>
-      <c r="AE2" s="114"/>
-      <c r="AF2" s="115"/>
-      <c r="AG2" s="147">
+      <c r="AD2" s="146"/>
+      <c r="AE2" s="146"/>
+      <c r="AF2" s="147"/>
+      <c r="AG2" s="151">
         <f ca="1">IF(INDIRECT("変更履歴!AG2")&lt;&gt;"",INDIRECT("変更履歴!AG2"),"")</f>
         <v>44848</v>
       </c>
-      <c r="AH2" s="148"/>
-      <c r="AI2" s="149"/>
+      <c r="AH2" s="152"/>
+      <c r="AI2" s="153"/>
       <c r="AJ2" s="6"/>
       <c r="AN2" s="7"/>
       <c r="AO2" s="6"/>
@@ -20511,52 +21261,52 @@
       <c r="AW2" s="6"/>
     </row>
     <row r="3" spans="1:49" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="84" t="s">
+      <c r="A3" s="116" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="85"/>
-      <c r="C3" s="85"/>
-      <c r="D3" s="86"/>
-      <c r="E3" s="87" t="str">
+      <c r="B3" s="117"/>
+      <c r="C3" s="117"/>
+      <c r="D3" s="118"/>
+      <c r="E3" s="119" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E3")&lt;&gt;"",INDIRECT("変更履歴!E3"),"")</f>
         <v/>
       </c>
-      <c r="F3" s="88"/>
-      <c r="G3" s="88"/>
-      <c r="H3" s="88"/>
-      <c r="I3" s="88"/>
-      <c r="J3" s="88"/>
-      <c r="K3" s="88"/>
-      <c r="L3" s="88"/>
-      <c r="M3" s="88"/>
-      <c r="N3" s="89"/>
-      <c r="O3" s="168"/>
-      <c r="P3" s="169"/>
-      <c r="Q3" s="169"/>
-      <c r="R3" s="170"/>
-      <c r="S3" s="159"/>
-      <c r="T3" s="160"/>
-      <c r="U3" s="160"/>
-      <c r="V3" s="160"/>
-      <c r="W3" s="160"/>
-      <c r="X3" s="160"/>
-      <c r="Y3" s="160"/>
-      <c r="Z3" s="161"/>
-      <c r="AA3" s="84"/>
-      <c r="AB3" s="86"/>
-      <c r="AC3" s="113" t="str">
+      <c r="F3" s="120"/>
+      <c r="G3" s="120"/>
+      <c r="H3" s="120"/>
+      <c r="I3" s="120"/>
+      <c r="J3" s="120"/>
+      <c r="K3" s="120"/>
+      <c r="L3" s="120"/>
+      <c r="M3" s="120"/>
+      <c r="N3" s="121"/>
+      <c r="O3" s="160"/>
+      <c r="P3" s="161"/>
+      <c r="Q3" s="161"/>
+      <c r="R3" s="162"/>
+      <c r="S3" s="169"/>
+      <c r="T3" s="170"/>
+      <c r="U3" s="170"/>
+      <c r="V3" s="170"/>
+      <c r="W3" s="170"/>
+      <c r="X3" s="170"/>
+      <c r="Y3" s="170"/>
+      <c r="Z3" s="171"/>
+      <c r="AA3" s="116"/>
+      <c r="AB3" s="118"/>
+      <c r="AC3" s="145" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC3")&lt;&gt;"",INDIRECT("変更履歴!AC3"),"")</f>
         <v/>
       </c>
-      <c r="AD3" s="114"/>
-      <c r="AE3" s="114"/>
-      <c r="AF3" s="115"/>
-      <c r="AG3" s="147" t="str">
+      <c r="AD3" s="146"/>
+      <c r="AE3" s="146"/>
+      <c r="AF3" s="147"/>
+      <c r="AG3" s="151" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AG3")&lt;&gt;"",INDIRECT("変更履歴!AG3"),"")</f>
         <v/>
       </c>
-      <c r="AH3" s="148"/>
-      <c r="AI3" s="149"/>
+      <c r="AH3" s="152"/>
+      <c r="AI3" s="153"/>
       <c r="AJ3" s="9"/>
       <c r="AK3" s="1"/>
       <c r="AL3" s="1"/>
@@ -20728,6 +21478,14 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="AG1:AI1"/>
+    <mergeCell ref="AC1:AF1"/>
+    <mergeCell ref="AC2:AF2"/>
+    <mergeCell ref="AG2:AI2"/>
+    <mergeCell ref="E3:N3"/>
+    <mergeCell ref="AA3:AB3"/>
+    <mergeCell ref="AC3:AF3"/>
+    <mergeCell ref="AG3:AI3"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="E1:N1"/>
     <mergeCell ref="O1:R3"/>
@@ -20737,14 +21495,6 @@
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="E2:N2"/>
     <mergeCell ref="AA2:AB2"/>
-    <mergeCell ref="AG1:AI1"/>
-    <mergeCell ref="AC1:AF1"/>
-    <mergeCell ref="AC2:AF2"/>
-    <mergeCell ref="AG2:AI2"/>
-    <mergeCell ref="E3:N3"/>
-    <mergeCell ref="AA3:AB3"/>
-    <mergeCell ref="AC3:AF3"/>
-    <mergeCell ref="AG3:AI3"/>
   </mergeCells>
   <phoneticPr fontId="10"/>
   <printOptions horizontalCentered="1"/>

--- a/030_設計ドキュメント/Nablarch開発標準設計書一覧.xlsx
+++ b/030_設計ドキュメント/Nablarch開発標準設計書一覧.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26731"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87493DE4-ED9D-4F1C-A3D6-399A1B9AA9EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B883EF5-A1FA-4CB4-9F4D-21A2356D04D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21390" tabRatio="822" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1380" yWindow="3735" windowWidth="28800" windowHeight="15435" tabRatio="822" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="34" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="256">
   <si>
     <t>PJ名</t>
   </si>
@@ -1424,10 +1424,6 @@
     <t>Jakarta Transactions</t>
   </si>
   <si>
-    <t>JBatch / JSR352</t>
-    <phoneticPr fontId="30"/>
-  </si>
-  <si>
     <t>Jakarta Batch</t>
   </si>
   <si>
@@ -1520,6 +1516,54 @@
   </si>
   <si>
     <t>1.2. 本書におけるJakartaEE仕様への読み替えについて</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>jBatch / JSR352</t>
+    <phoneticPr fontId="30"/>
+  </si>
+  <si>
+    <t>1.2版</t>
+    <rPh sb="3" eb="4">
+      <t>バン</t>
+    </rPh>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>追加</t>
+    <rPh sb="0" eb="2">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>「1. 概要」シート</t>
+    <rPh sb="4" eb="6">
+      <t>ガイヨウ</t>
+    </rPh>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>「1.2. 本書におけるJakartaEE仕様への読み替えについて」を追加</t>
+    <rPh sb="6" eb="8">
+      <t>ホンショ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>TIS</t>
     <phoneticPr fontId="10"/>
   </si>
 </sst>
@@ -2417,7 +2461,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="183">
+  <cellXfs count="187">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="41"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="41" applyAlignment="1">
@@ -2579,101 +2623,21 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="44"/>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="20" xfId="44" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="10" xfId="44" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="11" xfId="44" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="12" xfId="44" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="44" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="44" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="44" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="44" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="44" applyFont="1"/>
     <xf numFmtId="31" fontId="7" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="23" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="22" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="177" fontId="2" fillId="0" borderId="10" xfId="45" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
@@ -2792,14 +2756,98 @@
     <xf numFmtId="14" fontId="2" fillId="0" borderId="12" xfId="41" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="41" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="10" xfId="41" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="12" xfId="41" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="23" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="22" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="177" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
@@ -2810,31 +2858,13 @@
     <xf numFmtId="177" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="24" borderId="13" xfId="41" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="10" xfId="41" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="24" borderId="14" xfId="41" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="12" xfId="41" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="24" borderId="15" xfId="41" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="24" borderId="24" xfId="41" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="24" borderId="0" xfId="41" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="24" borderId="25" xfId="41" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="24" borderId="16" xfId="41" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="24" borderId="17" xfId="41" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="24" borderId="18" xfId="41" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="41" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="41" applyBorder="1" applyAlignment="1">
@@ -2864,19 +2894,43 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="41" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="44"/>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="20" xfId="44" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="10" xfId="44" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="11" xfId="44" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="12" xfId="44" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="44" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="44" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="44" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="33" fillId="24" borderId="13" xfId="41" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="44" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="44" applyFont="1"/>
+    <xf numFmtId="0" fontId="33" fillId="24" borderId="14" xfId="41" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="24" borderId="15" xfId="41" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="24" borderId="24" xfId="41" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="24" borderId="0" xfId="41" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="24" borderId="25" xfId="41" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="24" borderId="16" xfId="41" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="24" borderId="17" xfId="41" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="24" borderId="18" xfId="41" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="44" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="52">
     <cellStyle name="20% - アクセント 1" xfId="1" builtinId="30" customBuiltin="1"/>
@@ -13799,12 +13853,12 @@
       <c r="F25" s="22"/>
       <c r="G25" s="22"/>
       <c r="H25" s="22"/>
-      <c r="I25" s="77">
+      <c r="I25" s="88">
         <f ca="1">IF(INDIRECT("変更履歴!D8")="","",MAX(INDIRECT("変更履歴!D8"):INDIRECT("変更履歴!F33")))</f>
-        <v>44848</v>
-      </c>
-      <c r="J25" s="77"/>
-      <c r="K25" s="77"/>
+        <v>45464</v>
+      </c>
+      <c r="J25" s="88"/>
+      <c r="K25" s="88"/>
     </row>
     <row r="26" spans="6:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F26" s="22"/>
@@ -14398,55 +14452,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="125" t="s">
+      <c r="A1" s="105" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="117"/>
-      <c r="C1" s="117"/>
-      <c r="D1" s="118"/>
-      <c r="E1" s="126"/>
-      <c r="F1" s="120"/>
-      <c r="G1" s="120"/>
-      <c r="H1" s="120"/>
-      <c r="I1" s="120"/>
-      <c r="J1" s="120"/>
-      <c r="K1" s="120"/>
-      <c r="L1" s="120"/>
-      <c r="M1" s="120"/>
-      <c r="N1" s="121"/>
-      <c r="O1" s="127" t="s">
+      <c r="B1" s="97"/>
+      <c r="C1" s="97"/>
+      <c r="D1" s="98"/>
+      <c r="E1" s="106"/>
+      <c r="F1" s="100"/>
+      <c r="G1" s="100"/>
+      <c r="H1" s="100"/>
+      <c r="I1" s="100"/>
+      <c r="J1" s="100"/>
+      <c r="K1" s="100"/>
+      <c r="L1" s="100"/>
+      <c r="M1" s="100"/>
+      <c r="N1" s="101"/>
+      <c r="O1" s="107" t="s">
         <v>11</v>
       </c>
-      <c r="P1" s="128"/>
-      <c r="Q1" s="128"/>
-      <c r="R1" s="129"/>
-      <c r="S1" s="136" t="s">
+      <c r="P1" s="108"/>
+      <c r="Q1" s="108"/>
+      <c r="R1" s="109"/>
+      <c r="S1" s="116" t="s">
         <v>44</v>
       </c>
-      <c r="T1" s="137"/>
-      <c r="U1" s="137"/>
-      <c r="V1" s="137"/>
-      <c r="W1" s="137"/>
-      <c r="X1" s="137"/>
-      <c r="Y1" s="137"/>
-      <c r="Z1" s="138"/>
-      <c r="AA1" s="116" t="s">
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
+      <c r="V1" s="117"/>
+      <c r="W1" s="117"/>
+      <c r="X1" s="117"/>
+      <c r="Y1" s="117"/>
+      <c r="Z1" s="118"/>
+      <c r="AA1" s="96" t="s">
         <v>12</v>
       </c>
-      <c r="AB1" s="118"/>
-      <c r="AC1" s="145" t="str">
+      <c r="AB1" s="98"/>
+      <c r="AC1" s="125" t="str">
         <f>IF(AF8="","",AF8)</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="146"/>
-      <c r="AE1" s="146"/>
-      <c r="AF1" s="147"/>
-      <c r="AG1" s="109">
+      <c r="AD1" s="126"/>
+      <c r="AE1" s="126"/>
+      <c r="AF1" s="127"/>
+      <c r="AG1" s="89">
         <f>IF(D8="","",D8)</f>
         <v>43336</v>
       </c>
-      <c r="AH1" s="110"/>
-      <c r="AI1" s="111"/>
+      <c r="AH1" s="90"/>
+      <c r="AI1" s="91"/>
       <c r="AJ1" s="1"/>
       <c r="AK1" s="1"/>
       <c r="AL1" s="1"/>
@@ -14454,51 +14508,51 @@
       <c r="AN1" s="2"/>
     </row>
     <row r="2" spans="1:40" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="116" t="s">
+      <c r="A2" s="96" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="117"/>
-      <c r="C2" s="117"/>
-      <c r="D2" s="118"/>
-      <c r="E2" s="119"/>
-      <c r="F2" s="120"/>
-      <c r="G2" s="120"/>
-      <c r="H2" s="120"/>
-      <c r="I2" s="120"/>
-      <c r="J2" s="120"/>
-      <c r="K2" s="120"/>
-      <c r="L2" s="120"/>
-      <c r="M2" s="120"/>
-      <c r="N2" s="121"/>
-      <c r="O2" s="130"/>
-      <c r="P2" s="131"/>
-      <c r="Q2" s="131"/>
-      <c r="R2" s="132"/>
-      <c r="S2" s="139"/>
-      <c r="T2" s="140"/>
-      <c r="U2" s="140"/>
-      <c r="V2" s="140"/>
-      <c r="W2" s="140"/>
-      <c r="X2" s="140"/>
-      <c r="Y2" s="140"/>
-      <c r="Z2" s="141"/>
-      <c r="AA2" s="116" t="s">
+      <c r="B2" s="97"/>
+      <c r="C2" s="97"/>
+      <c r="D2" s="98"/>
+      <c r="E2" s="99"/>
+      <c r="F2" s="100"/>
+      <c r="G2" s="100"/>
+      <c r="H2" s="100"/>
+      <c r="I2" s="100"/>
+      <c r="J2" s="100"/>
+      <c r="K2" s="100"/>
+      <c r="L2" s="100"/>
+      <c r="M2" s="100"/>
+      <c r="N2" s="101"/>
+      <c r="O2" s="110"/>
+      <c r="P2" s="111"/>
+      <c r="Q2" s="111"/>
+      <c r="R2" s="112"/>
+      <c r="S2" s="119"/>
+      <c r="T2" s="120"/>
+      <c r="U2" s="120"/>
+      <c r="V2" s="120"/>
+      <c r="W2" s="120"/>
+      <c r="X2" s="120"/>
+      <c r="Y2" s="120"/>
+      <c r="Z2" s="121"/>
+      <c r="AA2" s="96" t="s">
         <v>13</v>
       </c>
-      <c r="AB2" s="118"/>
-      <c r="AC2" s="122" t="str">
+      <c r="AB2" s="98"/>
+      <c r="AC2" s="102" t="str">
         <f ca="1">IF(COUNTA(AF9:AF33)&lt;&gt;0,INDIRECT("AF"&amp;(COUNTA(AF9:AF33)+8)),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD2" s="123"/>
-      <c r="AE2" s="123"/>
-      <c r="AF2" s="124"/>
-      <c r="AG2" s="109">
+      <c r="AD2" s="103"/>
+      <c r="AE2" s="103"/>
+      <c r="AF2" s="104"/>
+      <c r="AG2" s="89">
         <f>IF(D9="","",MAX(D9:F33))</f>
-        <v>44848</v>
-      </c>
-      <c r="AH2" s="110"/>
-      <c r="AI2" s="111"/>
+        <v>45464</v>
+      </c>
+      <c r="AH2" s="90"/>
+      <c r="AI2" s="91"/>
       <c r="AJ2" s="1"/>
       <c r="AK2" s="1"/>
       <c r="AL2" s="1"/>
@@ -14506,43 +14560,43 @@
       <c r="AN2" s="1"/>
     </row>
     <row r="3" spans="1:40" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="116" t="s">
+      <c r="A3" s="96" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="117"/>
-      <c r="C3" s="117"/>
-      <c r="D3" s="118"/>
-      <c r="E3" s="119"/>
-      <c r="F3" s="120"/>
-      <c r="G3" s="120"/>
-      <c r="H3" s="120"/>
-      <c r="I3" s="120"/>
-      <c r="J3" s="120"/>
-      <c r="K3" s="120"/>
-      <c r="L3" s="120"/>
-      <c r="M3" s="120"/>
-      <c r="N3" s="121"/>
-      <c r="O3" s="133"/>
-      <c r="P3" s="134"/>
-      <c r="Q3" s="134"/>
-      <c r="R3" s="135"/>
-      <c r="S3" s="142"/>
-      <c r="T3" s="143"/>
-      <c r="U3" s="143"/>
-      <c r="V3" s="143"/>
-      <c r="W3" s="143"/>
-      <c r="X3" s="143"/>
-      <c r="Y3" s="143"/>
-      <c r="Z3" s="144"/>
-      <c r="AA3" s="116"/>
-      <c r="AB3" s="118"/>
-      <c r="AC3" s="145"/>
-      <c r="AD3" s="146"/>
-      <c r="AE3" s="146"/>
-      <c r="AF3" s="147"/>
-      <c r="AG3" s="109"/>
-      <c r="AH3" s="110"/>
-      <c r="AI3" s="111"/>
+      <c r="B3" s="97"/>
+      <c r="C3" s="97"/>
+      <c r="D3" s="98"/>
+      <c r="E3" s="99"/>
+      <c r="F3" s="100"/>
+      <c r="G3" s="100"/>
+      <c r="H3" s="100"/>
+      <c r="I3" s="100"/>
+      <c r="J3" s="100"/>
+      <c r="K3" s="100"/>
+      <c r="L3" s="100"/>
+      <c r="M3" s="100"/>
+      <c r="N3" s="101"/>
+      <c r="O3" s="113"/>
+      <c r="P3" s="114"/>
+      <c r="Q3" s="114"/>
+      <c r="R3" s="115"/>
+      <c r="S3" s="122"/>
+      <c r="T3" s="123"/>
+      <c r="U3" s="123"/>
+      <c r="V3" s="123"/>
+      <c r="W3" s="123"/>
+      <c r="X3" s="123"/>
+      <c r="Y3" s="123"/>
+      <c r="Z3" s="124"/>
+      <c r="AA3" s="96"/>
+      <c r="AB3" s="98"/>
+      <c r="AC3" s="125"/>
+      <c r="AD3" s="126"/>
+      <c r="AE3" s="126"/>
+      <c r="AF3" s="127"/>
+      <c r="AG3" s="89"/>
+      <c r="AH3" s="90"/>
+      <c r="AI3" s="91"/>
       <c r="AJ3" s="1"/>
       <c r="AK3" s="1"/>
       <c r="AL3" s="1"/>
@@ -14579,1048 +14633,1218 @@
       <c r="A7" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="112" t="s">
+      <c r="B7" s="92" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="113"/>
-      <c r="D7" s="112" t="s">
+      <c r="C7" s="93"/>
+      <c r="D7" s="92" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="114"/>
-      <c r="F7" s="113"/>
-      <c r="G7" s="112" t="s">
+      <c r="E7" s="94"/>
+      <c r="F7" s="93"/>
+      <c r="G7" s="92" t="s">
         <v>8</v>
       </c>
-      <c r="H7" s="114"/>
-      <c r="I7" s="113"/>
-      <c r="J7" s="115" t="s">
+      <c r="H7" s="94"/>
+      <c r="I7" s="93"/>
+      <c r="J7" s="95" t="s">
         <v>23</v>
       </c>
-      <c r="K7" s="114"/>
-      <c r="L7" s="114"/>
-      <c r="M7" s="114"/>
-      <c r="N7" s="114"/>
-      <c r="O7" s="114"/>
-      <c r="P7" s="113"/>
-      <c r="Q7" s="112" t="s">
+      <c r="K7" s="94"/>
+      <c r="L7" s="94"/>
+      <c r="M7" s="94"/>
+      <c r="N7" s="94"/>
+      <c r="O7" s="94"/>
+      <c r="P7" s="93"/>
+      <c r="Q7" s="92" t="s">
         <v>9</v>
       </c>
-      <c r="R7" s="114"/>
-      <c r="S7" s="114"/>
-      <c r="T7" s="114"/>
-      <c r="U7" s="114"/>
-      <c r="V7" s="114"/>
-      <c r="W7" s="114"/>
-      <c r="X7" s="114"/>
-      <c r="Y7" s="114"/>
-      <c r="Z7" s="114"/>
-      <c r="AA7" s="114"/>
-      <c r="AB7" s="114"/>
-      <c r="AC7" s="114"/>
-      <c r="AD7" s="114"/>
-      <c r="AE7" s="113"/>
-      <c r="AF7" s="112" t="s">
+      <c r="R7" s="94"/>
+      <c r="S7" s="94"/>
+      <c r="T7" s="94"/>
+      <c r="U7" s="94"/>
+      <c r="V7" s="94"/>
+      <c r="W7" s="94"/>
+      <c r="X7" s="94"/>
+      <c r="Y7" s="94"/>
+      <c r="Z7" s="94"/>
+      <c r="AA7" s="94"/>
+      <c r="AB7" s="94"/>
+      <c r="AC7" s="94"/>
+      <c r="AD7" s="94"/>
+      <c r="AE7" s="93"/>
+      <c r="AF7" s="92" t="s">
         <v>10</v>
       </c>
-      <c r="AG7" s="114"/>
-      <c r="AH7" s="114"/>
-      <c r="AI7" s="113"/>
+      <c r="AG7" s="94"/>
+      <c r="AH7" s="94"/>
+      <c r="AI7" s="93"/>
     </row>
     <row r="8" spans="1:40" s="12" customFormat="1" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
       <c r="A8" s="16">
         <v>1</v>
       </c>
-      <c r="B8" s="95" t="s">
+      <c r="B8" s="141" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="96"/>
-      <c r="D8" s="97">
+      <c r="C8" s="142"/>
+      <c r="D8" s="143">
         <v>43336</v>
       </c>
-      <c r="E8" s="98"/>
-      <c r="F8" s="99"/>
-      <c r="G8" s="100" t="s">
+      <c r="E8" s="144"/>
+      <c r="F8" s="145"/>
+      <c r="G8" s="146" t="s">
         <v>18</v>
       </c>
-      <c r="H8" s="101"/>
-      <c r="I8" s="102"/>
-      <c r="J8" s="103" t="s">
+      <c r="H8" s="147"/>
+      <c r="I8" s="148"/>
+      <c r="J8" s="149" t="s">
         <v>19</v>
       </c>
-      <c r="K8" s="104"/>
-      <c r="L8" s="104"/>
-      <c r="M8" s="104"/>
-      <c r="N8" s="104"/>
-      <c r="O8" s="104"/>
-      <c r="P8" s="105"/>
-      <c r="Q8" s="106" t="s">
+      <c r="K8" s="150"/>
+      <c r="L8" s="150"/>
+      <c r="M8" s="150"/>
+      <c r="N8" s="150"/>
+      <c r="O8" s="150"/>
+      <c r="P8" s="151"/>
+      <c r="Q8" s="152" t="s">
         <v>20</v>
       </c>
-      <c r="R8" s="107"/>
-      <c r="S8" s="107"/>
-      <c r="T8" s="107"/>
-      <c r="U8" s="107"/>
-      <c r="V8" s="107"/>
-      <c r="W8" s="107"/>
-      <c r="X8" s="107"/>
-      <c r="Y8" s="107"/>
-      <c r="Z8" s="107"/>
-      <c r="AA8" s="107"/>
-      <c r="AB8" s="107"/>
-      <c r="AC8" s="107"/>
-      <c r="AD8" s="107"/>
-      <c r="AE8" s="108"/>
-      <c r="AF8" s="103" t="s">
+      <c r="R8" s="153"/>
+      <c r="S8" s="153"/>
+      <c r="T8" s="153"/>
+      <c r="U8" s="153"/>
+      <c r="V8" s="153"/>
+      <c r="W8" s="153"/>
+      <c r="X8" s="153"/>
+      <c r="Y8" s="153"/>
+      <c r="Z8" s="153"/>
+      <c r="AA8" s="153"/>
+      <c r="AB8" s="153"/>
+      <c r="AC8" s="153"/>
+      <c r="AD8" s="153"/>
+      <c r="AE8" s="154"/>
+      <c r="AF8" s="149" t="s">
         <v>21</v>
       </c>
-      <c r="AG8" s="104"/>
-      <c r="AH8" s="104"/>
-      <c r="AI8" s="105"/>
+      <c r="AG8" s="150"/>
+      <c r="AH8" s="150"/>
+      <c r="AI8" s="151"/>
     </row>
     <row r="9" spans="1:40" s="12" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="13">
         <v>2</v>
       </c>
-      <c r="B9" s="91" t="s">
+      <c r="B9" s="128" t="s">
         <v>199</v>
       </c>
-      <c r="C9" s="79"/>
-      <c r="D9" s="80">
+      <c r="C9" s="129"/>
+      <c r="D9" s="130">
         <v>44848</v>
       </c>
-      <c r="E9" s="81"/>
-      <c r="F9" s="82"/>
-      <c r="G9" s="92" t="s">
+      <c r="E9" s="131"/>
+      <c r="F9" s="132"/>
+      <c r="G9" s="133" t="s">
         <v>4</v>
       </c>
-      <c r="H9" s="83"/>
-      <c r="I9" s="79"/>
-      <c r="J9" s="93" t="s">
+      <c r="H9" s="134"/>
+      <c r="I9" s="129"/>
+      <c r="J9" s="135" t="s">
         <v>43</v>
       </c>
-      <c r="K9" s="85"/>
-      <c r="L9" s="85"/>
-      <c r="M9" s="85"/>
-      <c r="N9" s="85"/>
-      <c r="O9" s="85"/>
-      <c r="P9" s="86"/>
-      <c r="Q9" s="94" t="s">
+      <c r="K9" s="136"/>
+      <c r="L9" s="136"/>
+      <c r="M9" s="136"/>
+      <c r="N9" s="136"/>
+      <c r="O9" s="136"/>
+      <c r="P9" s="137"/>
+      <c r="Q9" s="138" t="s">
         <v>206</v>
       </c>
-      <c r="R9" s="88"/>
-      <c r="S9" s="88"/>
-      <c r="T9" s="88"/>
-      <c r="U9" s="88"/>
-      <c r="V9" s="88"/>
-      <c r="W9" s="88"/>
-      <c r="X9" s="88"/>
-      <c r="Y9" s="88"/>
-      <c r="Z9" s="88"/>
-      <c r="AA9" s="88"/>
-      <c r="AB9" s="88"/>
-      <c r="AC9" s="88"/>
-      <c r="AD9" s="88"/>
-      <c r="AE9" s="89"/>
-      <c r="AF9" s="93" t="s">
+      <c r="R9" s="139"/>
+      <c r="S9" s="139"/>
+      <c r="T9" s="139"/>
+      <c r="U9" s="139"/>
+      <c r="V9" s="139"/>
+      <c r="W9" s="139"/>
+      <c r="X9" s="139"/>
+      <c r="Y9" s="139"/>
+      <c r="Z9" s="139"/>
+      <c r="AA9" s="139"/>
+      <c r="AB9" s="139"/>
+      <c r="AC9" s="139"/>
+      <c r="AD9" s="139"/>
+      <c r="AE9" s="140"/>
+      <c r="AF9" s="135" t="s">
         <v>21</v>
       </c>
-      <c r="AG9" s="85"/>
-      <c r="AH9" s="85"/>
-      <c r="AI9" s="86"/>
+      <c r="AG9" s="136"/>
+      <c r="AH9" s="136"/>
+      <c r="AI9" s="137"/>
     </row>
     <row r="10" spans="1:40" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="13"/>
-      <c r="B10" s="78"/>
-      <c r="C10" s="79"/>
-      <c r="D10" s="80"/>
-      <c r="E10" s="81"/>
-      <c r="F10" s="82"/>
-      <c r="G10" s="78"/>
-      <c r="H10" s="83"/>
-      <c r="I10" s="79"/>
-      <c r="J10" s="84"/>
-      <c r="K10" s="85"/>
-      <c r="L10" s="85"/>
-      <c r="M10" s="85"/>
-      <c r="N10" s="85"/>
-      <c r="O10" s="85"/>
-      <c r="P10" s="86"/>
-      <c r="Q10" s="87"/>
-      <c r="R10" s="88"/>
-      <c r="S10" s="88"/>
-      <c r="T10" s="88"/>
-      <c r="U10" s="88"/>
-      <c r="V10" s="88"/>
-      <c r="W10" s="88"/>
-      <c r="X10" s="88"/>
-      <c r="Y10" s="88"/>
-      <c r="Z10" s="88"/>
-      <c r="AA10" s="88"/>
-      <c r="AB10" s="88"/>
-      <c r="AC10" s="88"/>
-      <c r="AD10" s="88"/>
-      <c r="AE10" s="89"/>
-      <c r="AF10" s="84"/>
-      <c r="AG10" s="85"/>
-      <c r="AH10" s="85"/>
-      <c r="AI10" s="86"/>
+      <c r="A10" s="13">
+        <v>3</v>
+      </c>
+      <c r="B10" s="184" t="s">
+        <v>251</v>
+      </c>
+      <c r="C10" s="129"/>
+      <c r="D10" s="130">
+        <v>45464</v>
+      </c>
+      <c r="E10" s="131"/>
+      <c r="F10" s="132"/>
+      <c r="G10" s="184" t="s">
+        <v>252</v>
+      </c>
+      <c r="H10" s="134"/>
+      <c r="I10" s="129"/>
+      <c r="J10" s="185" t="s">
+        <v>253</v>
+      </c>
+      <c r="K10" s="136"/>
+      <c r="L10" s="136"/>
+      <c r="M10" s="136"/>
+      <c r="N10" s="136"/>
+      <c r="O10" s="136"/>
+      <c r="P10" s="137"/>
+      <c r="Q10" s="186" t="s">
+        <v>254</v>
+      </c>
+      <c r="R10" s="139"/>
+      <c r="S10" s="139"/>
+      <c r="T10" s="139"/>
+      <c r="U10" s="139"/>
+      <c r="V10" s="139"/>
+      <c r="W10" s="139"/>
+      <c r="X10" s="139"/>
+      <c r="Y10" s="139"/>
+      <c r="Z10" s="139"/>
+      <c r="AA10" s="139"/>
+      <c r="AB10" s="139"/>
+      <c r="AC10" s="139"/>
+      <c r="AD10" s="139"/>
+      <c r="AE10" s="140"/>
+      <c r="AF10" s="185" t="s">
+        <v>255</v>
+      </c>
+      <c r="AG10" s="136"/>
+      <c r="AH10" s="136"/>
+      <c r="AI10" s="137"/>
     </row>
     <row r="11" spans="1:40" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="13"/>
-      <c r="B11" s="78"/>
-      <c r="C11" s="79"/>
-      <c r="D11" s="80"/>
-      <c r="E11" s="81"/>
-      <c r="F11" s="82"/>
-      <c r="G11" s="78"/>
-      <c r="H11" s="83"/>
-      <c r="I11" s="79"/>
-      <c r="J11" s="84"/>
-      <c r="K11" s="85"/>
-      <c r="L11" s="85"/>
-      <c r="M11" s="85"/>
-      <c r="N11" s="85"/>
-      <c r="O11" s="85"/>
-      <c r="P11" s="86"/>
-      <c r="Q11" s="87"/>
-      <c r="R11" s="88"/>
-      <c r="S11" s="88"/>
-      <c r="T11" s="88"/>
-      <c r="U11" s="88"/>
-      <c r="V11" s="88"/>
-      <c r="W11" s="88"/>
-      <c r="X11" s="88"/>
-      <c r="Y11" s="88"/>
-      <c r="Z11" s="88"/>
-      <c r="AA11" s="88"/>
-      <c r="AB11" s="88"/>
-      <c r="AC11" s="88"/>
-      <c r="AD11" s="88"/>
-      <c r="AE11" s="89"/>
-      <c r="AF11" s="84"/>
-      <c r="AG11" s="85"/>
-      <c r="AH11" s="85"/>
-      <c r="AI11" s="86"/>
+      <c r="B11" s="155"/>
+      <c r="C11" s="129"/>
+      <c r="D11" s="130"/>
+      <c r="E11" s="131"/>
+      <c r="F11" s="132"/>
+      <c r="G11" s="155"/>
+      <c r="H11" s="134"/>
+      <c r="I11" s="129"/>
+      <c r="J11" s="156"/>
+      <c r="K11" s="136"/>
+      <c r="L11" s="136"/>
+      <c r="M11" s="136"/>
+      <c r="N11" s="136"/>
+      <c r="O11" s="136"/>
+      <c r="P11" s="137"/>
+      <c r="Q11" s="157"/>
+      <c r="R11" s="139"/>
+      <c r="S11" s="139"/>
+      <c r="T11" s="139"/>
+      <c r="U11" s="139"/>
+      <c r="V11" s="139"/>
+      <c r="W11" s="139"/>
+      <c r="X11" s="139"/>
+      <c r="Y11" s="139"/>
+      <c r="Z11" s="139"/>
+      <c r="AA11" s="139"/>
+      <c r="AB11" s="139"/>
+      <c r="AC11" s="139"/>
+      <c r="AD11" s="139"/>
+      <c r="AE11" s="140"/>
+      <c r="AF11" s="156"/>
+      <c r="AG11" s="136"/>
+      <c r="AH11" s="136"/>
+      <c r="AI11" s="137"/>
     </row>
     <row r="12" spans="1:40" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="13"/>
-      <c r="B12" s="78"/>
-      <c r="C12" s="79"/>
-      <c r="D12" s="80"/>
-      <c r="E12" s="81"/>
-      <c r="F12" s="82"/>
-      <c r="G12" s="78"/>
-      <c r="H12" s="83"/>
-      <c r="I12" s="79"/>
-      <c r="J12" s="84"/>
-      <c r="K12" s="85"/>
-      <c r="L12" s="85"/>
-      <c r="M12" s="85"/>
-      <c r="N12" s="85"/>
-      <c r="O12" s="85"/>
-      <c r="P12" s="86"/>
-      <c r="Q12" s="87"/>
-      <c r="R12" s="88"/>
-      <c r="S12" s="88"/>
-      <c r="T12" s="88"/>
-      <c r="U12" s="88"/>
-      <c r="V12" s="88"/>
-      <c r="W12" s="88"/>
-      <c r="X12" s="88"/>
-      <c r="Y12" s="88"/>
-      <c r="Z12" s="88"/>
-      <c r="AA12" s="88"/>
-      <c r="AB12" s="88"/>
-      <c r="AC12" s="88"/>
-      <c r="AD12" s="88"/>
-      <c r="AE12" s="89"/>
-      <c r="AF12" s="84"/>
-      <c r="AG12" s="85"/>
-      <c r="AH12" s="85"/>
-      <c r="AI12" s="86"/>
+      <c r="B12" s="155"/>
+      <c r="C12" s="129"/>
+      <c r="D12" s="130"/>
+      <c r="E12" s="131"/>
+      <c r="F12" s="132"/>
+      <c r="G12" s="155"/>
+      <c r="H12" s="134"/>
+      <c r="I12" s="129"/>
+      <c r="J12" s="156"/>
+      <c r="K12" s="136"/>
+      <c r="L12" s="136"/>
+      <c r="M12" s="136"/>
+      <c r="N12" s="136"/>
+      <c r="O12" s="136"/>
+      <c r="P12" s="137"/>
+      <c r="Q12" s="157"/>
+      <c r="R12" s="139"/>
+      <c r="S12" s="139"/>
+      <c r="T12" s="139"/>
+      <c r="U12" s="139"/>
+      <c r="V12" s="139"/>
+      <c r="W12" s="139"/>
+      <c r="X12" s="139"/>
+      <c r="Y12" s="139"/>
+      <c r="Z12" s="139"/>
+      <c r="AA12" s="139"/>
+      <c r="AB12" s="139"/>
+      <c r="AC12" s="139"/>
+      <c r="AD12" s="139"/>
+      <c r="AE12" s="140"/>
+      <c r="AF12" s="156"/>
+      <c r="AG12" s="136"/>
+      <c r="AH12" s="136"/>
+      <c r="AI12" s="137"/>
     </row>
     <row r="13" spans="1:40" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="13"/>
-      <c r="B13" s="78"/>
-      <c r="C13" s="79"/>
-      <c r="D13" s="80"/>
-      <c r="E13" s="81"/>
-      <c r="F13" s="82"/>
-      <c r="G13" s="78"/>
-      <c r="H13" s="83"/>
-      <c r="I13" s="79"/>
-      <c r="J13" s="84"/>
-      <c r="K13" s="85"/>
-      <c r="L13" s="85"/>
-      <c r="M13" s="85"/>
-      <c r="N13" s="85"/>
-      <c r="O13" s="85"/>
-      <c r="P13" s="86"/>
-      <c r="Q13" s="87"/>
-      <c r="R13" s="88"/>
-      <c r="S13" s="88"/>
-      <c r="T13" s="88"/>
-      <c r="U13" s="88"/>
-      <c r="V13" s="88"/>
-      <c r="W13" s="88"/>
-      <c r="X13" s="88"/>
-      <c r="Y13" s="88"/>
-      <c r="Z13" s="88"/>
-      <c r="AA13" s="88"/>
-      <c r="AB13" s="88"/>
-      <c r="AC13" s="88"/>
-      <c r="AD13" s="88"/>
-      <c r="AE13" s="89"/>
-      <c r="AF13" s="84"/>
-      <c r="AG13" s="85"/>
-      <c r="AH13" s="85"/>
-      <c r="AI13" s="86"/>
+      <c r="B13" s="155"/>
+      <c r="C13" s="129"/>
+      <c r="D13" s="130"/>
+      <c r="E13" s="131"/>
+      <c r="F13" s="132"/>
+      <c r="G13" s="155"/>
+      <c r="H13" s="134"/>
+      <c r="I13" s="129"/>
+      <c r="J13" s="156"/>
+      <c r="K13" s="136"/>
+      <c r="L13" s="136"/>
+      <c r="M13" s="136"/>
+      <c r="N13" s="136"/>
+      <c r="O13" s="136"/>
+      <c r="P13" s="137"/>
+      <c r="Q13" s="157"/>
+      <c r="R13" s="139"/>
+      <c r="S13" s="139"/>
+      <c r="T13" s="139"/>
+      <c r="U13" s="139"/>
+      <c r="V13" s="139"/>
+      <c r="W13" s="139"/>
+      <c r="X13" s="139"/>
+      <c r="Y13" s="139"/>
+      <c r="Z13" s="139"/>
+      <c r="AA13" s="139"/>
+      <c r="AB13" s="139"/>
+      <c r="AC13" s="139"/>
+      <c r="AD13" s="139"/>
+      <c r="AE13" s="140"/>
+      <c r="AF13" s="156"/>
+      <c r="AG13" s="136"/>
+      <c r="AH13" s="136"/>
+      <c r="AI13" s="137"/>
     </row>
     <row r="14" spans="1:40" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="13"/>
-      <c r="B14" s="78"/>
-      <c r="C14" s="79"/>
-      <c r="D14" s="80"/>
-      <c r="E14" s="81"/>
-      <c r="F14" s="82"/>
-      <c r="G14" s="78"/>
-      <c r="H14" s="83"/>
-      <c r="I14" s="79"/>
-      <c r="J14" s="84"/>
-      <c r="K14" s="85"/>
-      <c r="L14" s="85"/>
-      <c r="M14" s="85"/>
-      <c r="N14" s="85"/>
-      <c r="O14" s="85"/>
-      <c r="P14" s="86"/>
-      <c r="Q14" s="87"/>
-      <c r="R14" s="88"/>
-      <c r="S14" s="88"/>
-      <c r="T14" s="88"/>
-      <c r="U14" s="88"/>
-      <c r="V14" s="88"/>
-      <c r="W14" s="88"/>
-      <c r="X14" s="88"/>
-      <c r="Y14" s="88"/>
-      <c r="Z14" s="88"/>
-      <c r="AA14" s="88"/>
-      <c r="AB14" s="88"/>
-      <c r="AC14" s="88"/>
-      <c r="AD14" s="88"/>
-      <c r="AE14" s="89"/>
-      <c r="AF14" s="84"/>
-      <c r="AG14" s="85"/>
-      <c r="AH14" s="85"/>
-      <c r="AI14" s="86"/>
+      <c r="B14" s="155"/>
+      <c r="C14" s="129"/>
+      <c r="D14" s="130"/>
+      <c r="E14" s="131"/>
+      <c r="F14" s="132"/>
+      <c r="G14" s="155"/>
+      <c r="H14" s="134"/>
+      <c r="I14" s="129"/>
+      <c r="J14" s="156"/>
+      <c r="K14" s="136"/>
+      <c r="L14" s="136"/>
+      <c r="M14" s="136"/>
+      <c r="N14" s="136"/>
+      <c r="O14" s="136"/>
+      <c r="P14" s="137"/>
+      <c r="Q14" s="157"/>
+      <c r="R14" s="139"/>
+      <c r="S14" s="139"/>
+      <c r="T14" s="139"/>
+      <c r="U14" s="139"/>
+      <c r="V14" s="139"/>
+      <c r="W14" s="139"/>
+      <c r="X14" s="139"/>
+      <c r="Y14" s="139"/>
+      <c r="Z14" s="139"/>
+      <c r="AA14" s="139"/>
+      <c r="AB14" s="139"/>
+      <c r="AC14" s="139"/>
+      <c r="AD14" s="139"/>
+      <c r="AE14" s="140"/>
+      <c r="AF14" s="156"/>
+      <c r="AG14" s="136"/>
+      <c r="AH14" s="136"/>
+      <c r="AI14" s="137"/>
     </row>
     <row r="15" spans="1:40" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="13"/>
-      <c r="B15" s="78"/>
-      <c r="C15" s="79"/>
-      <c r="D15" s="80"/>
-      <c r="E15" s="81"/>
-      <c r="F15" s="82"/>
-      <c r="G15" s="78"/>
-      <c r="H15" s="83"/>
-      <c r="I15" s="79"/>
-      <c r="J15" s="84"/>
-      <c r="K15" s="85"/>
-      <c r="L15" s="85"/>
-      <c r="M15" s="85"/>
-      <c r="N15" s="85"/>
-      <c r="O15" s="85"/>
-      <c r="P15" s="86"/>
-      <c r="Q15" s="87"/>
-      <c r="R15" s="88"/>
-      <c r="S15" s="88"/>
-      <c r="T15" s="88"/>
-      <c r="U15" s="88"/>
-      <c r="V15" s="88"/>
-      <c r="W15" s="88"/>
-      <c r="X15" s="88"/>
-      <c r="Y15" s="88"/>
-      <c r="Z15" s="88"/>
-      <c r="AA15" s="88"/>
-      <c r="AB15" s="88"/>
-      <c r="AC15" s="88"/>
-      <c r="AD15" s="88"/>
-      <c r="AE15" s="89"/>
-      <c r="AF15" s="84"/>
-      <c r="AG15" s="85"/>
-      <c r="AH15" s="85"/>
-      <c r="AI15" s="86"/>
+      <c r="B15" s="155"/>
+      <c r="C15" s="129"/>
+      <c r="D15" s="130"/>
+      <c r="E15" s="131"/>
+      <c r="F15" s="132"/>
+      <c r="G15" s="155"/>
+      <c r="H15" s="134"/>
+      <c r="I15" s="129"/>
+      <c r="J15" s="156"/>
+      <c r="K15" s="136"/>
+      <c r="L15" s="136"/>
+      <c r="M15" s="136"/>
+      <c r="N15" s="136"/>
+      <c r="O15" s="136"/>
+      <c r="P15" s="137"/>
+      <c r="Q15" s="157"/>
+      <c r="R15" s="139"/>
+      <c r="S15" s="139"/>
+      <c r="T15" s="139"/>
+      <c r="U15" s="139"/>
+      <c r="V15" s="139"/>
+      <c r="W15" s="139"/>
+      <c r="X15" s="139"/>
+      <c r="Y15" s="139"/>
+      <c r="Z15" s="139"/>
+      <c r="AA15" s="139"/>
+      <c r="AB15" s="139"/>
+      <c r="AC15" s="139"/>
+      <c r="AD15" s="139"/>
+      <c r="AE15" s="140"/>
+      <c r="AF15" s="156"/>
+      <c r="AG15" s="136"/>
+      <c r="AH15" s="136"/>
+      <c r="AI15" s="137"/>
     </row>
     <row r="16" spans="1:40" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="13"/>
-      <c r="B16" s="78"/>
-      <c r="C16" s="79"/>
-      <c r="D16" s="80"/>
-      <c r="E16" s="81"/>
-      <c r="F16" s="82"/>
-      <c r="G16" s="78"/>
-      <c r="H16" s="83"/>
-      <c r="I16" s="79"/>
-      <c r="J16" s="84"/>
-      <c r="K16" s="85"/>
-      <c r="L16" s="85"/>
-      <c r="M16" s="85"/>
-      <c r="N16" s="85"/>
-      <c r="O16" s="85"/>
-      <c r="P16" s="86"/>
-      <c r="Q16" s="87"/>
-      <c r="R16" s="88"/>
-      <c r="S16" s="88"/>
-      <c r="T16" s="88"/>
-      <c r="U16" s="88"/>
-      <c r="V16" s="88"/>
-      <c r="W16" s="88"/>
-      <c r="X16" s="88"/>
-      <c r="Y16" s="88"/>
-      <c r="Z16" s="88"/>
-      <c r="AA16" s="88"/>
-      <c r="AB16" s="88"/>
-      <c r="AC16" s="88"/>
-      <c r="AD16" s="88"/>
-      <c r="AE16" s="89"/>
-      <c r="AF16" s="84"/>
-      <c r="AG16" s="85"/>
-      <c r="AH16" s="85"/>
-      <c r="AI16" s="86"/>
+      <c r="B16" s="155"/>
+      <c r="C16" s="129"/>
+      <c r="D16" s="130"/>
+      <c r="E16" s="131"/>
+      <c r="F16" s="132"/>
+      <c r="G16" s="155"/>
+      <c r="H16" s="134"/>
+      <c r="I16" s="129"/>
+      <c r="J16" s="156"/>
+      <c r="K16" s="136"/>
+      <c r="L16" s="136"/>
+      <c r="M16" s="136"/>
+      <c r="N16" s="136"/>
+      <c r="O16" s="136"/>
+      <c r="P16" s="137"/>
+      <c r="Q16" s="157"/>
+      <c r="R16" s="139"/>
+      <c r="S16" s="139"/>
+      <c r="T16" s="139"/>
+      <c r="U16" s="139"/>
+      <c r="V16" s="139"/>
+      <c r="W16" s="139"/>
+      <c r="X16" s="139"/>
+      <c r="Y16" s="139"/>
+      <c r="Z16" s="139"/>
+      <c r="AA16" s="139"/>
+      <c r="AB16" s="139"/>
+      <c r="AC16" s="139"/>
+      <c r="AD16" s="139"/>
+      <c r="AE16" s="140"/>
+      <c r="AF16" s="156"/>
+      <c r="AG16" s="136"/>
+      <c r="AH16" s="136"/>
+      <c r="AI16" s="137"/>
     </row>
     <row r="17" spans="1:35" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="13"/>
-      <c r="B17" s="78"/>
-      <c r="C17" s="79"/>
-      <c r="D17" s="80"/>
-      <c r="E17" s="81"/>
-      <c r="F17" s="82"/>
-      <c r="G17" s="78"/>
-      <c r="H17" s="83"/>
-      <c r="I17" s="79"/>
-      <c r="J17" s="84"/>
-      <c r="K17" s="85"/>
-      <c r="L17" s="85"/>
-      <c r="M17" s="85"/>
-      <c r="N17" s="85"/>
-      <c r="O17" s="85"/>
-      <c r="P17" s="86"/>
-      <c r="Q17" s="87"/>
-      <c r="R17" s="88"/>
-      <c r="S17" s="88"/>
-      <c r="T17" s="88"/>
-      <c r="U17" s="88"/>
-      <c r="V17" s="88"/>
-      <c r="W17" s="88"/>
-      <c r="X17" s="88"/>
-      <c r="Y17" s="88"/>
-      <c r="Z17" s="88"/>
-      <c r="AA17" s="88"/>
-      <c r="AB17" s="88"/>
-      <c r="AC17" s="88"/>
-      <c r="AD17" s="88"/>
-      <c r="AE17" s="89"/>
-      <c r="AF17" s="84"/>
-      <c r="AG17" s="85"/>
-      <c r="AH17" s="85"/>
-      <c r="AI17" s="86"/>
+      <c r="B17" s="155"/>
+      <c r="C17" s="129"/>
+      <c r="D17" s="130"/>
+      <c r="E17" s="131"/>
+      <c r="F17" s="132"/>
+      <c r="G17" s="155"/>
+      <c r="H17" s="134"/>
+      <c r="I17" s="129"/>
+      <c r="J17" s="156"/>
+      <c r="K17" s="136"/>
+      <c r="L17" s="136"/>
+      <c r="M17" s="136"/>
+      <c r="N17" s="136"/>
+      <c r="O17" s="136"/>
+      <c r="P17" s="137"/>
+      <c r="Q17" s="157"/>
+      <c r="R17" s="139"/>
+      <c r="S17" s="139"/>
+      <c r="T17" s="139"/>
+      <c r="U17" s="139"/>
+      <c r="V17" s="139"/>
+      <c r="W17" s="139"/>
+      <c r="X17" s="139"/>
+      <c r="Y17" s="139"/>
+      <c r="Z17" s="139"/>
+      <c r="AA17" s="139"/>
+      <c r="AB17" s="139"/>
+      <c r="AC17" s="139"/>
+      <c r="AD17" s="139"/>
+      <c r="AE17" s="140"/>
+      <c r="AF17" s="156"/>
+      <c r="AG17" s="136"/>
+      <c r="AH17" s="136"/>
+      <c r="AI17" s="137"/>
     </row>
     <row r="18" spans="1:35" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="13"/>
-      <c r="B18" s="78"/>
-      <c r="C18" s="79"/>
-      <c r="D18" s="80"/>
-      <c r="E18" s="81"/>
-      <c r="F18" s="82"/>
-      <c r="G18" s="78"/>
-      <c r="H18" s="83"/>
-      <c r="I18" s="79"/>
-      <c r="J18" s="84"/>
-      <c r="K18" s="85"/>
-      <c r="L18" s="85"/>
-      <c r="M18" s="85"/>
-      <c r="N18" s="85"/>
-      <c r="O18" s="85"/>
-      <c r="P18" s="86"/>
-      <c r="Q18" s="87"/>
-      <c r="R18" s="88"/>
-      <c r="S18" s="88"/>
-      <c r="T18" s="88"/>
-      <c r="U18" s="88"/>
-      <c r="V18" s="88"/>
-      <c r="W18" s="88"/>
-      <c r="X18" s="88"/>
-      <c r="Y18" s="88"/>
-      <c r="Z18" s="88"/>
-      <c r="AA18" s="88"/>
-      <c r="AB18" s="88"/>
-      <c r="AC18" s="88"/>
-      <c r="AD18" s="88"/>
-      <c r="AE18" s="89"/>
-      <c r="AF18" s="84"/>
-      <c r="AG18" s="85"/>
-      <c r="AH18" s="85"/>
-      <c r="AI18" s="86"/>
+      <c r="B18" s="155"/>
+      <c r="C18" s="129"/>
+      <c r="D18" s="130"/>
+      <c r="E18" s="131"/>
+      <c r="F18" s="132"/>
+      <c r="G18" s="155"/>
+      <c r="H18" s="134"/>
+      <c r="I18" s="129"/>
+      <c r="J18" s="156"/>
+      <c r="K18" s="136"/>
+      <c r="L18" s="136"/>
+      <c r="M18" s="136"/>
+      <c r="N18" s="136"/>
+      <c r="O18" s="136"/>
+      <c r="P18" s="137"/>
+      <c r="Q18" s="157"/>
+      <c r="R18" s="139"/>
+      <c r="S18" s="139"/>
+      <c r="T18" s="139"/>
+      <c r="U18" s="139"/>
+      <c r="V18" s="139"/>
+      <c r="W18" s="139"/>
+      <c r="X18" s="139"/>
+      <c r="Y18" s="139"/>
+      <c r="Z18" s="139"/>
+      <c r="AA18" s="139"/>
+      <c r="AB18" s="139"/>
+      <c r="AC18" s="139"/>
+      <c r="AD18" s="139"/>
+      <c r="AE18" s="140"/>
+      <c r="AF18" s="156"/>
+      <c r="AG18" s="136"/>
+      <c r="AH18" s="136"/>
+      <c r="AI18" s="137"/>
     </row>
     <row r="19" spans="1:35" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="13"/>
-      <c r="B19" s="78"/>
-      <c r="C19" s="79"/>
-      <c r="D19" s="80"/>
-      <c r="E19" s="81"/>
-      <c r="F19" s="82"/>
-      <c r="G19" s="78"/>
-      <c r="H19" s="83"/>
-      <c r="I19" s="79"/>
-      <c r="J19" s="84"/>
-      <c r="K19" s="85"/>
-      <c r="L19" s="85"/>
-      <c r="M19" s="85"/>
-      <c r="N19" s="85"/>
-      <c r="O19" s="85"/>
-      <c r="P19" s="86"/>
-      <c r="Q19" s="87"/>
-      <c r="R19" s="88"/>
-      <c r="S19" s="88"/>
-      <c r="T19" s="88"/>
-      <c r="U19" s="88"/>
-      <c r="V19" s="88"/>
-      <c r="W19" s="88"/>
-      <c r="X19" s="88"/>
-      <c r="Y19" s="88"/>
-      <c r="Z19" s="88"/>
-      <c r="AA19" s="88"/>
-      <c r="AB19" s="88"/>
-      <c r="AC19" s="88"/>
-      <c r="AD19" s="88"/>
-      <c r="AE19" s="89"/>
-      <c r="AF19" s="84"/>
-      <c r="AG19" s="85"/>
-      <c r="AH19" s="85"/>
-      <c r="AI19" s="86"/>
+      <c r="B19" s="155"/>
+      <c r="C19" s="129"/>
+      <c r="D19" s="130"/>
+      <c r="E19" s="131"/>
+      <c r="F19" s="132"/>
+      <c r="G19" s="155"/>
+      <c r="H19" s="134"/>
+      <c r="I19" s="129"/>
+      <c r="J19" s="156"/>
+      <c r="K19" s="136"/>
+      <c r="L19" s="136"/>
+      <c r="M19" s="136"/>
+      <c r="N19" s="136"/>
+      <c r="O19" s="136"/>
+      <c r="P19" s="137"/>
+      <c r="Q19" s="157"/>
+      <c r="R19" s="139"/>
+      <c r="S19" s="139"/>
+      <c r="T19" s="139"/>
+      <c r="U19" s="139"/>
+      <c r="V19" s="139"/>
+      <c r="W19" s="139"/>
+      <c r="X19" s="139"/>
+      <c r="Y19" s="139"/>
+      <c r="Z19" s="139"/>
+      <c r="AA19" s="139"/>
+      <c r="AB19" s="139"/>
+      <c r="AC19" s="139"/>
+      <c r="AD19" s="139"/>
+      <c r="AE19" s="140"/>
+      <c r="AF19" s="156"/>
+      <c r="AG19" s="136"/>
+      <c r="AH19" s="136"/>
+      <c r="AI19" s="137"/>
     </row>
     <row r="20" spans="1:35" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="13"/>
-      <c r="B20" s="78"/>
-      <c r="C20" s="79"/>
-      <c r="D20" s="80"/>
-      <c r="E20" s="81"/>
-      <c r="F20" s="82"/>
-      <c r="G20" s="78"/>
-      <c r="H20" s="83"/>
-      <c r="I20" s="79"/>
-      <c r="J20" s="84"/>
-      <c r="K20" s="85"/>
-      <c r="L20" s="85"/>
-      <c r="M20" s="85"/>
-      <c r="N20" s="85"/>
-      <c r="O20" s="85"/>
-      <c r="P20" s="86"/>
-      <c r="Q20" s="87"/>
-      <c r="R20" s="88"/>
-      <c r="S20" s="88"/>
-      <c r="T20" s="88"/>
-      <c r="U20" s="88"/>
-      <c r="V20" s="88"/>
-      <c r="W20" s="88"/>
-      <c r="X20" s="88"/>
-      <c r="Y20" s="88"/>
-      <c r="Z20" s="88"/>
-      <c r="AA20" s="88"/>
-      <c r="AB20" s="88"/>
-      <c r="AC20" s="88"/>
-      <c r="AD20" s="88"/>
-      <c r="AE20" s="89"/>
-      <c r="AF20" s="84"/>
-      <c r="AG20" s="85"/>
-      <c r="AH20" s="85"/>
-      <c r="AI20" s="86"/>
+      <c r="B20" s="155"/>
+      <c r="C20" s="129"/>
+      <c r="D20" s="130"/>
+      <c r="E20" s="131"/>
+      <c r="F20" s="132"/>
+      <c r="G20" s="155"/>
+      <c r="H20" s="134"/>
+      <c r="I20" s="129"/>
+      <c r="J20" s="156"/>
+      <c r="K20" s="136"/>
+      <c r="L20" s="136"/>
+      <c r="M20" s="136"/>
+      <c r="N20" s="136"/>
+      <c r="O20" s="136"/>
+      <c r="P20" s="137"/>
+      <c r="Q20" s="157"/>
+      <c r="R20" s="139"/>
+      <c r="S20" s="139"/>
+      <c r="T20" s="139"/>
+      <c r="U20" s="139"/>
+      <c r="V20" s="139"/>
+      <c r="W20" s="139"/>
+      <c r="X20" s="139"/>
+      <c r="Y20" s="139"/>
+      <c r="Z20" s="139"/>
+      <c r="AA20" s="139"/>
+      <c r="AB20" s="139"/>
+      <c r="AC20" s="139"/>
+      <c r="AD20" s="139"/>
+      <c r="AE20" s="140"/>
+      <c r="AF20" s="156"/>
+      <c r="AG20" s="136"/>
+      <c r="AH20" s="136"/>
+      <c r="AI20" s="137"/>
     </row>
     <row r="21" spans="1:35" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="13"/>
-      <c r="B21" s="78"/>
-      <c r="C21" s="79"/>
-      <c r="D21" s="80"/>
-      <c r="E21" s="81"/>
-      <c r="F21" s="82"/>
-      <c r="G21" s="78"/>
-      <c r="H21" s="83"/>
-      <c r="I21" s="79"/>
-      <c r="J21" s="84"/>
-      <c r="K21" s="85"/>
-      <c r="L21" s="85"/>
-      <c r="M21" s="85"/>
-      <c r="N21" s="85"/>
-      <c r="O21" s="85"/>
-      <c r="P21" s="86"/>
-      <c r="Q21" s="87"/>
-      <c r="R21" s="88"/>
-      <c r="S21" s="88"/>
-      <c r="T21" s="88"/>
-      <c r="U21" s="88"/>
-      <c r="V21" s="88"/>
-      <c r="W21" s="88"/>
-      <c r="X21" s="88"/>
-      <c r="Y21" s="88"/>
-      <c r="Z21" s="88"/>
-      <c r="AA21" s="88"/>
-      <c r="AB21" s="88"/>
-      <c r="AC21" s="88"/>
-      <c r="AD21" s="88"/>
-      <c r="AE21" s="89"/>
-      <c r="AF21" s="84"/>
-      <c r="AG21" s="85"/>
-      <c r="AH21" s="85"/>
-      <c r="AI21" s="86"/>
+      <c r="B21" s="155"/>
+      <c r="C21" s="129"/>
+      <c r="D21" s="130"/>
+      <c r="E21" s="131"/>
+      <c r="F21" s="132"/>
+      <c r="G21" s="155"/>
+      <c r="H21" s="134"/>
+      <c r="I21" s="129"/>
+      <c r="J21" s="156"/>
+      <c r="K21" s="136"/>
+      <c r="L21" s="136"/>
+      <c r="M21" s="136"/>
+      <c r="N21" s="136"/>
+      <c r="O21" s="136"/>
+      <c r="P21" s="137"/>
+      <c r="Q21" s="157"/>
+      <c r="R21" s="139"/>
+      <c r="S21" s="139"/>
+      <c r="T21" s="139"/>
+      <c r="U21" s="139"/>
+      <c r="V21" s="139"/>
+      <c r="W21" s="139"/>
+      <c r="X21" s="139"/>
+      <c r="Y21" s="139"/>
+      <c r="Z21" s="139"/>
+      <c r="AA21" s="139"/>
+      <c r="AB21" s="139"/>
+      <c r="AC21" s="139"/>
+      <c r="AD21" s="139"/>
+      <c r="AE21" s="140"/>
+      <c r="AF21" s="156"/>
+      <c r="AG21" s="136"/>
+      <c r="AH21" s="136"/>
+      <c r="AI21" s="137"/>
     </row>
     <row r="22" spans="1:35" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="13"/>
-      <c r="B22" s="78"/>
-      <c r="C22" s="79"/>
-      <c r="D22" s="80"/>
-      <c r="E22" s="81"/>
-      <c r="F22" s="82"/>
-      <c r="G22" s="78"/>
-      <c r="H22" s="83"/>
-      <c r="I22" s="79"/>
-      <c r="J22" s="84"/>
-      <c r="K22" s="85"/>
-      <c r="L22" s="85"/>
-      <c r="M22" s="85"/>
-      <c r="N22" s="85"/>
-      <c r="O22" s="85"/>
-      <c r="P22" s="86"/>
-      <c r="Q22" s="87"/>
-      <c r="R22" s="88"/>
-      <c r="S22" s="88"/>
-      <c r="T22" s="88"/>
-      <c r="U22" s="88"/>
-      <c r="V22" s="88"/>
-      <c r="W22" s="88"/>
-      <c r="X22" s="88"/>
-      <c r="Y22" s="88"/>
-      <c r="Z22" s="88"/>
-      <c r="AA22" s="88"/>
-      <c r="AB22" s="88"/>
-      <c r="AC22" s="88"/>
-      <c r="AD22" s="88"/>
-      <c r="AE22" s="89"/>
-      <c r="AF22" s="84"/>
-      <c r="AG22" s="85"/>
-      <c r="AH22" s="85"/>
-      <c r="AI22" s="86"/>
+      <c r="B22" s="155"/>
+      <c r="C22" s="129"/>
+      <c r="D22" s="130"/>
+      <c r="E22" s="131"/>
+      <c r="F22" s="132"/>
+      <c r="G22" s="155"/>
+      <c r="H22" s="134"/>
+      <c r="I22" s="129"/>
+      <c r="J22" s="156"/>
+      <c r="K22" s="136"/>
+      <c r="L22" s="136"/>
+      <c r="M22" s="136"/>
+      <c r="N22" s="136"/>
+      <c r="O22" s="136"/>
+      <c r="P22" s="137"/>
+      <c r="Q22" s="157"/>
+      <c r="R22" s="139"/>
+      <c r="S22" s="139"/>
+      <c r="T22" s="139"/>
+      <c r="U22" s="139"/>
+      <c r="V22" s="139"/>
+      <c r="W22" s="139"/>
+      <c r="X22" s="139"/>
+      <c r="Y22" s="139"/>
+      <c r="Z22" s="139"/>
+      <c r="AA22" s="139"/>
+      <c r="AB22" s="139"/>
+      <c r="AC22" s="139"/>
+      <c r="AD22" s="139"/>
+      <c r="AE22" s="140"/>
+      <c r="AF22" s="156"/>
+      <c r="AG22" s="136"/>
+      <c r="AH22" s="136"/>
+      <c r="AI22" s="137"/>
     </row>
     <row r="23" spans="1:35" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="13"/>
-      <c r="B23" s="78"/>
-      <c r="C23" s="79"/>
-      <c r="D23" s="80"/>
-      <c r="E23" s="81"/>
-      <c r="F23" s="82"/>
-      <c r="G23" s="78"/>
-      <c r="H23" s="83"/>
-      <c r="I23" s="79"/>
-      <c r="J23" s="84"/>
-      <c r="K23" s="85"/>
-      <c r="L23" s="85"/>
-      <c r="M23" s="85"/>
-      <c r="N23" s="85"/>
-      <c r="O23" s="85"/>
-      <c r="P23" s="86"/>
-      <c r="Q23" s="87"/>
-      <c r="R23" s="88"/>
-      <c r="S23" s="88"/>
-      <c r="T23" s="88"/>
-      <c r="U23" s="88"/>
-      <c r="V23" s="88"/>
-      <c r="W23" s="88"/>
-      <c r="X23" s="88"/>
-      <c r="Y23" s="88"/>
-      <c r="Z23" s="88"/>
-      <c r="AA23" s="88"/>
-      <c r="AB23" s="88"/>
-      <c r="AC23" s="88"/>
-      <c r="AD23" s="88"/>
-      <c r="AE23" s="89"/>
-      <c r="AF23" s="84"/>
-      <c r="AG23" s="85"/>
-      <c r="AH23" s="85"/>
-      <c r="AI23" s="86"/>
+      <c r="B23" s="155"/>
+      <c r="C23" s="129"/>
+      <c r="D23" s="130"/>
+      <c r="E23" s="131"/>
+      <c r="F23" s="132"/>
+      <c r="G23" s="155"/>
+      <c r="H23" s="134"/>
+      <c r="I23" s="129"/>
+      <c r="J23" s="156"/>
+      <c r="K23" s="136"/>
+      <c r="L23" s="136"/>
+      <c r="M23" s="136"/>
+      <c r="N23" s="136"/>
+      <c r="O23" s="136"/>
+      <c r="P23" s="137"/>
+      <c r="Q23" s="157"/>
+      <c r="R23" s="139"/>
+      <c r="S23" s="139"/>
+      <c r="T23" s="139"/>
+      <c r="U23" s="139"/>
+      <c r="V23" s="139"/>
+      <c r="W23" s="139"/>
+      <c r="X23" s="139"/>
+      <c r="Y23" s="139"/>
+      <c r="Z23" s="139"/>
+      <c r="AA23" s="139"/>
+      <c r="AB23" s="139"/>
+      <c r="AC23" s="139"/>
+      <c r="AD23" s="139"/>
+      <c r="AE23" s="140"/>
+      <c r="AF23" s="156"/>
+      <c r="AG23" s="136"/>
+      <c r="AH23" s="136"/>
+      <c r="AI23" s="137"/>
     </row>
     <row r="24" spans="1:35" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="13"/>
-      <c r="B24" s="78"/>
-      <c r="C24" s="79"/>
-      <c r="D24" s="80"/>
-      <c r="E24" s="81"/>
-      <c r="F24" s="82"/>
-      <c r="G24" s="78"/>
-      <c r="H24" s="83"/>
-      <c r="I24" s="79"/>
-      <c r="J24" s="84"/>
-      <c r="K24" s="85"/>
-      <c r="L24" s="85"/>
-      <c r="M24" s="85"/>
-      <c r="N24" s="85"/>
-      <c r="O24" s="85"/>
-      <c r="P24" s="86"/>
-      <c r="Q24" s="87"/>
-      <c r="R24" s="88"/>
-      <c r="S24" s="88"/>
-      <c r="T24" s="88"/>
-      <c r="U24" s="88"/>
-      <c r="V24" s="88"/>
-      <c r="W24" s="88"/>
-      <c r="X24" s="88"/>
-      <c r="Y24" s="88"/>
-      <c r="Z24" s="88"/>
-      <c r="AA24" s="88"/>
-      <c r="AB24" s="88"/>
-      <c r="AC24" s="88"/>
-      <c r="AD24" s="88"/>
-      <c r="AE24" s="89"/>
-      <c r="AF24" s="84"/>
-      <c r="AG24" s="85"/>
-      <c r="AH24" s="85"/>
-      <c r="AI24" s="86"/>
+      <c r="B24" s="155"/>
+      <c r="C24" s="129"/>
+      <c r="D24" s="130"/>
+      <c r="E24" s="131"/>
+      <c r="F24" s="132"/>
+      <c r="G24" s="155"/>
+      <c r="H24" s="134"/>
+      <c r="I24" s="129"/>
+      <c r="J24" s="156"/>
+      <c r="K24" s="136"/>
+      <c r="L24" s="136"/>
+      <c r="M24" s="136"/>
+      <c r="N24" s="136"/>
+      <c r="O24" s="136"/>
+      <c r="P24" s="137"/>
+      <c r="Q24" s="157"/>
+      <c r="R24" s="139"/>
+      <c r="S24" s="139"/>
+      <c r="T24" s="139"/>
+      <c r="U24" s="139"/>
+      <c r="V24" s="139"/>
+      <c r="W24" s="139"/>
+      <c r="X24" s="139"/>
+      <c r="Y24" s="139"/>
+      <c r="Z24" s="139"/>
+      <c r="AA24" s="139"/>
+      <c r="AB24" s="139"/>
+      <c r="AC24" s="139"/>
+      <c r="AD24" s="139"/>
+      <c r="AE24" s="140"/>
+      <c r="AF24" s="156"/>
+      <c r="AG24" s="136"/>
+      <c r="AH24" s="136"/>
+      <c r="AI24" s="137"/>
     </row>
     <row r="25" spans="1:35" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="13"/>
-      <c r="B25" s="78"/>
-      <c r="C25" s="79"/>
-      <c r="D25" s="80"/>
-      <c r="E25" s="81"/>
-      <c r="F25" s="82"/>
-      <c r="G25" s="78"/>
-      <c r="H25" s="83"/>
-      <c r="I25" s="79"/>
-      <c r="J25" s="84"/>
-      <c r="K25" s="85"/>
-      <c r="L25" s="85"/>
-      <c r="M25" s="85"/>
-      <c r="N25" s="85"/>
-      <c r="O25" s="85"/>
-      <c r="P25" s="86"/>
-      <c r="Q25" s="87"/>
-      <c r="R25" s="88"/>
-      <c r="S25" s="88"/>
-      <c r="T25" s="88"/>
-      <c r="U25" s="88"/>
-      <c r="V25" s="88"/>
-      <c r="W25" s="88"/>
-      <c r="X25" s="88"/>
-      <c r="Y25" s="88"/>
-      <c r="Z25" s="88"/>
-      <c r="AA25" s="88"/>
-      <c r="AB25" s="88"/>
-      <c r="AC25" s="88"/>
-      <c r="AD25" s="88"/>
-      <c r="AE25" s="89"/>
-      <c r="AF25" s="84"/>
-      <c r="AG25" s="85"/>
-      <c r="AH25" s="85"/>
-      <c r="AI25" s="86"/>
+      <c r="B25" s="155"/>
+      <c r="C25" s="129"/>
+      <c r="D25" s="130"/>
+      <c r="E25" s="131"/>
+      <c r="F25" s="132"/>
+      <c r="G25" s="155"/>
+      <c r="H25" s="134"/>
+      <c r="I25" s="129"/>
+      <c r="J25" s="156"/>
+      <c r="K25" s="136"/>
+      <c r="L25" s="136"/>
+      <c r="M25" s="136"/>
+      <c r="N25" s="136"/>
+      <c r="O25" s="136"/>
+      <c r="P25" s="137"/>
+      <c r="Q25" s="157"/>
+      <c r="R25" s="139"/>
+      <c r="S25" s="139"/>
+      <c r="T25" s="139"/>
+      <c r="U25" s="139"/>
+      <c r="V25" s="139"/>
+      <c r="W25" s="139"/>
+      <c r="X25" s="139"/>
+      <c r="Y25" s="139"/>
+      <c r="Z25" s="139"/>
+      <c r="AA25" s="139"/>
+      <c r="AB25" s="139"/>
+      <c r="AC25" s="139"/>
+      <c r="AD25" s="139"/>
+      <c r="AE25" s="140"/>
+      <c r="AF25" s="156"/>
+      <c r="AG25" s="136"/>
+      <c r="AH25" s="136"/>
+      <c r="AI25" s="137"/>
     </row>
     <row r="26" spans="1:35" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="13"/>
-      <c r="B26" s="78"/>
-      <c r="C26" s="79"/>
-      <c r="D26" s="80"/>
-      <c r="E26" s="81"/>
-      <c r="F26" s="82"/>
-      <c r="G26" s="78"/>
-      <c r="H26" s="83"/>
-      <c r="I26" s="79"/>
-      <c r="J26" s="84"/>
-      <c r="K26" s="85"/>
-      <c r="L26" s="85"/>
-      <c r="M26" s="85"/>
-      <c r="N26" s="85"/>
-      <c r="O26" s="85"/>
-      <c r="P26" s="86"/>
-      <c r="Q26" s="87"/>
-      <c r="R26" s="88"/>
-      <c r="S26" s="88"/>
-      <c r="T26" s="88"/>
-      <c r="U26" s="88"/>
-      <c r="V26" s="88"/>
-      <c r="W26" s="88"/>
-      <c r="X26" s="88"/>
-      <c r="Y26" s="88"/>
-      <c r="Z26" s="88"/>
-      <c r="AA26" s="88"/>
-      <c r="AB26" s="88"/>
-      <c r="AC26" s="88"/>
-      <c r="AD26" s="88"/>
-      <c r="AE26" s="89"/>
-      <c r="AF26" s="84"/>
-      <c r="AG26" s="85"/>
-      <c r="AH26" s="85"/>
-      <c r="AI26" s="86"/>
+      <c r="B26" s="155"/>
+      <c r="C26" s="129"/>
+      <c r="D26" s="130"/>
+      <c r="E26" s="131"/>
+      <c r="F26" s="132"/>
+      <c r="G26" s="155"/>
+      <c r="H26" s="134"/>
+      <c r="I26" s="129"/>
+      <c r="J26" s="156"/>
+      <c r="K26" s="136"/>
+      <c r="L26" s="136"/>
+      <c r="M26" s="136"/>
+      <c r="N26" s="136"/>
+      <c r="O26" s="136"/>
+      <c r="P26" s="137"/>
+      <c r="Q26" s="157"/>
+      <c r="R26" s="139"/>
+      <c r="S26" s="139"/>
+      <c r="T26" s="139"/>
+      <c r="U26" s="139"/>
+      <c r="V26" s="139"/>
+      <c r="W26" s="139"/>
+      <c r="X26" s="139"/>
+      <c r="Y26" s="139"/>
+      <c r="Z26" s="139"/>
+      <c r="AA26" s="139"/>
+      <c r="AB26" s="139"/>
+      <c r="AC26" s="139"/>
+      <c r="AD26" s="139"/>
+      <c r="AE26" s="140"/>
+      <c r="AF26" s="156"/>
+      <c r="AG26" s="136"/>
+      <c r="AH26" s="136"/>
+      <c r="AI26" s="137"/>
     </row>
     <row r="27" spans="1:35" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="13"/>
-      <c r="B27" s="78"/>
-      <c r="C27" s="79"/>
-      <c r="D27" s="80"/>
-      <c r="E27" s="81"/>
-      <c r="F27" s="82"/>
-      <c r="G27" s="78"/>
-      <c r="H27" s="83"/>
-      <c r="I27" s="79"/>
-      <c r="J27" s="84"/>
-      <c r="K27" s="85"/>
-      <c r="L27" s="85"/>
-      <c r="M27" s="85"/>
-      <c r="N27" s="85"/>
-      <c r="O27" s="85"/>
-      <c r="P27" s="86"/>
-      <c r="Q27" s="87"/>
-      <c r="R27" s="88"/>
-      <c r="S27" s="88"/>
-      <c r="T27" s="88"/>
-      <c r="U27" s="88"/>
-      <c r="V27" s="88"/>
-      <c r="W27" s="88"/>
-      <c r="X27" s="88"/>
-      <c r="Y27" s="88"/>
-      <c r="Z27" s="88"/>
-      <c r="AA27" s="88"/>
-      <c r="AB27" s="88"/>
-      <c r="AC27" s="88"/>
-      <c r="AD27" s="88"/>
-      <c r="AE27" s="89"/>
-      <c r="AF27" s="84"/>
-      <c r="AG27" s="85"/>
-      <c r="AH27" s="85"/>
-      <c r="AI27" s="86"/>
+      <c r="B27" s="155"/>
+      <c r="C27" s="129"/>
+      <c r="D27" s="130"/>
+      <c r="E27" s="131"/>
+      <c r="F27" s="132"/>
+      <c r="G27" s="155"/>
+      <c r="H27" s="134"/>
+      <c r="I27" s="129"/>
+      <c r="J27" s="156"/>
+      <c r="K27" s="136"/>
+      <c r="L27" s="136"/>
+      <c r="M27" s="136"/>
+      <c r="N27" s="136"/>
+      <c r="O27" s="136"/>
+      <c r="P27" s="137"/>
+      <c r="Q27" s="157"/>
+      <c r="R27" s="139"/>
+      <c r="S27" s="139"/>
+      <c r="T27" s="139"/>
+      <c r="U27" s="139"/>
+      <c r="V27" s="139"/>
+      <c r="W27" s="139"/>
+      <c r="X27" s="139"/>
+      <c r="Y27" s="139"/>
+      <c r="Z27" s="139"/>
+      <c r="AA27" s="139"/>
+      <c r="AB27" s="139"/>
+      <c r="AC27" s="139"/>
+      <c r="AD27" s="139"/>
+      <c r="AE27" s="140"/>
+      <c r="AF27" s="156"/>
+      <c r="AG27" s="136"/>
+      <c r="AH27" s="136"/>
+      <c r="AI27" s="137"/>
     </row>
     <row r="28" spans="1:35" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="13"/>
-      <c r="B28" s="78"/>
-      <c r="C28" s="79"/>
-      <c r="D28" s="80"/>
-      <c r="E28" s="81"/>
-      <c r="F28" s="82"/>
-      <c r="G28" s="78"/>
-      <c r="H28" s="83"/>
-      <c r="I28" s="79"/>
-      <c r="J28" s="84"/>
-      <c r="K28" s="85"/>
-      <c r="L28" s="85"/>
-      <c r="M28" s="85"/>
-      <c r="N28" s="85"/>
-      <c r="O28" s="85"/>
-      <c r="P28" s="86"/>
-      <c r="Q28" s="87"/>
-      <c r="R28" s="88"/>
-      <c r="S28" s="88"/>
-      <c r="T28" s="88"/>
-      <c r="U28" s="88"/>
-      <c r="V28" s="88"/>
-      <c r="W28" s="88"/>
-      <c r="X28" s="88"/>
-      <c r="Y28" s="88"/>
-      <c r="Z28" s="88"/>
-      <c r="AA28" s="88"/>
-      <c r="AB28" s="88"/>
-      <c r="AC28" s="88"/>
-      <c r="AD28" s="88"/>
-      <c r="AE28" s="89"/>
-      <c r="AF28" s="84"/>
-      <c r="AG28" s="85"/>
-      <c r="AH28" s="85"/>
-      <c r="AI28" s="86"/>
+      <c r="B28" s="155"/>
+      <c r="C28" s="129"/>
+      <c r="D28" s="130"/>
+      <c r="E28" s="131"/>
+      <c r="F28" s="132"/>
+      <c r="G28" s="155"/>
+      <c r="H28" s="134"/>
+      <c r="I28" s="129"/>
+      <c r="J28" s="156"/>
+      <c r="K28" s="136"/>
+      <c r="L28" s="136"/>
+      <c r="M28" s="136"/>
+      <c r="N28" s="136"/>
+      <c r="O28" s="136"/>
+      <c r="P28" s="137"/>
+      <c r="Q28" s="157"/>
+      <c r="R28" s="139"/>
+      <c r="S28" s="139"/>
+      <c r="T28" s="139"/>
+      <c r="U28" s="139"/>
+      <c r="V28" s="139"/>
+      <c r="W28" s="139"/>
+      <c r="X28" s="139"/>
+      <c r="Y28" s="139"/>
+      <c r="Z28" s="139"/>
+      <c r="AA28" s="139"/>
+      <c r="AB28" s="139"/>
+      <c r="AC28" s="139"/>
+      <c r="AD28" s="139"/>
+      <c r="AE28" s="140"/>
+      <c r="AF28" s="156"/>
+      <c r="AG28" s="136"/>
+      <c r="AH28" s="136"/>
+      <c r="AI28" s="137"/>
     </row>
     <row r="29" spans="1:35" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="13"/>
-      <c r="B29" s="78"/>
-      <c r="C29" s="79"/>
-      <c r="D29" s="80"/>
-      <c r="E29" s="81"/>
-      <c r="F29" s="82"/>
-      <c r="G29" s="78"/>
-      <c r="H29" s="83"/>
-      <c r="I29" s="79"/>
-      <c r="J29" s="84"/>
-      <c r="K29" s="85"/>
-      <c r="L29" s="85"/>
-      <c r="M29" s="85"/>
-      <c r="N29" s="85"/>
-      <c r="O29" s="85"/>
-      <c r="P29" s="86"/>
-      <c r="Q29" s="87"/>
-      <c r="R29" s="88"/>
-      <c r="S29" s="88"/>
-      <c r="T29" s="88"/>
-      <c r="U29" s="88"/>
-      <c r="V29" s="88"/>
-      <c r="W29" s="88"/>
-      <c r="X29" s="88"/>
-      <c r="Y29" s="88"/>
-      <c r="Z29" s="88"/>
-      <c r="AA29" s="88"/>
-      <c r="AB29" s="88"/>
-      <c r="AC29" s="88"/>
-      <c r="AD29" s="88"/>
-      <c r="AE29" s="89"/>
-      <c r="AF29" s="84"/>
-      <c r="AG29" s="85"/>
-      <c r="AH29" s="85"/>
-      <c r="AI29" s="86"/>
+      <c r="B29" s="155"/>
+      <c r="C29" s="129"/>
+      <c r="D29" s="130"/>
+      <c r="E29" s="131"/>
+      <c r="F29" s="132"/>
+      <c r="G29" s="155"/>
+      <c r="H29" s="134"/>
+      <c r="I29" s="129"/>
+      <c r="J29" s="156"/>
+      <c r="K29" s="136"/>
+      <c r="L29" s="136"/>
+      <c r="M29" s="136"/>
+      <c r="N29" s="136"/>
+      <c r="O29" s="136"/>
+      <c r="P29" s="137"/>
+      <c r="Q29" s="157"/>
+      <c r="R29" s="139"/>
+      <c r="S29" s="139"/>
+      <c r="T29" s="139"/>
+      <c r="U29" s="139"/>
+      <c r="V29" s="139"/>
+      <c r="W29" s="139"/>
+      <c r="X29" s="139"/>
+      <c r="Y29" s="139"/>
+      <c r="Z29" s="139"/>
+      <c r="AA29" s="139"/>
+      <c r="AB29" s="139"/>
+      <c r="AC29" s="139"/>
+      <c r="AD29" s="139"/>
+      <c r="AE29" s="140"/>
+      <c r="AF29" s="156"/>
+      <c r="AG29" s="136"/>
+      <c r="AH29" s="136"/>
+      <c r="AI29" s="137"/>
     </row>
     <row r="30" spans="1:35" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="13"/>
-      <c r="B30" s="78"/>
-      <c r="C30" s="79"/>
-      <c r="D30" s="80"/>
-      <c r="E30" s="81"/>
-      <c r="F30" s="82"/>
-      <c r="G30" s="78"/>
-      <c r="H30" s="83"/>
-      <c r="I30" s="79"/>
-      <c r="J30" s="84"/>
-      <c r="K30" s="85"/>
-      <c r="L30" s="85"/>
-      <c r="M30" s="85"/>
-      <c r="N30" s="85"/>
-      <c r="O30" s="85"/>
-      <c r="P30" s="86"/>
-      <c r="Q30" s="87"/>
-      <c r="R30" s="88"/>
-      <c r="S30" s="88"/>
-      <c r="T30" s="88"/>
-      <c r="U30" s="88"/>
-      <c r="V30" s="88"/>
-      <c r="W30" s="88"/>
-      <c r="X30" s="88"/>
-      <c r="Y30" s="88"/>
-      <c r="Z30" s="88"/>
-      <c r="AA30" s="88"/>
-      <c r="AB30" s="88"/>
-      <c r="AC30" s="88"/>
-      <c r="AD30" s="88"/>
-      <c r="AE30" s="89"/>
-      <c r="AF30" s="84"/>
-      <c r="AG30" s="85"/>
-      <c r="AH30" s="85"/>
-      <c r="AI30" s="86"/>
+      <c r="B30" s="155"/>
+      <c r="C30" s="129"/>
+      <c r="D30" s="130"/>
+      <c r="E30" s="131"/>
+      <c r="F30" s="132"/>
+      <c r="G30" s="155"/>
+      <c r="H30" s="134"/>
+      <c r="I30" s="129"/>
+      <c r="J30" s="156"/>
+      <c r="K30" s="136"/>
+      <c r="L30" s="136"/>
+      <c r="M30" s="136"/>
+      <c r="N30" s="136"/>
+      <c r="O30" s="136"/>
+      <c r="P30" s="137"/>
+      <c r="Q30" s="157"/>
+      <c r="R30" s="139"/>
+      <c r="S30" s="139"/>
+      <c r="T30" s="139"/>
+      <c r="U30" s="139"/>
+      <c r="V30" s="139"/>
+      <c r="W30" s="139"/>
+      <c r="X30" s="139"/>
+      <c r="Y30" s="139"/>
+      <c r="Z30" s="139"/>
+      <c r="AA30" s="139"/>
+      <c r="AB30" s="139"/>
+      <c r="AC30" s="139"/>
+      <c r="AD30" s="139"/>
+      <c r="AE30" s="140"/>
+      <c r="AF30" s="156"/>
+      <c r="AG30" s="136"/>
+      <c r="AH30" s="136"/>
+      <c r="AI30" s="137"/>
     </row>
     <row r="31" spans="1:35" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="13"/>
-      <c r="B31" s="78"/>
-      <c r="C31" s="79"/>
-      <c r="D31" s="80"/>
-      <c r="E31" s="81"/>
-      <c r="F31" s="82"/>
-      <c r="G31" s="78"/>
-      <c r="H31" s="83"/>
-      <c r="I31" s="79"/>
-      <c r="J31" s="84"/>
-      <c r="K31" s="85"/>
-      <c r="L31" s="85"/>
-      <c r="M31" s="85"/>
-      <c r="N31" s="85"/>
-      <c r="O31" s="85"/>
-      <c r="P31" s="86"/>
-      <c r="Q31" s="87"/>
-      <c r="R31" s="88"/>
-      <c r="S31" s="88"/>
-      <c r="T31" s="88"/>
-      <c r="U31" s="88"/>
-      <c r="V31" s="88"/>
-      <c r="W31" s="88"/>
-      <c r="X31" s="88"/>
-      <c r="Y31" s="88"/>
-      <c r="Z31" s="88"/>
-      <c r="AA31" s="88"/>
-      <c r="AB31" s="88"/>
-      <c r="AC31" s="88"/>
-      <c r="AD31" s="88"/>
-      <c r="AE31" s="89"/>
-      <c r="AF31" s="84"/>
-      <c r="AG31" s="85"/>
-      <c r="AH31" s="85"/>
-      <c r="AI31" s="86"/>
+      <c r="B31" s="155"/>
+      <c r="C31" s="129"/>
+      <c r="D31" s="130"/>
+      <c r="E31" s="131"/>
+      <c r="F31" s="132"/>
+      <c r="G31" s="155"/>
+      <c r="H31" s="134"/>
+      <c r="I31" s="129"/>
+      <c r="J31" s="156"/>
+      <c r="K31" s="136"/>
+      <c r="L31" s="136"/>
+      <c r="M31" s="136"/>
+      <c r="N31" s="136"/>
+      <c r="O31" s="136"/>
+      <c r="P31" s="137"/>
+      <c r="Q31" s="157"/>
+      <c r="R31" s="139"/>
+      <c r="S31" s="139"/>
+      <c r="T31" s="139"/>
+      <c r="U31" s="139"/>
+      <c r="V31" s="139"/>
+      <c r="W31" s="139"/>
+      <c r="X31" s="139"/>
+      <c r="Y31" s="139"/>
+      <c r="Z31" s="139"/>
+      <c r="AA31" s="139"/>
+      <c r="AB31" s="139"/>
+      <c r="AC31" s="139"/>
+      <c r="AD31" s="139"/>
+      <c r="AE31" s="140"/>
+      <c r="AF31" s="156"/>
+      <c r="AG31" s="136"/>
+      <c r="AH31" s="136"/>
+      <c r="AI31" s="137"/>
     </row>
     <row r="32" spans="1:35" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="13"/>
-      <c r="B32" s="78"/>
-      <c r="C32" s="79"/>
-      <c r="D32" s="80"/>
-      <c r="E32" s="81"/>
-      <c r="F32" s="82"/>
-      <c r="G32" s="78"/>
-      <c r="H32" s="83"/>
-      <c r="I32" s="79"/>
-      <c r="J32" s="84"/>
-      <c r="K32" s="90"/>
-      <c r="L32" s="85"/>
-      <c r="M32" s="85"/>
-      <c r="N32" s="85"/>
-      <c r="O32" s="85"/>
-      <c r="P32" s="86"/>
-      <c r="Q32" s="87"/>
-      <c r="R32" s="88"/>
-      <c r="S32" s="88"/>
-      <c r="T32" s="88"/>
-      <c r="U32" s="88"/>
-      <c r="V32" s="88"/>
-      <c r="W32" s="88"/>
-      <c r="X32" s="88"/>
-      <c r="Y32" s="88"/>
-      <c r="Z32" s="88"/>
-      <c r="AA32" s="88"/>
-      <c r="AB32" s="88"/>
-      <c r="AC32" s="88"/>
-      <c r="AD32" s="88"/>
-      <c r="AE32" s="89"/>
-      <c r="AF32" s="84"/>
-      <c r="AG32" s="85"/>
-      <c r="AH32" s="85"/>
-      <c r="AI32" s="86"/>
+      <c r="B32" s="155"/>
+      <c r="C32" s="129"/>
+      <c r="D32" s="130"/>
+      <c r="E32" s="131"/>
+      <c r="F32" s="132"/>
+      <c r="G32" s="155"/>
+      <c r="H32" s="134"/>
+      <c r="I32" s="129"/>
+      <c r="J32" s="156"/>
+      <c r="K32" s="158"/>
+      <c r="L32" s="136"/>
+      <c r="M32" s="136"/>
+      <c r="N32" s="136"/>
+      <c r="O32" s="136"/>
+      <c r="P32" s="137"/>
+      <c r="Q32" s="157"/>
+      <c r="R32" s="139"/>
+      <c r="S32" s="139"/>
+      <c r="T32" s="139"/>
+      <c r="U32" s="139"/>
+      <c r="V32" s="139"/>
+      <c r="W32" s="139"/>
+      <c r="X32" s="139"/>
+      <c r="Y32" s="139"/>
+      <c r="Z32" s="139"/>
+      <c r="AA32" s="139"/>
+      <c r="AB32" s="139"/>
+      <c r="AC32" s="139"/>
+      <c r="AD32" s="139"/>
+      <c r="AE32" s="140"/>
+      <c r="AF32" s="156"/>
+      <c r="AG32" s="136"/>
+      <c r="AH32" s="136"/>
+      <c r="AI32" s="137"/>
     </row>
     <row r="33" spans="1:35" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="13"/>
-      <c r="B33" s="78"/>
-      <c r="C33" s="79"/>
-      <c r="D33" s="80"/>
-      <c r="E33" s="81"/>
-      <c r="F33" s="82"/>
-      <c r="G33" s="78"/>
-      <c r="H33" s="83"/>
-      <c r="I33" s="79"/>
-      <c r="J33" s="84"/>
-      <c r="K33" s="85"/>
-      <c r="L33" s="85"/>
-      <c r="M33" s="85"/>
-      <c r="N33" s="85"/>
-      <c r="O33" s="85"/>
-      <c r="P33" s="86"/>
-      <c r="Q33" s="87"/>
-      <c r="R33" s="88"/>
-      <c r="S33" s="88"/>
-      <c r="T33" s="88"/>
-      <c r="U33" s="88"/>
-      <c r="V33" s="88"/>
-      <c r="W33" s="88"/>
-      <c r="X33" s="88"/>
-      <c r="Y33" s="88"/>
-      <c r="Z33" s="88"/>
-      <c r="AA33" s="88"/>
-      <c r="AB33" s="88"/>
-      <c r="AC33" s="88"/>
-      <c r="AD33" s="88"/>
-      <c r="AE33" s="89"/>
-      <c r="AF33" s="84"/>
-      <c r="AG33" s="85"/>
-      <c r="AH33" s="85"/>
-      <c r="AI33" s="86"/>
+      <c r="B33" s="155"/>
+      <c r="C33" s="129"/>
+      <c r="D33" s="130"/>
+      <c r="E33" s="131"/>
+      <c r="F33" s="132"/>
+      <c r="G33" s="155"/>
+      <c r="H33" s="134"/>
+      <c r="I33" s="129"/>
+      <c r="J33" s="156"/>
+      <c r="K33" s="136"/>
+      <c r="L33" s="136"/>
+      <c r="M33" s="136"/>
+      <c r="N33" s="136"/>
+      <c r="O33" s="136"/>
+      <c r="P33" s="137"/>
+      <c r="Q33" s="157"/>
+      <c r="R33" s="139"/>
+      <c r="S33" s="139"/>
+      <c r="T33" s="139"/>
+      <c r="U33" s="139"/>
+      <c r="V33" s="139"/>
+      <c r="W33" s="139"/>
+      <c r="X33" s="139"/>
+      <c r="Y33" s="139"/>
+      <c r="Z33" s="139"/>
+      <c r="AA33" s="139"/>
+      <c r="AB33" s="139"/>
+      <c r="AC33" s="139"/>
+      <c r="AD33" s="139"/>
+      <c r="AE33" s="140"/>
+      <c r="AF33" s="156"/>
+      <c r="AG33" s="136"/>
+      <c r="AH33" s="136"/>
+      <c r="AI33" s="137"/>
     </row>
     <row r="34" spans="1:35" ht="14.25" x14ac:dyDescent="0.15">
       <c r="K34" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="179">
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="J33:P33"/>
+    <mergeCell ref="Q33:AE33"/>
+    <mergeCell ref="AF33:AI33"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="J32:P32"/>
+    <mergeCell ref="Q32:AE32"/>
+    <mergeCell ref="AF32:AI32"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:P31"/>
+    <mergeCell ref="Q31:AE31"/>
+    <mergeCell ref="AF31:AI31"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:P30"/>
+    <mergeCell ref="Q30:AE30"/>
+    <mergeCell ref="AF30:AI30"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:P29"/>
+    <mergeCell ref="Q29:AE29"/>
+    <mergeCell ref="AF29:AI29"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:P28"/>
+    <mergeCell ref="Q28:AE28"/>
+    <mergeCell ref="AF28:AI28"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:P27"/>
+    <mergeCell ref="Q27:AE27"/>
+    <mergeCell ref="AF27:AI27"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="J26:P26"/>
+    <mergeCell ref="Q26:AE26"/>
+    <mergeCell ref="AF26:AI26"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:P25"/>
+    <mergeCell ref="Q25:AE25"/>
+    <mergeCell ref="AF25:AI25"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:P24"/>
+    <mergeCell ref="Q24:AE24"/>
+    <mergeCell ref="AF24:AI24"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:P23"/>
+    <mergeCell ref="Q23:AE23"/>
+    <mergeCell ref="AF23:AI23"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:P22"/>
+    <mergeCell ref="Q22:AE22"/>
+    <mergeCell ref="AF22:AI22"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:P21"/>
+    <mergeCell ref="Q21:AE21"/>
+    <mergeCell ref="AF21:AI21"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:P20"/>
+    <mergeCell ref="Q20:AE20"/>
+    <mergeCell ref="AF20:AI20"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:P19"/>
+    <mergeCell ref="Q19:AE19"/>
+    <mergeCell ref="AF19:AI19"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="J18:P18"/>
+    <mergeCell ref="Q18:AE18"/>
+    <mergeCell ref="AF18:AI18"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:P17"/>
+    <mergeCell ref="Q17:AE17"/>
+    <mergeCell ref="AF17:AI17"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:P16"/>
+    <mergeCell ref="Q16:AE16"/>
+    <mergeCell ref="AF16:AI16"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:P15"/>
+    <mergeCell ref="Q15:AE15"/>
+    <mergeCell ref="AF15:AI15"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="J14:P14"/>
+    <mergeCell ref="Q14:AE14"/>
+    <mergeCell ref="AF14:AI14"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="J13:P13"/>
+    <mergeCell ref="Q13:AE13"/>
+    <mergeCell ref="AF13:AI13"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="J12:P12"/>
+    <mergeCell ref="Q12:AE12"/>
+    <mergeCell ref="AF12:AI12"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="J11:P11"/>
+    <mergeCell ref="Q11:AE11"/>
+    <mergeCell ref="AF11:AI11"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="J10:P10"/>
+    <mergeCell ref="Q10:AE10"/>
+    <mergeCell ref="AF10:AI10"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="J9:P9"/>
+    <mergeCell ref="Q9:AE9"/>
+    <mergeCell ref="AF9:AI9"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="J8:P8"/>
+    <mergeCell ref="Q8:AE8"/>
+    <mergeCell ref="AF8:AI8"/>
     <mergeCell ref="AG3:AI3"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="D7:F7"/>
@@ -15644,162 +15868,6 @@
     <mergeCell ref="E3:N3"/>
     <mergeCell ref="AA3:AB3"/>
     <mergeCell ref="AC3:AF3"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="J9:P9"/>
-    <mergeCell ref="Q9:AE9"/>
-    <mergeCell ref="AF9:AI9"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="J8:P8"/>
-    <mergeCell ref="Q8:AE8"/>
-    <mergeCell ref="AF8:AI8"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="J11:P11"/>
-    <mergeCell ref="Q11:AE11"/>
-    <mergeCell ref="AF11:AI11"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="J10:P10"/>
-    <mergeCell ref="Q10:AE10"/>
-    <mergeCell ref="AF10:AI10"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="J13:P13"/>
-    <mergeCell ref="Q13:AE13"/>
-    <mergeCell ref="AF13:AI13"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="J12:P12"/>
-    <mergeCell ref="Q12:AE12"/>
-    <mergeCell ref="AF12:AI12"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:P15"/>
-    <mergeCell ref="Q15:AE15"/>
-    <mergeCell ref="AF15:AI15"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="J14:P14"/>
-    <mergeCell ref="Q14:AE14"/>
-    <mergeCell ref="AF14:AI14"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:P17"/>
-    <mergeCell ref="Q17:AE17"/>
-    <mergeCell ref="AF17:AI17"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:P16"/>
-    <mergeCell ref="Q16:AE16"/>
-    <mergeCell ref="AF16:AI16"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:P19"/>
-    <mergeCell ref="Q19:AE19"/>
-    <mergeCell ref="AF19:AI19"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="J18:P18"/>
-    <mergeCell ref="Q18:AE18"/>
-    <mergeCell ref="AF18:AI18"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:P21"/>
-    <mergeCell ref="Q21:AE21"/>
-    <mergeCell ref="AF21:AI21"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:P20"/>
-    <mergeCell ref="Q20:AE20"/>
-    <mergeCell ref="AF20:AI20"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:P23"/>
-    <mergeCell ref="Q23:AE23"/>
-    <mergeCell ref="AF23:AI23"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:P22"/>
-    <mergeCell ref="Q22:AE22"/>
-    <mergeCell ref="AF22:AI22"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:P25"/>
-    <mergeCell ref="Q25:AE25"/>
-    <mergeCell ref="AF25:AI25"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:P24"/>
-    <mergeCell ref="Q24:AE24"/>
-    <mergeCell ref="AF24:AI24"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:P27"/>
-    <mergeCell ref="Q27:AE27"/>
-    <mergeCell ref="AF27:AI27"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="J26:P26"/>
-    <mergeCell ref="Q26:AE26"/>
-    <mergeCell ref="AF26:AI26"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:P29"/>
-    <mergeCell ref="Q29:AE29"/>
-    <mergeCell ref="AF29:AI29"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:P28"/>
-    <mergeCell ref="Q28:AE28"/>
-    <mergeCell ref="AF28:AI28"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:P31"/>
-    <mergeCell ref="Q31:AE31"/>
-    <mergeCell ref="AF31:AI31"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:P30"/>
-    <mergeCell ref="Q30:AE30"/>
-    <mergeCell ref="AF30:AI30"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="J33:P33"/>
-    <mergeCell ref="Q33:AE33"/>
-    <mergeCell ref="AF33:AI33"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="J32:P32"/>
-    <mergeCell ref="Q32:AE32"/>
-    <mergeCell ref="AF32:AI32"/>
   </mergeCells>
   <phoneticPr fontId="10"/>
   <printOptions horizontalCentered="1"/>
@@ -15951,163 +16019,163 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="116" t="s">
+      <c r="A1" s="96" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="117"/>
-      <c r="C1" s="117"/>
-      <c r="D1" s="118"/>
-      <c r="E1" s="119" t="str">
+      <c r="B1" s="97"/>
+      <c r="C1" s="97"/>
+      <c r="D1" s="98"/>
+      <c r="E1" s="99" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E1")&lt;&gt;"",INDIRECT("変更履歴!E1"),"")</f>
         <v/>
       </c>
-      <c r="F1" s="120"/>
-      <c r="G1" s="120"/>
-      <c r="H1" s="120"/>
-      <c r="I1" s="120"/>
-      <c r="J1" s="120"/>
-      <c r="K1" s="120"/>
-      <c r="L1" s="120"/>
-      <c r="M1" s="120"/>
-      <c r="N1" s="121"/>
-      <c r="O1" s="127" t="s">
+      <c r="F1" s="100"/>
+      <c r="G1" s="100"/>
+      <c r="H1" s="100"/>
+      <c r="I1" s="100"/>
+      <c r="J1" s="100"/>
+      <c r="K1" s="100"/>
+      <c r="L1" s="100"/>
+      <c r="M1" s="100"/>
+      <c r="N1" s="101"/>
+      <c r="O1" s="107" t="s">
         <v>11</v>
       </c>
-      <c r="P1" s="128"/>
-      <c r="Q1" s="128"/>
-      <c r="R1" s="129"/>
-      <c r="S1" s="148" t="str">
+      <c r="P1" s="108"/>
+      <c r="Q1" s="108"/>
+      <c r="R1" s="109"/>
+      <c r="S1" s="164" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!S1")&lt;&gt;"",INDIRECT("変更履歴!S1"),"")</f>
         <v>Nablarch開発標準設計書一覧</v>
       </c>
-      <c r="T1" s="137"/>
-      <c r="U1" s="137"/>
-      <c r="V1" s="137"/>
-      <c r="W1" s="137"/>
-      <c r="X1" s="137"/>
-      <c r="Y1" s="137"/>
-      <c r="Z1" s="138"/>
-      <c r="AA1" s="149" t="s">
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
+      <c r="V1" s="117"/>
+      <c r="W1" s="117"/>
+      <c r="X1" s="117"/>
+      <c r="Y1" s="117"/>
+      <c r="Z1" s="118"/>
+      <c r="AA1" s="162" t="s">
         <v>12</v>
       </c>
-      <c r="AB1" s="150"/>
-      <c r="AC1" s="145" t="str">
+      <c r="AB1" s="163"/>
+      <c r="AC1" s="125" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC1")&lt;&gt;"",INDIRECT("変更履歴!AC1"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="146"/>
-      <c r="AE1" s="146"/>
-      <c r="AF1" s="147"/>
-      <c r="AG1" s="151">
+      <c r="AD1" s="126"/>
+      <c r="AE1" s="126"/>
+      <c r="AF1" s="127"/>
+      <c r="AG1" s="159">
         <f ca="1">IF(INDIRECT("変更履歴!AG1")&lt;&gt;"",INDIRECT("変更履歴!AG1"),"")</f>
         <v>43336</v>
       </c>
-      <c r="AH1" s="152"/>
-      <c r="AI1" s="153"/>
+      <c r="AH1" s="160"/>
+      <c r="AI1" s="161"/>
       <c r="AJ1" s="1"/>
       <c r="AK1" s="1"/>
       <c r="AL1" s="2"/>
     </row>
     <row r="2" spans="1:38" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="116" t="s">
+      <c r="A2" s="96" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="117"/>
-      <c r="C2" s="117"/>
-      <c r="D2" s="118"/>
-      <c r="E2" s="119" t="str">
+      <c r="B2" s="97"/>
+      <c r="C2" s="97"/>
+      <c r="D2" s="98"/>
+      <c r="E2" s="99" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E2")&lt;&gt;"",INDIRECT("変更履歴!E2"),"")</f>
         <v/>
       </c>
-      <c r="F2" s="120"/>
-      <c r="G2" s="120"/>
-      <c r="H2" s="120"/>
-      <c r="I2" s="120"/>
-      <c r="J2" s="120"/>
-      <c r="K2" s="120"/>
-      <c r="L2" s="120"/>
-      <c r="M2" s="120"/>
-      <c r="N2" s="121"/>
-      <c r="O2" s="130"/>
-      <c r="P2" s="131"/>
-      <c r="Q2" s="131"/>
-      <c r="R2" s="132"/>
-      <c r="S2" s="139"/>
-      <c r="T2" s="140"/>
-      <c r="U2" s="140"/>
-      <c r="V2" s="140"/>
-      <c r="W2" s="140"/>
-      <c r="X2" s="140"/>
-      <c r="Y2" s="140"/>
-      <c r="Z2" s="141"/>
-      <c r="AA2" s="149" t="s">
+      <c r="F2" s="100"/>
+      <c r="G2" s="100"/>
+      <c r="H2" s="100"/>
+      <c r="I2" s="100"/>
+      <c r="J2" s="100"/>
+      <c r="K2" s="100"/>
+      <c r="L2" s="100"/>
+      <c r="M2" s="100"/>
+      <c r="N2" s="101"/>
+      <c r="O2" s="110"/>
+      <c r="P2" s="111"/>
+      <c r="Q2" s="111"/>
+      <c r="R2" s="112"/>
+      <c r="S2" s="119"/>
+      <c r="T2" s="120"/>
+      <c r="U2" s="120"/>
+      <c r="V2" s="120"/>
+      <c r="W2" s="120"/>
+      <c r="X2" s="120"/>
+      <c r="Y2" s="120"/>
+      <c r="Z2" s="121"/>
+      <c r="AA2" s="162" t="s">
         <v>13</v>
       </c>
-      <c r="AB2" s="150"/>
-      <c r="AC2" s="145" t="str">
+      <c r="AB2" s="163"/>
+      <c r="AC2" s="125" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC2")&lt;&gt;"",INDIRECT("変更履歴!AC2"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD2" s="146"/>
-      <c r="AE2" s="146"/>
-      <c r="AF2" s="147"/>
-      <c r="AG2" s="151">
+      <c r="AD2" s="126"/>
+      <c r="AE2" s="126"/>
+      <c r="AF2" s="127"/>
+      <c r="AG2" s="159">
         <f ca="1">IF(INDIRECT("変更履歴!AG2")&lt;&gt;"",INDIRECT("変更履歴!AG2"),"")</f>
-        <v>44848</v>
-      </c>
-      <c r="AH2" s="152"/>
-      <c r="AI2" s="153"/>
+        <v>45464</v>
+      </c>
+      <c r="AH2" s="160"/>
+      <c r="AI2" s="161"/>
       <c r="AJ2" s="1"/>
       <c r="AK2" s="1"/>
       <c r="AL2" s="1"/>
     </row>
     <row r="3" spans="1:38" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="116" t="s">
+      <c r="A3" s="96" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="117"/>
-      <c r="C3" s="117"/>
-      <c r="D3" s="118"/>
-      <c r="E3" s="119" t="str">
+      <c r="B3" s="97"/>
+      <c r="C3" s="97"/>
+      <c r="D3" s="98"/>
+      <c r="E3" s="99" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E3")&lt;&gt;"",INDIRECT("変更履歴!E3"),"")</f>
         <v/>
       </c>
-      <c r="F3" s="120"/>
-      <c r="G3" s="120"/>
-      <c r="H3" s="120"/>
-      <c r="I3" s="120"/>
-      <c r="J3" s="120"/>
-      <c r="K3" s="120"/>
-      <c r="L3" s="120"/>
-      <c r="M3" s="120"/>
-      <c r="N3" s="121"/>
-      <c r="O3" s="133"/>
-      <c r="P3" s="134"/>
-      <c r="Q3" s="134"/>
-      <c r="R3" s="135"/>
-      <c r="S3" s="142"/>
-      <c r="T3" s="143"/>
-      <c r="U3" s="143"/>
-      <c r="V3" s="143"/>
-      <c r="W3" s="143"/>
-      <c r="X3" s="143"/>
-      <c r="Y3" s="143"/>
-      <c r="Z3" s="144"/>
-      <c r="AA3" s="149"/>
-      <c r="AB3" s="150"/>
-      <c r="AC3" s="145" t="str">
+      <c r="F3" s="100"/>
+      <c r="G3" s="100"/>
+      <c r="H3" s="100"/>
+      <c r="I3" s="100"/>
+      <c r="J3" s="100"/>
+      <c r="K3" s="100"/>
+      <c r="L3" s="100"/>
+      <c r="M3" s="100"/>
+      <c r="N3" s="101"/>
+      <c r="O3" s="113"/>
+      <c r="P3" s="114"/>
+      <c r="Q3" s="114"/>
+      <c r="R3" s="115"/>
+      <c r="S3" s="122"/>
+      <c r="T3" s="123"/>
+      <c r="U3" s="123"/>
+      <c r="V3" s="123"/>
+      <c r="W3" s="123"/>
+      <c r="X3" s="123"/>
+      <c r="Y3" s="123"/>
+      <c r="Z3" s="124"/>
+      <c r="AA3" s="162"/>
+      <c r="AB3" s="163"/>
+      <c r="AC3" s="125" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC3")&lt;&gt;"",INDIRECT("変更履歴!AC3"),"")</f>
         <v/>
       </c>
-      <c r="AD3" s="146"/>
-      <c r="AE3" s="146"/>
-      <c r="AF3" s="147"/>
-      <c r="AG3" s="151" t="str">
+      <c r="AD3" s="126"/>
+      <c r="AE3" s="126"/>
+      <c r="AF3" s="127"/>
+      <c r="AG3" s="159" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AG3")&lt;&gt;"",INDIRECT("変更履歴!AG3"),"")</f>
         <v/>
       </c>
-      <c r="AH3" s="152"/>
-      <c r="AI3" s="153"/>
+      <c r="AH3" s="160"/>
+      <c r="AI3" s="161"/>
       <c r="AJ3" s="1"/>
       <c r="AK3" s="1"/>
       <c r="AL3" s="1"/>
@@ -16148,7 +16216,7 @@
     <row r="9" spans="1:38" s="39" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B9" s="38"/>
       <c r="D9" s="38" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P9" s="40"/>
       <c r="R9" s="40"/>
@@ -16377,14 +16445,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="AG1:AI1"/>
-    <mergeCell ref="AC1:AF1"/>
-    <mergeCell ref="AC2:AF2"/>
-    <mergeCell ref="AG2:AI2"/>
-    <mergeCell ref="E3:N3"/>
-    <mergeCell ref="AA3:AB3"/>
-    <mergeCell ref="AC3:AF3"/>
-    <mergeCell ref="AG3:AI3"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="E1:N1"/>
     <mergeCell ref="O1:R3"/>
@@ -16394,6 +16454,14 @@
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="E2:N2"/>
     <mergeCell ref="AA2:AB2"/>
+    <mergeCell ref="AG1:AI1"/>
+    <mergeCell ref="AC1:AF1"/>
+    <mergeCell ref="AC2:AF2"/>
+    <mergeCell ref="AG2:AI2"/>
+    <mergeCell ref="E3:N3"/>
+    <mergeCell ref="AA3:AB3"/>
+    <mergeCell ref="AC3:AF3"/>
+    <mergeCell ref="AG3:AI3"/>
   </mergeCells>
   <phoneticPr fontId="10"/>
   <printOptions horizontalCentered="1"/>
@@ -16416,59 +16484,59 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:50" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="116" t="s">
+      <c r="A1" s="96" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="117"/>
-      <c r="C1" s="117"/>
-      <c r="D1" s="118"/>
-      <c r="E1" s="119" t="str">
+      <c r="B1" s="97"/>
+      <c r="C1" s="97"/>
+      <c r="D1" s="98"/>
+      <c r="E1" s="99" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E1")&lt;&gt;"",INDIRECT("変更履歴!E1"),"")</f>
         <v/>
       </c>
-      <c r="F1" s="120"/>
-      <c r="G1" s="120"/>
-      <c r="H1" s="120"/>
-      <c r="I1" s="120"/>
-      <c r="J1" s="120"/>
-      <c r="K1" s="120"/>
-      <c r="L1" s="120"/>
-      <c r="M1" s="120"/>
-      <c r="N1" s="121"/>
-      <c r="O1" s="154" t="s">
+      <c r="F1" s="100"/>
+      <c r="G1" s="100"/>
+      <c r="H1" s="100"/>
+      <c r="I1" s="100"/>
+      <c r="J1" s="100"/>
+      <c r="K1" s="100"/>
+      <c r="L1" s="100"/>
+      <c r="M1" s="100"/>
+      <c r="N1" s="101"/>
+      <c r="O1" s="174" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="155"/>
-      <c r="Q1" s="155"/>
-      <c r="R1" s="156"/>
-      <c r="S1" s="163" t="str">
+      <c r="P1" s="175"/>
+      <c r="Q1" s="175"/>
+      <c r="R1" s="176"/>
+      <c r="S1" s="165" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!S1")&lt;&gt;"",INDIRECT("変更履歴!S1"),"")</f>
         <v>Nablarch開発標準設計書一覧</v>
       </c>
-      <c r="T1" s="164"/>
-      <c r="U1" s="164"/>
-      <c r="V1" s="164"/>
-      <c r="W1" s="164"/>
-      <c r="X1" s="164"/>
-      <c r="Y1" s="164"/>
-      <c r="Z1" s="165"/>
-      <c r="AA1" s="116" t="s">
+      <c r="T1" s="166"/>
+      <c r="U1" s="166"/>
+      <c r="V1" s="166"/>
+      <c r="W1" s="166"/>
+      <c r="X1" s="166"/>
+      <c r="Y1" s="166"/>
+      <c r="Z1" s="167"/>
+      <c r="AA1" s="96" t="s">
         <v>3</v>
       </c>
-      <c r="AB1" s="118"/>
-      <c r="AC1" s="145" t="str">
+      <c r="AB1" s="98"/>
+      <c r="AC1" s="125" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC1")&lt;&gt;"",INDIRECT("変更履歴!AC1"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="146"/>
-      <c r="AE1" s="146"/>
-      <c r="AF1" s="147"/>
-      <c r="AG1" s="151">
+      <c r="AD1" s="126"/>
+      <c r="AE1" s="126"/>
+      <c r="AF1" s="127"/>
+      <c r="AG1" s="159">
         <f ca="1">IF(INDIRECT("変更履歴!AG1")&lt;&gt;"",INDIRECT("変更履歴!AG1"),"")</f>
         <v>43336</v>
       </c>
-      <c r="AH1" s="152"/>
-      <c r="AI1" s="153"/>
+      <c r="AH1" s="160"/>
+      <c r="AI1" s="161"/>
       <c r="AJ1" s="6"/>
       <c r="AN1" s="7"/>
       <c r="AO1" s="6"/>
@@ -16482,54 +16550,54 @@
       <c r="AW1" s="6"/>
     </row>
     <row r="2" spans="1:50" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="116" t="s">
+      <c r="A2" s="96" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="117"/>
-      <c r="C2" s="117"/>
-      <c r="D2" s="118"/>
-      <c r="E2" s="119" t="str">
+      <c r="B2" s="97"/>
+      <c r="C2" s="97"/>
+      <c r="D2" s="98"/>
+      <c r="E2" s="99" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E2")&lt;&gt;"",INDIRECT("変更履歴!E2"),"")</f>
         <v/>
       </c>
-      <c r="F2" s="120"/>
-      <c r="G2" s="120"/>
-      <c r="H2" s="120"/>
-      <c r="I2" s="120"/>
-      <c r="J2" s="120"/>
-      <c r="K2" s="120"/>
-      <c r="L2" s="120"/>
-      <c r="M2" s="120"/>
-      <c r="N2" s="121"/>
-      <c r="O2" s="157"/>
-      <c r="P2" s="158"/>
-      <c r="Q2" s="158"/>
-      <c r="R2" s="159"/>
-      <c r="S2" s="166"/>
-      <c r="T2" s="167"/>
-      <c r="U2" s="167"/>
-      <c r="V2" s="167"/>
-      <c r="W2" s="167"/>
-      <c r="X2" s="167"/>
-      <c r="Y2" s="167"/>
-      <c r="Z2" s="168"/>
-      <c r="AA2" s="116" t="s">
+      <c r="F2" s="100"/>
+      <c r="G2" s="100"/>
+      <c r="H2" s="100"/>
+      <c r="I2" s="100"/>
+      <c r="J2" s="100"/>
+      <c r="K2" s="100"/>
+      <c r="L2" s="100"/>
+      <c r="M2" s="100"/>
+      <c r="N2" s="101"/>
+      <c r="O2" s="177"/>
+      <c r="P2" s="178"/>
+      <c r="Q2" s="178"/>
+      <c r="R2" s="179"/>
+      <c r="S2" s="168"/>
+      <c r="T2" s="169"/>
+      <c r="U2" s="169"/>
+      <c r="V2" s="169"/>
+      <c r="W2" s="169"/>
+      <c r="X2" s="169"/>
+      <c r="Y2" s="169"/>
+      <c r="Z2" s="170"/>
+      <c r="AA2" s="96" t="s">
         <v>4</v>
       </c>
-      <c r="AB2" s="118"/>
-      <c r="AC2" s="145" t="str">
+      <c r="AB2" s="98"/>
+      <c r="AC2" s="125" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC2")&lt;&gt;"",INDIRECT("変更履歴!AC2"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD2" s="146"/>
-      <c r="AE2" s="146"/>
-      <c r="AF2" s="147"/>
-      <c r="AG2" s="151">
+      <c r="AD2" s="126"/>
+      <c r="AE2" s="126"/>
+      <c r="AF2" s="127"/>
+      <c r="AG2" s="159">
         <f ca="1">IF(INDIRECT("変更履歴!AG2")&lt;&gt;"",INDIRECT("変更履歴!AG2"),"")</f>
-        <v>44848</v>
-      </c>
-      <c r="AH2" s="152"/>
-      <c r="AI2" s="153"/>
+        <v>45464</v>
+      </c>
+      <c r="AH2" s="160"/>
+      <c r="AI2" s="161"/>
       <c r="AJ2" s="6"/>
       <c r="AN2" s="7"/>
       <c r="AO2" s="6"/>
@@ -16543,52 +16611,52 @@
       <c r="AW2" s="6"/>
     </row>
     <row r="3" spans="1:50" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="116" t="s">
+      <c r="A3" s="96" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="117"/>
-      <c r="C3" s="117"/>
-      <c r="D3" s="118"/>
-      <c r="E3" s="119" t="str">
+      <c r="B3" s="97"/>
+      <c r="C3" s="97"/>
+      <c r="D3" s="98"/>
+      <c r="E3" s="99" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E3")&lt;&gt;"",INDIRECT("変更履歴!E3"),"")</f>
         <v/>
       </c>
-      <c r="F3" s="120"/>
-      <c r="G3" s="120"/>
-      <c r="H3" s="120"/>
-      <c r="I3" s="120"/>
-      <c r="J3" s="120"/>
-      <c r="K3" s="120"/>
-      <c r="L3" s="120"/>
-      <c r="M3" s="120"/>
-      <c r="N3" s="121"/>
-      <c r="O3" s="160"/>
-      <c r="P3" s="161"/>
-      <c r="Q3" s="161"/>
-      <c r="R3" s="162"/>
-      <c r="S3" s="169"/>
-      <c r="T3" s="170"/>
-      <c r="U3" s="170"/>
-      <c r="V3" s="170"/>
-      <c r="W3" s="170"/>
-      <c r="X3" s="170"/>
-      <c r="Y3" s="170"/>
-      <c r="Z3" s="171"/>
-      <c r="AA3" s="116"/>
-      <c r="AB3" s="118"/>
-      <c r="AC3" s="145" t="str">
+      <c r="F3" s="100"/>
+      <c r="G3" s="100"/>
+      <c r="H3" s="100"/>
+      <c r="I3" s="100"/>
+      <c r="J3" s="100"/>
+      <c r="K3" s="100"/>
+      <c r="L3" s="100"/>
+      <c r="M3" s="100"/>
+      <c r="N3" s="101"/>
+      <c r="O3" s="180"/>
+      <c r="P3" s="181"/>
+      <c r="Q3" s="181"/>
+      <c r="R3" s="182"/>
+      <c r="S3" s="171"/>
+      <c r="T3" s="172"/>
+      <c r="U3" s="172"/>
+      <c r="V3" s="172"/>
+      <c r="W3" s="172"/>
+      <c r="X3" s="172"/>
+      <c r="Y3" s="172"/>
+      <c r="Z3" s="173"/>
+      <c r="AA3" s="96"/>
+      <c r="AB3" s="98"/>
+      <c r="AC3" s="125" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC3")&lt;&gt;"",INDIRECT("変更履歴!AC3"),"")</f>
         <v/>
       </c>
-      <c r="AD3" s="146"/>
-      <c r="AE3" s="146"/>
-      <c r="AF3" s="147"/>
-      <c r="AG3" s="151" t="str">
+      <c r="AD3" s="126"/>
+      <c r="AE3" s="126"/>
+      <c r="AF3" s="127"/>
+      <c r="AG3" s="159" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AG3")&lt;&gt;"",INDIRECT("変更履歴!AG3"),"")</f>
         <v/>
       </c>
-      <c r="AH3" s="152"/>
-      <c r="AI3" s="153"/>
+      <c r="AH3" s="160"/>
+      <c r="AI3" s="161"/>
       <c r="AJ3" s="9"/>
       <c r="AK3" s="1"/>
       <c r="AL3" s="1"/>
@@ -16670,537 +16738,537 @@
       <c r="AW9" s="6"/>
       <c r="AX9" s="6"/>
     </row>
-    <row r="10" spans="1:50" s="172" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C10" s="182" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="11" spans="1:50" s="172" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="12" spans="1:50" s="172" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="D12" s="172" t="s">
+    <row r="10" spans="1:50" s="77" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C10" s="87" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="11" spans="1:50" s="77" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="12" spans="1:50" s="77" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="D12" s="77" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="13" spans="1:50" s="172" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="14" spans="1:50" s="172" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="D14" s="173" t="s">
+    <row r="13" spans="1:50" s="77" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="14" spans="1:50" s="77" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="D14" s="78" t="s">
         <v>208</v>
       </c>
-      <c r="E14" s="174" t="s">
+      <c r="E14" s="79" t="s">
         <v>209</v>
       </c>
-      <c r="F14" s="175"/>
-      <c r="G14" s="175"/>
-      <c r="H14" s="175"/>
-      <c r="I14" s="174" t="s">
+      <c r="F14" s="80"/>
+      <c r="G14" s="80"/>
+      <c r="H14" s="80"/>
+      <c r="I14" s="79" t="s">
         <v>210</v>
       </c>
-      <c r="J14" s="176"/>
-      <c r="K14" s="175"/>
-      <c r="L14" s="175"/>
-      <c r="M14" s="175"/>
-      <c r="N14" s="175"/>
-      <c r="O14" s="175"/>
-      <c r="P14" s="175"/>
-      <c r="Q14" s="175"/>
-      <c r="R14" s="175"/>
-      <c r="S14" s="175"/>
-      <c r="T14" s="176"/>
-      <c r="U14" s="177"/>
-    </row>
-    <row r="15" spans="1:50" s="172" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="D15" s="178">
+      <c r="J14" s="81"/>
+      <c r="K14" s="80"/>
+      <c r="L14" s="80"/>
+      <c r="M14" s="80"/>
+      <c r="N14" s="80"/>
+      <c r="O14" s="80"/>
+      <c r="P14" s="80"/>
+      <c r="Q14" s="80"/>
+      <c r="R14" s="80"/>
+      <c r="S14" s="80"/>
+      <c r="T14" s="81"/>
+      <c r="U14" s="82"/>
+    </row>
+    <row r="15" spans="1:50" s="77" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="D15" s="83">
         <v>1</v>
       </c>
-      <c r="E15" s="178" t="s">
+      <c r="E15" s="83" t="s">
         <v>211</v>
       </c>
-      <c r="F15" s="179"/>
-      <c r="G15" s="179"/>
-      <c r="H15" s="179"/>
-      <c r="I15" s="180" t="s">
+      <c r="F15" s="84"/>
+      <c r="G15" s="84"/>
+      <c r="H15" s="84"/>
+      <c r="I15" s="85" t="s">
         <v>212</v>
       </c>
-      <c r="J15" s="181"/>
-      <c r="K15" s="179"/>
-      <c r="L15" s="179"/>
-      <c r="M15" s="179"/>
-      <c r="N15" s="179"/>
-      <c r="O15" s="179"/>
-      <c r="P15" s="179"/>
-      <c r="Q15" s="179"/>
-      <c r="R15" s="179"/>
-      <c r="S15" s="179"/>
-      <c r="T15" s="181"/>
-      <c r="U15" s="177"/>
-    </row>
-    <row r="16" spans="1:50" s="172" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="D16" s="178">
+      <c r="J15" s="86"/>
+      <c r="K15" s="84"/>
+      <c r="L15" s="84"/>
+      <c r="M15" s="84"/>
+      <c r="N15" s="84"/>
+      <c r="O15" s="84"/>
+      <c r="P15" s="84"/>
+      <c r="Q15" s="84"/>
+      <c r="R15" s="84"/>
+      <c r="S15" s="84"/>
+      <c r="T15" s="86"/>
+      <c r="U15" s="82"/>
+    </row>
+    <row r="16" spans="1:50" s="77" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="D16" s="83">
         <v>2</v>
       </c>
-      <c r="E16" s="178" t="s">
+      <c r="E16" s="83" t="s">
         <v>213</v>
       </c>
-      <c r="F16" s="179"/>
-      <c r="G16" s="179"/>
-      <c r="H16" s="179"/>
-      <c r="I16" s="180" t="s">
+      <c r="F16" s="84"/>
+      <c r="G16" s="84"/>
+      <c r="H16" s="84"/>
+      <c r="I16" s="85" t="s">
         <v>214</v>
       </c>
-      <c r="J16" s="181"/>
-      <c r="K16" s="179"/>
-      <c r="L16" s="179"/>
-      <c r="M16" s="179"/>
-      <c r="N16" s="179"/>
-      <c r="O16" s="179"/>
-      <c r="P16" s="179"/>
-      <c r="Q16" s="179"/>
-      <c r="R16" s="179"/>
-      <c r="S16" s="179"/>
-      <c r="T16" s="181"/>
-      <c r="U16" s="177"/>
-    </row>
-    <row r="17" spans="4:21" s="172" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="D17" s="178">
+      <c r="J16" s="86"/>
+      <c r="K16" s="84"/>
+      <c r="L16" s="84"/>
+      <c r="M16" s="84"/>
+      <c r="N16" s="84"/>
+      <c r="O16" s="84"/>
+      <c r="P16" s="84"/>
+      <c r="Q16" s="84"/>
+      <c r="R16" s="84"/>
+      <c r="S16" s="84"/>
+      <c r="T16" s="86"/>
+      <c r="U16" s="82"/>
+    </row>
+    <row r="17" spans="4:21" s="77" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="D17" s="83">
         <v>3</v>
       </c>
-      <c r="E17" s="178" t="s">
+      <c r="E17" s="83" t="s">
         <v>215</v>
       </c>
-      <c r="F17" s="179"/>
-      <c r="G17" s="179"/>
-      <c r="H17" s="179"/>
-      <c r="I17" s="180" t="s">
+      <c r="F17" s="84"/>
+      <c r="G17" s="84"/>
+      <c r="H17" s="84"/>
+      <c r="I17" s="85" t="s">
         <v>216</v>
       </c>
-      <c r="J17" s="181"/>
-      <c r="K17" s="179"/>
-      <c r="L17" s="179"/>
-      <c r="M17" s="179"/>
-      <c r="N17" s="179"/>
-      <c r="O17" s="179"/>
-      <c r="P17" s="179"/>
-      <c r="Q17" s="179"/>
-      <c r="R17" s="179"/>
-      <c r="S17" s="179"/>
-      <c r="T17" s="181"/>
-      <c r="U17" s="177"/>
-    </row>
-    <row r="18" spans="4:21" s="172" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="D18" s="178">
+      <c r="J17" s="86"/>
+      <c r="K17" s="84"/>
+      <c r="L17" s="84"/>
+      <c r="M17" s="84"/>
+      <c r="N17" s="84"/>
+      <c r="O17" s="84"/>
+      <c r="P17" s="84"/>
+      <c r="Q17" s="84"/>
+      <c r="R17" s="84"/>
+      <c r="S17" s="84"/>
+      <c r="T17" s="86"/>
+      <c r="U17" s="82"/>
+    </row>
+    <row r="18" spans="4:21" s="77" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="D18" s="83">
         <v>4</v>
       </c>
-      <c r="E18" s="178" t="s">
+      <c r="E18" s="83" t="s">
         <v>217</v>
       </c>
-      <c r="F18" s="179"/>
-      <c r="G18" s="179"/>
-      <c r="H18" s="179"/>
-      <c r="I18" s="180" t="s">
+      <c r="F18" s="84"/>
+      <c r="G18" s="84"/>
+      <c r="H18" s="84"/>
+      <c r="I18" s="85" t="s">
         <v>218</v>
       </c>
-      <c r="J18" s="181"/>
-      <c r="K18" s="179"/>
-      <c r="L18" s="179"/>
-      <c r="M18" s="179"/>
-      <c r="N18" s="179"/>
-      <c r="O18" s="179"/>
-      <c r="P18" s="179"/>
-      <c r="Q18" s="179"/>
-      <c r="R18" s="179"/>
-      <c r="S18" s="179"/>
-      <c r="T18" s="181"/>
-      <c r="U18" s="177"/>
-    </row>
-    <row r="19" spans="4:21" s="172" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="D19" s="178">
+      <c r="J18" s="86"/>
+      <c r="K18" s="84"/>
+      <c r="L18" s="84"/>
+      <c r="M18" s="84"/>
+      <c r="N18" s="84"/>
+      <c r="O18" s="84"/>
+      <c r="P18" s="84"/>
+      <c r="Q18" s="84"/>
+      <c r="R18" s="84"/>
+      <c r="S18" s="84"/>
+      <c r="T18" s="86"/>
+      <c r="U18" s="82"/>
+    </row>
+    <row r="19" spans="4:21" s="77" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="D19" s="83">
         <v>5</v>
       </c>
-      <c r="E19" s="178" t="s">
+      <c r="E19" s="83" t="s">
         <v>219</v>
       </c>
-      <c r="F19" s="179"/>
-      <c r="G19" s="179"/>
-      <c r="H19" s="179"/>
-      <c r="I19" s="180" t="s">
+      <c r="F19" s="84"/>
+      <c r="G19" s="84"/>
+      <c r="H19" s="84"/>
+      <c r="I19" s="85" t="s">
         <v>220</v>
       </c>
-      <c r="J19" s="181"/>
-      <c r="K19" s="179"/>
-      <c r="L19" s="179"/>
-      <c r="M19" s="179"/>
-      <c r="N19" s="179"/>
-      <c r="O19" s="179"/>
-      <c r="P19" s="179"/>
-      <c r="Q19" s="179"/>
-      <c r="R19" s="179"/>
-      <c r="S19" s="179"/>
-      <c r="T19" s="181"/>
-      <c r="U19" s="177"/>
-    </row>
-    <row r="20" spans="4:21" s="172" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="D20" s="178">
+      <c r="J19" s="86"/>
+      <c r="K19" s="84"/>
+      <c r="L19" s="84"/>
+      <c r="M19" s="84"/>
+      <c r="N19" s="84"/>
+      <c r="O19" s="84"/>
+      <c r="P19" s="84"/>
+      <c r="Q19" s="84"/>
+      <c r="R19" s="84"/>
+      <c r="S19" s="84"/>
+      <c r="T19" s="86"/>
+      <c r="U19" s="82"/>
+    </row>
+    <row r="20" spans="4:21" s="77" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="D20" s="83">
         <v>6</v>
       </c>
-      <c r="E20" s="178" t="s">
+      <c r="E20" s="83" t="s">
         <v>221</v>
       </c>
-      <c r="F20" s="179"/>
-      <c r="G20" s="179"/>
-      <c r="H20" s="179"/>
-      <c r="I20" s="180" t="s">
+      <c r="F20" s="84"/>
+      <c r="G20" s="84"/>
+      <c r="H20" s="84"/>
+      <c r="I20" s="85" t="s">
         <v>222</v>
       </c>
-      <c r="J20" s="181"/>
-      <c r="K20" s="179"/>
-      <c r="L20" s="179"/>
-      <c r="M20" s="179"/>
-      <c r="N20" s="179"/>
-      <c r="O20" s="179"/>
-      <c r="P20" s="179"/>
-      <c r="Q20" s="179"/>
-      <c r="R20" s="179"/>
-      <c r="S20" s="179"/>
-      <c r="T20" s="181"/>
-      <c r="U20" s="177"/>
-    </row>
-    <row r="21" spans="4:21" s="172" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="D21" s="178">
+      <c r="J20" s="86"/>
+      <c r="K20" s="84"/>
+      <c r="L20" s="84"/>
+      <c r="M20" s="84"/>
+      <c r="N20" s="84"/>
+      <c r="O20" s="84"/>
+      <c r="P20" s="84"/>
+      <c r="Q20" s="84"/>
+      <c r="R20" s="84"/>
+      <c r="S20" s="84"/>
+      <c r="T20" s="86"/>
+      <c r="U20" s="82"/>
+    </row>
+    <row r="21" spans="4:21" s="77" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="D21" s="83">
         <v>7</v>
       </c>
-      <c r="E21" s="178" t="s">
+      <c r="E21" s="183" t="s">
+        <v>250</v>
+      </c>
+      <c r="F21" s="84"/>
+      <c r="G21" s="84"/>
+      <c r="H21" s="84"/>
+      <c r="I21" s="85" t="s">
         <v>223</v>
       </c>
-      <c r="F21" s="179"/>
-      <c r="G21" s="179"/>
-      <c r="H21" s="179"/>
-      <c r="I21" s="180" t="s">
+      <c r="J21" s="86"/>
+      <c r="K21" s="84"/>
+      <c r="L21" s="84"/>
+      <c r="M21" s="84"/>
+      <c r="N21" s="84"/>
+      <c r="O21" s="84"/>
+      <c r="P21" s="84"/>
+      <c r="Q21" s="84"/>
+      <c r="R21" s="84"/>
+      <c r="S21" s="84"/>
+      <c r="T21" s="86"/>
+      <c r="U21" s="82"/>
+    </row>
+    <row r="22" spans="4:21" s="77" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="D22" s="83">
+        <v>8</v>
+      </c>
+      <c r="E22" s="83" t="s">
         <v>224</v>
       </c>
-      <c r="J21" s="181"/>
-      <c r="K21" s="179"/>
-      <c r="L21" s="179"/>
-      <c r="M21" s="179"/>
-      <c r="N21" s="179"/>
-      <c r="O21" s="179"/>
-      <c r="P21" s="179"/>
-      <c r="Q21" s="179"/>
-      <c r="R21" s="179"/>
-      <c r="S21" s="179"/>
-      <c r="T21" s="181"/>
-      <c r="U21" s="177"/>
-    </row>
-    <row r="22" spans="4:21" s="172" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="D22" s="178">
-        <v>8</v>
-      </c>
-      <c r="E22" s="178" t="s">
+      <c r="F22" s="84"/>
+      <c r="G22" s="84"/>
+      <c r="H22" s="84"/>
+      <c r="I22" s="85" t="s">
         <v>225</v>
       </c>
-      <c r="F22" s="179"/>
-      <c r="G22" s="179"/>
-      <c r="H22" s="179"/>
-      <c r="I22" s="180" t="s">
+      <c r="J22" s="86"/>
+      <c r="K22" s="84"/>
+      <c r="L22" s="84"/>
+      <c r="M22" s="84"/>
+      <c r="N22" s="84"/>
+      <c r="O22" s="84"/>
+      <c r="P22" s="84"/>
+      <c r="Q22" s="84"/>
+      <c r="R22" s="84"/>
+      <c r="S22" s="84"/>
+      <c r="T22" s="86"/>
+      <c r="U22" s="82"/>
+    </row>
+    <row r="23" spans="4:21" s="77" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="D23" s="83">
+        <v>9</v>
+      </c>
+      <c r="E23" s="83" t="s">
         <v>226</v>
       </c>
-      <c r="J22" s="181"/>
-      <c r="K22" s="179"/>
-      <c r="L22" s="179"/>
-      <c r="M22" s="179"/>
-      <c r="N22" s="179"/>
-      <c r="O22" s="179"/>
-      <c r="P22" s="179"/>
-      <c r="Q22" s="179"/>
-      <c r="R22" s="179"/>
-      <c r="S22" s="179"/>
-      <c r="T22" s="181"/>
-      <c r="U22" s="177"/>
-    </row>
-    <row r="23" spans="4:21" s="172" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="D23" s="178">
-        <v>9</v>
-      </c>
-      <c r="E23" s="178" t="s">
+      <c r="F23" s="84"/>
+      <c r="G23" s="84"/>
+      <c r="H23" s="84"/>
+      <c r="I23" s="85" t="s">
         <v>227</v>
       </c>
-      <c r="F23" s="179"/>
-      <c r="G23" s="179"/>
-      <c r="H23" s="179"/>
-      <c r="I23" s="180" t="s">
+      <c r="J23" s="86"/>
+      <c r="K23" s="84"/>
+      <c r="L23" s="84"/>
+      <c r="M23" s="84"/>
+      <c r="N23" s="84"/>
+      <c r="O23" s="84"/>
+      <c r="P23" s="84"/>
+      <c r="Q23" s="84"/>
+      <c r="R23" s="84"/>
+      <c r="S23" s="84"/>
+      <c r="T23" s="86"/>
+      <c r="U23" s="82"/>
+    </row>
+    <row r="24" spans="4:21" s="77" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="D24" s="83">
+        <v>10</v>
+      </c>
+      <c r="E24" s="83" t="s">
         <v>228</v>
       </c>
-      <c r="J23" s="181"/>
-      <c r="K23" s="179"/>
-      <c r="L23" s="179"/>
-      <c r="M23" s="179"/>
-      <c r="N23" s="179"/>
-      <c r="O23" s="179"/>
-      <c r="P23" s="179"/>
-      <c r="Q23" s="179"/>
-      <c r="R23" s="179"/>
-      <c r="S23" s="179"/>
-      <c r="T23" s="181"/>
-      <c r="U23" s="177"/>
-    </row>
-    <row r="24" spans="4:21" s="172" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="D24" s="178">
-        <v>10</v>
-      </c>
-      <c r="E24" s="178" t="s">
+      <c r="F24" s="84"/>
+      <c r="G24" s="84"/>
+      <c r="H24" s="84"/>
+      <c r="I24" s="85" t="s">
         <v>229</v>
       </c>
-      <c r="F24" s="179"/>
-      <c r="G24" s="179"/>
-      <c r="H24" s="179"/>
-      <c r="I24" s="180" t="s">
+      <c r="J24" s="86"/>
+      <c r="K24" s="84"/>
+      <c r="L24" s="84"/>
+      <c r="M24" s="84"/>
+      <c r="N24" s="84"/>
+      <c r="O24" s="84"/>
+      <c r="P24" s="84"/>
+      <c r="Q24" s="84"/>
+      <c r="R24" s="84"/>
+      <c r="S24" s="84"/>
+      <c r="T24" s="86"/>
+      <c r="U24" s="82"/>
+    </row>
+    <row r="25" spans="4:21" s="77" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="D25" s="83">
+        <v>11</v>
+      </c>
+      <c r="E25" s="83" t="s">
         <v>230</v>
       </c>
-      <c r="J24" s="181"/>
-      <c r="K24" s="179"/>
-      <c r="L24" s="179"/>
-      <c r="M24" s="179"/>
-      <c r="N24" s="179"/>
-      <c r="O24" s="179"/>
-      <c r="P24" s="179"/>
-      <c r="Q24" s="179"/>
-      <c r="R24" s="179"/>
-      <c r="S24" s="179"/>
-      <c r="T24" s="181"/>
-      <c r="U24" s="177"/>
-    </row>
-    <row r="25" spans="4:21" s="172" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="D25" s="178">
-        <v>11</v>
-      </c>
-      <c r="E25" s="178" t="s">
+      <c r="F25" s="84"/>
+      <c r="G25" s="84"/>
+      <c r="H25" s="84"/>
+      <c r="I25" s="85" t="s">
         <v>231</v>
       </c>
-      <c r="F25" s="179"/>
-      <c r="G25" s="179"/>
-      <c r="H25" s="179"/>
-      <c r="I25" s="180" t="s">
+      <c r="J25" s="86"/>
+      <c r="K25" s="84"/>
+      <c r="L25" s="84"/>
+      <c r="M25" s="84"/>
+      <c r="N25" s="84"/>
+      <c r="O25" s="84"/>
+      <c r="P25" s="84"/>
+      <c r="Q25" s="84"/>
+      <c r="R25" s="84"/>
+      <c r="S25" s="84"/>
+      <c r="T25" s="86"/>
+      <c r="U25" s="82"/>
+    </row>
+    <row r="26" spans="4:21" s="77" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="D26" s="83">
+        <v>12</v>
+      </c>
+      <c r="E26" s="83" t="s">
         <v>232</v>
       </c>
-      <c r="J25" s="181"/>
-      <c r="K25" s="179"/>
-      <c r="L25" s="179"/>
-      <c r="M25" s="179"/>
-      <c r="N25" s="179"/>
-      <c r="O25" s="179"/>
-      <c r="P25" s="179"/>
-      <c r="Q25" s="179"/>
-      <c r="R25" s="179"/>
-      <c r="S25" s="179"/>
-      <c r="T25" s="181"/>
-      <c r="U25" s="177"/>
-    </row>
-    <row r="26" spans="4:21" s="172" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="D26" s="178">
-        <v>12</v>
-      </c>
-      <c r="E26" s="178" t="s">
+      <c r="F26" s="84"/>
+      <c r="G26" s="84"/>
+      <c r="H26" s="84"/>
+      <c r="I26" s="85" t="s">
         <v>233</v>
       </c>
-      <c r="F26" s="179"/>
-      <c r="G26" s="179"/>
-      <c r="H26" s="179"/>
-      <c r="I26" s="180" t="s">
+      <c r="J26" s="86"/>
+      <c r="K26" s="84"/>
+      <c r="L26" s="84"/>
+      <c r="M26" s="84"/>
+      <c r="N26" s="84"/>
+      <c r="O26" s="84"/>
+      <c r="P26" s="84"/>
+      <c r="Q26" s="84"/>
+      <c r="R26" s="84"/>
+      <c r="S26" s="84"/>
+      <c r="T26" s="86"/>
+      <c r="U26" s="82"/>
+    </row>
+    <row r="27" spans="4:21" s="77" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="D27" s="83">
+        <v>13</v>
+      </c>
+      <c r="E27" s="83" t="s">
         <v>234</v>
       </c>
-      <c r="J26" s="181"/>
-      <c r="K26" s="179"/>
-      <c r="L26" s="179"/>
-      <c r="M26" s="179"/>
-      <c r="N26" s="179"/>
-      <c r="O26" s="179"/>
-      <c r="P26" s="179"/>
-      <c r="Q26" s="179"/>
-      <c r="R26" s="179"/>
-      <c r="S26" s="179"/>
-      <c r="T26" s="181"/>
-      <c r="U26" s="177"/>
-    </row>
-    <row r="27" spans="4:21" s="172" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="D27" s="178">
-        <v>13</v>
-      </c>
-      <c r="E27" s="178" t="s">
+      <c r="F27" s="84"/>
+      <c r="G27" s="84"/>
+      <c r="H27" s="84"/>
+      <c r="I27" s="85" t="s">
         <v>235</v>
       </c>
-      <c r="F27" s="179"/>
-      <c r="G27" s="179"/>
-      <c r="H27" s="179"/>
-      <c r="I27" s="180" t="s">
+      <c r="J27" s="86"/>
+      <c r="K27" s="84"/>
+      <c r="L27" s="84"/>
+      <c r="M27" s="84"/>
+      <c r="N27" s="84"/>
+      <c r="O27" s="84"/>
+      <c r="P27" s="84"/>
+      <c r="Q27" s="84"/>
+      <c r="R27" s="84"/>
+      <c r="S27" s="84"/>
+      <c r="T27" s="86"/>
+      <c r="U27" s="82"/>
+    </row>
+    <row r="28" spans="4:21" s="77" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="D28" s="83">
+        <v>14</v>
+      </c>
+      <c r="E28" s="83" t="s">
         <v>236</v>
       </c>
-      <c r="J27" s="181"/>
-      <c r="K27" s="179"/>
-      <c r="L27" s="179"/>
-      <c r="M27" s="179"/>
-      <c r="N27" s="179"/>
-      <c r="O27" s="179"/>
-      <c r="P27" s="179"/>
-      <c r="Q27" s="179"/>
-      <c r="R27" s="179"/>
-      <c r="S27" s="179"/>
-      <c r="T27" s="181"/>
-      <c r="U27" s="177"/>
-    </row>
-    <row r="28" spans="4:21" s="172" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="D28" s="178">
-        <v>14</v>
-      </c>
-      <c r="E28" s="178" t="s">
+      <c r="F28" s="84"/>
+      <c r="G28" s="84"/>
+      <c r="H28" s="84"/>
+      <c r="I28" s="85" t="s">
         <v>237</v>
       </c>
-      <c r="F28" s="179"/>
-      <c r="G28" s="179"/>
-      <c r="H28" s="179"/>
-      <c r="I28" s="180" t="s">
+      <c r="J28" s="86"/>
+      <c r="K28" s="84"/>
+      <c r="L28" s="84"/>
+      <c r="M28" s="84"/>
+      <c r="N28" s="84"/>
+      <c r="O28" s="84"/>
+      <c r="P28" s="84"/>
+      <c r="Q28" s="84"/>
+      <c r="R28" s="84"/>
+      <c r="S28" s="84"/>
+      <c r="T28" s="86"/>
+      <c r="U28" s="82"/>
+    </row>
+    <row r="29" spans="4:21" s="77" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="D29" s="83">
+        <v>15</v>
+      </c>
+      <c r="E29" s="83" t="s">
         <v>238</v>
       </c>
-      <c r="J28" s="181"/>
-      <c r="K28" s="179"/>
-      <c r="L28" s="179"/>
-      <c r="M28" s="179"/>
-      <c r="N28" s="179"/>
-      <c r="O28" s="179"/>
-      <c r="P28" s="179"/>
-      <c r="Q28" s="179"/>
-      <c r="R28" s="179"/>
-      <c r="S28" s="179"/>
-      <c r="T28" s="181"/>
-      <c r="U28" s="177"/>
-    </row>
-    <row r="29" spans="4:21" s="172" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="D29" s="178">
-        <v>15</v>
-      </c>
-      <c r="E29" s="178" t="s">
+      <c r="F29" s="84"/>
+      <c r="G29" s="84"/>
+      <c r="H29" s="84"/>
+      <c r="I29" s="85" t="s">
         <v>239</v>
       </c>
-      <c r="F29" s="179"/>
-      <c r="G29" s="179"/>
-      <c r="H29" s="179"/>
-      <c r="I29" s="180" t="s">
+      <c r="J29" s="86"/>
+      <c r="K29" s="84"/>
+      <c r="L29" s="84"/>
+      <c r="M29" s="84"/>
+      <c r="N29" s="84"/>
+      <c r="O29" s="84"/>
+      <c r="P29" s="84"/>
+      <c r="Q29" s="84"/>
+      <c r="R29" s="84"/>
+      <c r="S29" s="84"/>
+      <c r="T29" s="86"/>
+      <c r="U29" s="82"/>
+    </row>
+    <row r="30" spans="4:21" s="77" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="D30" s="83">
+        <v>16</v>
+      </c>
+      <c r="E30" s="83" t="s">
         <v>240</v>
       </c>
-      <c r="J29" s="181"/>
-      <c r="K29" s="179"/>
-      <c r="L29" s="179"/>
-      <c r="M29" s="179"/>
-      <c r="N29" s="179"/>
-      <c r="O29" s="179"/>
-      <c r="P29" s="179"/>
-      <c r="Q29" s="179"/>
-      <c r="R29" s="179"/>
-      <c r="S29" s="179"/>
-      <c r="T29" s="181"/>
-      <c r="U29" s="177"/>
-    </row>
-    <row r="30" spans="4:21" s="172" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="D30" s="178">
-        <v>16</v>
-      </c>
-      <c r="E30" s="178" t="s">
+      <c r="F30" s="84"/>
+      <c r="G30" s="84"/>
+      <c r="H30" s="84"/>
+      <c r="I30" s="85" t="s">
         <v>241</v>
       </c>
-      <c r="F30" s="179"/>
-      <c r="G30" s="179"/>
-      <c r="H30" s="179"/>
-      <c r="I30" s="180" t="s">
+      <c r="J30" s="86"/>
+      <c r="K30" s="84"/>
+      <c r="L30" s="84"/>
+      <c r="M30" s="84"/>
+      <c r="N30" s="84"/>
+      <c r="O30" s="84"/>
+      <c r="P30" s="84"/>
+      <c r="Q30" s="84"/>
+      <c r="R30" s="84"/>
+      <c r="S30" s="84"/>
+      <c r="T30" s="86"/>
+      <c r="U30" s="82"/>
+    </row>
+    <row r="31" spans="4:21" s="77" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="D31" s="83">
+        <v>17</v>
+      </c>
+      <c r="E31" s="83" t="s">
         <v>242</v>
       </c>
-      <c r="J30" s="181"/>
-      <c r="K30" s="179"/>
-      <c r="L30" s="179"/>
-      <c r="M30" s="179"/>
-      <c r="N30" s="179"/>
-      <c r="O30" s="179"/>
-      <c r="P30" s="179"/>
-      <c r="Q30" s="179"/>
-      <c r="R30" s="179"/>
-      <c r="S30" s="179"/>
-      <c r="T30" s="181"/>
-      <c r="U30" s="177"/>
-    </row>
-    <row r="31" spans="4:21" s="172" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="D31" s="178">
-        <v>17</v>
-      </c>
-      <c r="E31" s="178" t="s">
+      <c r="F31" s="84"/>
+      <c r="G31" s="84"/>
+      <c r="H31" s="84"/>
+      <c r="I31" s="85" t="s">
         <v>243</v>
       </c>
-      <c r="F31" s="179"/>
-      <c r="G31" s="179"/>
-      <c r="H31" s="179"/>
-      <c r="I31" s="180" t="s">
+      <c r="J31" s="86"/>
+      <c r="K31" s="84"/>
+      <c r="L31" s="84"/>
+      <c r="M31" s="84"/>
+      <c r="N31" s="84"/>
+      <c r="O31" s="84"/>
+      <c r="P31" s="84"/>
+      <c r="Q31" s="84"/>
+      <c r="R31" s="84"/>
+      <c r="S31" s="84"/>
+      <c r="T31" s="86"/>
+      <c r="U31" s="82"/>
+    </row>
+    <row r="32" spans="4:21" s="77" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="D32" s="83">
+        <v>18</v>
+      </c>
+      <c r="E32" s="83" t="s">
         <v>244</v>
       </c>
-      <c r="J31" s="181"/>
-      <c r="K31" s="179"/>
-      <c r="L31" s="179"/>
-      <c r="M31" s="179"/>
-      <c r="N31" s="179"/>
-      <c r="O31" s="179"/>
-      <c r="P31" s="179"/>
-      <c r="Q31" s="179"/>
-      <c r="R31" s="179"/>
-      <c r="S31" s="179"/>
-      <c r="T31" s="181"/>
-      <c r="U31" s="177"/>
-    </row>
-    <row r="32" spans="4:21" s="172" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="D32" s="178">
-        <v>18</v>
-      </c>
-      <c r="E32" s="178" t="s">
+      <c r="F32" s="84"/>
+      <c r="G32" s="84"/>
+      <c r="H32" s="84"/>
+      <c r="I32" s="85" t="s">
         <v>245</v>
       </c>
-      <c r="F32" s="179"/>
-      <c r="G32" s="179"/>
-      <c r="H32" s="179"/>
-      <c r="I32" s="180" t="s">
+      <c r="J32" s="86"/>
+      <c r="K32" s="84"/>
+      <c r="L32" s="84"/>
+      <c r="M32" s="84"/>
+      <c r="N32" s="84"/>
+      <c r="O32" s="84"/>
+      <c r="P32" s="84"/>
+      <c r="Q32" s="84"/>
+      <c r="R32" s="84"/>
+      <c r="S32" s="84"/>
+      <c r="T32" s="86"/>
+      <c r="U32" s="82"/>
+    </row>
+    <row r="33" spans="3:21" s="77" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="D33" s="83">
+        <v>19</v>
+      </c>
+      <c r="E33" s="83" t="s">
         <v>246</v>
       </c>
-      <c r="J32" s="181"/>
-      <c r="K32" s="179"/>
-      <c r="L32" s="179"/>
-      <c r="M32" s="179"/>
-      <c r="N32" s="179"/>
-      <c r="O32" s="179"/>
-      <c r="P32" s="179"/>
-      <c r="Q32" s="179"/>
-      <c r="R32" s="179"/>
-      <c r="S32" s="179"/>
-      <c r="T32" s="181"/>
-      <c r="U32" s="177"/>
-    </row>
-    <row r="33" spans="3:21" s="172" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="D33" s="178">
-        <v>19</v>
-      </c>
-      <c r="E33" s="178" t="s">
+      <c r="F33" s="84"/>
+      <c r="G33" s="84"/>
+      <c r="H33" s="84"/>
+      <c r="I33" s="85" t="s">
         <v>247</v>
       </c>
-      <c r="F33" s="179"/>
-      <c r="G33" s="179"/>
-      <c r="H33" s="179"/>
-      <c r="I33" s="180" t="s">
-        <v>248</v>
-      </c>
-      <c r="J33" s="181"/>
-      <c r="K33" s="179"/>
-      <c r="L33" s="179"/>
-      <c r="M33" s="179"/>
-      <c r="N33" s="179"/>
-      <c r="O33" s="179"/>
-      <c r="P33" s="179"/>
-      <c r="Q33" s="179"/>
-      <c r="R33" s="179"/>
-      <c r="S33" s="179"/>
-      <c r="T33" s="181"/>
-      <c r="U33" s="177"/>
+      <c r="J33" s="86"/>
+      <c r="K33" s="84"/>
+      <c r="L33" s="84"/>
+      <c r="M33" s="84"/>
+      <c r="N33" s="84"/>
+      <c r="O33" s="84"/>
+      <c r="P33" s="84"/>
+      <c r="Q33" s="84"/>
+      <c r="R33" s="84"/>
+      <c r="S33" s="84"/>
+      <c r="T33" s="86"/>
+      <c r="U33" s="82"/>
     </row>
     <row r="34" spans="3:21" x14ac:dyDescent="0.15">
       <c r="D34" s="38"/>
@@ -17211,6 +17279,13 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="O1:R3"/>
+    <mergeCell ref="AA1:AB1"/>
+    <mergeCell ref="AA2:AB2"/>
+    <mergeCell ref="AA3:AB3"/>
     <mergeCell ref="AC3:AF3"/>
     <mergeCell ref="AG3:AI3"/>
     <mergeCell ref="E1:N1"/>
@@ -17221,13 +17296,6 @@
     <mergeCell ref="AC2:AF2"/>
     <mergeCell ref="AG2:AI2"/>
     <mergeCell ref="S1:Z3"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="O1:R3"/>
-    <mergeCell ref="AA1:AB1"/>
-    <mergeCell ref="AA2:AB2"/>
-    <mergeCell ref="AA3:AB3"/>
   </mergeCells>
   <phoneticPr fontId="10"/>
   <hyperlinks>
@@ -17273,59 +17341,59 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:49" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="116" t="s">
+      <c r="A1" s="96" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="117"/>
-      <c r="C1" s="117"/>
-      <c r="D1" s="118"/>
-      <c r="E1" s="119" t="str">
+      <c r="B1" s="97"/>
+      <c r="C1" s="97"/>
+      <c r="D1" s="98"/>
+      <c r="E1" s="99" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E1")&lt;&gt;"",INDIRECT("変更履歴!E1"),"")</f>
         <v/>
       </c>
-      <c r="F1" s="120"/>
-      <c r="G1" s="120"/>
-      <c r="H1" s="120"/>
-      <c r="I1" s="120"/>
-      <c r="J1" s="120"/>
-      <c r="K1" s="120"/>
-      <c r="L1" s="120"/>
-      <c r="M1" s="120"/>
-      <c r="N1" s="121"/>
-      <c r="O1" s="154" t="s">
+      <c r="F1" s="100"/>
+      <c r="G1" s="100"/>
+      <c r="H1" s="100"/>
+      <c r="I1" s="100"/>
+      <c r="J1" s="100"/>
+      <c r="K1" s="100"/>
+      <c r="L1" s="100"/>
+      <c r="M1" s="100"/>
+      <c r="N1" s="101"/>
+      <c r="O1" s="174" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="155"/>
-      <c r="Q1" s="155"/>
-      <c r="R1" s="156"/>
-      <c r="S1" s="163" t="str">
+      <c r="P1" s="175"/>
+      <c r="Q1" s="175"/>
+      <c r="R1" s="176"/>
+      <c r="S1" s="165" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!S1")&lt;&gt;"",INDIRECT("変更履歴!S1"),"")</f>
         <v>Nablarch開発標準設計書一覧</v>
       </c>
-      <c r="T1" s="164"/>
-      <c r="U1" s="164"/>
-      <c r="V1" s="164"/>
-      <c r="W1" s="164"/>
-      <c r="X1" s="164"/>
-      <c r="Y1" s="164"/>
-      <c r="Z1" s="165"/>
-      <c r="AA1" s="116" t="s">
+      <c r="T1" s="166"/>
+      <c r="U1" s="166"/>
+      <c r="V1" s="166"/>
+      <c r="W1" s="166"/>
+      <c r="X1" s="166"/>
+      <c r="Y1" s="166"/>
+      <c r="Z1" s="167"/>
+      <c r="AA1" s="96" t="s">
         <v>3</v>
       </c>
-      <c r="AB1" s="118"/>
-      <c r="AC1" s="145" t="str">
+      <c r="AB1" s="98"/>
+      <c r="AC1" s="125" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC1")&lt;&gt;"",INDIRECT("変更履歴!AC1"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="146"/>
-      <c r="AE1" s="146"/>
-      <c r="AF1" s="147"/>
-      <c r="AG1" s="151">
+      <c r="AD1" s="126"/>
+      <c r="AE1" s="126"/>
+      <c r="AF1" s="127"/>
+      <c r="AG1" s="159">
         <f ca="1">IF(INDIRECT("変更履歴!AG1")&lt;&gt;"",INDIRECT("変更履歴!AG1"),"")</f>
         <v>43336</v>
       </c>
-      <c r="AH1" s="152"/>
-      <c r="AI1" s="153"/>
+      <c r="AH1" s="160"/>
+      <c r="AI1" s="161"/>
       <c r="AJ1" s="6"/>
       <c r="AN1" s="7"/>
       <c r="AO1" s="6"/>
@@ -17339,54 +17407,54 @@
       <c r="AW1" s="6"/>
     </row>
     <row r="2" spans="1:49" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="116" t="s">
+      <c r="A2" s="96" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="117"/>
-      <c r="C2" s="117"/>
-      <c r="D2" s="118"/>
-      <c r="E2" s="119" t="str">
+      <c r="B2" s="97"/>
+      <c r="C2" s="97"/>
+      <c r="D2" s="98"/>
+      <c r="E2" s="99" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E2")&lt;&gt;"",INDIRECT("変更履歴!E2"),"")</f>
         <v/>
       </c>
-      <c r="F2" s="120"/>
-      <c r="G2" s="120"/>
-      <c r="H2" s="120"/>
-      <c r="I2" s="120"/>
-      <c r="J2" s="120"/>
-      <c r="K2" s="120"/>
-      <c r="L2" s="120"/>
-      <c r="M2" s="120"/>
-      <c r="N2" s="121"/>
-      <c r="O2" s="157"/>
-      <c r="P2" s="158"/>
-      <c r="Q2" s="158"/>
-      <c r="R2" s="159"/>
-      <c r="S2" s="166"/>
-      <c r="T2" s="167"/>
-      <c r="U2" s="167"/>
-      <c r="V2" s="167"/>
-      <c r="W2" s="167"/>
-      <c r="X2" s="167"/>
-      <c r="Y2" s="167"/>
-      <c r="Z2" s="168"/>
-      <c r="AA2" s="116" t="s">
+      <c r="F2" s="100"/>
+      <c r="G2" s="100"/>
+      <c r="H2" s="100"/>
+      <c r="I2" s="100"/>
+      <c r="J2" s="100"/>
+      <c r="K2" s="100"/>
+      <c r="L2" s="100"/>
+      <c r="M2" s="100"/>
+      <c r="N2" s="101"/>
+      <c r="O2" s="177"/>
+      <c r="P2" s="178"/>
+      <c r="Q2" s="178"/>
+      <c r="R2" s="179"/>
+      <c r="S2" s="168"/>
+      <c r="T2" s="169"/>
+      <c r="U2" s="169"/>
+      <c r="V2" s="169"/>
+      <c r="W2" s="169"/>
+      <c r="X2" s="169"/>
+      <c r="Y2" s="169"/>
+      <c r="Z2" s="170"/>
+      <c r="AA2" s="96" t="s">
         <v>4</v>
       </c>
-      <c r="AB2" s="118"/>
-      <c r="AC2" s="145" t="str">
+      <c r="AB2" s="98"/>
+      <c r="AC2" s="125" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC2")&lt;&gt;"",INDIRECT("変更履歴!AC2"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD2" s="146"/>
-      <c r="AE2" s="146"/>
-      <c r="AF2" s="147"/>
-      <c r="AG2" s="151">
+      <c r="AD2" s="126"/>
+      <c r="AE2" s="126"/>
+      <c r="AF2" s="127"/>
+      <c r="AG2" s="159">
         <f ca="1">IF(INDIRECT("変更履歴!AG2")&lt;&gt;"",INDIRECT("変更履歴!AG2"),"")</f>
-        <v>44848</v>
-      </c>
-      <c r="AH2" s="152"/>
-      <c r="AI2" s="153"/>
+        <v>45464</v>
+      </c>
+      <c r="AH2" s="160"/>
+      <c r="AI2" s="161"/>
       <c r="AJ2" s="6"/>
       <c r="AN2" s="7"/>
       <c r="AO2" s="6"/>
@@ -17400,52 +17468,52 @@
       <c r="AW2" s="6"/>
     </row>
     <row r="3" spans="1:49" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="116" t="s">
+      <c r="A3" s="96" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="117"/>
-      <c r="C3" s="117"/>
-      <c r="D3" s="118"/>
-      <c r="E3" s="119" t="str">
+      <c r="B3" s="97"/>
+      <c r="C3" s="97"/>
+      <c r="D3" s="98"/>
+      <c r="E3" s="99" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E3")&lt;&gt;"",INDIRECT("変更履歴!E3"),"")</f>
         <v/>
       </c>
-      <c r="F3" s="120"/>
-      <c r="G3" s="120"/>
-      <c r="H3" s="120"/>
-      <c r="I3" s="120"/>
-      <c r="J3" s="120"/>
-      <c r="K3" s="120"/>
-      <c r="L3" s="120"/>
-      <c r="M3" s="120"/>
-      <c r="N3" s="121"/>
-      <c r="O3" s="160"/>
-      <c r="P3" s="161"/>
-      <c r="Q3" s="161"/>
-      <c r="R3" s="162"/>
-      <c r="S3" s="169"/>
-      <c r="T3" s="170"/>
-      <c r="U3" s="170"/>
-      <c r="V3" s="170"/>
-      <c r="W3" s="170"/>
-      <c r="X3" s="170"/>
-      <c r="Y3" s="170"/>
-      <c r="Z3" s="171"/>
-      <c r="AA3" s="116"/>
-      <c r="AB3" s="118"/>
-      <c r="AC3" s="145" t="str">
+      <c r="F3" s="100"/>
+      <c r="G3" s="100"/>
+      <c r="H3" s="100"/>
+      <c r="I3" s="100"/>
+      <c r="J3" s="100"/>
+      <c r="K3" s="100"/>
+      <c r="L3" s="100"/>
+      <c r="M3" s="100"/>
+      <c r="N3" s="101"/>
+      <c r="O3" s="180"/>
+      <c r="P3" s="181"/>
+      <c r="Q3" s="181"/>
+      <c r="R3" s="182"/>
+      <c r="S3" s="171"/>
+      <c r="T3" s="172"/>
+      <c r="U3" s="172"/>
+      <c r="V3" s="172"/>
+      <c r="W3" s="172"/>
+      <c r="X3" s="172"/>
+      <c r="Y3" s="172"/>
+      <c r="Z3" s="173"/>
+      <c r="AA3" s="96"/>
+      <c r="AB3" s="98"/>
+      <c r="AC3" s="125" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC3")&lt;&gt;"",INDIRECT("変更履歴!AC3"),"")</f>
         <v/>
       </c>
-      <c r="AD3" s="146"/>
-      <c r="AE3" s="146"/>
-      <c r="AF3" s="147"/>
-      <c r="AG3" s="151" t="str">
+      <c r="AD3" s="126"/>
+      <c r="AE3" s="126"/>
+      <c r="AF3" s="127"/>
+      <c r="AG3" s="159" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AG3")&lt;&gt;"",INDIRECT("変更履歴!AG3"),"")</f>
         <v/>
       </c>
-      <c r="AH3" s="152"/>
-      <c r="AI3" s="153"/>
+      <c r="AH3" s="160"/>
+      <c r="AI3" s="161"/>
       <c r="AJ3" s="9"/>
       <c r="AK3" s="1"/>
       <c r="AL3" s="1"/>
@@ -17487,6 +17555,14 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="AG1:AI1"/>
+    <mergeCell ref="AC1:AF1"/>
+    <mergeCell ref="AC2:AF2"/>
+    <mergeCell ref="AG2:AI2"/>
+    <mergeCell ref="E3:N3"/>
+    <mergeCell ref="AA3:AB3"/>
+    <mergeCell ref="AC3:AF3"/>
+    <mergeCell ref="AG3:AI3"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="E1:N1"/>
     <mergeCell ref="O1:R3"/>
@@ -17496,14 +17572,6 @@
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="E2:N2"/>
     <mergeCell ref="AA2:AB2"/>
-    <mergeCell ref="AG1:AI1"/>
-    <mergeCell ref="AC1:AF1"/>
-    <mergeCell ref="AC2:AF2"/>
-    <mergeCell ref="AG2:AI2"/>
-    <mergeCell ref="E3:N3"/>
-    <mergeCell ref="AA3:AB3"/>
-    <mergeCell ref="AC3:AF3"/>
-    <mergeCell ref="AG3:AI3"/>
   </mergeCells>
   <phoneticPr fontId="10"/>
   <printOptions horizontalCentered="1"/>
@@ -17533,59 +17601,59 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="116" t="s">
+      <c r="A1" s="96" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="117"/>
-      <c r="C1" s="117"/>
-      <c r="D1" s="118"/>
-      <c r="E1" s="119" t="str">
+      <c r="B1" s="97"/>
+      <c r="C1" s="97"/>
+      <c r="D1" s="98"/>
+      <c r="E1" s="99" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E1")&lt;&gt;"",INDIRECT("変更履歴!E1"),"")</f>
         <v/>
       </c>
-      <c r="F1" s="120"/>
-      <c r="G1" s="120"/>
-      <c r="H1" s="120"/>
-      <c r="I1" s="120"/>
-      <c r="J1" s="120"/>
-      <c r="K1" s="120"/>
-      <c r="L1" s="120"/>
-      <c r="M1" s="120"/>
-      <c r="N1" s="121"/>
-      <c r="O1" s="154" t="s">
+      <c r="F1" s="100"/>
+      <c r="G1" s="100"/>
+      <c r="H1" s="100"/>
+      <c r="I1" s="100"/>
+      <c r="J1" s="100"/>
+      <c r="K1" s="100"/>
+      <c r="L1" s="100"/>
+      <c r="M1" s="100"/>
+      <c r="N1" s="101"/>
+      <c r="O1" s="174" t="s">
         <v>73</v>
       </c>
-      <c r="P1" s="155"/>
-      <c r="Q1" s="155"/>
-      <c r="R1" s="156"/>
-      <c r="S1" s="163" t="str">
+      <c r="P1" s="175"/>
+      <c r="Q1" s="175"/>
+      <c r="R1" s="176"/>
+      <c r="S1" s="165" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!S1")&lt;&gt;"",INDIRECT("変更履歴!S1"),"")</f>
         <v>Nablarch開発標準設計書一覧</v>
       </c>
-      <c r="T1" s="164"/>
-      <c r="U1" s="164"/>
-      <c r="V1" s="164"/>
-      <c r="W1" s="164"/>
-      <c r="X1" s="164"/>
-      <c r="Y1" s="164"/>
-      <c r="Z1" s="165"/>
-      <c r="AA1" s="116" t="s">
+      <c r="T1" s="166"/>
+      <c r="U1" s="166"/>
+      <c r="V1" s="166"/>
+      <c r="W1" s="166"/>
+      <c r="X1" s="166"/>
+      <c r="Y1" s="166"/>
+      <c r="Z1" s="167"/>
+      <c r="AA1" s="96" t="s">
         <v>3</v>
       </c>
-      <c r="AB1" s="118"/>
-      <c r="AC1" s="145" t="str">
+      <c r="AB1" s="98"/>
+      <c r="AC1" s="125" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC1")&lt;&gt;"",INDIRECT("変更履歴!AC1"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="146"/>
-      <c r="AE1" s="146"/>
-      <c r="AF1" s="147"/>
-      <c r="AG1" s="151">
+      <c r="AD1" s="126"/>
+      <c r="AE1" s="126"/>
+      <c r="AF1" s="127"/>
+      <c r="AG1" s="159">
         <f ca="1">IF(INDIRECT("変更履歴!AG1")&lt;&gt;"",INDIRECT("変更履歴!AG1"),"")</f>
         <v>43336</v>
       </c>
-      <c r="AH1" s="152"/>
-      <c r="AI1" s="153"/>
+      <c r="AH1" s="160"/>
+      <c r="AI1" s="161"/>
       <c r="AJ1" s="6"/>
       <c r="AM1" s="6"/>
       <c r="AN1" s="6"/>
@@ -17593,54 +17661,54 @@
       <c r="AP1" s="6"/>
     </row>
     <row r="2" spans="1:42" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="116" t="s">
+      <c r="A2" s="96" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="117"/>
-      <c r="C2" s="117"/>
-      <c r="D2" s="118"/>
-      <c r="E2" s="119" t="str">
+      <c r="B2" s="97"/>
+      <c r="C2" s="97"/>
+      <c r="D2" s="98"/>
+      <c r="E2" s="99" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E2")&lt;&gt;"",INDIRECT("変更履歴!E2"),"")</f>
         <v/>
       </c>
-      <c r="F2" s="120"/>
-      <c r="G2" s="120"/>
-      <c r="H2" s="120"/>
-      <c r="I2" s="120"/>
-      <c r="J2" s="120"/>
-      <c r="K2" s="120"/>
-      <c r="L2" s="120"/>
-      <c r="M2" s="120"/>
-      <c r="N2" s="121"/>
-      <c r="O2" s="157"/>
-      <c r="P2" s="158"/>
-      <c r="Q2" s="158"/>
-      <c r="R2" s="159"/>
-      <c r="S2" s="166"/>
-      <c r="T2" s="167"/>
-      <c r="U2" s="167"/>
-      <c r="V2" s="167"/>
-      <c r="W2" s="167"/>
-      <c r="X2" s="167"/>
-      <c r="Y2" s="167"/>
-      <c r="Z2" s="168"/>
-      <c r="AA2" s="116" t="s">
+      <c r="F2" s="100"/>
+      <c r="G2" s="100"/>
+      <c r="H2" s="100"/>
+      <c r="I2" s="100"/>
+      <c r="J2" s="100"/>
+      <c r="K2" s="100"/>
+      <c r="L2" s="100"/>
+      <c r="M2" s="100"/>
+      <c r="N2" s="101"/>
+      <c r="O2" s="177"/>
+      <c r="P2" s="178"/>
+      <c r="Q2" s="178"/>
+      <c r="R2" s="179"/>
+      <c r="S2" s="168"/>
+      <c r="T2" s="169"/>
+      <c r="U2" s="169"/>
+      <c r="V2" s="169"/>
+      <c r="W2" s="169"/>
+      <c r="X2" s="169"/>
+      <c r="Y2" s="169"/>
+      <c r="Z2" s="170"/>
+      <c r="AA2" s="96" t="s">
         <v>4</v>
       </c>
-      <c r="AB2" s="118"/>
-      <c r="AC2" s="145" t="str">
+      <c r="AB2" s="98"/>
+      <c r="AC2" s="125" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC2")&lt;&gt;"",INDIRECT("変更履歴!AC2"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD2" s="146"/>
-      <c r="AE2" s="146"/>
-      <c r="AF2" s="147"/>
-      <c r="AG2" s="151">
+      <c r="AD2" s="126"/>
+      <c r="AE2" s="126"/>
+      <c r="AF2" s="127"/>
+      <c r="AG2" s="159">
         <f ca="1">IF(INDIRECT("変更履歴!AG2")&lt;&gt;"",INDIRECT("変更履歴!AG2"),"")</f>
-        <v>44848</v>
-      </c>
-      <c r="AH2" s="152"/>
-      <c r="AI2" s="153"/>
+        <v>45464</v>
+      </c>
+      <c r="AH2" s="160"/>
+      <c r="AI2" s="161"/>
       <c r="AJ2" s="6"/>
       <c r="AM2" s="6"/>
       <c r="AN2" s="6"/>
@@ -17648,52 +17716,52 @@
       <c r="AP2" s="6"/>
     </row>
     <row r="3" spans="1:42" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="116" t="s">
+      <c r="A3" s="96" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="117"/>
-      <c r="C3" s="117"/>
-      <c r="D3" s="118"/>
-      <c r="E3" s="119" t="str">
+      <c r="B3" s="97"/>
+      <c r="C3" s="97"/>
+      <c r="D3" s="98"/>
+      <c r="E3" s="99" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E3")&lt;&gt;"",INDIRECT("変更履歴!E3"),"")</f>
         <v/>
       </c>
-      <c r="F3" s="120"/>
-      <c r="G3" s="120"/>
-      <c r="H3" s="120"/>
-      <c r="I3" s="120"/>
-      <c r="J3" s="120"/>
-      <c r="K3" s="120"/>
-      <c r="L3" s="120"/>
-      <c r="M3" s="120"/>
-      <c r="N3" s="121"/>
-      <c r="O3" s="160"/>
-      <c r="P3" s="161"/>
-      <c r="Q3" s="161"/>
-      <c r="R3" s="162"/>
-      <c r="S3" s="169"/>
-      <c r="T3" s="170"/>
-      <c r="U3" s="170"/>
-      <c r="V3" s="170"/>
-      <c r="W3" s="170"/>
-      <c r="X3" s="170"/>
-      <c r="Y3" s="170"/>
-      <c r="Z3" s="171"/>
-      <c r="AA3" s="116"/>
-      <c r="AB3" s="118"/>
-      <c r="AC3" s="145" t="str">
+      <c r="F3" s="100"/>
+      <c r="G3" s="100"/>
+      <c r="H3" s="100"/>
+      <c r="I3" s="100"/>
+      <c r="J3" s="100"/>
+      <c r="K3" s="100"/>
+      <c r="L3" s="100"/>
+      <c r="M3" s="100"/>
+      <c r="N3" s="101"/>
+      <c r="O3" s="180"/>
+      <c r="P3" s="181"/>
+      <c r="Q3" s="181"/>
+      <c r="R3" s="182"/>
+      <c r="S3" s="171"/>
+      <c r="T3" s="172"/>
+      <c r="U3" s="172"/>
+      <c r="V3" s="172"/>
+      <c r="W3" s="172"/>
+      <c r="X3" s="172"/>
+      <c r="Y3" s="172"/>
+      <c r="Z3" s="173"/>
+      <c r="AA3" s="96"/>
+      <c r="AB3" s="98"/>
+      <c r="AC3" s="125" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC3")&lt;&gt;"",INDIRECT("変更履歴!AC3"),"")</f>
         <v/>
       </c>
-      <c r="AD3" s="146"/>
-      <c r="AE3" s="146"/>
-      <c r="AF3" s="147"/>
-      <c r="AG3" s="151" t="str">
+      <c r="AD3" s="126"/>
+      <c r="AE3" s="126"/>
+      <c r="AF3" s="127"/>
+      <c r="AG3" s="159" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AG3")&lt;&gt;"",INDIRECT("変更履歴!AG3"),"")</f>
         <v/>
       </c>
-      <c r="AH3" s="152"/>
-      <c r="AI3" s="153"/>
+      <c r="AH3" s="160"/>
+      <c r="AI3" s="161"/>
       <c r="AJ3" s="9"/>
       <c r="AK3" s="1"/>
       <c r="AL3" s="1"/>
@@ -21090,14 +21158,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="AG1:AI1"/>
-    <mergeCell ref="AC1:AF1"/>
-    <mergeCell ref="AC2:AF2"/>
-    <mergeCell ref="AG2:AI2"/>
-    <mergeCell ref="E3:N3"/>
-    <mergeCell ref="AA3:AB3"/>
-    <mergeCell ref="AC3:AF3"/>
-    <mergeCell ref="AG3:AI3"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="E1:N1"/>
     <mergeCell ref="O1:R3"/>
@@ -21107,6 +21167,14 @@
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="E2:N2"/>
     <mergeCell ref="AA2:AB2"/>
+    <mergeCell ref="AG1:AI1"/>
+    <mergeCell ref="AC1:AF1"/>
+    <mergeCell ref="AC2:AF2"/>
+    <mergeCell ref="AG2:AI2"/>
+    <mergeCell ref="E3:N3"/>
+    <mergeCell ref="AA3:AB3"/>
+    <mergeCell ref="AC3:AF3"/>
+    <mergeCell ref="AG3:AI3"/>
   </mergeCells>
   <phoneticPr fontId="10"/>
   <printOptions horizontalCentered="1"/>
@@ -21134,59 +21202,59 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:49" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="116" t="s">
+      <c r="A1" s="96" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="117"/>
-      <c r="C1" s="117"/>
-      <c r="D1" s="118"/>
-      <c r="E1" s="119" t="str">
+      <c r="B1" s="97"/>
+      <c r="C1" s="97"/>
+      <c r="D1" s="98"/>
+      <c r="E1" s="99" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E1")&lt;&gt;"",INDIRECT("変更履歴!E1"),"")</f>
         <v/>
       </c>
-      <c r="F1" s="120"/>
-      <c r="G1" s="120"/>
-      <c r="H1" s="120"/>
-      <c r="I1" s="120"/>
-      <c r="J1" s="120"/>
-      <c r="K1" s="120"/>
-      <c r="L1" s="120"/>
-      <c r="M1" s="120"/>
-      <c r="N1" s="121"/>
-      <c r="O1" s="154" t="s">
+      <c r="F1" s="100"/>
+      <c r="G1" s="100"/>
+      <c r="H1" s="100"/>
+      <c r="I1" s="100"/>
+      <c r="J1" s="100"/>
+      <c r="K1" s="100"/>
+      <c r="L1" s="100"/>
+      <c r="M1" s="100"/>
+      <c r="N1" s="101"/>
+      <c r="O1" s="174" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="155"/>
-      <c r="Q1" s="155"/>
-      <c r="R1" s="156"/>
-      <c r="S1" s="163" t="str">
+      <c r="P1" s="175"/>
+      <c r="Q1" s="175"/>
+      <c r="R1" s="176"/>
+      <c r="S1" s="165" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!S1")&lt;&gt;"",INDIRECT("変更履歴!S1"),"")</f>
         <v>Nablarch開発標準設計書一覧</v>
       </c>
-      <c r="T1" s="164"/>
-      <c r="U1" s="164"/>
-      <c r="V1" s="164"/>
-      <c r="W1" s="164"/>
-      <c r="X1" s="164"/>
-      <c r="Y1" s="164"/>
-      <c r="Z1" s="165"/>
-      <c r="AA1" s="116" t="s">
+      <c r="T1" s="166"/>
+      <c r="U1" s="166"/>
+      <c r="V1" s="166"/>
+      <c r="W1" s="166"/>
+      <c r="X1" s="166"/>
+      <c r="Y1" s="166"/>
+      <c r="Z1" s="167"/>
+      <c r="AA1" s="96" t="s">
         <v>3</v>
       </c>
-      <c r="AB1" s="118"/>
-      <c r="AC1" s="145" t="str">
+      <c r="AB1" s="98"/>
+      <c r="AC1" s="125" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC1")&lt;&gt;"",INDIRECT("変更履歴!AC1"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="146"/>
-      <c r="AE1" s="146"/>
-      <c r="AF1" s="147"/>
-      <c r="AG1" s="151">
+      <c r="AD1" s="126"/>
+      <c r="AE1" s="126"/>
+      <c r="AF1" s="127"/>
+      <c r="AG1" s="159">
         <f ca="1">IF(INDIRECT("変更履歴!AG1")&lt;&gt;"",INDIRECT("変更履歴!AG1"),"")</f>
         <v>43336</v>
       </c>
-      <c r="AH1" s="152"/>
-      <c r="AI1" s="153"/>
+      <c r="AH1" s="160"/>
+      <c r="AI1" s="161"/>
       <c r="AJ1" s="6"/>
       <c r="AN1" s="7"/>
       <c r="AO1" s="6"/>
@@ -21200,54 +21268,54 @@
       <c r="AW1" s="6"/>
     </row>
     <row r="2" spans="1:49" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="116" t="s">
+      <c r="A2" s="96" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="117"/>
-      <c r="C2" s="117"/>
-      <c r="D2" s="118"/>
-      <c r="E2" s="119" t="str">
+      <c r="B2" s="97"/>
+      <c r="C2" s="97"/>
+      <c r="D2" s="98"/>
+      <c r="E2" s="99" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E2")&lt;&gt;"",INDIRECT("変更履歴!E2"),"")</f>
         <v/>
       </c>
-      <c r="F2" s="120"/>
-      <c r="G2" s="120"/>
-      <c r="H2" s="120"/>
-      <c r="I2" s="120"/>
-      <c r="J2" s="120"/>
-      <c r="K2" s="120"/>
-      <c r="L2" s="120"/>
-      <c r="M2" s="120"/>
-      <c r="N2" s="121"/>
-      <c r="O2" s="157"/>
-      <c r="P2" s="158"/>
-      <c r="Q2" s="158"/>
-      <c r="R2" s="159"/>
-      <c r="S2" s="166"/>
-      <c r="T2" s="167"/>
-      <c r="U2" s="167"/>
-      <c r="V2" s="167"/>
-      <c r="W2" s="167"/>
-      <c r="X2" s="167"/>
-      <c r="Y2" s="167"/>
-      <c r="Z2" s="168"/>
-      <c r="AA2" s="116" t="s">
+      <c r="F2" s="100"/>
+      <c r="G2" s="100"/>
+      <c r="H2" s="100"/>
+      <c r="I2" s="100"/>
+      <c r="J2" s="100"/>
+      <c r="K2" s="100"/>
+      <c r="L2" s="100"/>
+      <c r="M2" s="100"/>
+      <c r="N2" s="101"/>
+      <c r="O2" s="177"/>
+      <c r="P2" s="178"/>
+      <c r="Q2" s="178"/>
+      <c r="R2" s="179"/>
+      <c r="S2" s="168"/>
+      <c r="T2" s="169"/>
+      <c r="U2" s="169"/>
+      <c r="V2" s="169"/>
+      <c r="W2" s="169"/>
+      <c r="X2" s="169"/>
+      <c r="Y2" s="169"/>
+      <c r="Z2" s="170"/>
+      <c r="AA2" s="96" t="s">
         <v>4</v>
       </c>
-      <c r="AB2" s="118"/>
-      <c r="AC2" s="145" t="str">
+      <c r="AB2" s="98"/>
+      <c r="AC2" s="125" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC2")&lt;&gt;"",INDIRECT("変更履歴!AC2"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD2" s="146"/>
-      <c r="AE2" s="146"/>
-      <c r="AF2" s="147"/>
-      <c r="AG2" s="151">
+      <c r="AD2" s="126"/>
+      <c r="AE2" s="126"/>
+      <c r="AF2" s="127"/>
+      <c r="AG2" s="159">
         <f ca="1">IF(INDIRECT("変更履歴!AG2")&lt;&gt;"",INDIRECT("変更履歴!AG2"),"")</f>
-        <v>44848</v>
-      </c>
-      <c r="AH2" s="152"/>
-      <c r="AI2" s="153"/>
+        <v>45464</v>
+      </c>
+      <c r="AH2" s="160"/>
+      <c r="AI2" s="161"/>
       <c r="AJ2" s="6"/>
       <c r="AN2" s="7"/>
       <c r="AO2" s="6"/>
@@ -21261,52 +21329,52 @@
       <c r="AW2" s="6"/>
     </row>
     <row r="3" spans="1:49" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="116" t="s">
+      <c r="A3" s="96" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="117"/>
-      <c r="C3" s="117"/>
-      <c r="D3" s="118"/>
-      <c r="E3" s="119" t="str">
+      <c r="B3" s="97"/>
+      <c r="C3" s="97"/>
+      <c r="D3" s="98"/>
+      <c r="E3" s="99" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E3")&lt;&gt;"",INDIRECT("変更履歴!E3"),"")</f>
         <v/>
       </c>
-      <c r="F3" s="120"/>
-      <c r="G3" s="120"/>
-      <c r="H3" s="120"/>
-      <c r="I3" s="120"/>
-      <c r="J3" s="120"/>
-      <c r="K3" s="120"/>
-      <c r="L3" s="120"/>
-      <c r="M3" s="120"/>
-      <c r="N3" s="121"/>
-      <c r="O3" s="160"/>
-      <c r="P3" s="161"/>
-      <c r="Q3" s="161"/>
-      <c r="R3" s="162"/>
-      <c r="S3" s="169"/>
-      <c r="T3" s="170"/>
-      <c r="U3" s="170"/>
-      <c r="V3" s="170"/>
-      <c r="W3" s="170"/>
-      <c r="X3" s="170"/>
-      <c r="Y3" s="170"/>
-      <c r="Z3" s="171"/>
-      <c r="AA3" s="116"/>
-      <c r="AB3" s="118"/>
-      <c r="AC3" s="145" t="str">
+      <c r="F3" s="100"/>
+      <c r="G3" s="100"/>
+      <c r="H3" s="100"/>
+      <c r="I3" s="100"/>
+      <c r="J3" s="100"/>
+      <c r="K3" s="100"/>
+      <c r="L3" s="100"/>
+      <c r="M3" s="100"/>
+      <c r="N3" s="101"/>
+      <c r="O3" s="180"/>
+      <c r="P3" s="181"/>
+      <c r="Q3" s="181"/>
+      <c r="R3" s="182"/>
+      <c r="S3" s="171"/>
+      <c r="T3" s="172"/>
+      <c r="U3" s="172"/>
+      <c r="V3" s="172"/>
+      <c r="W3" s="172"/>
+      <c r="X3" s="172"/>
+      <c r="Y3" s="172"/>
+      <c r="Z3" s="173"/>
+      <c r="AA3" s="96"/>
+      <c r="AB3" s="98"/>
+      <c r="AC3" s="125" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC3")&lt;&gt;"",INDIRECT("変更履歴!AC3"),"")</f>
         <v/>
       </c>
-      <c r="AD3" s="146"/>
-      <c r="AE3" s="146"/>
-      <c r="AF3" s="147"/>
-      <c r="AG3" s="151" t="str">
+      <c r="AD3" s="126"/>
+      <c r="AE3" s="126"/>
+      <c r="AF3" s="127"/>
+      <c r="AG3" s="159" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AG3")&lt;&gt;"",INDIRECT("変更履歴!AG3"),"")</f>
         <v/>
       </c>
-      <c r="AH3" s="152"/>
-      <c r="AI3" s="153"/>
+      <c r="AH3" s="160"/>
+      <c r="AI3" s="161"/>
       <c r="AJ3" s="9"/>
       <c r="AK3" s="1"/>
       <c r="AL3" s="1"/>
@@ -21478,14 +21546,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="AG1:AI1"/>
-    <mergeCell ref="AC1:AF1"/>
-    <mergeCell ref="AC2:AF2"/>
-    <mergeCell ref="AG2:AI2"/>
-    <mergeCell ref="E3:N3"/>
-    <mergeCell ref="AA3:AB3"/>
-    <mergeCell ref="AC3:AF3"/>
-    <mergeCell ref="AG3:AI3"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="E1:N1"/>
     <mergeCell ref="O1:R3"/>
@@ -21495,6 +21555,14 @@
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="E2:N2"/>
     <mergeCell ref="AA2:AB2"/>
+    <mergeCell ref="AG1:AI1"/>
+    <mergeCell ref="AC1:AF1"/>
+    <mergeCell ref="AC2:AF2"/>
+    <mergeCell ref="AG2:AI2"/>
+    <mergeCell ref="E3:N3"/>
+    <mergeCell ref="AA3:AB3"/>
+    <mergeCell ref="AC3:AF3"/>
+    <mergeCell ref="AG3:AI3"/>
   </mergeCells>
   <phoneticPr fontId="10"/>
   <printOptions horizontalCentered="1"/>

--- a/030_設計ドキュメント/Nablarch開発標準設計書一覧.xlsx
+++ b/030_設計ドキュメント/Nablarch開発標準設計書一覧.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26731"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B883EF5-A1FA-4CB4-9F4D-21A2356D04D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EE88BF5-D614-4FD4-B4F9-9F8D5DC1B216}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1380" yWindow="3735" windowWidth="28800" windowHeight="15435" tabRatio="822" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2745" yWindow="1875" windowWidth="28800" windowHeight="15435" tabRatio="822" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="34" r:id="rId1"/>
@@ -2636,8 +2636,111 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="44" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="44" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="44" applyFont="1" applyBorder="1"/>
     <xf numFmtId="31" fontId="7" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="23" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="22" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="177" fontId="2" fillId="0" borderId="10" xfId="45" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
@@ -2756,98 +2859,14 @@
     <xf numFmtId="14" fontId="2" fillId="0" borderId="12" xfId="41" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="41" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="10" xfId="41" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="23" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="22" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="12" xfId="41" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="177" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
@@ -2857,42 +2876,6 @@
     </xf>
     <xf numFmtId="177" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="10" xfId="41" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="12" xfId="41" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="41" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="41" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="41" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="41" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="41" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="41" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="41" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="41" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="41" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="41" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="24" borderId="13" xfId="41" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -2921,14 +2904,31 @@
     <xf numFmtId="0" fontId="33" fillId="24" borderId="18" xfId="41" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="44" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="41" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="41" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="41" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="41" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="41" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="41" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="41" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="41" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="41" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -13853,12 +13853,12 @@
       <c r="F25" s="22"/>
       <c r="G25" s="22"/>
       <c r="H25" s="22"/>
-      <c r="I25" s="88">
+      <c r="I25" s="89">
         <f ca="1">IF(INDIRECT("変更履歴!D8")="","",MAX(INDIRECT("変更履歴!D8"):INDIRECT("変更履歴!F33")))</f>
-        <v>45464</v>
-      </c>
-      <c r="J25" s="88"/>
-      <c r="K25" s="88"/>
+        <v>45565</v>
+      </c>
+      <c r="J25" s="89"/>
+      <c r="K25" s="89"/>
     </row>
     <row r="26" spans="6:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F26" s="22"/>
@@ -14452,55 +14452,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="105" t="s">
+      <c r="A1" s="140" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="97"/>
-      <c r="D1" s="98"/>
-      <c r="E1" s="106"/>
-      <c r="F1" s="100"/>
-      <c r="G1" s="100"/>
-      <c r="H1" s="100"/>
-      <c r="I1" s="100"/>
-      <c r="J1" s="100"/>
-      <c r="K1" s="100"/>
-      <c r="L1" s="100"/>
-      <c r="M1" s="100"/>
-      <c r="N1" s="101"/>
-      <c r="O1" s="107" t="s">
+      <c r="B1" s="132"/>
+      <c r="C1" s="132"/>
+      <c r="D1" s="133"/>
+      <c r="E1" s="141"/>
+      <c r="F1" s="135"/>
+      <c r="G1" s="135"/>
+      <c r="H1" s="135"/>
+      <c r="I1" s="135"/>
+      <c r="J1" s="135"/>
+      <c r="K1" s="135"/>
+      <c r="L1" s="135"/>
+      <c r="M1" s="135"/>
+      <c r="N1" s="136"/>
+      <c r="O1" s="142" t="s">
         <v>11</v>
       </c>
-      <c r="P1" s="108"/>
-      <c r="Q1" s="108"/>
-      <c r="R1" s="109"/>
-      <c r="S1" s="116" t="s">
+      <c r="P1" s="143"/>
+      <c r="Q1" s="143"/>
+      <c r="R1" s="144"/>
+      <c r="S1" s="151" t="s">
         <v>44</v>
       </c>
-      <c r="T1" s="117"/>
-      <c r="U1" s="117"/>
-      <c r="V1" s="117"/>
-      <c r="W1" s="117"/>
-      <c r="X1" s="117"/>
-      <c r="Y1" s="117"/>
-      <c r="Z1" s="118"/>
-      <c r="AA1" s="96" t="s">
+      <c r="T1" s="152"/>
+      <c r="U1" s="152"/>
+      <c r="V1" s="152"/>
+      <c r="W1" s="152"/>
+      <c r="X1" s="152"/>
+      <c r="Y1" s="152"/>
+      <c r="Z1" s="153"/>
+      <c r="AA1" s="131" t="s">
         <v>12</v>
       </c>
-      <c r="AB1" s="98"/>
-      <c r="AC1" s="125" t="str">
+      <c r="AB1" s="133"/>
+      <c r="AC1" s="160" t="str">
         <f>IF(AF8="","",AF8)</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="126"/>
-      <c r="AE1" s="126"/>
-      <c r="AF1" s="127"/>
-      <c r="AG1" s="89">
+      <c r="AD1" s="161"/>
+      <c r="AE1" s="161"/>
+      <c r="AF1" s="162"/>
+      <c r="AG1" s="124">
         <f>IF(D8="","",D8)</f>
         <v>43336</v>
       </c>
-      <c r="AH1" s="90"/>
-      <c r="AI1" s="91"/>
+      <c r="AH1" s="125"/>
+      <c r="AI1" s="126"/>
       <c r="AJ1" s="1"/>
       <c r="AK1" s="1"/>
       <c r="AL1" s="1"/>
@@ -14508,51 +14508,51 @@
       <c r="AN1" s="2"/>
     </row>
     <row r="2" spans="1:40" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="96" t="s">
+      <c r="A2" s="131" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="97"/>
-      <c r="C2" s="97"/>
-      <c r="D2" s="98"/>
-      <c r="E2" s="99"/>
-      <c r="F2" s="100"/>
-      <c r="G2" s="100"/>
-      <c r="H2" s="100"/>
-      <c r="I2" s="100"/>
-      <c r="J2" s="100"/>
-      <c r="K2" s="100"/>
-      <c r="L2" s="100"/>
-      <c r="M2" s="100"/>
-      <c r="N2" s="101"/>
-      <c r="O2" s="110"/>
-      <c r="P2" s="111"/>
-      <c r="Q2" s="111"/>
-      <c r="R2" s="112"/>
-      <c r="S2" s="119"/>
-      <c r="T2" s="120"/>
-      <c r="U2" s="120"/>
-      <c r="V2" s="120"/>
-      <c r="W2" s="120"/>
-      <c r="X2" s="120"/>
-      <c r="Y2" s="120"/>
-      <c r="Z2" s="121"/>
-      <c r="AA2" s="96" t="s">
+      <c r="B2" s="132"/>
+      <c r="C2" s="132"/>
+      <c r="D2" s="133"/>
+      <c r="E2" s="134"/>
+      <c r="F2" s="135"/>
+      <c r="G2" s="135"/>
+      <c r="H2" s="135"/>
+      <c r="I2" s="135"/>
+      <c r="J2" s="135"/>
+      <c r="K2" s="135"/>
+      <c r="L2" s="135"/>
+      <c r="M2" s="135"/>
+      <c r="N2" s="136"/>
+      <c r="O2" s="145"/>
+      <c r="P2" s="146"/>
+      <c r="Q2" s="146"/>
+      <c r="R2" s="147"/>
+      <c r="S2" s="154"/>
+      <c r="T2" s="155"/>
+      <c r="U2" s="155"/>
+      <c r="V2" s="155"/>
+      <c r="W2" s="155"/>
+      <c r="X2" s="155"/>
+      <c r="Y2" s="155"/>
+      <c r="Z2" s="156"/>
+      <c r="AA2" s="131" t="s">
         <v>13</v>
       </c>
-      <c r="AB2" s="98"/>
-      <c r="AC2" s="102" t="str">
+      <c r="AB2" s="133"/>
+      <c r="AC2" s="137" t="str">
         <f ca="1">IF(COUNTA(AF9:AF33)&lt;&gt;0,INDIRECT("AF"&amp;(COUNTA(AF9:AF33)+8)),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD2" s="103"/>
-      <c r="AE2" s="103"/>
-      <c r="AF2" s="104"/>
-      <c r="AG2" s="89">
+      <c r="AD2" s="138"/>
+      <c r="AE2" s="138"/>
+      <c r="AF2" s="139"/>
+      <c r="AG2" s="124">
         <f>IF(D9="","",MAX(D9:F33))</f>
-        <v>45464</v>
-      </c>
-      <c r="AH2" s="90"/>
-      <c r="AI2" s="91"/>
+        <v>45565</v>
+      </c>
+      <c r="AH2" s="125"/>
+      <c r="AI2" s="126"/>
       <c r="AJ2" s="1"/>
       <c r="AK2" s="1"/>
       <c r="AL2" s="1"/>
@@ -14560,43 +14560,43 @@
       <c r="AN2" s="1"/>
     </row>
     <row r="3" spans="1:40" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="96" t="s">
+      <c r="A3" s="131" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="97"/>
-      <c r="C3" s="97"/>
-      <c r="D3" s="98"/>
-      <c r="E3" s="99"/>
-      <c r="F3" s="100"/>
-      <c r="G3" s="100"/>
-      <c r="H3" s="100"/>
-      <c r="I3" s="100"/>
-      <c r="J3" s="100"/>
-      <c r="K3" s="100"/>
-      <c r="L3" s="100"/>
-      <c r="M3" s="100"/>
-      <c r="N3" s="101"/>
-      <c r="O3" s="113"/>
-      <c r="P3" s="114"/>
-      <c r="Q3" s="114"/>
-      <c r="R3" s="115"/>
-      <c r="S3" s="122"/>
-      <c r="T3" s="123"/>
-      <c r="U3" s="123"/>
-      <c r="V3" s="123"/>
-      <c r="W3" s="123"/>
-      <c r="X3" s="123"/>
-      <c r="Y3" s="123"/>
-      <c r="Z3" s="124"/>
-      <c r="AA3" s="96"/>
-      <c r="AB3" s="98"/>
-      <c r="AC3" s="125"/>
-      <c r="AD3" s="126"/>
-      <c r="AE3" s="126"/>
-      <c r="AF3" s="127"/>
-      <c r="AG3" s="89"/>
-      <c r="AH3" s="90"/>
-      <c r="AI3" s="91"/>
+      <c r="B3" s="132"/>
+      <c r="C3" s="132"/>
+      <c r="D3" s="133"/>
+      <c r="E3" s="134"/>
+      <c r="F3" s="135"/>
+      <c r="G3" s="135"/>
+      <c r="H3" s="135"/>
+      <c r="I3" s="135"/>
+      <c r="J3" s="135"/>
+      <c r="K3" s="135"/>
+      <c r="L3" s="135"/>
+      <c r="M3" s="135"/>
+      <c r="N3" s="136"/>
+      <c r="O3" s="148"/>
+      <c r="P3" s="149"/>
+      <c r="Q3" s="149"/>
+      <c r="R3" s="150"/>
+      <c r="S3" s="157"/>
+      <c r="T3" s="158"/>
+      <c r="U3" s="158"/>
+      <c r="V3" s="158"/>
+      <c r="W3" s="158"/>
+      <c r="X3" s="158"/>
+      <c r="Y3" s="158"/>
+      <c r="Z3" s="159"/>
+      <c r="AA3" s="131"/>
+      <c r="AB3" s="133"/>
+      <c r="AC3" s="160"/>
+      <c r="AD3" s="161"/>
+      <c r="AE3" s="161"/>
+      <c r="AF3" s="162"/>
+      <c r="AG3" s="124"/>
+      <c r="AH3" s="125"/>
+      <c r="AI3" s="126"/>
       <c r="AJ3" s="1"/>
       <c r="AK3" s="1"/>
       <c r="AL3" s="1"/>
@@ -14633,1218 +14633,1062 @@
       <c r="A7" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="92" t="s">
+      <c r="B7" s="127" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="93"/>
-      <c r="D7" s="92" t="s">
+      <c r="C7" s="128"/>
+      <c r="D7" s="127" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="94"/>
-      <c r="F7" s="93"/>
-      <c r="G7" s="92" t="s">
+      <c r="E7" s="129"/>
+      <c r="F7" s="128"/>
+      <c r="G7" s="127" t="s">
         <v>8</v>
       </c>
-      <c r="H7" s="94"/>
-      <c r="I7" s="93"/>
-      <c r="J7" s="95" t="s">
+      <c r="H7" s="129"/>
+      <c r="I7" s="128"/>
+      <c r="J7" s="130" t="s">
         <v>23</v>
       </c>
-      <c r="K7" s="94"/>
-      <c r="L7" s="94"/>
-      <c r="M7" s="94"/>
-      <c r="N7" s="94"/>
-      <c r="O7" s="94"/>
-      <c r="P7" s="93"/>
-      <c r="Q7" s="92" t="s">
+      <c r="K7" s="129"/>
+      <c r="L7" s="129"/>
+      <c r="M7" s="129"/>
+      <c r="N7" s="129"/>
+      <c r="O7" s="129"/>
+      <c r="P7" s="128"/>
+      <c r="Q7" s="127" t="s">
         <v>9</v>
       </c>
-      <c r="R7" s="94"/>
-      <c r="S7" s="94"/>
-      <c r="T7" s="94"/>
-      <c r="U7" s="94"/>
-      <c r="V7" s="94"/>
-      <c r="W7" s="94"/>
-      <c r="X7" s="94"/>
-      <c r="Y7" s="94"/>
-      <c r="Z7" s="94"/>
-      <c r="AA7" s="94"/>
-      <c r="AB7" s="94"/>
-      <c r="AC7" s="94"/>
-      <c r="AD7" s="94"/>
-      <c r="AE7" s="93"/>
-      <c r="AF7" s="92" t="s">
+      <c r="R7" s="129"/>
+      <c r="S7" s="129"/>
+      <c r="T7" s="129"/>
+      <c r="U7" s="129"/>
+      <c r="V7" s="129"/>
+      <c r="W7" s="129"/>
+      <c r="X7" s="129"/>
+      <c r="Y7" s="129"/>
+      <c r="Z7" s="129"/>
+      <c r="AA7" s="129"/>
+      <c r="AB7" s="129"/>
+      <c r="AC7" s="129"/>
+      <c r="AD7" s="129"/>
+      <c r="AE7" s="128"/>
+      <c r="AF7" s="127" t="s">
         <v>10</v>
       </c>
-      <c r="AG7" s="94"/>
-      <c r="AH7" s="94"/>
-      <c r="AI7" s="93"/>
+      <c r="AG7" s="129"/>
+      <c r="AH7" s="129"/>
+      <c r="AI7" s="128"/>
     </row>
     <row r="8" spans="1:40" s="12" customFormat="1" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
       <c r="A8" s="16">
         <v>1</v>
       </c>
-      <c r="B8" s="141" t="s">
+      <c r="B8" s="110" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="142"/>
-      <c r="D8" s="143">
+      <c r="C8" s="111"/>
+      <c r="D8" s="112">
         <v>43336</v>
       </c>
-      <c r="E8" s="144"/>
-      <c r="F8" s="145"/>
-      <c r="G8" s="146" t="s">
+      <c r="E8" s="113"/>
+      <c r="F8" s="114"/>
+      <c r="G8" s="115" t="s">
         <v>18</v>
       </c>
-      <c r="H8" s="147"/>
-      <c r="I8" s="148"/>
-      <c r="J8" s="149" t="s">
+      <c r="H8" s="116"/>
+      <c r="I8" s="117"/>
+      <c r="J8" s="118" t="s">
         <v>19</v>
       </c>
-      <c r="K8" s="150"/>
-      <c r="L8" s="150"/>
-      <c r="M8" s="150"/>
-      <c r="N8" s="150"/>
-      <c r="O8" s="150"/>
-      <c r="P8" s="151"/>
-      <c r="Q8" s="152" t="s">
+      <c r="K8" s="119"/>
+      <c r="L8" s="119"/>
+      <c r="M8" s="119"/>
+      <c r="N8" s="119"/>
+      <c r="O8" s="119"/>
+      <c r="P8" s="120"/>
+      <c r="Q8" s="121" t="s">
         <v>20</v>
       </c>
-      <c r="R8" s="153"/>
-      <c r="S8" s="153"/>
-      <c r="T8" s="153"/>
-      <c r="U8" s="153"/>
-      <c r="V8" s="153"/>
-      <c r="W8" s="153"/>
-      <c r="X8" s="153"/>
-      <c r="Y8" s="153"/>
-      <c r="Z8" s="153"/>
-      <c r="AA8" s="153"/>
-      <c r="AB8" s="153"/>
-      <c r="AC8" s="153"/>
-      <c r="AD8" s="153"/>
-      <c r="AE8" s="154"/>
-      <c r="AF8" s="149" t="s">
+      <c r="R8" s="122"/>
+      <c r="S8" s="122"/>
+      <c r="T8" s="122"/>
+      <c r="U8" s="122"/>
+      <c r="V8" s="122"/>
+      <c r="W8" s="122"/>
+      <c r="X8" s="122"/>
+      <c r="Y8" s="122"/>
+      <c r="Z8" s="122"/>
+      <c r="AA8" s="122"/>
+      <c r="AB8" s="122"/>
+      <c r="AC8" s="122"/>
+      <c r="AD8" s="122"/>
+      <c r="AE8" s="123"/>
+      <c r="AF8" s="118" t="s">
         <v>21</v>
       </c>
-      <c r="AG8" s="150"/>
-      <c r="AH8" s="150"/>
-      <c r="AI8" s="151"/>
+      <c r="AG8" s="119"/>
+      <c r="AH8" s="119"/>
+      <c r="AI8" s="120"/>
     </row>
     <row r="9" spans="1:40" s="12" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="13">
         <v>2</v>
       </c>
-      <c r="B9" s="128" t="s">
+      <c r="B9" s="106" t="s">
         <v>199</v>
       </c>
-      <c r="C9" s="129"/>
-      <c r="D9" s="130">
+      <c r="C9" s="91"/>
+      <c r="D9" s="92">
         <v>44848</v>
       </c>
-      <c r="E9" s="131"/>
-      <c r="F9" s="132"/>
-      <c r="G9" s="133" t="s">
+      <c r="E9" s="93"/>
+      <c r="F9" s="94"/>
+      <c r="G9" s="107" t="s">
         <v>4</v>
       </c>
-      <c r="H9" s="134"/>
-      <c r="I9" s="129"/>
-      <c r="J9" s="135" t="s">
+      <c r="H9" s="95"/>
+      <c r="I9" s="91"/>
+      <c r="J9" s="108" t="s">
         <v>43</v>
       </c>
-      <c r="K9" s="136"/>
-      <c r="L9" s="136"/>
-      <c r="M9" s="136"/>
-      <c r="N9" s="136"/>
-      <c r="O9" s="136"/>
-      <c r="P9" s="137"/>
-      <c r="Q9" s="138" t="s">
+      <c r="K9" s="97"/>
+      <c r="L9" s="97"/>
+      <c r="M9" s="97"/>
+      <c r="N9" s="97"/>
+      <c r="O9" s="97"/>
+      <c r="P9" s="98"/>
+      <c r="Q9" s="109" t="s">
         <v>206</v>
       </c>
-      <c r="R9" s="139"/>
-      <c r="S9" s="139"/>
-      <c r="T9" s="139"/>
-      <c r="U9" s="139"/>
-      <c r="V9" s="139"/>
-      <c r="W9" s="139"/>
-      <c r="X9" s="139"/>
-      <c r="Y9" s="139"/>
-      <c r="Z9" s="139"/>
-      <c r="AA9" s="139"/>
-      <c r="AB9" s="139"/>
-      <c r="AC9" s="139"/>
-      <c r="AD9" s="139"/>
-      <c r="AE9" s="140"/>
-      <c r="AF9" s="135" t="s">
+      <c r="R9" s="100"/>
+      <c r="S9" s="100"/>
+      <c r="T9" s="100"/>
+      <c r="U9" s="100"/>
+      <c r="V9" s="100"/>
+      <c r="W9" s="100"/>
+      <c r="X9" s="100"/>
+      <c r="Y9" s="100"/>
+      <c r="Z9" s="100"/>
+      <c r="AA9" s="100"/>
+      <c r="AB9" s="100"/>
+      <c r="AC9" s="100"/>
+      <c r="AD9" s="100"/>
+      <c r="AE9" s="101"/>
+      <c r="AF9" s="108" t="s">
         <v>21</v>
       </c>
-      <c r="AG9" s="136"/>
-      <c r="AH9" s="136"/>
-      <c r="AI9" s="137"/>
+      <c r="AG9" s="97"/>
+      <c r="AH9" s="97"/>
+      <c r="AI9" s="98"/>
     </row>
     <row r="10" spans="1:40" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="13">
         <v>3</v>
       </c>
-      <c r="B10" s="184" t="s">
+      <c r="B10" s="103" t="s">
         <v>251</v>
       </c>
-      <c r="C10" s="129"/>
-      <c r="D10" s="130">
-        <v>45464</v>
-      </c>
-      <c r="E10" s="131"/>
-      <c r="F10" s="132"/>
-      <c r="G10" s="184" t="s">
+      <c r="C10" s="91"/>
+      <c r="D10" s="92">
+        <v>45565</v>
+      </c>
+      <c r="E10" s="93"/>
+      <c r="F10" s="94"/>
+      <c r="G10" s="103" t="s">
         <v>252</v>
       </c>
-      <c r="H10" s="134"/>
-      <c r="I10" s="129"/>
-      <c r="J10" s="185" t="s">
+      <c r="H10" s="95"/>
+      <c r="I10" s="91"/>
+      <c r="J10" s="104" t="s">
         <v>253</v>
       </c>
-      <c r="K10" s="136"/>
-      <c r="L10" s="136"/>
-      <c r="M10" s="136"/>
-      <c r="N10" s="136"/>
-      <c r="O10" s="136"/>
-      <c r="P10" s="137"/>
-      <c r="Q10" s="186" t="s">
+      <c r="K10" s="97"/>
+      <c r="L10" s="97"/>
+      <c r="M10" s="97"/>
+      <c r="N10" s="97"/>
+      <c r="O10" s="97"/>
+      <c r="P10" s="98"/>
+      <c r="Q10" s="105" t="s">
         <v>254</v>
       </c>
-      <c r="R10" s="139"/>
-      <c r="S10" s="139"/>
-      <c r="T10" s="139"/>
-      <c r="U10" s="139"/>
-      <c r="V10" s="139"/>
-      <c r="W10" s="139"/>
-      <c r="X10" s="139"/>
-      <c r="Y10" s="139"/>
-      <c r="Z10" s="139"/>
-      <c r="AA10" s="139"/>
-      <c r="AB10" s="139"/>
-      <c r="AC10" s="139"/>
-      <c r="AD10" s="139"/>
-      <c r="AE10" s="140"/>
-      <c r="AF10" s="185" t="s">
+      <c r="R10" s="100"/>
+      <c r="S10" s="100"/>
+      <c r="T10" s="100"/>
+      <c r="U10" s="100"/>
+      <c r="V10" s="100"/>
+      <c r="W10" s="100"/>
+      <c r="X10" s="100"/>
+      <c r="Y10" s="100"/>
+      <c r="Z10" s="100"/>
+      <c r="AA10" s="100"/>
+      <c r="AB10" s="100"/>
+      <c r="AC10" s="100"/>
+      <c r="AD10" s="100"/>
+      <c r="AE10" s="101"/>
+      <c r="AF10" s="104" t="s">
         <v>255</v>
       </c>
-      <c r="AG10" s="136"/>
-      <c r="AH10" s="136"/>
-      <c r="AI10" s="137"/>
+      <c r="AG10" s="97"/>
+      <c r="AH10" s="97"/>
+      <c r="AI10" s="98"/>
     </row>
     <row r="11" spans="1:40" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="13"/>
-      <c r="B11" s="155"/>
-      <c r="C11" s="129"/>
-      <c r="D11" s="130"/>
-      <c r="E11" s="131"/>
-      <c r="F11" s="132"/>
-      <c r="G11" s="155"/>
-      <c r="H11" s="134"/>
-      <c r="I11" s="129"/>
-      <c r="J11" s="156"/>
-      <c r="K11" s="136"/>
-      <c r="L11" s="136"/>
-      <c r="M11" s="136"/>
-      <c r="N11" s="136"/>
-      <c r="O11" s="136"/>
-      <c r="P11" s="137"/>
-      <c r="Q11" s="157"/>
-      <c r="R11" s="139"/>
-      <c r="S11" s="139"/>
-      <c r="T11" s="139"/>
-      <c r="U11" s="139"/>
-      <c r="V11" s="139"/>
-      <c r="W11" s="139"/>
-      <c r="X11" s="139"/>
-      <c r="Y11" s="139"/>
-      <c r="Z11" s="139"/>
-      <c r="AA11" s="139"/>
-      <c r="AB11" s="139"/>
-      <c r="AC11" s="139"/>
-      <c r="AD11" s="139"/>
-      <c r="AE11" s="140"/>
-      <c r="AF11" s="156"/>
-      <c r="AG11" s="136"/>
-      <c r="AH11" s="136"/>
-      <c r="AI11" s="137"/>
+      <c r="B11" s="90"/>
+      <c r="C11" s="91"/>
+      <c r="D11" s="92"/>
+      <c r="E11" s="93"/>
+      <c r="F11" s="94"/>
+      <c r="G11" s="90"/>
+      <c r="H11" s="95"/>
+      <c r="I11" s="91"/>
+      <c r="J11" s="96"/>
+      <c r="K11" s="97"/>
+      <c r="L11" s="97"/>
+      <c r="M11" s="97"/>
+      <c r="N11" s="97"/>
+      <c r="O11" s="97"/>
+      <c r="P11" s="98"/>
+      <c r="Q11" s="99"/>
+      <c r="R11" s="100"/>
+      <c r="S11" s="100"/>
+      <c r="T11" s="100"/>
+      <c r="U11" s="100"/>
+      <c r="V11" s="100"/>
+      <c r="W11" s="100"/>
+      <c r="X11" s="100"/>
+      <c r="Y11" s="100"/>
+      <c r="Z11" s="100"/>
+      <c r="AA11" s="100"/>
+      <c r="AB11" s="100"/>
+      <c r="AC11" s="100"/>
+      <c r="AD11" s="100"/>
+      <c r="AE11" s="101"/>
+      <c r="AF11" s="96"/>
+      <c r="AG11" s="97"/>
+      <c r="AH11" s="97"/>
+      <c r="AI11" s="98"/>
     </row>
     <row r="12" spans="1:40" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="13"/>
-      <c r="B12" s="155"/>
-      <c r="C12" s="129"/>
-      <c r="D12" s="130"/>
-      <c r="E12" s="131"/>
-      <c r="F12" s="132"/>
-      <c r="G12" s="155"/>
-      <c r="H12" s="134"/>
-      <c r="I12" s="129"/>
-      <c r="J12" s="156"/>
-      <c r="K12" s="136"/>
-      <c r="L12" s="136"/>
-      <c r="M12" s="136"/>
-      <c r="N12" s="136"/>
-      <c r="O12" s="136"/>
-      <c r="P12" s="137"/>
-      <c r="Q12" s="157"/>
-      <c r="R12" s="139"/>
-      <c r="S12" s="139"/>
-      <c r="T12" s="139"/>
-      <c r="U12" s="139"/>
-      <c r="V12" s="139"/>
-      <c r="W12" s="139"/>
-      <c r="X12" s="139"/>
-      <c r="Y12" s="139"/>
-      <c r="Z12" s="139"/>
-      <c r="AA12" s="139"/>
-      <c r="AB12" s="139"/>
-      <c r="AC12" s="139"/>
-      <c r="AD12" s="139"/>
-      <c r="AE12" s="140"/>
-      <c r="AF12" s="156"/>
-      <c r="AG12" s="136"/>
-      <c r="AH12" s="136"/>
-      <c r="AI12" s="137"/>
+      <c r="B12" s="90"/>
+      <c r="C12" s="91"/>
+      <c r="D12" s="92"/>
+      <c r="E12" s="93"/>
+      <c r="F12" s="94"/>
+      <c r="G12" s="90"/>
+      <c r="H12" s="95"/>
+      <c r="I12" s="91"/>
+      <c r="J12" s="96"/>
+      <c r="K12" s="97"/>
+      <c r="L12" s="97"/>
+      <c r="M12" s="97"/>
+      <c r="N12" s="97"/>
+      <c r="O12" s="97"/>
+      <c r="P12" s="98"/>
+      <c r="Q12" s="99"/>
+      <c r="R12" s="100"/>
+      <c r="S12" s="100"/>
+      <c r="T12" s="100"/>
+      <c r="U12" s="100"/>
+      <c r="V12" s="100"/>
+      <c r="W12" s="100"/>
+      <c r="X12" s="100"/>
+      <c r="Y12" s="100"/>
+      <c r="Z12" s="100"/>
+      <c r="AA12" s="100"/>
+      <c r="AB12" s="100"/>
+      <c r="AC12" s="100"/>
+      <c r="AD12" s="100"/>
+      <c r="AE12" s="101"/>
+      <c r="AF12" s="96"/>
+      <c r="AG12" s="97"/>
+      <c r="AH12" s="97"/>
+      <c r="AI12" s="98"/>
     </row>
     <row r="13" spans="1:40" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="13"/>
-      <c r="B13" s="155"/>
-      <c r="C13" s="129"/>
-      <c r="D13" s="130"/>
-      <c r="E13" s="131"/>
-      <c r="F13" s="132"/>
-      <c r="G13" s="155"/>
-      <c r="H13" s="134"/>
-      <c r="I13" s="129"/>
-      <c r="J13" s="156"/>
-      <c r="K13" s="136"/>
-      <c r="L13" s="136"/>
-      <c r="M13" s="136"/>
-      <c r="N13" s="136"/>
-      <c r="O13" s="136"/>
-      <c r="P13" s="137"/>
-      <c r="Q13" s="157"/>
-      <c r="R13" s="139"/>
-      <c r="S13" s="139"/>
-      <c r="T13" s="139"/>
-      <c r="U13" s="139"/>
-      <c r="V13" s="139"/>
-      <c r="W13" s="139"/>
-      <c r="X13" s="139"/>
-      <c r="Y13" s="139"/>
-      <c r="Z13" s="139"/>
-      <c r="AA13" s="139"/>
-      <c r="AB13" s="139"/>
-      <c r="AC13" s="139"/>
-      <c r="AD13" s="139"/>
-      <c r="AE13" s="140"/>
-      <c r="AF13" s="156"/>
-      <c r="AG13" s="136"/>
-      <c r="AH13" s="136"/>
-      <c r="AI13" s="137"/>
+      <c r="B13" s="90"/>
+      <c r="C13" s="91"/>
+      <c r="D13" s="92"/>
+      <c r="E13" s="93"/>
+      <c r="F13" s="94"/>
+      <c r="G13" s="90"/>
+      <c r="H13" s="95"/>
+      <c r="I13" s="91"/>
+      <c r="J13" s="96"/>
+      <c r="K13" s="97"/>
+      <c r="L13" s="97"/>
+      <c r="M13" s="97"/>
+      <c r="N13" s="97"/>
+      <c r="O13" s="97"/>
+      <c r="P13" s="98"/>
+      <c r="Q13" s="99"/>
+      <c r="R13" s="100"/>
+      <c r="S13" s="100"/>
+      <c r="T13" s="100"/>
+      <c r="U13" s="100"/>
+      <c r="V13" s="100"/>
+      <c r="W13" s="100"/>
+      <c r="X13" s="100"/>
+      <c r="Y13" s="100"/>
+      <c r="Z13" s="100"/>
+      <c r="AA13" s="100"/>
+      <c r="AB13" s="100"/>
+      <c r="AC13" s="100"/>
+      <c r="AD13" s="100"/>
+      <c r="AE13" s="101"/>
+      <c r="AF13" s="96"/>
+      <c r="AG13" s="97"/>
+      <c r="AH13" s="97"/>
+      <c r="AI13" s="98"/>
     </row>
     <row r="14" spans="1:40" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="13"/>
-      <c r="B14" s="155"/>
-      <c r="C14" s="129"/>
-      <c r="D14" s="130"/>
-      <c r="E14" s="131"/>
-      <c r="F14" s="132"/>
-      <c r="G14" s="155"/>
-      <c r="H14" s="134"/>
-      <c r="I14" s="129"/>
-      <c r="J14" s="156"/>
-      <c r="K14" s="136"/>
-      <c r="L14" s="136"/>
-      <c r="M14" s="136"/>
-      <c r="N14" s="136"/>
-      <c r="O14" s="136"/>
-      <c r="P14" s="137"/>
-      <c r="Q14" s="157"/>
-      <c r="R14" s="139"/>
-      <c r="S14" s="139"/>
-      <c r="T14" s="139"/>
-      <c r="U14" s="139"/>
-      <c r="V14" s="139"/>
-      <c r="W14" s="139"/>
-      <c r="X14" s="139"/>
-      <c r="Y14" s="139"/>
-      <c r="Z14" s="139"/>
-      <c r="AA14" s="139"/>
-      <c r="AB14" s="139"/>
-      <c r="AC14" s="139"/>
-      <c r="AD14" s="139"/>
-      <c r="AE14" s="140"/>
-      <c r="AF14" s="156"/>
-      <c r="AG14" s="136"/>
-      <c r="AH14" s="136"/>
-      <c r="AI14" s="137"/>
+      <c r="B14" s="90"/>
+      <c r="C14" s="91"/>
+      <c r="D14" s="92"/>
+      <c r="E14" s="93"/>
+      <c r="F14" s="94"/>
+      <c r="G14" s="90"/>
+      <c r="H14" s="95"/>
+      <c r="I14" s="91"/>
+      <c r="J14" s="96"/>
+      <c r="K14" s="97"/>
+      <c r="L14" s="97"/>
+      <c r="M14" s="97"/>
+      <c r="N14" s="97"/>
+      <c r="O14" s="97"/>
+      <c r="P14" s="98"/>
+      <c r="Q14" s="99"/>
+      <c r="R14" s="100"/>
+      <c r="S14" s="100"/>
+      <c r="T14" s="100"/>
+      <c r="U14" s="100"/>
+      <c r="V14" s="100"/>
+      <c r="W14" s="100"/>
+      <c r="X14" s="100"/>
+      <c r="Y14" s="100"/>
+      <c r="Z14" s="100"/>
+      <c r="AA14" s="100"/>
+      <c r="AB14" s="100"/>
+      <c r="AC14" s="100"/>
+      <c r="AD14" s="100"/>
+      <c r="AE14" s="101"/>
+      <c r="AF14" s="96"/>
+      <c r="AG14" s="97"/>
+      <c r="AH14" s="97"/>
+      <c r="AI14" s="98"/>
     </row>
     <row r="15" spans="1:40" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="13"/>
-      <c r="B15" s="155"/>
-      <c r="C15" s="129"/>
-      <c r="D15" s="130"/>
-      <c r="E15" s="131"/>
-      <c r="F15" s="132"/>
-      <c r="G15" s="155"/>
-      <c r="H15" s="134"/>
-      <c r="I15" s="129"/>
-      <c r="J15" s="156"/>
-      <c r="K15" s="136"/>
-      <c r="L15" s="136"/>
-      <c r="M15" s="136"/>
-      <c r="N15" s="136"/>
-      <c r="O15" s="136"/>
-      <c r="P15" s="137"/>
-      <c r="Q15" s="157"/>
-      <c r="R15" s="139"/>
-      <c r="S15" s="139"/>
-      <c r="T15" s="139"/>
-      <c r="U15" s="139"/>
-      <c r="V15" s="139"/>
-      <c r="W15" s="139"/>
-      <c r="X15" s="139"/>
-      <c r="Y15" s="139"/>
-      <c r="Z15" s="139"/>
-      <c r="AA15" s="139"/>
-      <c r="AB15" s="139"/>
-      <c r="AC15" s="139"/>
-      <c r="AD15" s="139"/>
-      <c r="AE15" s="140"/>
-      <c r="AF15" s="156"/>
-      <c r="AG15" s="136"/>
-      <c r="AH15" s="136"/>
-      <c r="AI15" s="137"/>
+      <c r="B15" s="90"/>
+      <c r="C15" s="91"/>
+      <c r="D15" s="92"/>
+      <c r="E15" s="93"/>
+      <c r="F15" s="94"/>
+      <c r="G15" s="90"/>
+      <c r="H15" s="95"/>
+      <c r="I15" s="91"/>
+      <c r="J15" s="96"/>
+      <c r="K15" s="97"/>
+      <c r="L15" s="97"/>
+      <c r="M15" s="97"/>
+      <c r="N15" s="97"/>
+      <c r="O15" s="97"/>
+      <c r="P15" s="98"/>
+      <c r="Q15" s="99"/>
+      <c r="R15" s="100"/>
+      <c r="S15" s="100"/>
+      <c r="T15" s="100"/>
+      <c r="U15" s="100"/>
+      <c r="V15" s="100"/>
+      <c r="W15" s="100"/>
+      <c r="X15" s="100"/>
+      <c r="Y15" s="100"/>
+      <c r="Z15" s="100"/>
+      <c r="AA15" s="100"/>
+      <c r="AB15" s="100"/>
+      <c r="AC15" s="100"/>
+      <c r="AD15" s="100"/>
+      <c r="AE15" s="101"/>
+      <c r="AF15" s="96"/>
+      <c r="AG15" s="97"/>
+      <c r="AH15" s="97"/>
+      <c r="AI15" s="98"/>
     </row>
     <row r="16" spans="1:40" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="13"/>
-      <c r="B16" s="155"/>
-      <c r="C16" s="129"/>
-      <c r="D16" s="130"/>
-      <c r="E16" s="131"/>
-      <c r="F16" s="132"/>
-      <c r="G16" s="155"/>
-      <c r="H16" s="134"/>
-      <c r="I16" s="129"/>
-      <c r="J16" s="156"/>
-      <c r="K16" s="136"/>
-      <c r="L16" s="136"/>
-      <c r="M16" s="136"/>
-      <c r="N16" s="136"/>
-      <c r="O16" s="136"/>
-      <c r="P16" s="137"/>
-      <c r="Q16" s="157"/>
-      <c r="R16" s="139"/>
-      <c r="S16" s="139"/>
-      <c r="T16" s="139"/>
-      <c r="U16" s="139"/>
-      <c r="V16" s="139"/>
-      <c r="W16" s="139"/>
-      <c r="X16" s="139"/>
-      <c r="Y16" s="139"/>
-      <c r="Z16" s="139"/>
-      <c r="AA16" s="139"/>
-      <c r="AB16" s="139"/>
-      <c r="AC16" s="139"/>
-      <c r="AD16" s="139"/>
-      <c r="AE16" s="140"/>
-      <c r="AF16" s="156"/>
-      <c r="AG16" s="136"/>
-      <c r="AH16" s="136"/>
-      <c r="AI16" s="137"/>
+      <c r="B16" s="90"/>
+      <c r="C16" s="91"/>
+      <c r="D16" s="92"/>
+      <c r="E16" s="93"/>
+      <c r="F16" s="94"/>
+      <c r="G16" s="90"/>
+      <c r="H16" s="95"/>
+      <c r="I16" s="91"/>
+      <c r="J16" s="96"/>
+      <c r="K16" s="97"/>
+      <c r="L16" s="97"/>
+      <c r="M16" s="97"/>
+      <c r="N16" s="97"/>
+      <c r="O16" s="97"/>
+      <c r="P16" s="98"/>
+      <c r="Q16" s="99"/>
+      <c r="R16" s="100"/>
+      <c r="S16" s="100"/>
+      <c r="T16" s="100"/>
+      <c r="U16" s="100"/>
+      <c r="V16" s="100"/>
+      <c r="W16" s="100"/>
+      <c r="X16" s="100"/>
+      <c r="Y16" s="100"/>
+      <c r="Z16" s="100"/>
+      <c r="AA16" s="100"/>
+      <c r="AB16" s="100"/>
+      <c r="AC16" s="100"/>
+      <c r="AD16" s="100"/>
+      <c r="AE16" s="101"/>
+      <c r="AF16" s="96"/>
+      <c r="AG16" s="97"/>
+      <c r="AH16" s="97"/>
+      <c r="AI16" s="98"/>
     </row>
     <row r="17" spans="1:35" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="13"/>
-      <c r="B17" s="155"/>
-      <c r="C17" s="129"/>
-      <c r="D17" s="130"/>
-      <c r="E17" s="131"/>
-      <c r="F17" s="132"/>
-      <c r="G17" s="155"/>
-      <c r="H17" s="134"/>
-      <c r="I17" s="129"/>
-      <c r="J17" s="156"/>
-      <c r="K17" s="136"/>
-      <c r="L17" s="136"/>
-      <c r="M17" s="136"/>
-      <c r="N17" s="136"/>
-      <c r="O17" s="136"/>
-      <c r="P17" s="137"/>
-      <c r="Q17" s="157"/>
-      <c r="R17" s="139"/>
-      <c r="S17" s="139"/>
-      <c r="T17" s="139"/>
-      <c r="U17" s="139"/>
-      <c r="V17" s="139"/>
-      <c r="W17" s="139"/>
-      <c r="X17" s="139"/>
-      <c r="Y17" s="139"/>
-      <c r="Z17" s="139"/>
-      <c r="AA17" s="139"/>
-      <c r="AB17" s="139"/>
-      <c r="AC17" s="139"/>
-      <c r="AD17" s="139"/>
-      <c r="AE17" s="140"/>
-      <c r="AF17" s="156"/>
-      <c r="AG17" s="136"/>
-      <c r="AH17" s="136"/>
-      <c r="AI17" s="137"/>
+      <c r="B17" s="90"/>
+      <c r="C17" s="91"/>
+      <c r="D17" s="92"/>
+      <c r="E17" s="93"/>
+      <c r="F17" s="94"/>
+      <c r="G17" s="90"/>
+      <c r="H17" s="95"/>
+      <c r="I17" s="91"/>
+      <c r="J17" s="96"/>
+      <c r="K17" s="97"/>
+      <c r="L17" s="97"/>
+      <c r="M17" s="97"/>
+      <c r="N17" s="97"/>
+      <c r="O17" s="97"/>
+      <c r="P17" s="98"/>
+      <c r="Q17" s="99"/>
+      <c r="R17" s="100"/>
+      <c r="S17" s="100"/>
+      <c r="T17" s="100"/>
+      <c r="U17" s="100"/>
+      <c r="V17" s="100"/>
+      <c r="W17" s="100"/>
+      <c r="X17" s="100"/>
+      <c r="Y17" s="100"/>
+      <c r="Z17" s="100"/>
+      <c r="AA17" s="100"/>
+      <c r="AB17" s="100"/>
+      <c r="AC17" s="100"/>
+      <c r="AD17" s="100"/>
+      <c r="AE17" s="101"/>
+      <c r="AF17" s="96"/>
+      <c r="AG17" s="97"/>
+      <c r="AH17" s="97"/>
+      <c r="AI17" s="98"/>
     </row>
     <row r="18" spans="1:35" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="13"/>
-      <c r="B18" s="155"/>
-      <c r="C18" s="129"/>
-      <c r="D18" s="130"/>
-      <c r="E18" s="131"/>
-      <c r="F18" s="132"/>
-      <c r="G18" s="155"/>
-      <c r="H18" s="134"/>
-      <c r="I18" s="129"/>
-      <c r="J18" s="156"/>
-      <c r="K18" s="136"/>
-      <c r="L18" s="136"/>
-      <c r="M18" s="136"/>
-      <c r="N18" s="136"/>
-      <c r="O18" s="136"/>
-      <c r="P18" s="137"/>
-      <c r="Q18" s="157"/>
-      <c r="R18" s="139"/>
-      <c r="S18" s="139"/>
-      <c r="T18" s="139"/>
-      <c r="U18" s="139"/>
-      <c r="V18" s="139"/>
-      <c r="W18" s="139"/>
-      <c r="X18" s="139"/>
-      <c r="Y18" s="139"/>
-      <c r="Z18" s="139"/>
-      <c r="AA18" s="139"/>
-      <c r="AB18" s="139"/>
-      <c r="AC18" s="139"/>
-      <c r="AD18" s="139"/>
-      <c r="AE18" s="140"/>
-      <c r="AF18" s="156"/>
-      <c r="AG18" s="136"/>
-      <c r="AH18" s="136"/>
-      <c r="AI18" s="137"/>
+      <c r="B18" s="90"/>
+      <c r="C18" s="91"/>
+      <c r="D18" s="92"/>
+      <c r="E18" s="93"/>
+      <c r="F18" s="94"/>
+      <c r="G18" s="90"/>
+      <c r="H18" s="95"/>
+      <c r="I18" s="91"/>
+      <c r="J18" s="96"/>
+      <c r="K18" s="97"/>
+      <c r="L18" s="97"/>
+      <c r="M18" s="97"/>
+      <c r="N18" s="97"/>
+      <c r="O18" s="97"/>
+      <c r="P18" s="98"/>
+      <c r="Q18" s="99"/>
+      <c r="R18" s="100"/>
+      <c r="S18" s="100"/>
+      <c r="T18" s="100"/>
+      <c r="U18" s="100"/>
+      <c r="V18" s="100"/>
+      <c r="W18" s="100"/>
+      <c r="X18" s="100"/>
+      <c r="Y18" s="100"/>
+      <c r="Z18" s="100"/>
+      <c r="AA18" s="100"/>
+      <c r="AB18" s="100"/>
+      <c r="AC18" s="100"/>
+      <c r="AD18" s="100"/>
+      <c r="AE18" s="101"/>
+      <c r="AF18" s="96"/>
+      <c r="AG18" s="97"/>
+      <c r="AH18" s="97"/>
+      <c r="AI18" s="98"/>
     </row>
     <row r="19" spans="1:35" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="13"/>
-      <c r="B19" s="155"/>
-      <c r="C19" s="129"/>
-      <c r="D19" s="130"/>
-      <c r="E19" s="131"/>
-      <c r="F19" s="132"/>
-      <c r="G19" s="155"/>
-      <c r="H19" s="134"/>
-      <c r="I19" s="129"/>
-      <c r="J19" s="156"/>
-      <c r="K19" s="136"/>
-      <c r="L19" s="136"/>
-      <c r="M19" s="136"/>
-      <c r="N19" s="136"/>
-      <c r="O19" s="136"/>
-      <c r="P19" s="137"/>
-      <c r="Q19" s="157"/>
-      <c r="R19" s="139"/>
-      <c r="S19" s="139"/>
-      <c r="T19" s="139"/>
-      <c r="U19" s="139"/>
-      <c r="V19" s="139"/>
-      <c r="W19" s="139"/>
-      <c r="X19" s="139"/>
-      <c r="Y19" s="139"/>
-      <c r="Z19" s="139"/>
-      <c r="AA19" s="139"/>
-      <c r="AB19" s="139"/>
-      <c r="AC19" s="139"/>
-      <c r="AD19" s="139"/>
-      <c r="AE19" s="140"/>
-      <c r="AF19" s="156"/>
-      <c r="AG19" s="136"/>
-      <c r="AH19" s="136"/>
-      <c r="AI19" s="137"/>
+      <c r="B19" s="90"/>
+      <c r="C19" s="91"/>
+      <c r="D19" s="92"/>
+      <c r="E19" s="93"/>
+      <c r="F19" s="94"/>
+      <c r="G19" s="90"/>
+      <c r="H19" s="95"/>
+      <c r="I19" s="91"/>
+      <c r="J19" s="96"/>
+      <c r="K19" s="97"/>
+      <c r="L19" s="97"/>
+      <c r="M19" s="97"/>
+      <c r="N19" s="97"/>
+      <c r="O19" s="97"/>
+      <c r="P19" s="98"/>
+      <c r="Q19" s="99"/>
+      <c r="R19" s="100"/>
+      <c r="S19" s="100"/>
+      <c r="T19" s="100"/>
+      <c r="U19" s="100"/>
+      <c r="V19" s="100"/>
+      <c r="W19" s="100"/>
+      <c r="X19" s="100"/>
+      <c r="Y19" s="100"/>
+      <c r="Z19" s="100"/>
+      <c r="AA19" s="100"/>
+      <c r="AB19" s="100"/>
+      <c r="AC19" s="100"/>
+      <c r="AD19" s="100"/>
+      <c r="AE19" s="101"/>
+      <c r="AF19" s="96"/>
+      <c r="AG19" s="97"/>
+      <c r="AH19" s="97"/>
+      <c r="AI19" s="98"/>
     </row>
     <row r="20" spans="1:35" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="13"/>
-      <c r="B20" s="155"/>
-      <c r="C20" s="129"/>
-      <c r="D20" s="130"/>
-      <c r="E20" s="131"/>
-      <c r="F20" s="132"/>
-      <c r="G20" s="155"/>
-      <c r="H20" s="134"/>
-      <c r="I20" s="129"/>
-      <c r="J20" s="156"/>
-      <c r="K20" s="136"/>
-      <c r="L20" s="136"/>
-      <c r="M20" s="136"/>
-      <c r="N20" s="136"/>
-      <c r="O20" s="136"/>
-      <c r="P20" s="137"/>
-      <c r="Q20" s="157"/>
-      <c r="R20" s="139"/>
-      <c r="S20" s="139"/>
-      <c r="T20" s="139"/>
-      <c r="U20" s="139"/>
-      <c r="V20" s="139"/>
-      <c r="W20" s="139"/>
-      <c r="X20" s="139"/>
-      <c r="Y20" s="139"/>
-      <c r="Z20" s="139"/>
-      <c r="AA20" s="139"/>
-      <c r="AB20" s="139"/>
-      <c r="AC20" s="139"/>
-      <c r="AD20" s="139"/>
-      <c r="AE20" s="140"/>
-      <c r="AF20" s="156"/>
-      <c r="AG20" s="136"/>
-      <c r="AH20" s="136"/>
-      <c r="AI20" s="137"/>
+      <c r="B20" s="90"/>
+      <c r="C20" s="91"/>
+      <c r="D20" s="92"/>
+      <c r="E20" s="93"/>
+      <c r="F20" s="94"/>
+      <c r="G20" s="90"/>
+      <c r="H20" s="95"/>
+      <c r="I20" s="91"/>
+      <c r="J20" s="96"/>
+      <c r="K20" s="97"/>
+      <c r="L20" s="97"/>
+      <c r="M20" s="97"/>
+      <c r="N20" s="97"/>
+      <c r="O20" s="97"/>
+      <c r="P20" s="98"/>
+      <c r="Q20" s="99"/>
+      <c r="R20" s="100"/>
+      <c r="S20" s="100"/>
+      <c r="T20" s="100"/>
+      <c r="U20" s="100"/>
+      <c r="V20" s="100"/>
+      <c r="W20" s="100"/>
+      <c r="X20" s="100"/>
+      <c r="Y20" s="100"/>
+      <c r="Z20" s="100"/>
+      <c r="AA20" s="100"/>
+      <c r="AB20" s="100"/>
+      <c r="AC20" s="100"/>
+      <c r="AD20" s="100"/>
+      <c r="AE20" s="101"/>
+      <c r="AF20" s="96"/>
+      <c r="AG20" s="97"/>
+      <c r="AH20" s="97"/>
+      <c r="AI20" s="98"/>
     </row>
     <row r="21" spans="1:35" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="13"/>
-      <c r="B21" s="155"/>
-      <c r="C21" s="129"/>
-      <c r="D21" s="130"/>
-      <c r="E21" s="131"/>
-      <c r="F21" s="132"/>
-      <c r="G21" s="155"/>
-      <c r="H21" s="134"/>
-      <c r="I21" s="129"/>
-      <c r="J21" s="156"/>
-      <c r="K21" s="136"/>
-      <c r="L21" s="136"/>
-      <c r="M21" s="136"/>
-      <c r="N21" s="136"/>
-      <c r="O21" s="136"/>
-      <c r="P21" s="137"/>
-      <c r="Q21" s="157"/>
-      <c r="R21" s="139"/>
-      <c r="S21" s="139"/>
-      <c r="T21" s="139"/>
-      <c r="U21" s="139"/>
-      <c r="V21" s="139"/>
-      <c r="W21" s="139"/>
-      <c r="X21" s="139"/>
-      <c r="Y21" s="139"/>
-      <c r="Z21" s="139"/>
-      <c r="AA21" s="139"/>
-      <c r="AB21" s="139"/>
-      <c r="AC21" s="139"/>
-      <c r="AD21" s="139"/>
-      <c r="AE21" s="140"/>
-      <c r="AF21" s="156"/>
-      <c r="AG21" s="136"/>
-      <c r="AH21" s="136"/>
-      <c r="AI21" s="137"/>
+      <c r="B21" s="90"/>
+      <c r="C21" s="91"/>
+      <c r="D21" s="92"/>
+      <c r="E21" s="93"/>
+      <c r="F21" s="94"/>
+      <c r="G21" s="90"/>
+      <c r="H21" s="95"/>
+      <c r="I21" s="91"/>
+      <c r="J21" s="96"/>
+      <c r="K21" s="97"/>
+      <c r="L21" s="97"/>
+      <c r="M21" s="97"/>
+      <c r="N21" s="97"/>
+      <c r="O21" s="97"/>
+      <c r="P21" s="98"/>
+      <c r="Q21" s="99"/>
+      <c r="R21" s="100"/>
+      <c r="S21" s="100"/>
+      <c r="T21" s="100"/>
+      <c r="U21" s="100"/>
+      <c r="V21" s="100"/>
+      <c r="W21" s="100"/>
+      <c r="X21" s="100"/>
+      <c r="Y21" s="100"/>
+      <c r="Z21" s="100"/>
+      <c r="AA21" s="100"/>
+      <c r="AB21" s="100"/>
+      <c r="AC21" s="100"/>
+      <c r="AD21" s="100"/>
+      <c r="AE21" s="101"/>
+      <c r="AF21" s="96"/>
+      <c r="AG21" s="97"/>
+      <c r="AH21" s="97"/>
+      <c r="AI21" s="98"/>
     </row>
     <row r="22" spans="1:35" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="13"/>
-      <c r="B22" s="155"/>
-      <c r="C22" s="129"/>
-      <c r="D22" s="130"/>
-      <c r="E22" s="131"/>
-      <c r="F22" s="132"/>
-      <c r="G22" s="155"/>
-      <c r="H22" s="134"/>
-      <c r="I22" s="129"/>
-      <c r="J22" s="156"/>
-      <c r="K22" s="136"/>
-      <c r="L22" s="136"/>
-      <c r="M22" s="136"/>
-      <c r="N22" s="136"/>
-      <c r="O22" s="136"/>
-      <c r="P22" s="137"/>
-      <c r="Q22" s="157"/>
-      <c r="R22" s="139"/>
-      <c r="S22" s="139"/>
-      <c r="T22" s="139"/>
-      <c r="U22" s="139"/>
-      <c r="V22" s="139"/>
-      <c r="W22" s="139"/>
-      <c r="X22" s="139"/>
-      <c r="Y22" s="139"/>
-      <c r="Z22" s="139"/>
-      <c r="AA22" s="139"/>
-      <c r="AB22" s="139"/>
-      <c r="AC22" s="139"/>
-      <c r="AD22" s="139"/>
-      <c r="AE22" s="140"/>
-      <c r="AF22" s="156"/>
-      <c r="AG22" s="136"/>
-      <c r="AH22" s="136"/>
-      <c r="AI22" s="137"/>
+      <c r="B22" s="90"/>
+      <c r="C22" s="91"/>
+      <c r="D22" s="92"/>
+      <c r="E22" s="93"/>
+      <c r="F22" s="94"/>
+      <c r="G22" s="90"/>
+      <c r="H22" s="95"/>
+      <c r="I22" s="91"/>
+      <c r="J22" s="96"/>
+      <c r="K22" s="97"/>
+      <c r="L22" s="97"/>
+      <c r="M22" s="97"/>
+      <c r="N22" s="97"/>
+      <c r="O22" s="97"/>
+      <c r="P22" s="98"/>
+      <c r="Q22" s="99"/>
+      <c r="R22" s="100"/>
+      <c r="S22" s="100"/>
+      <c r="T22" s="100"/>
+      <c r="U22" s="100"/>
+      <c r="V22" s="100"/>
+      <c r="W22" s="100"/>
+      <c r="X22" s="100"/>
+      <c r="Y22" s="100"/>
+      <c r="Z22" s="100"/>
+      <c r="AA22" s="100"/>
+      <c r="AB22" s="100"/>
+      <c r="AC22" s="100"/>
+      <c r="AD22" s="100"/>
+      <c r="AE22" s="101"/>
+      <c r="AF22" s="96"/>
+      <c r="AG22" s="97"/>
+      <c r="AH22" s="97"/>
+      <c r="AI22" s="98"/>
     </row>
     <row r="23" spans="1:35" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="13"/>
-      <c r="B23" s="155"/>
-      <c r="C23" s="129"/>
-      <c r="D23" s="130"/>
-      <c r="E23" s="131"/>
-      <c r="F23" s="132"/>
-      <c r="G23" s="155"/>
-      <c r="H23" s="134"/>
-      <c r="I23" s="129"/>
-      <c r="J23" s="156"/>
-      <c r="K23" s="136"/>
-      <c r="L23" s="136"/>
-      <c r="M23" s="136"/>
-      <c r="N23" s="136"/>
-      <c r="O23" s="136"/>
-      <c r="P23" s="137"/>
-      <c r="Q23" s="157"/>
-      <c r="R23" s="139"/>
-      <c r="S23" s="139"/>
-      <c r="T23" s="139"/>
-      <c r="U23" s="139"/>
-      <c r="V23" s="139"/>
-      <c r="W23" s="139"/>
-      <c r="X23" s="139"/>
-      <c r="Y23" s="139"/>
-      <c r="Z23" s="139"/>
-      <c r="AA23" s="139"/>
-      <c r="AB23" s="139"/>
-      <c r="AC23" s="139"/>
-      <c r="AD23" s="139"/>
-      <c r="AE23" s="140"/>
-      <c r="AF23" s="156"/>
-      <c r="AG23" s="136"/>
-      <c r="AH23" s="136"/>
-      <c r="AI23" s="137"/>
+      <c r="B23" s="90"/>
+      <c r="C23" s="91"/>
+      <c r="D23" s="92"/>
+      <c r="E23" s="93"/>
+      <c r="F23" s="94"/>
+      <c r="G23" s="90"/>
+      <c r="H23" s="95"/>
+      <c r="I23" s="91"/>
+      <c r="J23" s="96"/>
+      <c r="K23" s="97"/>
+      <c r="L23" s="97"/>
+      <c r="M23" s="97"/>
+      <c r="N23" s="97"/>
+      <c r="O23" s="97"/>
+      <c r="P23" s="98"/>
+      <c r="Q23" s="99"/>
+      <c r="R23" s="100"/>
+      <c r="S23" s="100"/>
+      <c r="T23" s="100"/>
+      <c r="U23" s="100"/>
+      <c r="V23" s="100"/>
+      <c r="W23" s="100"/>
+      <c r="X23" s="100"/>
+      <c r="Y23" s="100"/>
+      <c r="Z23" s="100"/>
+      <c r="AA23" s="100"/>
+      <c r="AB23" s="100"/>
+      <c r="AC23" s="100"/>
+      <c r="AD23" s="100"/>
+      <c r="AE23" s="101"/>
+      <c r="AF23" s="96"/>
+      <c r="AG23" s="97"/>
+      <c r="AH23" s="97"/>
+      <c r="AI23" s="98"/>
     </row>
     <row r="24" spans="1:35" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="13"/>
-      <c r="B24" s="155"/>
-      <c r="C24" s="129"/>
-      <c r="D24" s="130"/>
-      <c r="E24" s="131"/>
-      <c r="F24" s="132"/>
-      <c r="G24" s="155"/>
-      <c r="H24" s="134"/>
-      <c r="I24" s="129"/>
-      <c r="J24" s="156"/>
-      <c r="K24" s="136"/>
-      <c r="L24" s="136"/>
-      <c r="M24" s="136"/>
-      <c r="N24" s="136"/>
-      <c r="O24" s="136"/>
-      <c r="P24" s="137"/>
-      <c r="Q24" s="157"/>
-      <c r="R24" s="139"/>
-      <c r="S24" s="139"/>
-      <c r="T24" s="139"/>
-      <c r="U24" s="139"/>
-      <c r="V24" s="139"/>
-      <c r="W24" s="139"/>
-      <c r="X24" s="139"/>
-      <c r="Y24" s="139"/>
-      <c r="Z24" s="139"/>
-      <c r="AA24" s="139"/>
-      <c r="AB24" s="139"/>
-      <c r="AC24" s="139"/>
-      <c r="AD24" s="139"/>
-      <c r="AE24" s="140"/>
-      <c r="AF24" s="156"/>
-      <c r="AG24" s="136"/>
-      <c r="AH24" s="136"/>
-      <c r="AI24" s="137"/>
+      <c r="B24" s="90"/>
+      <c r="C24" s="91"/>
+      <c r="D24" s="92"/>
+      <c r="E24" s="93"/>
+      <c r="F24" s="94"/>
+      <c r="G24" s="90"/>
+      <c r="H24" s="95"/>
+      <c r="I24" s="91"/>
+      <c r="J24" s="96"/>
+      <c r="K24" s="97"/>
+      <c r="L24" s="97"/>
+      <c r="M24" s="97"/>
+      <c r="N24" s="97"/>
+      <c r="O24" s="97"/>
+      <c r="P24" s="98"/>
+      <c r="Q24" s="99"/>
+      <c r="R24" s="100"/>
+      <c r="S24" s="100"/>
+      <c r="T24" s="100"/>
+      <c r="U24" s="100"/>
+      <c r="V24" s="100"/>
+      <c r="W24" s="100"/>
+      <c r="X24" s="100"/>
+      <c r="Y24" s="100"/>
+      <c r="Z24" s="100"/>
+      <c r="AA24" s="100"/>
+      <c r="AB24" s="100"/>
+      <c r="AC24" s="100"/>
+      <c r="AD24" s="100"/>
+      <c r="AE24" s="101"/>
+      <c r="AF24" s="96"/>
+      <c r="AG24" s="97"/>
+      <c r="AH24" s="97"/>
+      <c r="AI24" s="98"/>
     </row>
     <row r="25" spans="1:35" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="13"/>
-      <c r="B25" s="155"/>
-      <c r="C25" s="129"/>
-      <c r="D25" s="130"/>
-      <c r="E25" s="131"/>
-      <c r="F25" s="132"/>
-      <c r="G25" s="155"/>
-      <c r="H25" s="134"/>
-      <c r="I25" s="129"/>
-      <c r="J25" s="156"/>
-      <c r="K25" s="136"/>
-      <c r="L25" s="136"/>
-      <c r="M25" s="136"/>
-      <c r="N25" s="136"/>
-      <c r="O25" s="136"/>
-      <c r="P25" s="137"/>
-      <c r="Q25" s="157"/>
-      <c r="R25" s="139"/>
-      <c r="S25" s="139"/>
-      <c r="T25" s="139"/>
-      <c r="U25" s="139"/>
-      <c r="V25" s="139"/>
-      <c r="W25" s="139"/>
-      <c r="X25" s="139"/>
-      <c r="Y25" s="139"/>
-      <c r="Z25" s="139"/>
-      <c r="AA25" s="139"/>
-      <c r="AB25" s="139"/>
-      <c r="AC25" s="139"/>
-      <c r="AD25" s="139"/>
-      <c r="AE25" s="140"/>
-      <c r="AF25" s="156"/>
-      <c r="AG25" s="136"/>
-      <c r="AH25" s="136"/>
-      <c r="AI25" s="137"/>
+      <c r="B25" s="90"/>
+      <c r="C25" s="91"/>
+      <c r="D25" s="92"/>
+      <c r="E25" s="93"/>
+      <c r="F25" s="94"/>
+      <c r="G25" s="90"/>
+      <c r="H25" s="95"/>
+      <c r="I25" s="91"/>
+      <c r="J25" s="96"/>
+      <c r="K25" s="97"/>
+      <c r="L25" s="97"/>
+      <c r="M25" s="97"/>
+      <c r="N25" s="97"/>
+      <c r="O25" s="97"/>
+      <c r="P25" s="98"/>
+      <c r="Q25" s="99"/>
+      <c r="R25" s="100"/>
+      <c r="S25" s="100"/>
+      <c r="T25" s="100"/>
+      <c r="U25" s="100"/>
+      <c r="V25" s="100"/>
+      <c r="W25" s="100"/>
+      <c r="X25" s="100"/>
+      <c r="Y25" s="100"/>
+      <c r="Z25" s="100"/>
+      <c r="AA25" s="100"/>
+      <c r="AB25" s="100"/>
+      <c r="AC25" s="100"/>
+      <c r="AD25" s="100"/>
+      <c r="AE25" s="101"/>
+      <c r="AF25" s="96"/>
+      <c r="AG25" s="97"/>
+      <c r="AH25" s="97"/>
+      <c r="AI25" s="98"/>
     </row>
     <row r="26" spans="1:35" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="13"/>
-      <c r="B26" s="155"/>
-      <c r="C26" s="129"/>
-      <c r="D26" s="130"/>
-      <c r="E26" s="131"/>
-      <c r="F26" s="132"/>
-      <c r="G26" s="155"/>
-      <c r="H26" s="134"/>
-      <c r="I26" s="129"/>
-      <c r="J26" s="156"/>
-      <c r="K26" s="136"/>
-      <c r="L26" s="136"/>
-      <c r="M26" s="136"/>
-      <c r="N26" s="136"/>
-      <c r="O26" s="136"/>
-      <c r="P26" s="137"/>
-      <c r="Q26" s="157"/>
-      <c r="R26" s="139"/>
-      <c r="S26" s="139"/>
-      <c r="T26" s="139"/>
-      <c r="U26" s="139"/>
-      <c r="V26" s="139"/>
-      <c r="W26" s="139"/>
-      <c r="X26" s="139"/>
-      <c r="Y26" s="139"/>
-      <c r="Z26" s="139"/>
-      <c r="AA26" s="139"/>
-      <c r="AB26" s="139"/>
-      <c r="AC26" s="139"/>
-      <c r="AD26" s="139"/>
-      <c r="AE26" s="140"/>
-      <c r="AF26" s="156"/>
-      <c r="AG26" s="136"/>
-      <c r="AH26" s="136"/>
-      <c r="AI26" s="137"/>
+      <c r="B26" s="90"/>
+      <c r="C26" s="91"/>
+      <c r="D26" s="92"/>
+      <c r="E26" s="93"/>
+      <c r="F26" s="94"/>
+      <c r="G26" s="90"/>
+      <c r="H26" s="95"/>
+      <c r="I26" s="91"/>
+      <c r="J26" s="96"/>
+      <c r="K26" s="97"/>
+      <c r="L26" s="97"/>
+      <c r="M26" s="97"/>
+      <c r="N26" s="97"/>
+      <c r="O26" s="97"/>
+      <c r="P26" s="98"/>
+      <c r="Q26" s="99"/>
+      <c r="R26" s="100"/>
+      <c r="S26" s="100"/>
+      <c r="T26" s="100"/>
+      <c r="U26" s="100"/>
+      <c r="V26" s="100"/>
+      <c r="W26" s="100"/>
+      <c r="X26" s="100"/>
+      <c r="Y26" s="100"/>
+      <c r="Z26" s="100"/>
+      <c r="AA26" s="100"/>
+      <c r="AB26" s="100"/>
+      <c r="AC26" s="100"/>
+      <c r="AD26" s="100"/>
+      <c r="AE26" s="101"/>
+      <c r="AF26" s="96"/>
+      <c r="AG26" s="97"/>
+      <c r="AH26" s="97"/>
+      <c r="AI26" s="98"/>
     </row>
     <row r="27" spans="1:35" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="13"/>
-      <c r="B27" s="155"/>
-      <c r="C27" s="129"/>
-      <c r="D27" s="130"/>
-      <c r="E27" s="131"/>
-      <c r="F27" s="132"/>
-      <c r="G27" s="155"/>
-      <c r="H27" s="134"/>
-      <c r="I27" s="129"/>
-      <c r="J27" s="156"/>
-      <c r="K27" s="136"/>
-      <c r="L27" s="136"/>
-      <c r="M27" s="136"/>
-      <c r="N27" s="136"/>
-      <c r="O27" s="136"/>
-      <c r="P27" s="137"/>
-      <c r="Q27" s="157"/>
-      <c r="R27" s="139"/>
-      <c r="S27" s="139"/>
-      <c r="T27" s="139"/>
-      <c r="U27" s="139"/>
-      <c r="V27" s="139"/>
-      <c r="W27" s="139"/>
-      <c r="X27" s="139"/>
-      <c r="Y27" s="139"/>
-      <c r="Z27" s="139"/>
-      <c r="AA27" s="139"/>
-      <c r="AB27" s="139"/>
-      <c r="AC27" s="139"/>
-      <c r="AD27" s="139"/>
-      <c r="AE27" s="140"/>
-      <c r="AF27" s="156"/>
-      <c r="AG27" s="136"/>
-      <c r="AH27" s="136"/>
-      <c r="AI27" s="137"/>
+      <c r="B27" s="90"/>
+      <c r="C27" s="91"/>
+      <c r="D27" s="92"/>
+      <c r="E27" s="93"/>
+      <c r="F27" s="94"/>
+      <c r="G27" s="90"/>
+      <c r="H27" s="95"/>
+      <c r="I27" s="91"/>
+      <c r="J27" s="96"/>
+      <c r="K27" s="97"/>
+      <c r="L27" s="97"/>
+      <c r="M27" s="97"/>
+      <c r="N27" s="97"/>
+      <c r="O27" s="97"/>
+      <c r="P27" s="98"/>
+      <c r="Q27" s="99"/>
+      <c r="R27" s="100"/>
+      <c r="S27" s="100"/>
+      <c r="T27" s="100"/>
+      <c r="U27" s="100"/>
+      <c r="V27" s="100"/>
+      <c r="W27" s="100"/>
+      <c r="X27" s="100"/>
+      <c r="Y27" s="100"/>
+      <c r="Z27" s="100"/>
+      <c r="AA27" s="100"/>
+      <c r="AB27" s="100"/>
+      <c r="AC27" s="100"/>
+      <c r="AD27" s="100"/>
+      <c r="AE27" s="101"/>
+      <c r="AF27" s="96"/>
+      <c r="AG27" s="97"/>
+      <c r="AH27" s="97"/>
+      <c r="AI27" s="98"/>
     </row>
     <row r="28" spans="1:35" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="13"/>
-      <c r="B28" s="155"/>
-      <c r="C28" s="129"/>
-      <c r="D28" s="130"/>
-      <c r="E28" s="131"/>
-      <c r="F28" s="132"/>
-      <c r="G28" s="155"/>
-      <c r="H28" s="134"/>
-      <c r="I28" s="129"/>
-      <c r="J28" s="156"/>
-      <c r="K28" s="136"/>
-      <c r="L28" s="136"/>
-      <c r="M28" s="136"/>
-      <c r="N28" s="136"/>
-      <c r="O28" s="136"/>
-      <c r="P28" s="137"/>
-      <c r="Q28" s="157"/>
-      <c r="R28" s="139"/>
-      <c r="S28" s="139"/>
-      <c r="T28" s="139"/>
-      <c r="U28" s="139"/>
-      <c r="V28" s="139"/>
-      <c r="W28" s="139"/>
-      <c r="X28" s="139"/>
-      <c r="Y28" s="139"/>
-      <c r="Z28" s="139"/>
-      <c r="AA28" s="139"/>
-      <c r="AB28" s="139"/>
-      <c r="AC28" s="139"/>
-      <c r="AD28" s="139"/>
-      <c r="AE28" s="140"/>
-      <c r="AF28" s="156"/>
-      <c r="AG28" s="136"/>
-      <c r="AH28" s="136"/>
-      <c r="AI28" s="137"/>
+      <c r="B28" s="90"/>
+      <c r="C28" s="91"/>
+      <c r="D28" s="92"/>
+      <c r="E28" s="93"/>
+      <c r="F28" s="94"/>
+      <c r="G28" s="90"/>
+      <c r="H28" s="95"/>
+      <c r="I28" s="91"/>
+      <c r="J28" s="96"/>
+      <c r="K28" s="97"/>
+      <c r="L28" s="97"/>
+      <c r="M28" s="97"/>
+      <c r="N28" s="97"/>
+      <c r="O28" s="97"/>
+      <c r="P28" s="98"/>
+      <c r="Q28" s="99"/>
+      <c r="R28" s="100"/>
+      <c r="S28" s="100"/>
+      <c r="T28" s="100"/>
+      <c r="U28" s="100"/>
+      <c r="V28" s="100"/>
+      <c r="W28" s="100"/>
+      <c r="X28" s="100"/>
+      <c r="Y28" s="100"/>
+      <c r="Z28" s="100"/>
+      <c r="AA28" s="100"/>
+      <c r="AB28" s="100"/>
+      <c r="AC28" s="100"/>
+      <c r="AD28" s="100"/>
+      <c r="AE28" s="101"/>
+      <c r="AF28" s="96"/>
+      <c r="AG28" s="97"/>
+      <c r="AH28" s="97"/>
+      <c r="AI28" s="98"/>
     </row>
     <row r="29" spans="1:35" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="13"/>
-      <c r="B29" s="155"/>
-      <c r="C29" s="129"/>
-      <c r="D29" s="130"/>
-      <c r="E29" s="131"/>
-      <c r="F29" s="132"/>
-      <c r="G29" s="155"/>
-      <c r="H29" s="134"/>
-      <c r="I29" s="129"/>
-      <c r="J29" s="156"/>
-      <c r="K29" s="136"/>
-      <c r="L29" s="136"/>
-      <c r="M29" s="136"/>
-      <c r="N29" s="136"/>
-      <c r="O29" s="136"/>
-      <c r="P29" s="137"/>
-      <c r="Q29" s="157"/>
-      <c r="R29" s="139"/>
-      <c r="S29" s="139"/>
-      <c r="T29" s="139"/>
-      <c r="U29" s="139"/>
-      <c r="V29" s="139"/>
-      <c r="W29" s="139"/>
-      <c r="X29" s="139"/>
-      <c r="Y29" s="139"/>
-      <c r="Z29" s="139"/>
-      <c r="AA29" s="139"/>
-      <c r="AB29" s="139"/>
-      <c r="AC29" s="139"/>
-      <c r="AD29" s="139"/>
-      <c r="AE29" s="140"/>
-      <c r="AF29" s="156"/>
-      <c r="AG29" s="136"/>
-      <c r="AH29" s="136"/>
-      <c r="AI29" s="137"/>
+      <c r="B29" s="90"/>
+      <c r="C29" s="91"/>
+      <c r="D29" s="92"/>
+      <c r="E29" s="93"/>
+      <c r="F29" s="94"/>
+      <c r="G29" s="90"/>
+      <c r="H29" s="95"/>
+      <c r="I29" s="91"/>
+      <c r="J29" s="96"/>
+      <c r="K29" s="97"/>
+      <c r="L29" s="97"/>
+      <c r="M29" s="97"/>
+      <c r="N29" s="97"/>
+      <c r="O29" s="97"/>
+      <c r="P29" s="98"/>
+      <c r="Q29" s="99"/>
+      <c r="R29" s="100"/>
+      <c r="S29" s="100"/>
+      <c r="T29" s="100"/>
+      <c r="U29" s="100"/>
+      <c r="V29" s="100"/>
+      <c r="W29" s="100"/>
+      <c r="X29" s="100"/>
+      <c r="Y29" s="100"/>
+      <c r="Z29" s="100"/>
+      <c r="AA29" s="100"/>
+      <c r="AB29" s="100"/>
+      <c r="AC29" s="100"/>
+      <c r="AD29" s="100"/>
+      <c r="AE29" s="101"/>
+      <c r="AF29" s="96"/>
+      <c r="AG29" s="97"/>
+      <c r="AH29" s="97"/>
+      <c r="AI29" s="98"/>
     </row>
     <row r="30" spans="1:35" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="13"/>
-      <c r="B30" s="155"/>
-      <c r="C30" s="129"/>
-      <c r="D30" s="130"/>
-      <c r="E30" s="131"/>
-      <c r="F30" s="132"/>
-      <c r="G30" s="155"/>
-      <c r="H30" s="134"/>
-      <c r="I30" s="129"/>
-      <c r="J30" s="156"/>
-      <c r="K30" s="136"/>
-      <c r="L30" s="136"/>
-      <c r="M30" s="136"/>
-      <c r="N30" s="136"/>
-      <c r="O30" s="136"/>
-      <c r="P30" s="137"/>
-      <c r="Q30" s="157"/>
-      <c r="R30" s="139"/>
-      <c r="S30" s="139"/>
-      <c r="T30" s="139"/>
-      <c r="U30" s="139"/>
-      <c r="V30" s="139"/>
-      <c r="W30" s="139"/>
-      <c r="X30" s="139"/>
-      <c r="Y30" s="139"/>
-      <c r="Z30" s="139"/>
-      <c r="AA30" s="139"/>
-      <c r="AB30" s="139"/>
-      <c r="AC30" s="139"/>
-      <c r="AD30" s="139"/>
-      <c r="AE30" s="140"/>
-      <c r="AF30" s="156"/>
-      <c r="AG30" s="136"/>
-      <c r="AH30" s="136"/>
-      <c r="AI30" s="137"/>
+      <c r="B30" s="90"/>
+      <c r="C30" s="91"/>
+      <c r="D30" s="92"/>
+      <c r="E30" s="93"/>
+      <c r="F30" s="94"/>
+      <c r="G30" s="90"/>
+      <c r="H30" s="95"/>
+      <c r="I30" s="91"/>
+      <c r="J30" s="96"/>
+      <c r="K30" s="97"/>
+      <c r="L30" s="97"/>
+      <c r="M30" s="97"/>
+      <c r="N30" s="97"/>
+      <c r="O30" s="97"/>
+      <c r="P30" s="98"/>
+      <c r="Q30" s="99"/>
+      <c r="R30" s="100"/>
+      <c r="S30" s="100"/>
+      <c r="T30" s="100"/>
+      <c r="U30" s="100"/>
+      <c r="V30" s="100"/>
+      <c r="W30" s="100"/>
+      <c r="X30" s="100"/>
+      <c r="Y30" s="100"/>
+      <c r="Z30" s="100"/>
+      <c r="AA30" s="100"/>
+      <c r="AB30" s="100"/>
+      <c r="AC30" s="100"/>
+      <c r="AD30" s="100"/>
+      <c r="AE30" s="101"/>
+      <c r="AF30" s="96"/>
+      <c r="AG30" s="97"/>
+      <c r="AH30" s="97"/>
+      <c r="AI30" s="98"/>
     </row>
     <row r="31" spans="1:35" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="13"/>
-      <c r="B31" s="155"/>
-      <c r="C31" s="129"/>
-      <c r="D31" s="130"/>
-      <c r="E31" s="131"/>
-      <c r="F31" s="132"/>
-      <c r="G31" s="155"/>
-      <c r="H31" s="134"/>
-      <c r="I31" s="129"/>
-      <c r="J31" s="156"/>
-      <c r="K31" s="136"/>
-      <c r="L31" s="136"/>
-      <c r="M31" s="136"/>
-      <c r="N31" s="136"/>
-      <c r="O31" s="136"/>
-      <c r="P31" s="137"/>
-      <c r="Q31" s="157"/>
-      <c r="R31" s="139"/>
-      <c r="S31" s="139"/>
-      <c r="T31" s="139"/>
-      <c r="U31" s="139"/>
-      <c r="V31" s="139"/>
-      <c r="W31" s="139"/>
-      <c r="X31" s="139"/>
-      <c r="Y31" s="139"/>
-      <c r="Z31" s="139"/>
-      <c r="AA31" s="139"/>
-      <c r="AB31" s="139"/>
-      <c r="AC31" s="139"/>
-      <c r="AD31" s="139"/>
-      <c r="AE31" s="140"/>
-      <c r="AF31" s="156"/>
-      <c r="AG31" s="136"/>
-      <c r="AH31" s="136"/>
-      <c r="AI31" s="137"/>
+      <c r="B31" s="90"/>
+      <c r="C31" s="91"/>
+      <c r="D31" s="92"/>
+      <c r="E31" s="93"/>
+      <c r="F31" s="94"/>
+      <c r="G31" s="90"/>
+      <c r="H31" s="95"/>
+      <c r="I31" s="91"/>
+      <c r="J31" s="96"/>
+      <c r="K31" s="97"/>
+      <c r="L31" s="97"/>
+      <c r="M31" s="97"/>
+      <c r="N31" s="97"/>
+      <c r="O31" s="97"/>
+      <c r="P31" s="98"/>
+      <c r="Q31" s="99"/>
+      <c r="R31" s="100"/>
+      <c r="S31" s="100"/>
+      <c r="T31" s="100"/>
+      <c r="U31" s="100"/>
+      <c r="V31" s="100"/>
+      <c r="W31" s="100"/>
+      <c r="X31" s="100"/>
+      <c r="Y31" s="100"/>
+      <c r="Z31" s="100"/>
+      <c r="AA31" s="100"/>
+      <c r="AB31" s="100"/>
+      <c r="AC31" s="100"/>
+      <c r="AD31" s="100"/>
+      <c r="AE31" s="101"/>
+      <c r="AF31" s="96"/>
+      <c r="AG31" s="97"/>
+      <c r="AH31" s="97"/>
+      <c r="AI31" s="98"/>
     </row>
     <row r="32" spans="1:35" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="13"/>
-      <c r="B32" s="155"/>
-      <c r="C32" s="129"/>
-      <c r="D32" s="130"/>
-      <c r="E32" s="131"/>
-      <c r="F32" s="132"/>
-      <c r="G32" s="155"/>
-      <c r="H32" s="134"/>
-      <c r="I32" s="129"/>
-      <c r="J32" s="156"/>
-      <c r="K32" s="158"/>
-      <c r="L32" s="136"/>
-      <c r="M32" s="136"/>
-      <c r="N32" s="136"/>
-      <c r="O32" s="136"/>
-      <c r="P32" s="137"/>
-      <c r="Q32" s="157"/>
-      <c r="R32" s="139"/>
-      <c r="S32" s="139"/>
-      <c r="T32" s="139"/>
-      <c r="U32" s="139"/>
-      <c r="V32" s="139"/>
-      <c r="W32" s="139"/>
-      <c r="X32" s="139"/>
-      <c r="Y32" s="139"/>
-      <c r="Z32" s="139"/>
-      <c r="AA32" s="139"/>
-      <c r="AB32" s="139"/>
-      <c r="AC32" s="139"/>
-      <c r="AD32" s="139"/>
-      <c r="AE32" s="140"/>
-      <c r="AF32" s="156"/>
-      <c r="AG32" s="136"/>
-      <c r="AH32" s="136"/>
-      <c r="AI32" s="137"/>
+      <c r="B32" s="90"/>
+      <c r="C32" s="91"/>
+      <c r="D32" s="92"/>
+      <c r="E32" s="93"/>
+      <c r="F32" s="94"/>
+      <c r="G32" s="90"/>
+      <c r="H32" s="95"/>
+      <c r="I32" s="91"/>
+      <c r="J32" s="96"/>
+      <c r="K32" s="102"/>
+      <c r="L32" s="97"/>
+      <c r="M32" s="97"/>
+      <c r="N32" s="97"/>
+      <c r="O32" s="97"/>
+      <c r="P32" s="98"/>
+      <c r="Q32" s="99"/>
+      <c r="R32" s="100"/>
+      <c r="S32" s="100"/>
+      <c r="T32" s="100"/>
+      <c r="U32" s="100"/>
+      <c r="V32" s="100"/>
+      <c r="W32" s="100"/>
+      <c r="X32" s="100"/>
+      <c r="Y32" s="100"/>
+      <c r="Z32" s="100"/>
+      <c r="AA32" s="100"/>
+      <c r="AB32" s="100"/>
+      <c r="AC32" s="100"/>
+      <c r="AD32" s="100"/>
+      <c r="AE32" s="101"/>
+      <c r="AF32" s="96"/>
+      <c r="AG32" s="97"/>
+      <c r="AH32" s="97"/>
+      <c r="AI32" s="98"/>
     </row>
     <row r="33" spans="1:35" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="13"/>
-      <c r="B33" s="155"/>
-      <c r="C33" s="129"/>
-      <c r="D33" s="130"/>
-      <c r="E33" s="131"/>
-      <c r="F33" s="132"/>
-      <c r="G33" s="155"/>
-      <c r="H33" s="134"/>
-      <c r="I33" s="129"/>
-      <c r="J33" s="156"/>
-      <c r="K33" s="136"/>
-      <c r="L33" s="136"/>
-      <c r="M33" s="136"/>
-      <c r="N33" s="136"/>
-      <c r="O33" s="136"/>
-      <c r="P33" s="137"/>
-      <c r="Q33" s="157"/>
-      <c r="R33" s="139"/>
-      <c r="S33" s="139"/>
-      <c r="T33" s="139"/>
-      <c r="U33" s="139"/>
-      <c r="V33" s="139"/>
-      <c r="W33" s="139"/>
-      <c r="X33" s="139"/>
-      <c r="Y33" s="139"/>
-      <c r="Z33" s="139"/>
-      <c r="AA33" s="139"/>
-      <c r="AB33" s="139"/>
-      <c r="AC33" s="139"/>
-      <c r="AD33" s="139"/>
-      <c r="AE33" s="140"/>
-      <c r="AF33" s="156"/>
-      <c r="AG33" s="136"/>
-      <c r="AH33" s="136"/>
-      <c r="AI33" s="137"/>
+      <c r="B33" s="90"/>
+      <c r="C33" s="91"/>
+      <c r="D33" s="92"/>
+      <c r="E33" s="93"/>
+      <c r="F33" s="94"/>
+      <c r="G33" s="90"/>
+      <c r="H33" s="95"/>
+      <c r="I33" s="91"/>
+      <c r="J33" s="96"/>
+      <c r="K33" s="97"/>
+      <c r="L33" s="97"/>
+      <c r="M33" s="97"/>
+      <c r="N33" s="97"/>
+      <c r="O33" s="97"/>
+      <c r="P33" s="98"/>
+      <c r="Q33" s="99"/>
+      <c r="R33" s="100"/>
+      <c r="S33" s="100"/>
+      <c r="T33" s="100"/>
+      <c r="U33" s="100"/>
+      <c r="V33" s="100"/>
+      <c r="W33" s="100"/>
+      <c r="X33" s="100"/>
+      <c r="Y33" s="100"/>
+      <c r="Z33" s="100"/>
+      <c r="AA33" s="100"/>
+      <c r="AB33" s="100"/>
+      <c r="AC33" s="100"/>
+      <c r="AD33" s="100"/>
+      <c r="AE33" s="101"/>
+      <c r="AF33" s="96"/>
+      <c r="AG33" s="97"/>
+      <c r="AH33" s="97"/>
+      <c r="AI33" s="98"/>
     </row>
     <row r="34" spans="1:35" ht="14.25" x14ac:dyDescent="0.15">
       <c r="K34" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="179">
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="J33:P33"/>
-    <mergeCell ref="Q33:AE33"/>
-    <mergeCell ref="AF33:AI33"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="J32:P32"/>
-    <mergeCell ref="Q32:AE32"/>
-    <mergeCell ref="AF32:AI32"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:P31"/>
-    <mergeCell ref="Q31:AE31"/>
-    <mergeCell ref="AF31:AI31"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:P30"/>
-    <mergeCell ref="Q30:AE30"/>
-    <mergeCell ref="AF30:AI30"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:P29"/>
-    <mergeCell ref="Q29:AE29"/>
-    <mergeCell ref="AF29:AI29"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:P28"/>
-    <mergeCell ref="Q28:AE28"/>
-    <mergeCell ref="AF28:AI28"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:P27"/>
-    <mergeCell ref="Q27:AE27"/>
-    <mergeCell ref="AF27:AI27"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="J26:P26"/>
-    <mergeCell ref="Q26:AE26"/>
-    <mergeCell ref="AF26:AI26"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:P25"/>
-    <mergeCell ref="Q25:AE25"/>
-    <mergeCell ref="AF25:AI25"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:P24"/>
-    <mergeCell ref="Q24:AE24"/>
-    <mergeCell ref="AF24:AI24"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:P23"/>
-    <mergeCell ref="Q23:AE23"/>
-    <mergeCell ref="AF23:AI23"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:P22"/>
-    <mergeCell ref="Q22:AE22"/>
-    <mergeCell ref="AF22:AI22"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:P21"/>
-    <mergeCell ref="Q21:AE21"/>
-    <mergeCell ref="AF21:AI21"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:P20"/>
-    <mergeCell ref="Q20:AE20"/>
-    <mergeCell ref="AF20:AI20"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:P19"/>
-    <mergeCell ref="Q19:AE19"/>
-    <mergeCell ref="AF19:AI19"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="J18:P18"/>
-    <mergeCell ref="Q18:AE18"/>
-    <mergeCell ref="AF18:AI18"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:P17"/>
-    <mergeCell ref="Q17:AE17"/>
-    <mergeCell ref="AF17:AI17"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:P16"/>
-    <mergeCell ref="Q16:AE16"/>
-    <mergeCell ref="AF16:AI16"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:P15"/>
-    <mergeCell ref="Q15:AE15"/>
-    <mergeCell ref="AF15:AI15"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="J14:P14"/>
-    <mergeCell ref="Q14:AE14"/>
-    <mergeCell ref="AF14:AI14"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="J13:P13"/>
-    <mergeCell ref="Q13:AE13"/>
-    <mergeCell ref="AF13:AI13"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="J12:P12"/>
-    <mergeCell ref="Q12:AE12"/>
-    <mergeCell ref="AF12:AI12"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="J11:P11"/>
-    <mergeCell ref="Q11:AE11"/>
-    <mergeCell ref="AF11:AI11"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="J10:P10"/>
-    <mergeCell ref="Q10:AE10"/>
-    <mergeCell ref="AF10:AI10"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="J9:P9"/>
-    <mergeCell ref="Q9:AE9"/>
-    <mergeCell ref="AF9:AI9"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="J8:P8"/>
-    <mergeCell ref="Q8:AE8"/>
-    <mergeCell ref="AF8:AI8"/>
     <mergeCell ref="AG3:AI3"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="D7:F7"/>
@@ -15868,6 +15712,162 @@
     <mergeCell ref="E3:N3"/>
     <mergeCell ref="AA3:AB3"/>
     <mergeCell ref="AC3:AF3"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="J9:P9"/>
+    <mergeCell ref="Q9:AE9"/>
+    <mergeCell ref="AF9:AI9"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="J8:P8"/>
+    <mergeCell ref="Q8:AE8"/>
+    <mergeCell ref="AF8:AI8"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="J11:P11"/>
+    <mergeCell ref="Q11:AE11"/>
+    <mergeCell ref="AF11:AI11"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="J10:P10"/>
+    <mergeCell ref="Q10:AE10"/>
+    <mergeCell ref="AF10:AI10"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="J13:P13"/>
+    <mergeCell ref="Q13:AE13"/>
+    <mergeCell ref="AF13:AI13"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="J12:P12"/>
+    <mergeCell ref="Q12:AE12"/>
+    <mergeCell ref="AF12:AI12"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:P15"/>
+    <mergeCell ref="Q15:AE15"/>
+    <mergeCell ref="AF15:AI15"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="J14:P14"/>
+    <mergeCell ref="Q14:AE14"/>
+    <mergeCell ref="AF14:AI14"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:P17"/>
+    <mergeCell ref="Q17:AE17"/>
+    <mergeCell ref="AF17:AI17"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:P16"/>
+    <mergeCell ref="Q16:AE16"/>
+    <mergeCell ref="AF16:AI16"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:P19"/>
+    <mergeCell ref="Q19:AE19"/>
+    <mergeCell ref="AF19:AI19"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="J18:P18"/>
+    <mergeCell ref="Q18:AE18"/>
+    <mergeCell ref="AF18:AI18"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:P21"/>
+    <mergeCell ref="Q21:AE21"/>
+    <mergeCell ref="AF21:AI21"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:P20"/>
+    <mergeCell ref="Q20:AE20"/>
+    <mergeCell ref="AF20:AI20"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:P23"/>
+    <mergeCell ref="Q23:AE23"/>
+    <mergeCell ref="AF23:AI23"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:P22"/>
+    <mergeCell ref="Q22:AE22"/>
+    <mergeCell ref="AF22:AI22"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:P25"/>
+    <mergeCell ref="Q25:AE25"/>
+    <mergeCell ref="AF25:AI25"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:P24"/>
+    <mergeCell ref="Q24:AE24"/>
+    <mergeCell ref="AF24:AI24"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:P27"/>
+    <mergeCell ref="Q27:AE27"/>
+    <mergeCell ref="AF27:AI27"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="J26:P26"/>
+    <mergeCell ref="Q26:AE26"/>
+    <mergeCell ref="AF26:AI26"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:P29"/>
+    <mergeCell ref="Q29:AE29"/>
+    <mergeCell ref="AF29:AI29"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:P28"/>
+    <mergeCell ref="Q28:AE28"/>
+    <mergeCell ref="AF28:AI28"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:P31"/>
+    <mergeCell ref="Q31:AE31"/>
+    <mergeCell ref="AF31:AI31"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:P30"/>
+    <mergeCell ref="Q30:AE30"/>
+    <mergeCell ref="AF30:AI30"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="J33:P33"/>
+    <mergeCell ref="Q33:AE33"/>
+    <mergeCell ref="AF33:AI33"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="J32:P32"/>
+    <mergeCell ref="Q32:AE32"/>
+    <mergeCell ref="AF32:AI32"/>
   </mergeCells>
   <phoneticPr fontId="10"/>
   <printOptions horizontalCentered="1"/>
@@ -16019,163 +16019,163 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="131" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="97"/>
-      <c r="D1" s="98"/>
-      <c r="E1" s="99" t="str">
+      <c r="B1" s="132"/>
+      <c r="C1" s="132"/>
+      <c r="D1" s="133"/>
+      <c r="E1" s="134" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E1")&lt;&gt;"",INDIRECT("変更履歴!E1"),"")</f>
         <v/>
       </c>
-      <c r="F1" s="100"/>
-      <c r="G1" s="100"/>
-      <c r="H1" s="100"/>
-      <c r="I1" s="100"/>
-      <c r="J1" s="100"/>
-      <c r="K1" s="100"/>
-      <c r="L1" s="100"/>
-      <c r="M1" s="100"/>
-      <c r="N1" s="101"/>
-      <c r="O1" s="107" t="s">
+      <c r="F1" s="135"/>
+      <c r="G1" s="135"/>
+      <c r="H1" s="135"/>
+      <c r="I1" s="135"/>
+      <c r="J1" s="135"/>
+      <c r="K1" s="135"/>
+      <c r="L1" s="135"/>
+      <c r="M1" s="135"/>
+      <c r="N1" s="136"/>
+      <c r="O1" s="142" t="s">
         <v>11</v>
       </c>
-      <c r="P1" s="108"/>
-      <c r="Q1" s="108"/>
-      <c r="R1" s="109"/>
-      <c r="S1" s="164" t="str">
+      <c r="P1" s="143"/>
+      <c r="Q1" s="143"/>
+      <c r="R1" s="144"/>
+      <c r="S1" s="163" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!S1")&lt;&gt;"",INDIRECT("変更履歴!S1"),"")</f>
         <v>Nablarch開発標準設計書一覧</v>
       </c>
-      <c r="T1" s="117"/>
-      <c r="U1" s="117"/>
-      <c r="V1" s="117"/>
-      <c r="W1" s="117"/>
-      <c r="X1" s="117"/>
-      <c r="Y1" s="117"/>
-      <c r="Z1" s="118"/>
-      <c r="AA1" s="162" t="s">
+      <c r="T1" s="152"/>
+      <c r="U1" s="152"/>
+      <c r="V1" s="152"/>
+      <c r="W1" s="152"/>
+      <c r="X1" s="152"/>
+      <c r="Y1" s="152"/>
+      <c r="Z1" s="153"/>
+      <c r="AA1" s="164" t="s">
         <v>12</v>
       </c>
-      <c r="AB1" s="163"/>
-      <c r="AC1" s="125" t="str">
+      <c r="AB1" s="165"/>
+      <c r="AC1" s="160" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC1")&lt;&gt;"",INDIRECT("変更履歴!AC1"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="126"/>
-      <c r="AE1" s="126"/>
-      <c r="AF1" s="127"/>
-      <c r="AG1" s="159">
+      <c r="AD1" s="161"/>
+      <c r="AE1" s="161"/>
+      <c r="AF1" s="162"/>
+      <c r="AG1" s="166">
         <f ca="1">IF(INDIRECT("変更履歴!AG1")&lt;&gt;"",INDIRECT("変更履歴!AG1"),"")</f>
         <v>43336</v>
       </c>
-      <c r="AH1" s="160"/>
-      <c r="AI1" s="161"/>
+      <c r="AH1" s="167"/>
+      <c r="AI1" s="168"/>
       <c r="AJ1" s="1"/>
       <c r="AK1" s="1"/>
       <c r="AL1" s="2"/>
     </row>
     <row r="2" spans="1:38" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="96" t="s">
+      <c r="A2" s="131" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="97"/>
-      <c r="C2" s="97"/>
-      <c r="D2" s="98"/>
-      <c r="E2" s="99" t="str">
+      <c r="B2" s="132"/>
+      <c r="C2" s="132"/>
+      <c r="D2" s="133"/>
+      <c r="E2" s="134" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E2")&lt;&gt;"",INDIRECT("変更履歴!E2"),"")</f>
         <v/>
       </c>
-      <c r="F2" s="100"/>
-      <c r="G2" s="100"/>
-      <c r="H2" s="100"/>
-      <c r="I2" s="100"/>
-      <c r="J2" s="100"/>
-      <c r="K2" s="100"/>
-      <c r="L2" s="100"/>
-      <c r="M2" s="100"/>
-      <c r="N2" s="101"/>
-      <c r="O2" s="110"/>
-      <c r="P2" s="111"/>
-      <c r="Q2" s="111"/>
-      <c r="R2" s="112"/>
-      <c r="S2" s="119"/>
-      <c r="T2" s="120"/>
-      <c r="U2" s="120"/>
-      <c r="V2" s="120"/>
-      <c r="W2" s="120"/>
-      <c r="X2" s="120"/>
-      <c r="Y2" s="120"/>
-      <c r="Z2" s="121"/>
-      <c r="AA2" s="162" t="s">
+      <c r="F2" s="135"/>
+      <c r="G2" s="135"/>
+      <c r="H2" s="135"/>
+      <c r="I2" s="135"/>
+      <c r="J2" s="135"/>
+      <c r="K2" s="135"/>
+      <c r="L2" s="135"/>
+      <c r="M2" s="135"/>
+      <c r="N2" s="136"/>
+      <c r="O2" s="145"/>
+      <c r="P2" s="146"/>
+      <c r="Q2" s="146"/>
+      <c r="R2" s="147"/>
+      <c r="S2" s="154"/>
+      <c r="T2" s="155"/>
+      <c r="U2" s="155"/>
+      <c r="V2" s="155"/>
+      <c r="W2" s="155"/>
+      <c r="X2" s="155"/>
+      <c r="Y2" s="155"/>
+      <c r="Z2" s="156"/>
+      <c r="AA2" s="164" t="s">
         <v>13</v>
       </c>
-      <c r="AB2" s="163"/>
-      <c r="AC2" s="125" t="str">
+      <c r="AB2" s="165"/>
+      <c r="AC2" s="160" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC2")&lt;&gt;"",INDIRECT("変更履歴!AC2"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD2" s="126"/>
-      <c r="AE2" s="126"/>
-      <c r="AF2" s="127"/>
-      <c r="AG2" s="159">
+      <c r="AD2" s="161"/>
+      <c r="AE2" s="161"/>
+      <c r="AF2" s="162"/>
+      <c r="AG2" s="166">
         <f ca="1">IF(INDIRECT("変更履歴!AG2")&lt;&gt;"",INDIRECT("変更履歴!AG2"),"")</f>
-        <v>45464</v>
-      </c>
-      <c r="AH2" s="160"/>
-      <c r="AI2" s="161"/>
+        <v>45565</v>
+      </c>
+      <c r="AH2" s="167"/>
+      <c r="AI2" s="168"/>
       <c r="AJ2" s="1"/>
       <c r="AK2" s="1"/>
       <c r="AL2" s="1"/>
     </row>
     <row r="3" spans="1:38" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="96" t="s">
+      <c r="A3" s="131" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="97"/>
-      <c r="C3" s="97"/>
-      <c r="D3" s="98"/>
-      <c r="E3" s="99" t="str">
+      <c r="B3" s="132"/>
+      <c r="C3" s="132"/>
+      <c r="D3" s="133"/>
+      <c r="E3" s="134" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E3")&lt;&gt;"",INDIRECT("変更履歴!E3"),"")</f>
         <v/>
       </c>
-      <c r="F3" s="100"/>
-      <c r="G3" s="100"/>
-      <c r="H3" s="100"/>
-      <c r="I3" s="100"/>
-      <c r="J3" s="100"/>
-      <c r="K3" s="100"/>
-      <c r="L3" s="100"/>
-      <c r="M3" s="100"/>
-      <c r="N3" s="101"/>
-      <c r="O3" s="113"/>
-      <c r="P3" s="114"/>
-      <c r="Q3" s="114"/>
-      <c r="R3" s="115"/>
-      <c r="S3" s="122"/>
-      <c r="T3" s="123"/>
-      <c r="U3" s="123"/>
-      <c r="V3" s="123"/>
-      <c r="W3" s="123"/>
-      <c r="X3" s="123"/>
-      <c r="Y3" s="123"/>
-      <c r="Z3" s="124"/>
-      <c r="AA3" s="162"/>
-      <c r="AB3" s="163"/>
-      <c r="AC3" s="125" t="str">
+      <c r="F3" s="135"/>
+      <c r="G3" s="135"/>
+      <c r="H3" s="135"/>
+      <c r="I3" s="135"/>
+      <c r="J3" s="135"/>
+      <c r="K3" s="135"/>
+      <c r="L3" s="135"/>
+      <c r="M3" s="135"/>
+      <c r="N3" s="136"/>
+      <c r="O3" s="148"/>
+      <c r="P3" s="149"/>
+      <c r="Q3" s="149"/>
+      <c r="R3" s="150"/>
+      <c r="S3" s="157"/>
+      <c r="T3" s="158"/>
+      <c r="U3" s="158"/>
+      <c r="V3" s="158"/>
+      <c r="W3" s="158"/>
+      <c r="X3" s="158"/>
+      <c r="Y3" s="158"/>
+      <c r="Z3" s="159"/>
+      <c r="AA3" s="164"/>
+      <c r="AB3" s="165"/>
+      <c r="AC3" s="160" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC3")&lt;&gt;"",INDIRECT("変更履歴!AC3"),"")</f>
         <v/>
       </c>
-      <c r="AD3" s="126"/>
-      <c r="AE3" s="126"/>
-      <c r="AF3" s="127"/>
-      <c r="AG3" s="159" t="str">
+      <c r="AD3" s="161"/>
+      <c r="AE3" s="161"/>
+      <c r="AF3" s="162"/>
+      <c r="AG3" s="166" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AG3")&lt;&gt;"",INDIRECT("変更履歴!AG3"),"")</f>
         <v/>
       </c>
-      <c r="AH3" s="160"/>
-      <c r="AI3" s="161"/>
+      <c r="AH3" s="167"/>
+      <c r="AI3" s="168"/>
       <c r="AJ3" s="1"/>
       <c r="AK3" s="1"/>
       <c r="AL3" s="1"/>
@@ -16445,6 +16445,14 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="AG1:AI1"/>
+    <mergeCell ref="AC1:AF1"/>
+    <mergeCell ref="AC2:AF2"/>
+    <mergeCell ref="AG2:AI2"/>
+    <mergeCell ref="E3:N3"/>
+    <mergeCell ref="AA3:AB3"/>
+    <mergeCell ref="AC3:AF3"/>
+    <mergeCell ref="AG3:AI3"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="E1:N1"/>
     <mergeCell ref="O1:R3"/>
@@ -16454,14 +16462,6 @@
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="E2:N2"/>
     <mergeCell ref="AA2:AB2"/>
-    <mergeCell ref="AG1:AI1"/>
-    <mergeCell ref="AC1:AF1"/>
-    <mergeCell ref="AC2:AF2"/>
-    <mergeCell ref="AG2:AI2"/>
-    <mergeCell ref="E3:N3"/>
-    <mergeCell ref="AA3:AB3"/>
-    <mergeCell ref="AC3:AF3"/>
-    <mergeCell ref="AG3:AI3"/>
   </mergeCells>
   <phoneticPr fontId="10"/>
   <printOptions horizontalCentered="1"/>
@@ -16484,59 +16484,59 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:50" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="131" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="97"/>
-      <c r="D1" s="98"/>
-      <c r="E1" s="99" t="str">
+      <c r="B1" s="132"/>
+      <c r="C1" s="132"/>
+      <c r="D1" s="133"/>
+      <c r="E1" s="134" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E1")&lt;&gt;"",INDIRECT("変更履歴!E1"),"")</f>
         <v/>
       </c>
-      <c r="F1" s="100"/>
-      <c r="G1" s="100"/>
-      <c r="H1" s="100"/>
-      <c r="I1" s="100"/>
-      <c r="J1" s="100"/>
-      <c r="K1" s="100"/>
-      <c r="L1" s="100"/>
-      <c r="M1" s="100"/>
-      <c r="N1" s="101"/>
-      <c r="O1" s="174" t="s">
+      <c r="F1" s="135"/>
+      <c r="G1" s="135"/>
+      <c r="H1" s="135"/>
+      <c r="I1" s="135"/>
+      <c r="J1" s="135"/>
+      <c r="K1" s="135"/>
+      <c r="L1" s="135"/>
+      <c r="M1" s="135"/>
+      <c r="N1" s="136"/>
+      <c r="O1" s="169" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="175"/>
-      <c r="Q1" s="175"/>
-      <c r="R1" s="176"/>
-      <c r="S1" s="165" t="str">
+      <c r="P1" s="170"/>
+      <c r="Q1" s="170"/>
+      <c r="R1" s="171"/>
+      <c r="S1" s="178" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!S1")&lt;&gt;"",INDIRECT("変更履歴!S1"),"")</f>
         <v>Nablarch開発標準設計書一覧</v>
       </c>
-      <c r="T1" s="166"/>
-      <c r="U1" s="166"/>
-      <c r="V1" s="166"/>
-      <c r="W1" s="166"/>
-      <c r="X1" s="166"/>
-      <c r="Y1" s="166"/>
-      <c r="Z1" s="167"/>
-      <c r="AA1" s="96" t="s">
+      <c r="T1" s="179"/>
+      <c r="U1" s="179"/>
+      <c r="V1" s="179"/>
+      <c r="W1" s="179"/>
+      <c r="X1" s="179"/>
+      <c r="Y1" s="179"/>
+      <c r="Z1" s="180"/>
+      <c r="AA1" s="131" t="s">
         <v>3</v>
       </c>
-      <c r="AB1" s="98"/>
-      <c r="AC1" s="125" t="str">
+      <c r="AB1" s="133"/>
+      <c r="AC1" s="160" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC1")&lt;&gt;"",INDIRECT("変更履歴!AC1"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="126"/>
-      <c r="AE1" s="126"/>
-      <c r="AF1" s="127"/>
-      <c r="AG1" s="159">
+      <c r="AD1" s="161"/>
+      <c r="AE1" s="161"/>
+      <c r="AF1" s="162"/>
+      <c r="AG1" s="166">
         <f ca="1">IF(INDIRECT("変更履歴!AG1")&lt;&gt;"",INDIRECT("変更履歴!AG1"),"")</f>
         <v>43336</v>
       </c>
-      <c r="AH1" s="160"/>
-      <c r="AI1" s="161"/>
+      <c r="AH1" s="167"/>
+      <c r="AI1" s="168"/>
       <c r="AJ1" s="6"/>
       <c r="AN1" s="7"/>
       <c r="AO1" s="6"/>
@@ -16550,54 +16550,54 @@
       <c r="AW1" s="6"/>
     </row>
     <row r="2" spans="1:50" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="96" t="s">
+      <c r="A2" s="131" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="97"/>
-      <c r="C2" s="97"/>
-      <c r="D2" s="98"/>
-      <c r="E2" s="99" t="str">
+      <c r="B2" s="132"/>
+      <c r="C2" s="132"/>
+      <c r="D2" s="133"/>
+      <c r="E2" s="134" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E2")&lt;&gt;"",INDIRECT("変更履歴!E2"),"")</f>
         <v/>
       </c>
-      <c r="F2" s="100"/>
-      <c r="G2" s="100"/>
-      <c r="H2" s="100"/>
-      <c r="I2" s="100"/>
-      <c r="J2" s="100"/>
-      <c r="K2" s="100"/>
-      <c r="L2" s="100"/>
-      <c r="M2" s="100"/>
-      <c r="N2" s="101"/>
-      <c r="O2" s="177"/>
-      <c r="P2" s="178"/>
-      <c r="Q2" s="178"/>
-      <c r="R2" s="179"/>
-      <c r="S2" s="168"/>
-      <c r="T2" s="169"/>
-      <c r="U2" s="169"/>
-      <c r="V2" s="169"/>
-      <c r="W2" s="169"/>
-      <c r="X2" s="169"/>
-      <c r="Y2" s="169"/>
-      <c r="Z2" s="170"/>
-      <c r="AA2" s="96" t="s">
+      <c r="F2" s="135"/>
+      <c r="G2" s="135"/>
+      <c r="H2" s="135"/>
+      <c r="I2" s="135"/>
+      <c r="J2" s="135"/>
+      <c r="K2" s="135"/>
+      <c r="L2" s="135"/>
+      <c r="M2" s="135"/>
+      <c r="N2" s="136"/>
+      <c r="O2" s="172"/>
+      <c r="P2" s="173"/>
+      <c r="Q2" s="173"/>
+      <c r="R2" s="174"/>
+      <c r="S2" s="181"/>
+      <c r="T2" s="182"/>
+      <c r="U2" s="182"/>
+      <c r="V2" s="182"/>
+      <c r="W2" s="182"/>
+      <c r="X2" s="182"/>
+      <c r="Y2" s="182"/>
+      <c r="Z2" s="183"/>
+      <c r="AA2" s="131" t="s">
         <v>4</v>
       </c>
-      <c r="AB2" s="98"/>
-      <c r="AC2" s="125" t="str">
+      <c r="AB2" s="133"/>
+      <c r="AC2" s="160" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC2")&lt;&gt;"",INDIRECT("変更履歴!AC2"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD2" s="126"/>
-      <c r="AE2" s="126"/>
-      <c r="AF2" s="127"/>
-      <c r="AG2" s="159">
+      <c r="AD2" s="161"/>
+      <c r="AE2" s="161"/>
+      <c r="AF2" s="162"/>
+      <c r="AG2" s="166">
         <f ca="1">IF(INDIRECT("変更履歴!AG2")&lt;&gt;"",INDIRECT("変更履歴!AG2"),"")</f>
-        <v>45464</v>
-      </c>
-      <c r="AH2" s="160"/>
-      <c r="AI2" s="161"/>
+        <v>45565</v>
+      </c>
+      <c r="AH2" s="167"/>
+      <c r="AI2" s="168"/>
       <c r="AJ2" s="6"/>
       <c r="AN2" s="7"/>
       <c r="AO2" s="6"/>
@@ -16611,52 +16611,52 @@
       <c r="AW2" s="6"/>
     </row>
     <row r="3" spans="1:50" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="96" t="s">
+      <c r="A3" s="131" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="97"/>
-      <c r="C3" s="97"/>
-      <c r="D3" s="98"/>
-      <c r="E3" s="99" t="str">
+      <c r="B3" s="132"/>
+      <c r="C3" s="132"/>
+      <c r="D3" s="133"/>
+      <c r="E3" s="134" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E3")&lt;&gt;"",INDIRECT("変更履歴!E3"),"")</f>
         <v/>
       </c>
-      <c r="F3" s="100"/>
-      <c r="G3" s="100"/>
-      <c r="H3" s="100"/>
-      <c r="I3" s="100"/>
-      <c r="J3" s="100"/>
-      <c r="K3" s="100"/>
-      <c r="L3" s="100"/>
-      <c r="M3" s="100"/>
-      <c r="N3" s="101"/>
-      <c r="O3" s="180"/>
-      <c r="P3" s="181"/>
-      <c r="Q3" s="181"/>
-      <c r="R3" s="182"/>
-      <c r="S3" s="171"/>
-      <c r="T3" s="172"/>
-      <c r="U3" s="172"/>
-      <c r="V3" s="172"/>
-      <c r="W3" s="172"/>
-      <c r="X3" s="172"/>
-      <c r="Y3" s="172"/>
-      <c r="Z3" s="173"/>
-      <c r="AA3" s="96"/>
-      <c r="AB3" s="98"/>
-      <c r="AC3" s="125" t="str">
+      <c r="F3" s="135"/>
+      <c r="G3" s="135"/>
+      <c r="H3" s="135"/>
+      <c r="I3" s="135"/>
+      <c r="J3" s="135"/>
+      <c r="K3" s="135"/>
+      <c r="L3" s="135"/>
+      <c r="M3" s="135"/>
+      <c r="N3" s="136"/>
+      <c r="O3" s="175"/>
+      <c r="P3" s="176"/>
+      <c r="Q3" s="176"/>
+      <c r="R3" s="177"/>
+      <c r="S3" s="184"/>
+      <c r="T3" s="185"/>
+      <c r="U3" s="185"/>
+      <c r="V3" s="185"/>
+      <c r="W3" s="185"/>
+      <c r="X3" s="185"/>
+      <c r="Y3" s="185"/>
+      <c r="Z3" s="186"/>
+      <c r="AA3" s="131"/>
+      <c r="AB3" s="133"/>
+      <c r="AC3" s="160" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC3")&lt;&gt;"",INDIRECT("変更履歴!AC3"),"")</f>
         <v/>
       </c>
-      <c r="AD3" s="126"/>
-      <c r="AE3" s="126"/>
-      <c r="AF3" s="127"/>
-      <c r="AG3" s="159" t="str">
+      <c r="AD3" s="161"/>
+      <c r="AE3" s="161"/>
+      <c r="AF3" s="162"/>
+      <c r="AG3" s="166" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AG3")&lt;&gt;"",INDIRECT("変更履歴!AG3"),"")</f>
         <v/>
       </c>
-      <c r="AH3" s="160"/>
-      <c r="AI3" s="161"/>
+      <c r="AH3" s="167"/>
+      <c r="AI3" s="168"/>
       <c r="AJ3" s="9"/>
       <c r="AK3" s="1"/>
       <c r="AL3" s="1"/>
@@ -16936,7 +16936,7 @@
       <c r="D21" s="83">
         <v>7</v>
       </c>
-      <c r="E21" s="183" t="s">
+      <c r="E21" s="88" t="s">
         <v>250</v>
       </c>
       <c r="F21" s="84"/>
@@ -17279,13 +17279,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="O1:R3"/>
-    <mergeCell ref="AA1:AB1"/>
-    <mergeCell ref="AA2:AB2"/>
-    <mergeCell ref="AA3:AB3"/>
     <mergeCell ref="AC3:AF3"/>
     <mergeCell ref="AG3:AI3"/>
     <mergeCell ref="E1:N1"/>
@@ -17296,6 +17289,13 @@
     <mergeCell ref="AC2:AF2"/>
     <mergeCell ref="AG2:AI2"/>
     <mergeCell ref="S1:Z3"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="O1:R3"/>
+    <mergeCell ref="AA1:AB1"/>
+    <mergeCell ref="AA2:AB2"/>
+    <mergeCell ref="AA3:AB3"/>
   </mergeCells>
   <phoneticPr fontId="10"/>
   <hyperlinks>
@@ -17341,59 +17341,59 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:49" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="131" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="97"/>
-      <c r="D1" s="98"/>
-      <c r="E1" s="99" t="str">
+      <c r="B1" s="132"/>
+      <c r="C1" s="132"/>
+      <c r="D1" s="133"/>
+      <c r="E1" s="134" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E1")&lt;&gt;"",INDIRECT("変更履歴!E1"),"")</f>
         <v/>
       </c>
-      <c r="F1" s="100"/>
-      <c r="G1" s="100"/>
-      <c r="H1" s="100"/>
-      <c r="I1" s="100"/>
-      <c r="J1" s="100"/>
-      <c r="K1" s="100"/>
-      <c r="L1" s="100"/>
-      <c r="M1" s="100"/>
-      <c r="N1" s="101"/>
-      <c r="O1" s="174" t="s">
+      <c r="F1" s="135"/>
+      <c r="G1" s="135"/>
+      <c r="H1" s="135"/>
+      <c r="I1" s="135"/>
+      <c r="J1" s="135"/>
+      <c r="K1" s="135"/>
+      <c r="L1" s="135"/>
+      <c r="M1" s="135"/>
+      <c r="N1" s="136"/>
+      <c r="O1" s="169" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="175"/>
-      <c r="Q1" s="175"/>
-      <c r="R1" s="176"/>
-      <c r="S1" s="165" t="str">
+      <c r="P1" s="170"/>
+      <c r="Q1" s="170"/>
+      <c r="R1" s="171"/>
+      <c r="S1" s="178" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!S1")&lt;&gt;"",INDIRECT("変更履歴!S1"),"")</f>
         <v>Nablarch開発標準設計書一覧</v>
       </c>
-      <c r="T1" s="166"/>
-      <c r="U1" s="166"/>
-      <c r="V1" s="166"/>
-      <c r="W1" s="166"/>
-      <c r="X1" s="166"/>
-      <c r="Y1" s="166"/>
-      <c r="Z1" s="167"/>
-      <c r="AA1" s="96" t="s">
+      <c r="T1" s="179"/>
+      <c r="U1" s="179"/>
+      <c r="V1" s="179"/>
+      <c r="W1" s="179"/>
+      <c r="X1" s="179"/>
+      <c r="Y1" s="179"/>
+      <c r="Z1" s="180"/>
+      <c r="AA1" s="131" t="s">
         <v>3</v>
       </c>
-      <c r="AB1" s="98"/>
-      <c r="AC1" s="125" t="str">
+      <c r="AB1" s="133"/>
+      <c r="AC1" s="160" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC1")&lt;&gt;"",INDIRECT("変更履歴!AC1"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="126"/>
-      <c r="AE1" s="126"/>
-      <c r="AF1" s="127"/>
-      <c r="AG1" s="159">
+      <c r="AD1" s="161"/>
+      <c r="AE1" s="161"/>
+      <c r="AF1" s="162"/>
+      <c r="AG1" s="166">
         <f ca="1">IF(INDIRECT("変更履歴!AG1")&lt;&gt;"",INDIRECT("変更履歴!AG1"),"")</f>
         <v>43336</v>
       </c>
-      <c r="AH1" s="160"/>
-      <c r="AI1" s="161"/>
+      <c r="AH1" s="167"/>
+      <c r="AI1" s="168"/>
       <c r="AJ1" s="6"/>
       <c r="AN1" s="7"/>
       <c r="AO1" s="6"/>
@@ -17407,54 +17407,54 @@
       <c r="AW1" s="6"/>
     </row>
     <row r="2" spans="1:49" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="96" t="s">
+      <c r="A2" s="131" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="97"/>
-      <c r="C2" s="97"/>
-      <c r="D2" s="98"/>
-      <c r="E2" s="99" t="str">
+      <c r="B2" s="132"/>
+      <c r="C2" s="132"/>
+      <c r="D2" s="133"/>
+      <c r="E2" s="134" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E2")&lt;&gt;"",INDIRECT("変更履歴!E2"),"")</f>
         <v/>
       </c>
-      <c r="F2" s="100"/>
-      <c r="G2" s="100"/>
-      <c r="H2" s="100"/>
-      <c r="I2" s="100"/>
-      <c r="J2" s="100"/>
-      <c r="K2" s="100"/>
-      <c r="L2" s="100"/>
-      <c r="M2" s="100"/>
-      <c r="N2" s="101"/>
-      <c r="O2" s="177"/>
-      <c r="P2" s="178"/>
-      <c r="Q2" s="178"/>
-      <c r="R2" s="179"/>
-      <c r="S2" s="168"/>
-      <c r="T2" s="169"/>
-      <c r="U2" s="169"/>
-      <c r="V2" s="169"/>
-      <c r="W2" s="169"/>
-      <c r="X2" s="169"/>
-      <c r="Y2" s="169"/>
-      <c r="Z2" s="170"/>
-      <c r="AA2" s="96" t="s">
+      <c r="F2" s="135"/>
+      <c r="G2" s="135"/>
+      <c r="H2" s="135"/>
+      <c r="I2" s="135"/>
+      <c r="J2" s="135"/>
+      <c r="K2" s="135"/>
+      <c r="L2" s="135"/>
+      <c r="M2" s="135"/>
+      <c r="N2" s="136"/>
+      <c r="O2" s="172"/>
+      <c r="P2" s="173"/>
+      <c r="Q2" s="173"/>
+      <c r="R2" s="174"/>
+      <c r="S2" s="181"/>
+      <c r="T2" s="182"/>
+      <c r="U2" s="182"/>
+      <c r="V2" s="182"/>
+      <c r="W2" s="182"/>
+      <c r="X2" s="182"/>
+      <c r="Y2" s="182"/>
+      <c r="Z2" s="183"/>
+      <c r="AA2" s="131" t="s">
         <v>4</v>
       </c>
-      <c r="AB2" s="98"/>
-      <c r="AC2" s="125" t="str">
+      <c r="AB2" s="133"/>
+      <c r="AC2" s="160" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC2")&lt;&gt;"",INDIRECT("変更履歴!AC2"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD2" s="126"/>
-      <c r="AE2" s="126"/>
-      <c r="AF2" s="127"/>
-      <c r="AG2" s="159">
+      <c r="AD2" s="161"/>
+      <c r="AE2" s="161"/>
+      <c r="AF2" s="162"/>
+      <c r="AG2" s="166">
         <f ca="1">IF(INDIRECT("変更履歴!AG2")&lt;&gt;"",INDIRECT("変更履歴!AG2"),"")</f>
-        <v>45464</v>
-      </c>
-      <c r="AH2" s="160"/>
-      <c r="AI2" s="161"/>
+        <v>45565</v>
+      </c>
+      <c r="AH2" s="167"/>
+      <c r="AI2" s="168"/>
       <c r="AJ2" s="6"/>
       <c r="AN2" s="7"/>
       <c r="AO2" s="6"/>
@@ -17468,52 +17468,52 @@
       <c r="AW2" s="6"/>
     </row>
     <row r="3" spans="1:49" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="96" t="s">
+      <c r="A3" s="131" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="97"/>
-      <c r="C3" s="97"/>
-      <c r="D3" s="98"/>
-      <c r="E3" s="99" t="str">
+      <c r="B3" s="132"/>
+      <c r="C3" s="132"/>
+      <c r="D3" s="133"/>
+      <c r="E3" s="134" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E3")&lt;&gt;"",INDIRECT("変更履歴!E3"),"")</f>
         <v/>
       </c>
-      <c r="F3" s="100"/>
-      <c r="G3" s="100"/>
-      <c r="H3" s="100"/>
-      <c r="I3" s="100"/>
-      <c r="J3" s="100"/>
-      <c r="K3" s="100"/>
-      <c r="L3" s="100"/>
-      <c r="M3" s="100"/>
-      <c r="N3" s="101"/>
-      <c r="O3" s="180"/>
-      <c r="P3" s="181"/>
-      <c r="Q3" s="181"/>
-      <c r="R3" s="182"/>
-      <c r="S3" s="171"/>
-      <c r="T3" s="172"/>
-      <c r="U3" s="172"/>
-      <c r="V3" s="172"/>
-      <c r="W3" s="172"/>
-      <c r="X3" s="172"/>
-      <c r="Y3" s="172"/>
-      <c r="Z3" s="173"/>
-      <c r="AA3" s="96"/>
-      <c r="AB3" s="98"/>
-      <c r="AC3" s="125" t="str">
+      <c r="F3" s="135"/>
+      <c r="G3" s="135"/>
+      <c r="H3" s="135"/>
+      <c r="I3" s="135"/>
+      <c r="J3" s="135"/>
+      <c r="K3" s="135"/>
+      <c r="L3" s="135"/>
+      <c r="M3" s="135"/>
+      <c r="N3" s="136"/>
+      <c r="O3" s="175"/>
+      <c r="P3" s="176"/>
+      <c r="Q3" s="176"/>
+      <c r="R3" s="177"/>
+      <c r="S3" s="184"/>
+      <c r="T3" s="185"/>
+      <c r="U3" s="185"/>
+      <c r="V3" s="185"/>
+      <c r="W3" s="185"/>
+      <c r="X3" s="185"/>
+      <c r="Y3" s="185"/>
+      <c r="Z3" s="186"/>
+      <c r="AA3" s="131"/>
+      <c r="AB3" s="133"/>
+      <c r="AC3" s="160" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC3")&lt;&gt;"",INDIRECT("変更履歴!AC3"),"")</f>
         <v/>
       </c>
-      <c r="AD3" s="126"/>
-      <c r="AE3" s="126"/>
-      <c r="AF3" s="127"/>
-      <c r="AG3" s="159" t="str">
+      <c r="AD3" s="161"/>
+      <c r="AE3" s="161"/>
+      <c r="AF3" s="162"/>
+      <c r="AG3" s="166" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AG3")&lt;&gt;"",INDIRECT("変更履歴!AG3"),"")</f>
         <v/>
       </c>
-      <c r="AH3" s="160"/>
-      <c r="AI3" s="161"/>
+      <c r="AH3" s="167"/>
+      <c r="AI3" s="168"/>
       <c r="AJ3" s="9"/>
       <c r="AK3" s="1"/>
       <c r="AL3" s="1"/>
@@ -17555,14 +17555,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="AG1:AI1"/>
-    <mergeCell ref="AC1:AF1"/>
-    <mergeCell ref="AC2:AF2"/>
-    <mergeCell ref="AG2:AI2"/>
-    <mergeCell ref="E3:N3"/>
-    <mergeCell ref="AA3:AB3"/>
-    <mergeCell ref="AC3:AF3"/>
-    <mergeCell ref="AG3:AI3"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="E1:N1"/>
     <mergeCell ref="O1:R3"/>
@@ -17572,6 +17564,14 @@
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="E2:N2"/>
     <mergeCell ref="AA2:AB2"/>
+    <mergeCell ref="AG1:AI1"/>
+    <mergeCell ref="AC1:AF1"/>
+    <mergeCell ref="AC2:AF2"/>
+    <mergeCell ref="AG2:AI2"/>
+    <mergeCell ref="E3:N3"/>
+    <mergeCell ref="AA3:AB3"/>
+    <mergeCell ref="AC3:AF3"/>
+    <mergeCell ref="AG3:AI3"/>
   </mergeCells>
   <phoneticPr fontId="10"/>
   <printOptions horizontalCentered="1"/>
@@ -17601,59 +17601,59 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="131" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="97"/>
-      <c r="D1" s="98"/>
-      <c r="E1" s="99" t="str">
+      <c r="B1" s="132"/>
+      <c r="C1" s="132"/>
+      <c r="D1" s="133"/>
+      <c r="E1" s="134" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E1")&lt;&gt;"",INDIRECT("変更履歴!E1"),"")</f>
         <v/>
       </c>
-      <c r="F1" s="100"/>
-      <c r="G1" s="100"/>
-      <c r="H1" s="100"/>
-      <c r="I1" s="100"/>
-      <c r="J1" s="100"/>
-      <c r="K1" s="100"/>
-      <c r="L1" s="100"/>
-      <c r="M1" s="100"/>
-      <c r="N1" s="101"/>
-      <c r="O1" s="174" t="s">
+      <c r="F1" s="135"/>
+      <c r="G1" s="135"/>
+      <c r="H1" s="135"/>
+      <c r="I1" s="135"/>
+      <c r="J1" s="135"/>
+      <c r="K1" s="135"/>
+      <c r="L1" s="135"/>
+      <c r="M1" s="135"/>
+      <c r="N1" s="136"/>
+      <c r="O1" s="169" t="s">
         <v>73</v>
       </c>
-      <c r="P1" s="175"/>
-      <c r="Q1" s="175"/>
-      <c r="R1" s="176"/>
-      <c r="S1" s="165" t="str">
+      <c r="P1" s="170"/>
+      <c r="Q1" s="170"/>
+      <c r="R1" s="171"/>
+      <c r="S1" s="178" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!S1")&lt;&gt;"",INDIRECT("変更履歴!S1"),"")</f>
         <v>Nablarch開発標準設計書一覧</v>
       </c>
-      <c r="T1" s="166"/>
-      <c r="U1" s="166"/>
-      <c r="V1" s="166"/>
-      <c r="W1" s="166"/>
-      <c r="X1" s="166"/>
-      <c r="Y1" s="166"/>
-      <c r="Z1" s="167"/>
-      <c r="AA1" s="96" t="s">
+      <c r="T1" s="179"/>
+      <c r="U1" s="179"/>
+      <c r="V1" s="179"/>
+      <c r="W1" s="179"/>
+      <c r="X1" s="179"/>
+      <c r="Y1" s="179"/>
+      <c r="Z1" s="180"/>
+      <c r="AA1" s="131" t="s">
         <v>3</v>
       </c>
-      <c r="AB1" s="98"/>
-      <c r="AC1" s="125" t="str">
+      <c r="AB1" s="133"/>
+      <c r="AC1" s="160" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC1")&lt;&gt;"",INDIRECT("変更履歴!AC1"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="126"/>
-      <c r="AE1" s="126"/>
-      <c r="AF1" s="127"/>
-      <c r="AG1" s="159">
+      <c r="AD1" s="161"/>
+      <c r="AE1" s="161"/>
+      <c r="AF1" s="162"/>
+      <c r="AG1" s="166">
         <f ca="1">IF(INDIRECT("変更履歴!AG1")&lt;&gt;"",INDIRECT("変更履歴!AG1"),"")</f>
         <v>43336</v>
       </c>
-      <c r="AH1" s="160"/>
-      <c r="AI1" s="161"/>
+      <c r="AH1" s="167"/>
+      <c r="AI1" s="168"/>
       <c r="AJ1" s="6"/>
       <c r="AM1" s="6"/>
       <c r="AN1" s="6"/>
@@ -17661,54 +17661,54 @@
       <c r="AP1" s="6"/>
     </row>
     <row r="2" spans="1:42" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="96" t="s">
+      <c r="A2" s="131" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="97"/>
-      <c r="C2" s="97"/>
-      <c r="D2" s="98"/>
-      <c r="E2" s="99" t="str">
+      <c r="B2" s="132"/>
+      <c r="C2" s="132"/>
+      <c r="D2" s="133"/>
+      <c r="E2" s="134" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E2")&lt;&gt;"",INDIRECT("変更履歴!E2"),"")</f>
         <v/>
       </c>
-      <c r="F2" s="100"/>
-      <c r="G2" s="100"/>
-      <c r="H2" s="100"/>
-      <c r="I2" s="100"/>
-      <c r="J2" s="100"/>
-      <c r="K2" s="100"/>
-      <c r="L2" s="100"/>
-      <c r="M2" s="100"/>
-      <c r="N2" s="101"/>
-      <c r="O2" s="177"/>
-      <c r="P2" s="178"/>
-      <c r="Q2" s="178"/>
-      <c r="R2" s="179"/>
-      <c r="S2" s="168"/>
-      <c r="T2" s="169"/>
-      <c r="U2" s="169"/>
-      <c r="V2" s="169"/>
-      <c r="W2" s="169"/>
-      <c r="X2" s="169"/>
-      <c r="Y2" s="169"/>
-      <c r="Z2" s="170"/>
-      <c r="AA2" s="96" t="s">
+      <c r="F2" s="135"/>
+      <c r="G2" s="135"/>
+      <c r="H2" s="135"/>
+      <c r="I2" s="135"/>
+      <c r="J2" s="135"/>
+      <c r="K2" s="135"/>
+      <c r="L2" s="135"/>
+      <c r="M2" s="135"/>
+      <c r="N2" s="136"/>
+      <c r="O2" s="172"/>
+      <c r="P2" s="173"/>
+      <c r="Q2" s="173"/>
+      <c r="R2" s="174"/>
+      <c r="S2" s="181"/>
+      <c r="T2" s="182"/>
+      <c r="U2" s="182"/>
+      <c r="V2" s="182"/>
+      <c r="W2" s="182"/>
+      <c r="X2" s="182"/>
+      <c r="Y2" s="182"/>
+      <c r="Z2" s="183"/>
+      <c r="AA2" s="131" t="s">
         <v>4</v>
       </c>
-      <c r="AB2" s="98"/>
-      <c r="AC2" s="125" t="str">
+      <c r="AB2" s="133"/>
+      <c r="AC2" s="160" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC2")&lt;&gt;"",INDIRECT("変更履歴!AC2"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD2" s="126"/>
-      <c r="AE2" s="126"/>
-      <c r="AF2" s="127"/>
-      <c r="AG2" s="159">
+      <c r="AD2" s="161"/>
+      <c r="AE2" s="161"/>
+      <c r="AF2" s="162"/>
+      <c r="AG2" s="166">
         <f ca="1">IF(INDIRECT("変更履歴!AG2")&lt;&gt;"",INDIRECT("変更履歴!AG2"),"")</f>
-        <v>45464</v>
-      </c>
-      <c r="AH2" s="160"/>
-      <c r="AI2" s="161"/>
+        <v>45565</v>
+      </c>
+      <c r="AH2" s="167"/>
+      <c r="AI2" s="168"/>
       <c r="AJ2" s="6"/>
       <c r="AM2" s="6"/>
       <c r="AN2" s="6"/>
@@ -17716,52 +17716,52 @@
       <c r="AP2" s="6"/>
     </row>
     <row r="3" spans="1:42" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="96" t="s">
+      <c r="A3" s="131" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="97"/>
-      <c r="C3" s="97"/>
-      <c r="D3" s="98"/>
-      <c r="E3" s="99" t="str">
+      <c r="B3" s="132"/>
+      <c r="C3" s="132"/>
+      <c r="D3" s="133"/>
+      <c r="E3" s="134" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E3")&lt;&gt;"",INDIRECT("変更履歴!E3"),"")</f>
         <v/>
       </c>
-      <c r="F3" s="100"/>
-      <c r="G3" s="100"/>
-      <c r="H3" s="100"/>
-      <c r="I3" s="100"/>
-      <c r="J3" s="100"/>
-      <c r="K3" s="100"/>
-      <c r="L3" s="100"/>
-      <c r="M3" s="100"/>
-      <c r="N3" s="101"/>
-      <c r="O3" s="180"/>
-      <c r="P3" s="181"/>
-      <c r="Q3" s="181"/>
-      <c r="R3" s="182"/>
-      <c r="S3" s="171"/>
-      <c r="T3" s="172"/>
-      <c r="U3" s="172"/>
-      <c r="V3" s="172"/>
-      <c r="W3" s="172"/>
-      <c r="X3" s="172"/>
-      <c r="Y3" s="172"/>
-      <c r="Z3" s="173"/>
-      <c r="AA3" s="96"/>
-      <c r="AB3" s="98"/>
-      <c r="AC3" s="125" t="str">
+      <c r="F3" s="135"/>
+      <c r="G3" s="135"/>
+      <c r="H3" s="135"/>
+      <c r="I3" s="135"/>
+      <c r="J3" s="135"/>
+      <c r="K3" s="135"/>
+      <c r="L3" s="135"/>
+      <c r="M3" s="135"/>
+      <c r="N3" s="136"/>
+      <c r="O3" s="175"/>
+      <c r="P3" s="176"/>
+      <c r="Q3" s="176"/>
+      <c r="R3" s="177"/>
+      <c r="S3" s="184"/>
+      <c r="T3" s="185"/>
+      <c r="U3" s="185"/>
+      <c r="V3" s="185"/>
+      <c r="W3" s="185"/>
+      <c r="X3" s="185"/>
+      <c r="Y3" s="185"/>
+      <c r="Z3" s="186"/>
+      <c r="AA3" s="131"/>
+      <c r="AB3" s="133"/>
+      <c r="AC3" s="160" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC3")&lt;&gt;"",INDIRECT("変更履歴!AC3"),"")</f>
         <v/>
       </c>
-      <c r="AD3" s="126"/>
-      <c r="AE3" s="126"/>
-      <c r="AF3" s="127"/>
-      <c r="AG3" s="159" t="str">
+      <c r="AD3" s="161"/>
+      <c r="AE3" s="161"/>
+      <c r="AF3" s="162"/>
+      <c r="AG3" s="166" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AG3")&lt;&gt;"",INDIRECT("変更履歴!AG3"),"")</f>
         <v/>
       </c>
-      <c r="AH3" s="160"/>
-      <c r="AI3" s="161"/>
+      <c r="AH3" s="167"/>
+      <c r="AI3" s="168"/>
       <c r="AJ3" s="9"/>
       <c r="AK3" s="1"/>
       <c r="AL3" s="1"/>
@@ -21158,6 +21158,14 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="AG1:AI1"/>
+    <mergeCell ref="AC1:AF1"/>
+    <mergeCell ref="AC2:AF2"/>
+    <mergeCell ref="AG2:AI2"/>
+    <mergeCell ref="E3:N3"/>
+    <mergeCell ref="AA3:AB3"/>
+    <mergeCell ref="AC3:AF3"/>
+    <mergeCell ref="AG3:AI3"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="E1:N1"/>
     <mergeCell ref="O1:R3"/>
@@ -21167,14 +21175,6 @@
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="E2:N2"/>
     <mergeCell ref="AA2:AB2"/>
-    <mergeCell ref="AG1:AI1"/>
-    <mergeCell ref="AC1:AF1"/>
-    <mergeCell ref="AC2:AF2"/>
-    <mergeCell ref="AG2:AI2"/>
-    <mergeCell ref="E3:N3"/>
-    <mergeCell ref="AA3:AB3"/>
-    <mergeCell ref="AC3:AF3"/>
-    <mergeCell ref="AG3:AI3"/>
   </mergeCells>
   <phoneticPr fontId="10"/>
   <printOptions horizontalCentered="1"/>
@@ -21202,59 +21202,59 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:49" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="131" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="97"/>
-      <c r="D1" s="98"/>
-      <c r="E1" s="99" t="str">
+      <c r="B1" s="132"/>
+      <c r="C1" s="132"/>
+      <c r="D1" s="133"/>
+      <c r="E1" s="134" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E1")&lt;&gt;"",INDIRECT("変更履歴!E1"),"")</f>
         <v/>
       </c>
-      <c r="F1" s="100"/>
-      <c r="G1" s="100"/>
-      <c r="H1" s="100"/>
-      <c r="I1" s="100"/>
-      <c r="J1" s="100"/>
-      <c r="K1" s="100"/>
-      <c r="L1" s="100"/>
-      <c r="M1" s="100"/>
-      <c r="N1" s="101"/>
-      <c r="O1" s="174" t="s">
+      <c r="F1" s="135"/>
+      <c r="G1" s="135"/>
+      <c r="H1" s="135"/>
+      <c r="I1" s="135"/>
+      <c r="J1" s="135"/>
+      <c r="K1" s="135"/>
+      <c r="L1" s="135"/>
+      <c r="M1" s="135"/>
+      <c r="N1" s="136"/>
+      <c r="O1" s="169" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="175"/>
-      <c r="Q1" s="175"/>
-      <c r="R1" s="176"/>
-      <c r="S1" s="165" t="str">
+      <c r="P1" s="170"/>
+      <c r="Q1" s="170"/>
+      <c r="R1" s="171"/>
+      <c r="S1" s="178" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!S1")&lt;&gt;"",INDIRECT("変更履歴!S1"),"")</f>
         <v>Nablarch開発標準設計書一覧</v>
       </c>
-      <c r="T1" s="166"/>
-      <c r="U1" s="166"/>
-      <c r="V1" s="166"/>
-      <c r="W1" s="166"/>
-      <c r="X1" s="166"/>
-      <c r="Y1" s="166"/>
-      <c r="Z1" s="167"/>
-      <c r="AA1" s="96" t="s">
+      <c r="T1" s="179"/>
+      <c r="U1" s="179"/>
+      <c r="V1" s="179"/>
+      <c r="W1" s="179"/>
+      <c r="X1" s="179"/>
+      <c r="Y1" s="179"/>
+      <c r="Z1" s="180"/>
+      <c r="AA1" s="131" t="s">
         <v>3</v>
       </c>
-      <c r="AB1" s="98"/>
-      <c r="AC1" s="125" t="str">
+      <c r="AB1" s="133"/>
+      <c r="AC1" s="160" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC1")&lt;&gt;"",INDIRECT("変更履歴!AC1"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="126"/>
-      <c r="AE1" s="126"/>
-      <c r="AF1" s="127"/>
-      <c r="AG1" s="159">
+      <c r="AD1" s="161"/>
+      <c r="AE1" s="161"/>
+      <c r="AF1" s="162"/>
+      <c r="AG1" s="166">
         <f ca="1">IF(INDIRECT("変更履歴!AG1")&lt;&gt;"",INDIRECT("変更履歴!AG1"),"")</f>
         <v>43336</v>
       </c>
-      <c r="AH1" s="160"/>
-      <c r="AI1" s="161"/>
+      <c r="AH1" s="167"/>
+      <c r="AI1" s="168"/>
       <c r="AJ1" s="6"/>
       <c r="AN1" s="7"/>
       <c r="AO1" s="6"/>
@@ -21268,54 +21268,54 @@
       <c r="AW1" s="6"/>
     </row>
     <row r="2" spans="1:49" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="96" t="s">
+      <c r="A2" s="131" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="97"/>
-      <c r="C2" s="97"/>
-      <c r="D2" s="98"/>
-      <c r="E2" s="99" t="str">
+      <c r="B2" s="132"/>
+      <c r="C2" s="132"/>
+      <c r="D2" s="133"/>
+      <c r="E2" s="134" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E2")&lt;&gt;"",INDIRECT("変更履歴!E2"),"")</f>
         <v/>
       </c>
-      <c r="F2" s="100"/>
-      <c r="G2" s="100"/>
-      <c r="H2" s="100"/>
-      <c r="I2" s="100"/>
-      <c r="J2" s="100"/>
-      <c r="K2" s="100"/>
-      <c r="L2" s="100"/>
-      <c r="M2" s="100"/>
-      <c r="N2" s="101"/>
-      <c r="O2" s="177"/>
-      <c r="P2" s="178"/>
-      <c r="Q2" s="178"/>
-      <c r="R2" s="179"/>
-      <c r="S2" s="168"/>
-      <c r="T2" s="169"/>
-      <c r="U2" s="169"/>
-      <c r="V2" s="169"/>
-      <c r="W2" s="169"/>
-      <c r="X2" s="169"/>
-      <c r="Y2" s="169"/>
-      <c r="Z2" s="170"/>
-      <c r="AA2" s="96" t="s">
+      <c r="F2" s="135"/>
+      <c r="G2" s="135"/>
+      <c r="H2" s="135"/>
+      <c r="I2" s="135"/>
+      <c r="J2" s="135"/>
+      <c r="K2" s="135"/>
+      <c r="L2" s="135"/>
+      <c r="M2" s="135"/>
+      <c r="N2" s="136"/>
+      <c r="O2" s="172"/>
+      <c r="P2" s="173"/>
+      <c r="Q2" s="173"/>
+      <c r="R2" s="174"/>
+      <c r="S2" s="181"/>
+      <c r="T2" s="182"/>
+      <c r="U2" s="182"/>
+      <c r="V2" s="182"/>
+      <c r="W2" s="182"/>
+      <c r="X2" s="182"/>
+      <c r="Y2" s="182"/>
+      <c r="Z2" s="183"/>
+      <c r="AA2" s="131" t="s">
         <v>4</v>
       </c>
-      <c r="AB2" s="98"/>
-      <c r="AC2" s="125" t="str">
+      <c r="AB2" s="133"/>
+      <c r="AC2" s="160" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC2")&lt;&gt;"",INDIRECT("変更履歴!AC2"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD2" s="126"/>
-      <c r="AE2" s="126"/>
-      <c r="AF2" s="127"/>
-      <c r="AG2" s="159">
+      <c r="AD2" s="161"/>
+      <c r="AE2" s="161"/>
+      <c r="AF2" s="162"/>
+      <c r="AG2" s="166">
         <f ca="1">IF(INDIRECT("変更履歴!AG2")&lt;&gt;"",INDIRECT("変更履歴!AG2"),"")</f>
-        <v>45464</v>
-      </c>
-      <c r="AH2" s="160"/>
-      <c r="AI2" s="161"/>
+        <v>45565</v>
+      </c>
+      <c r="AH2" s="167"/>
+      <c r="AI2" s="168"/>
       <c r="AJ2" s="6"/>
       <c r="AN2" s="7"/>
       <c r="AO2" s="6"/>
@@ -21329,52 +21329,52 @@
       <c r="AW2" s="6"/>
     </row>
     <row r="3" spans="1:49" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="96" t="s">
+      <c r="A3" s="131" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="97"/>
-      <c r="C3" s="97"/>
-      <c r="D3" s="98"/>
-      <c r="E3" s="99" t="str">
+      <c r="B3" s="132"/>
+      <c r="C3" s="132"/>
+      <c r="D3" s="133"/>
+      <c r="E3" s="134" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E3")&lt;&gt;"",INDIRECT("変更履歴!E3"),"")</f>
         <v/>
       </c>
-      <c r="F3" s="100"/>
-      <c r="G3" s="100"/>
-      <c r="H3" s="100"/>
-      <c r="I3" s="100"/>
-      <c r="J3" s="100"/>
-      <c r="K3" s="100"/>
-      <c r="L3" s="100"/>
-      <c r="M3" s="100"/>
-      <c r="N3" s="101"/>
-      <c r="O3" s="180"/>
-      <c r="P3" s="181"/>
-      <c r="Q3" s="181"/>
-      <c r="R3" s="182"/>
-      <c r="S3" s="171"/>
-      <c r="T3" s="172"/>
-      <c r="U3" s="172"/>
-      <c r="V3" s="172"/>
-      <c r="W3" s="172"/>
-      <c r="X3" s="172"/>
-      <c r="Y3" s="172"/>
-      <c r="Z3" s="173"/>
-      <c r="AA3" s="96"/>
-      <c r="AB3" s="98"/>
-      <c r="AC3" s="125" t="str">
+      <c r="F3" s="135"/>
+      <c r="G3" s="135"/>
+      <c r="H3" s="135"/>
+      <c r="I3" s="135"/>
+      <c r="J3" s="135"/>
+      <c r="K3" s="135"/>
+      <c r="L3" s="135"/>
+      <c r="M3" s="135"/>
+      <c r="N3" s="136"/>
+      <c r="O3" s="175"/>
+      <c r="P3" s="176"/>
+      <c r="Q3" s="176"/>
+      <c r="R3" s="177"/>
+      <c r="S3" s="184"/>
+      <c r="T3" s="185"/>
+      <c r="U3" s="185"/>
+      <c r="V3" s="185"/>
+      <c r="W3" s="185"/>
+      <c r="X3" s="185"/>
+      <c r="Y3" s="185"/>
+      <c r="Z3" s="186"/>
+      <c r="AA3" s="131"/>
+      <c r="AB3" s="133"/>
+      <c r="AC3" s="160" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC3")&lt;&gt;"",INDIRECT("変更履歴!AC3"),"")</f>
         <v/>
       </c>
-      <c r="AD3" s="126"/>
-      <c r="AE3" s="126"/>
-      <c r="AF3" s="127"/>
-      <c r="AG3" s="159" t="str">
+      <c r="AD3" s="161"/>
+      <c r="AE3" s="161"/>
+      <c r="AF3" s="162"/>
+      <c r="AG3" s="166" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AG3")&lt;&gt;"",INDIRECT("変更履歴!AG3"),"")</f>
         <v/>
       </c>
-      <c r="AH3" s="160"/>
-      <c r="AI3" s="161"/>
+      <c r="AH3" s="167"/>
+      <c r="AI3" s="168"/>
       <c r="AJ3" s="9"/>
       <c r="AK3" s="1"/>
       <c r="AL3" s="1"/>
@@ -21546,6 +21546,14 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="AG1:AI1"/>
+    <mergeCell ref="AC1:AF1"/>
+    <mergeCell ref="AC2:AF2"/>
+    <mergeCell ref="AG2:AI2"/>
+    <mergeCell ref="E3:N3"/>
+    <mergeCell ref="AA3:AB3"/>
+    <mergeCell ref="AC3:AF3"/>
+    <mergeCell ref="AG3:AI3"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="E1:N1"/>
     <mergeCell ref="O1:R3"/>
@@ -21555,14 +21563,6 @@
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="E2:N2"/>
     <mergeCell ref="AA2:AB2"/>
-    <mergeCell ref="AG1:AI1"/>
-    <mergeCell ref="AC1:AF1"/>
-    <mergeCell ref="AC2:AF2"/>
-    <mergeCell ref="AG2:AI2"/>
-    <mergeCell ref="E3:N3"/>
-    <mergeCell ref="AA3:AB3"/>
-    <mergeCell ref="AC3:AF3"/>
-    <mergeCell ref="AG3:AI3"/>
   </mergeCells>
   <phoneticPr fontId="10"/>
   <printOptions horizontalCentered="1"/>

--- a/030_設計ドキュメント/Nablarch開発標準設計書一覧.xlsx
+++ b/030_設計ドキュメント/Nablarch開発標準設計書一覧.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24931"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26731"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C22ED196-2359-4B51-8C16-4BE44E4A5F7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EE88BF5-D614-4FD4-B4F9-9F8D5DC1B216}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2100" yWindow="1770" windowWidth="33090" windowHeight="18225" tabRatio="822" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2745" yWindow="1875" windowWidth="28800" windowHeight="15435" tabRatio="822" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="34" r:id="rId1"/>
@@ -17,13 +17,13 @@
     <sheet name="3. 設計書とソースコードの対応" sheetId="43" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'1. 概要'!$A$1:$AI$12</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'1. 概要'!$A$1:$AI$36</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'2.1. 設計書体系図'!$A$1:$BA$72</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'2.2. 設計書一覧'!$A$1:$AQ$75</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">'3. 設計書とソースコードの対応'!$A$1:$AI$125</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">表紙!$A$1:$S$39</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">変更履歴!$A$1:$AI$39</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">目次!$A$1:$AI$35</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">目次!$A$1:$AI$36</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'1. 概要'!$1:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'2.1. 設計書体系図'!$1:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'2.2. 設計書一覧'!$1:$11</definedName>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="256">
   <si>
     <t>PJ名</t>
   </si>
@@ -1351,6 +1351,219 @@
     <rPh sb="33" eb="35">
       <t>ヘンコウ</t>
     </rPh>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>特に断りがない限り、以下の表記はJakarta EEの仕様を指すものとする。</t>
+    <rPh sb="10" eb="12">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ヒョウキ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>サ</t>
+    </rPh>
+    <phoneticPr fontId="30"/>
+  </si>
+  <si>
+    <t>No.</t>
+    <phoneticPr fontId="30"/>
+  </si>
+  <si>
+    <t>表記</t>
+    <rPh sb="0" eb="2">
+      <t>ヒョウキ</t>
+    </rPh>
+    <phoneticPr fontId="30"/>
+  </si>
+  <si>
+    <t>Jakarta EE仕様</t>
+    <rPh sb="10" eb="12">
+      <t>シヨウ</t>
+    </rPh>
+    <phoneticPr fontId="30"/>
+  </si>
+  <si>
+    <t>JSF</t>
+  </si>
+  <si>
+    <t>Jakarta Faces</t>
+  </si>
+  <si>
+    <t>JASPIC</t>
+  </si>
+  <si>
+    <t>Jakarta Authentication</t>
+  </si>
+  <si>
+    <t>JACC</t>
+  </si>
+  <si>
+    <t>Jakarta Authorization</t>
+  </si>
+  <si>
+    <t>JMS</t>
+  </si>
+  <si>
+    <t>Jakarta Messaging</t>
+  </si>
+  <si>
+    <t>JPA</t>
+  </si>
+  <si>
+    <t>Jakarta Persistence</t>
+  </si>
+  <si>
+    <t>JTA</t>
+  </si>
+  <si>
+    <t>Jakarta Transactions</t>
+  </si>
+  <si>
+    <t>Jakarta Batch</t>
+  </si>
+  <si>
+    <t>JCA</t>
+  </si>
+  <si>
+    <t>Jakarta Connectors</t>
+  </si>
+  <si>
+    <t>JAF</t>
+  </si>
+  <si>
+    <t>Jakarta Activation</t>
+  </si>
+  <si>
+    <t>EL</t>
+  </si>
+  <si>
+    <t>Jakarta Expression Language</t>
+  </si>
+  <si>
+    <t>EJB</t>
+  </si>
+  <si>
+    <t>Jakarta Enterprise Beans</t>
+  </si>
+  <si>
+    <t>JAXB</t>
+  </si>
+  <si>
+    <t>Jakarta XML Binding</t>
+  </si>
+  <si>
+    <t>JSON-B</t>
+  </si>
+  <si>
+    <t>Jakarta JSON Binding</t>
+  </si>
+  <si>
+    <t>JSON-P</t>
+  </si>
+  <si>
+    <t>Jakarta JSON Processing</t>
+  </si>
+  <si>
+    <t>JSP</t>
+  </si>
+  <si>
+    <t>Jakarta Server Pages</t>
+  </si>
+  <si>
+    <t>JAX-WS</t>
+  </si>
+  <si>
+    <t>Jakarta XML Web Services</t>
+  </si>
+  <si>
+    <t>JAX-RS</t>
+  </si>
+  <si>
+    <t>Jakarta RESTful Web Services</t>
+  </si>
+  <si>
+    <t>JSTL</t>
+  </si>
+  <si>
+    <t>Jakarta Standard Tag Library</t>
+  </si>
+  <si>
+    <t>CDI</t>
+  </si>
+  <si>
+    <t>Jakarta Contexts and Dependency Injection</t>
+  </si>
+  <si>
+    <t>1.2. 本書におけるJakartaEE仕様への読み替えについて</t>
+    <rPh sb="5" eb="7">
+      <t>ホンショ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="30"/>
+  </si>
+  <si>
+    <t>1.2. 本書におけるJakartaEE仕様への読み替えについて</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>jBatch / JSR352</t>
+    <phoneticPr fontId="30"/>
+  </si>
+  <si>
+    <t>1.2版</t>
+    <rPh sb="3" eb="4">
+      <t>バン</t>
+    </rPh>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>追加</t>
+    <rPh sb="0" eb="2">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>「1. 概要」シート</t>
+    <rPh sb="4" eb="6">
+      <t>ガイヨウ</t>
+    </rPh>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>「1.2. 本書におけるJakartaEE仕様への読み替えについて」を追加</t>
+    <rPh sb="6" eb="8">
+      <t>ホンショ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>TIS</t>
     <phoneticPr fontId="10"/>
   </si>
 </sst>
@@ -1645,7 +1858,7 @@
       <charset val="128"/>
     </font>
   </fonts>
-  <fills count="26">
+  <fills count="27">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1771,6 +1984,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.34998626667073579"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2242,7 +2461,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="172">
+  <cellXfs count="187">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="41"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="41" applyAlignment="1">
@@ -2403,8 +2622,125 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="44"/>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="20" xfId="44" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="10" xfId="44" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="11" xfId="44" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="12" xfId="44" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="44" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="44" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="44" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="44" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="44" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="44" applyFont="1" applyBorder="1"/>
     <xf numFmtId="31" fontId="7" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="23" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="22" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="177" fontId="2" fillId="0" borderId="10" xfId="45" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
@@ -2523,98 +2859,14 @@
     <xf numFmtId="14" fontId="2" fillId="0" borderId="12" xfId="41" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="41" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="10" xfId="41" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="23" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="22" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="12" xfId="41" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="177" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
@@ -2625,13 +2877,31 @@
     <xf numFmtId="177" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="10" xfId="41" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="33" fillId="24" borderId="13" xfId="41" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="12" xfId="41" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="33" fillId="24" borderId="14" xfId="41" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="41" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="24" borderId="15" xfId="41" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="24" borderId="24" xfId="41" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="24" borderId="0" xfId="41" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="24" borderId="25" xfId="41" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="24" borderId="16" xfId="41" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="24" borderId="17" xfId="41" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="24" borderId="18" xfId="41" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="41" applyBorder="1" applyAlignment="1">
@@ -2661,34 +2931,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="41" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="24" borderId="13" xfId="41" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="24" borderId="14" xfId="41" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="24" borderId="15" xfId="41" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="24" borderId="24" xfId="41" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="24" borderId="0" xfId="41" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="24" borderId="25" xfId="41" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="24" borderId="16" xfId="41" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="24" borderId="17" xfId="41" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="24" borderId="18" xfId="41" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="52">
     <cellStyle name="20% - アクセント 1" xfId="1" builtinId="30" customBuiltin="1"/>
@@ -13611,12 +13853,12 @@
       <c r="F25" s="22"/>
       <c r="G25" s="22"/>
       <c r="H25" s="22"/>
-      <c r="I25" s="76">
+      <c r="I25" s="89">
         <f ca="1">IF(INDIRECT("変更履歴!D8")="","",MAX(INDIRECT("変更履歴!D8"):INDIRECT("変更履歴!F33")))</f>
-        <v>44848</v>
-      </c>
-      <c r="J25" s="76"/>
-      <c r="K25" s="76"/>
+        <v>45565</v>
+      </c>
+      <c r="J25" s="89"/>
+      <c r="K25" s="89"/>
     </row>
     <row r="26" spans="6:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F26" s="22"/>
@@ -14210,55 +14452,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="93" t="s">
+      <c r="A1" s="140" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="85"/>
-      <c r="D1" s="86"/>
-      <c r="E1" s="94"/>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
-      <c r="H1" s="88"/>
-      <c r="I1" s="88"/>
-      <c r="J1" s="88"/>
-      <c r="K1" s="88"/>
-      <c r="L1" s="88"/>
-      <c r="M1" s="88"/>
-      <c r="N1" s="89"/>
-      <c r="O1" s="95" t="s">
+      <c r="B1" s="132"/>
+      <c r="C1" s="132"/>
+      <c r="D1" s="133"/>
+      <c r="E1" s="141"/>
+      <c r="F1" s="135"/>
+      <c r="G1" s="135"/>
+      <c r="H1" s="135"/>
+      <c r="I1" s="135"/>
+      <c r="J1" s="135"/>
+      <c r="K1" s="135"/>
+      <c r="L1" s="135"/>
+      <c r="M1" s="135"/>
+      <c r="N1" s="136"/>
+      <c r="O1" s="142" t="s">
         <v>11</v>
       </c>
-      <c r="P1" s="96"/>
-      <c r="Q1" s="96"/>
-      <c r="R1" s="97"/>
-      <c r="S1" s="104" t="s">
+      <c r="P1" s="143"/>
+      <c r="Q1" s="143"/>
+      <c r="R1" s="144"/>
+      <c r="S1" s="151" t="s">
         <v>44</v>
       </c>
-      <c r="T1" s="105"/>
-      <c r="U1" s="105"/>
-      <c r="V1" s="105"/>
-      <c r="W1" s="105"/>
-      <c r="X1" s="105"/>
-      <c r="Y1" s="105"/>
-      <c r="Z1" s="106"/>
-      <c r="AA1" s="84" t="s">
+      <c r="T1" s="152"/>
+      <c r="U1" s="152"/>
+      <c r="V1" s="152"/>
+      <c r="W1" s="152"/>
+      <c r="X1" s="152"/>
+      <c r="Y1" s="152"/>
+      <c r="Z1" s="153"/>
+      <c r="AA1" s="131" t="s">
         <v>12</v>
       </c>
-      <c r="AB1" s="86"/>
-      <c r="AC1" s="113" t="str">
+      <c r="AB1" s="133"/>
+      <c r="AC1" s="160" t="str">
         <f>IF(AF8="","",AF8)</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="114"/>
-      <c r="AE1" s="114"/>
-      <c r="AF1" s="115"/>
-      <c r="AG1" s="77">
+      <c r="AD1" s="161"/>
+      <c r="AE1" s="161"/>
+      <c r="AF1" s="162"/>
+      <c r="AG1" s="124">
         <f>IF(D8="","",D8)</f>
         <v>43336</v>
       </c>
-      <c r="AH1" s="78"/>
-      <c r="AI1" s="79"/>
+      <c r="AH1" s="125"/>
+      <c r="AI1" s="126"/>
       <c r="AJ1" s="1"/>
       <c r="AK1" s="1"/>
       <c r="AL1" s="1"/>
@@ -14266,51 +14508,51 @@
       <c r="AN1" s="2"/>
     </row>
     <row r="2" spans="1:40" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="84" t="s">
+      <c r="A2" s="131" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="85"/>
-      <c r="C2" s="85"/>
-      <c r="D2" s="86"/>
-      <c r="E2" s="87"/>
-      <c r="F2" s="88"/>
-      <c r="G2" s="88"/>
-      <c r="H2" s="88"/>
-      <c r="I2" s="88"/>
-      <c r="J2" s="88"/>
-      <c r="K2" s="88"/>
-      <c r="L2" s="88"/>
-      <c r="M2" s="88"/>
-      <c r="N2" s="89"/>
-      <c r="O2" s="98"/>
-      <c r="P2" s="99"/>
-      <c r="Q2" s="99"/>
-      <c r="R2" s="100"/>
-      <c r="S2" s="107"/>
-      <c r="T2" s="108"/>
-      <c r="U2" s="108"/>
-      <c r="V2" s="108"/>
-      <c r="W2" s="108"/>
-      <c r="X2" s="108"/>
-      <c r="Y2" s="108"/>
-      <c r="Z2" s="109"/>
-      <c r="AA2" s="84" t="s">
+      <c r="B2" s="132"/>
+      <c r="C2" s="132"/>
+      <c r="D2" s="133"/>
+      <c r="E2" s="134"/>
+      <c r="F2" s="135"/>
+      <c r="G2" s="135"/>
+      <c r="H2" s="135"/>
+      <c r="I2" s="135"/>
+      <c r="J2" s="135"/>
+      <c r="K2" s="135"/>
+      <c r="L2" s="135"/>
+      <c r="M2" s="135"/>
+      <c r="N2" s="136"/>
+      <c r="O2" s="145"/>
+      <c r="P2" s="146"/>
+      <c r="Q2" s="146"/>
+      <c r="R2" s="147"/>
+      <c r="S2" s="154"/>
+      <c r="T2" s="155"/>
+      <c r="U2" s="155"/>
+      <c r="V2" s="155"/>
+      <c r="W2" s="155"/>
+      <c r="X2" s="155"/>
+      <c r="Y2" s="155"/>
+      <c r="Z2" s="156"/>
+      <c r="AA2" s="131" t="s">
         <v>13</v>
       </c>
-      <c r="AB2" s="86"/>
-      <c r="AC2" s="90" t="str">
+      <c r="AB2" s="133"/>
+      <c r="AC2" s="137" t="str">
         <f ca="1">IF(COUNTA(AF9:AF33)&lt;&gt;0,INDIRECT("AF"&amp;(COUNTA(AF9:AF33)+8)),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD2" s="91"/>
-      <c r="AE2" s="91"/>
-      <c r="AF2" s="92"/>
-      <c r="AG2" s="77">
+      <c r="AD2" s="138"/>
+      <c r="AE2" s="138"/>
+      <c r="AF2" s="139"/>
+      <c r="AG2" s="124">
         <f>IF(D9="","",MAX(D9:F33))</f>
-        <v>44848</v>
-      </c>
-      <c r="AH2" s="78"/>
-      <c r="AI2" s="79"/>
+        <v>45565</v>
+      </c>
+      <c r="AH2" s="125"/>
+      <c r="AI2" s="126"/>
       <c r="AJ2" s="1"/>
       <c r="AK2" s="1"/>
       <c r="AL2" s="1"/>
@@ -14318,43 +14560,43 @@
       <c r="AN2" s="1"/>
     </row>
     <row r="3" spans="1:40" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="84" t="s">
+      <c r="A3" s="131" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="85"/>
-      <c r="C3" s="85"/>
-      <c r="D3" s="86"/>
-      <c r="E3" s="87"/>
-      <c r="F3" s="88"/>
-      <c r="G3" s="88"/>
-      <c r="H3" s="88"/>
-      <c r="I3" s="88"/>
-      <c r="J3" s="88"/>
-      <c r="K3" s="88"/>
-      <c r="L3" s="88"/>
-      <c r="M3" s="88"/>
-      <c r="N3" s="89"/>
-      <c r="O3" s="101"/>
-      <c r="P3" s="102"/>
-      <c r="Q3" s="102"/>
-      <c r="R3" s="103"/>
-      <c r="S3" s="110"/>
-      <c r="T3" s="111"/>
-      <c r="U3" s="111"/>
-      <c r="V3" s="111"/>
-      <c r="W3" s="111"/>
-      <c r="X3" s="111"/>
-      <c r="Y3" s="111"/>
-      <c r="Z3" s="112"/>
-      <c r="AA3" s="84"/>
-      <c r="AB3" s="86"/>
-      <c r="AC3" s="113"/>
-      <c r="AD3" s="114"/>
-      <c r="AE3" s="114"/>
-      <c r="AF3" s="115"/>
-      <c r="AG3" s="77"/>
-      <c r="AH3" s="78"/>
-      <c r="AI3" s="79"/>
+      <c r="B3" s="132"/>
+      <c r="C3" s="132"/>
+      <c r="D3" s="133"/>
+      <c r="E3" s="134"/>
+      <c r="F3" s="135"/>
+      <c r="G3" s="135"/>
+      <c r="H3" s="135"/>
+      <c r="I3" s="135"/>
+      <c r="J3" s="135"/>
+      <c r="K3" s="135"/>
+      <c r="L3" s="135"/>
+      <c r="M3" s="135"/>
+      <c r="N3" s="136"/>
+      <c r="O3" s="148"/>
+      <c r="P3" s="149"/>
+      <c r="Q3" s="149"/>
+      <c r="R3" s="150"/>
+      <c r="S3" s="157"/>
+      <c r="T3" s="158"/>
+      <c r="U3" s="158"/>
+      <c r="V3" s="158"/>
+      <c r="W3" s="158"/>
+      <c r="X3" s="158"/>
+      <c r="Y3" s="158"/>
+      <c r="Z3" s="159"/>
+      <c r="AA3" s="131"/>
+      <c r="AB3" s="133"/>
+      <c r="AC3" s="160"/>
+      <c r="AD3" s="161"/>
+      <c r="AE3" s="161"/>
+      <c r="AF3" s="162"/>
+      <c r="AG3" s="124"/>
+      <c r="AH3" s="125"/>
+      <c r="AI3" s="126"/>
       <c r="AJ3" s="1"/>
       <c r="AK3" s="1"/>
       <c r="AL3" s="1"/>
@@ -14391,1204 +14633,1062 @@
       <c r="A7" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="80" t="s">
+      <c r="B7" s="127" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="81"/>
-      <c r="D7" s="80" t="s">
+      <c r="C7" s="128"/>
+      <c r="D7" s="127" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="82"/>
-      <c r="F7" s="81"/>
-      <c r="G7" s="80" t="s">
+      <c r="E7" s="129"/>
+      <c r="F7" s="128"/>
+      <c r="G7" s="127" t="s">
         <v>8</v>
       </c>
-      <c r="H7" s="82"/>
-      <c r="I7" s="81"/>
-      <c r="J7" s="83" t="s">
+      <c r="H7" s="129"/>
+      <c r="I7" s="128"/>
+      <c r="J7" s="130" t="s">
         <v>23</v>
       </c>
-      <c r="K7" s="82"/>
-      <c r="L7" s="82"/>
-      <c r="M7" s="82"/>
-      <c r="N7" s="82"/>
-      <c r="O7" s="82"/>
-      <c r="P7" s="81"/>
-      <c r="Q7" s="80" t="s">
+      <c r="K7" s="129"/>
+      <c r="L7" s="129"/>
+      <c r="M7" s="129"/>
+      <c r="N7" s="129"/>
+      <c r="O7" s="129"/>
+      <c r="P7" s="128"/>
+      <c r="Q7" s="127" t="s">
         <v>9</v>
       </c>
-      <c r="R7" s="82"/>
-      <c r="S7" s="82"/>
-      <c r="T7" s="82"/>
-      <c r="U7" s="82"/>
-      <c r="V7" s="82"/>
-      <c r="W7" s="82"/>
-      <c r="X7" s="82"/>
-      <c r="Y7" s="82"/>
-      <c r="Z7" s="82"/>
-      <c r="AA7" s="82"/>
-      <c r="AB7" s="82"/>
-      <c r="AC7" s="82"/>
-      <c r="AD7" s="82"/>
-      <c r="AE7" s="81"/>
-      <c r="AF7" s="80" t="s">
+      <c r="R7" s="129"/>
+      <c r="S7" s="129"/>
+      <c r="T7" s="129"/>
+      <c r="U7" s="129"/>
+      <c r="V7" s="129"/>
+      <c r="W7" s="129"/>
+      <c r="X7" s="129"/>
+      <c r="Y7" s="129"/>
+      <c r="Z7" s="129"/>
+      <c r="AA7" s="129"/>
+      <c r="AB7" s="129"/>
+      <c r="AC7" s="129"/>
+      <c r="AD7" s="129"/>
+      <c r="AE7" s="128"/>
+      <c r="AF7" s="127" t="s">
         <v>10</v>
       </c>
-      <c r="AG7" s="82"/>
-      <c r="AH7" s="82"/>
-      <c r="AI7" s="81"/>
+      <c r="AG7" s="129"/>
+      <c r="AH7" s="129"/>
+      <c r="AI7" s="128"/>
     </row>
     <row r="8" spans="1:40" s="12" customFormat="1" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
       <c r="A8" s="16">
         <v>1</v>
       </c>
-      <c r="B8" s="129" t="s">
+      <c r="B8" s="110" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="130"/>
-      <c r="D8" s="131">
+      <c r="C8" s="111"/>
+      <c r="D8" s="112">
         <v>43336</v>
       </c>
-      <c r="E8" s="132"/>
-      <c r="F8" s="133"/>
-      <c r="G8" s="134" t="s">
+      <c r="E8" s="113"/>
+      <c r="F8" s="114"/>
+      <c r="G8" s="115" t="s">
         <v>18</v>
       </c>
-      <c r="H8" s="135"/>
-      <c r="I8" s="136"/>
-      <c r="J8" s="137" t="s">
+      <c r="H8" s="116"/>
+      <c r="I8" s="117"/>
+      <c r="J8" s="118" t="s">
         <v>19</v>
       </c>
-      <c r="K8" s="138"/>
-      <c r="L8" s="138"/>
-      <c r="M8" s="138"/>
-      <c r="N8" s="138"/>
-      <c r="O8" s="138"/>
-      <c r="P8" s="139"/>
-      <c r="Q8" s="140" t="s">
+      <c r="K8" s="119"/>
+      <c r="L8" s="119"/>
+      <c r="M8" s="119"/>
+      <c r="N8" s="119"/>
+      <c r="O8" s="119"/>
+      <c r="P8" s="120"/>
+      <c r="Q8" s="121" t="s">
         <v>20</v>
       </c>
-      <c r="R8" s="141"/>
-      <c r="S8" s="141"/>
-      <c r="T8" s="141"/>
-      <c r="U8" s="141"/>
-      <c r="V8" s="141"/>
-      <c r="W8" s="141"/>
-      <c r="X8" s="141"/>
-      <c r="Y8" s="141"/>
-      <c r="Z8" s="141"/>
-      <c r="AA8" s="141"/>
-      <c r="AB8" s="141"/>
-      <c r="AC8" s="141"/>
-      <c r="AD8" s="141"/>
-      <c r="AE8" s="142"/>
-      <c r="AF8" s="137" t="s">
+      <c r="R8" s="122"/>
+      <c r="S8" s="122"/>
+      <c r="T8" s="122"/>
+      <c r="U8" s="122"/>
+      <c r="V8" s="122"/>
+      <c r="W8" s="122"/>
+      <c r="X8" s="122"/>
+      <c r="Y8" s="122"/>
+      <c r="Z8" s="122"/>
+      <c r="AA8" s="122"/>
+      <c r="AB8" s="122"/>
+      <c r="AC8" s="122"/>
+      <c r="AD8" s="122"/>
+      <c r="AE8" s="123"/>
+      <c r="AF8" s="118" t="s">
         <v>21</v>
       </c>
-      <c r="AG8" s="138"/>
-      <c r="AH8" s="138"/>
-      <c r="AI8" s="139"/>
+      <c r="AG8" s="119"/>
+      <c r="AH8" s="119"/>
+      <c r="AI8" s="120"/>
     </row>
     <row r="9" spans="1:40" s="12" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="13">
         <v>2</v>
       </c>
-      <c r="B9" s="116" t="s">
+      <c r="B9" s="106" t="s">
         <v>199</v>
       </c>
-      <c r="C9" s="117"/>
-      <c r="D9" s="118">
+      <c r="C9" s="91"/>
+      <c r="D9" s="92">
         <v>44848</v>
       </c>
-      <c r="E9" s="119"/>
-      <c r="F9" s="120"/>
-      <c r="G9" s="121" t="s">
+      <c r="E9" s="93"/>
+      <c r="F9" s="94"/>
+      <c r="G9" s="107" t="s">
         <v>4</v>
       </c>
-      <c r="H9" s="122"/>
-      <c r="I9" s="117"/>
-      <c r="J9" s="123" t="s">
+      <c r="H9" s="95"/>
+      <c r="I9" s="91"/>
+      <c r="J9" s="108" t="s">
         <v>43</v>
       </c>
-      <c r="K9" s="124"/>
-      <c r="L9" s="124"/>
-      <c r="M9" s="124"/>
-      <c r="N9" s="124"/>
-      <c r="O9" s="124"/>
-      <c r="P9" s="125"/>
-      <c r="Q9" s="126" t="s">
+      <c r="K9" s="97"/>
+      <c r="L9" s="97"/>
+      <c r="M9" s="97"/>
+      <c r="N9" s="97"/>
+      <c r="O9" s="97"/>
+      <c r="P9" s="98"/>
+      <c r="Q9" s="109" t="s">
         <v>206</v>
       </c>
-      <c r="R9" s="127"/>
-      <c r="S9" s="127"/>
-      <c r="T9" s="127"/>
-      <c r="U9" s="127"/>
-      <c r="V9" s="127"/>
-      <c r="W9" s="127"/>
-      <c r="X9" s="127"/>
-      <c r="Y9" s="127"/>
-      <c r="Z9" s="127"/>
-      <c r="AA9" s="127"/>
-      <c r="AB9" s="127"/>
-      <c r="AC9" s="127"/>
-      <c r="AD9" s="127"/>
-      <c r="AE9" s="128"/>
-      <c r="AF9" s="123" t="s">
+      <c r="R9" s="100"/>
+      <c r="S9" s="100"/>
+      <c r="T9" s="100"/>
+      <c r="U9" s="100"/>
+      <c r="V9" s="100"/>
+      <c r="W9" s="100"/>
+      <c r="X9" s="100"/>
+      <c r="Y9" s="100"/>
+      <c r="Z9" s="100"/>
+      <c r="AA9" s="100"/>
+      <c r="AB9" s="100"/>
+      <c r="AC9" s="100"/>
+      <c r="AD9" s="100"/>
+      <c r="AE9" s="101"/>
+      <c r="AF9" s="108" t="s">
         <v>21</v>
       </c>
-      <c r="AG9" s="124"/>
-      <c r="AH9" s="124"/>
-      <c r="AI9" s="125"/>
+      <c r="AG9" s="97"/>
+      <c r="AH9" s="97"/>
+      <c r="AI9" s="98"/>
     </row>
     <row r="10" spans="1:40" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="13"/>
-      <c r="B10" s="143"/>
-      <c r="C10" s="117"/>
-      <c r="D10" s="118"/>
-      <c r="E10" s="119"/>
-      <c r="F10" s="120"/>
-      <c r="G10" s="143"/>
-      <c r="H10" s="122"/>
-      <c r="I10" s="117"/>
-      <c r="J10" s="144"/>
-      <c r="K10" s="124"/>
-      <c r="L10" s="124"/>
-      <c r="M10" s="124"/>
-      <c r="N10" s="124"/>
-      <c r="O10" s="124"/>
-      <c r="P10" s="125"/>
-      <c r="Q10" s="145"/>
-      <c r="R10" s="127"/>
-      <c r="S10" s="127"/>
-      <c r="T10" s="127"/>
-      <c r="U10" s="127"/>
-      <c r="V10" s="127"/>
-      <c r="W10" s="127"/>
-      <c r="X10" s="127"/>
-      <c r="Y10" s="127"/>
-      <c r="Z10" s="127"/>
-      <c r="AA10" s="127"/>
-      <c r="AB10" s="127"/>
-      <c r="AC10" s="127"/>
-      <c r="AD10" s="127"/>
-      <c r="AE10" s="128"/>
-      <c r="AF10" s="144"/>
-      <c r="AG10" s="124"/>
-      <c r="AH10" s="124"/>
-      <c r="AI10" s="125"/>
+      <c r="A10" s="13">
+        <v>3</v>
+      </c>
+      <c r="B10" s="103" t="s">
+        <v>251</v>
+      </c>
+      <c r="C10" s="91"/>
+      <c r="D10" s="92">
+        <v>45565</v>
+      </c>
+      <c r="E10" s="93"/>
+      <c r="F10" s="94"/>
+      <c r="G10" s="103" t="s">
+        <v>252</v>
+      </c>
+      <c r="H10" s="95"/>
+      <c r="I10" s="91"/>
+      <c r="J10" s="104" t="s">
+        <v>253</v>
+      </c>
+      <c r="K10" s="97"/>
+      <c r="L10" s="97"/>
+      <c r="M10" s="97"/>
+      <c r="N10" s="97"/>
+      <c r="O10" s="97"/>
+      <c r="P10" s="98"/>
+      <c r="Q10" s="105" t="s">
+        <v>254</v>
+      </c>
+      <c r="R10" s="100"/>
+      <c r="S10" s="100"/>
+      <c r="T10" s="100"/>
+      <c r="U10" s="100"/>
+      <c r="V10" s="100"/>
+      <c r="W10" s="100"/>
+      <c r="X10" s="100"/>
+      <c r="Y10" s="100"/>
+      <c r="Z10" s="100"/>
+      <c r="AA10" s="100"/>
+      <c r="AB10" s="100"/>
+      <c r="AC10" s="100"/>
+      <c r="AD10" s="100"/>
+      <c r="AE10" s="101"/>
+      <c r="AF10" s="104" t="s">
+        <v>255</v>
+      </c>
+      <c r="AG10" s="97"/>
+      <c r="AH10" s="97"/>
+      <c r="AI10" s="98"/>
     </row>
     <row r="11" spans="1:40" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="13"/>
-      <c r="B11" s="143"/>
-      <c r="C11" s="117"/>
-      <c r="D11" s="118"/>
-      <c r="E11" s="119"/>
-      <c r="F11" s="120"/>
-      <c r="G11" s="143"/>
-      <c r="H11" s="122"/>
-      <c r="I11" s="117"/>
-      <c r="J11" s="144"/>
-      <c r="K11" s="124"/>
-      <c r="L11" s="124"/>
-      <c r="M11" s="124"/>
-      <c r="N11" s="124"/>
-      <c r="O11" s="124"/>
-      <c r="P11" s="125"/>
-      <c r="Q11" s="145"/>
-      <c r="R11" s="127"/>
-      <c r="S11" s="127"/>
-      <c r="T11" s="127"/>
-      <c r="U11" s="127"/>
-      <c r="V11" s="127"/>
-      <c r="W11" s="127"/>
-      <c r="X11" s="127"/>
-      <c r="Y11" s="127"/>
-      <c r="Z11" s="127"/>
-      <c r="AA11" s="127"/>
-      <c r="AB11" s="127"/>
-      <c r="AC11" s="127"/>
-      <c r="AD11" s="127"/>
-      <c r="AE11" s="128"/>
-      <c r="AF11" s="144"/>
-      <c r="AG11" s="124"/>
-      <c r="AH11" s="124"/>
-      <c r="AI11" s="125"/>
+      <c r="B11" s="90"/>
+      <c r="C11" s="91"/>
+      <c r="D11" s="92"/>
+      <c r="E11" s="93"/>
+      <c r="F11" s="94"/>
+      <c r="G11" s="90"/>
+      <c r="H11" s="95"/>
+      <c r="I11" s="91"/>
+      <c r="J11" s="96"/>
+      <c r="K11" s="97"/>
+      <c r="L11" s="97"/>
+      <c r="M11" s="97"/>
+      <c r="N11" s="97"/>
+      <c r="O11" s="97"/>
+      <c r="P11" s="98"/>
+      <c r="Q11" s="99"/>
+      <c r="R11" s="100"/>
+      <c r="S11" s="100"/>
+      <c r="T11" s="100"/>
+      <c r="U11" s="100"/>
+      <c r="V11" s="100"/>
+      <c r="W11" s="100"/>
+      <c r="X11" s="100"/>
+      <c r="Y11" s="100"/>
+      <c r="Z11" s="100"/>
+      <c r="AA11" s="100"/>
+      <c r="AB11" s="100"/>
+      <c r="AC11" s="100"/>
+      <c r="AD11" s="100"/>
+      <c r="AE11" s="101"/>
+      <c r="AF11" s="96"/>
+      <c r="AG11" s="97"/>
+      <c r="AH11" s="97"/>
+      <c r="AI11" s="98"/>
     </row>
     <row r="12" spans="1:40" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="13"/>
-      <c r="B12" s="143"/>
-      <c r="C12" s="117"/>
-      <c r="D12" s="118"/>
-      <c r="E12" s="119"/>
-      <c r="F12" s="120"/>
-      <c r="G12" s="143"/>
-      <c r="H12" s="122"/>
-      <c r="I12" s="117"/>
-      <c r="J12" s="144"/>
-      <c r="K12" s="124"/>
-      <c r="L12" s="124"/>
-      <c r="M12" s="124"/>
-      <c r="N12" s="124"/>
-      <c r="O12" s="124"/>
-      <c r="P12" s="125"/>
-      <c r="Q12" s="145"/>
-      <c r="R12" s="127"/>
-      <c r="S12" s="127"/>
-      <c r="T12" s="127"/>
-      <c r="U12" s="127"/>
-      <c r="V12" s="127"/>
-      <c r="W12" s="127"/>
-      <c r="X12" s="127"/>
-      <c r="Y12" s="127"/>
-      <c r="Z12" s="127"/>
-      <c r="AA12" s="127"/>
-      <c r="AB12" s="127"/>
-      <c r="AC12" s="127"/>
-      <c r="AD12" s="127"/>
-      <c r="AE12" s="128"/>
-      <c r="AF12" s="144"/>
-      <c r="AG12" s="124"/>
-      <c r="AH12" s="124"/>
-      <c r="AI12" s="125"/>
+      <c r="B12" s="90"/>
+      <c r="C12" s="91"/>
+      <c r="D12" s="92"/>
+      <c r="E12" s="93"/>
+      <c r="F12" s="94"/>
+      <c r="G12" s="90"/>
+      <c r="H12" s="95"/>
+      <c r="I12" s="91"/>
+      <c r="J12" s="96"/>
+      <c r="K12" s="97"/>
+      <c r="L12" s="97"/>
+      <c r="M12" s="97"/>
+      <c r="N12" s="97"/>
+      <c r="O12" s="97"/>
+      <c r="P12" s="98"/>
+      <c r="Q12" s="99"/>
+      <c r="R12" s="100"/>
+      <c r="S12" s="100"/>
+      <c r="T12" s="100"/>
+      <c r="U12" s="100"/>
+      <c r="V12" s="100"/>
+      <c r="W12" s="100"/>
+      <c r="X12" s="100"/>
+      <c r="Y12" s="100"/>
+      <c r="Z12" s="100"/>
+      <c r="AA12" s="100"/>
+      <c r="AB12" s="100"/>
+      <c r="AC12" s="100"/>
+      <c r="AD12" s="100"/>
+      <c r="AE12" s="101"/>
+      <c r="AF12" s="96"/>
+      <c r="AG12" s="97"/>
+      <c r="AH12" s="97"/>
+      <c r="AI12" s="98"/>
     </row>
     <row r="13" spans="1:40" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="13"/>
-      <c r="B13" s="143"/>
-      <c r="C13" s="117"/>
-      <c r="D13" s="118"/>
-      <c r="E13" s="119"/>
-      <c r="F13" s="120"/>
-      <c r="G13" s="143"/>
-      <c r="H13" s="122"/>
-      <c r="I13" s="117"/>
-      <c r="J13" s="144"/>
-      <c r="K13" s="124"/>
-      <c r="L13" s="124"/>
-      <c r="M13" s="124"/>
-      <c r="N13" s="124"/>
-      <c r="O13" s="124"/>
-      <c r="P13" s="125"/>
-      <c r="Q13" s="145"/>
-      <c r="R13" s="127"/>
-      <c r="S13" s="127"/>
-      <c r="T13" s="127"/>
-      <c r="U13" s="127"/>
-      <c r="V13" s="127"/>
-      <c r="W13" s="127"/>
-      <c r="X13" s="127"/>
-      <c r="Y13" s="127"/>
-      <c r="Z13" s="127"/>
-      <c r="AA13" s="127"/>
-      <c r="AB13" s="127"/>
-      <c r="AC13" s="127"/>
-      <c r="AD13" s="127"/>
-      <c r="AE13" s="128"/>
-      <c r="AF13" s="144"/>
-      <c r="AG13" s="124"/>
-      <c r="AH13" s="124"/>
-      <c r="AI13" s="125"/>
+      <c r="B13" s="90"/>
+      <c r="C13" s="91"/>
+      <c r="D13" s="92"/>
+      <c r="E13" s="93"/>
+      <c r="F13" s="94"/>
+      <c r="G13" s="90"/>
+      <c r="H13" s="95"/>
+      <c r="I13" s="91"/>
+      <c r="J13" s="96"/>
+      <c r="K13" s="97"/>
+      <c r="L13" s="97"/>
+      <c r="M13" s="97"/>
+      <c r="N13" s="97"/>
+      <c r="O13" s="97"/>
+      <c r="P13" s="98"/>
+      <c r="Q13" s="99"/>
+      <c r="R13" s="100"/>
+      <c r="S13" s="100"/>
+      <c r="T13" s="100"/>
+      <c r="U13" s="100"/>
+      <c r="V13" s="100"/>
+      <c r="W13" s="100"/>
+      <c r="X13" s="100"/>
+      <c r="Y13" s="100"/>
+      <c r="Z13" s="100"/>
+      <c r="AA13" s="100"/>
+      <c r="AB13" s="100"/>
+      <c r="AC13" s="100"/>
+      <c r="AD13" s="100"/>
+      <c r="AE13" s="101"/>
+      <c r="AF13" s="96"/>
+      <c r="AG13" s="97"/>
+      <c r="AH13" s="97"/>
+      <c r="AI13" s="98"/>
     </row>
     <row r="14" spans="1:40" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="13"/>
-      <c r="B14" s="143"/>
-      <c r="C14" s="117"/>
-      <c r="D14" s="118"/>
-      <c r="E14" s="119"/>
-      <c r="F14" s="120"/>
-      <c r="G14" s="143"/>
-      <c r="H14" s="122"/>
-      <c r="I14" s="117"/>
-      <c r="J14" s="144"/>
-      <c r="K14" s="124"/>
-      <c r="L14" s="124"/>
-      <c r="M14" s="124"/>
-      <c r="N14" s="124"/>
-      <c r="O14" s="124"/>
-      <c r="P14" s="125"/>
-      <c r="Q14" s="145"/>
-      <c r="R14" s="127"/>
-      <c r="S14" s="127"/>
-      <c r="T14" s="127"/>
-      <c r="U14" s="127"/>
-      <c r="V14" s="127"/>
-      <c r="W14" s="127"/>
-      <c r="X14" s="127"/>
-      <c r="Y14" s="127"/>
-      <c r="Z14" s="127"/>
-      <c r="AA14" s="127"/>
-      <c r="AB14" s="127"/>
-      <c r="AC14" s="127"/>
-      <c r="AD14" s="127"/>
-      <c r="AE14" s="128"/>
-      <c r="AF14" s="144"/>
-      <c r="AG14" s="124"/>
-      <c r="AH14" s="124"/>
-      <c r="AI14" s="125"/>
+      <c r="B14" s="90"/>
+      <c r="C14" s="91"/>
+      <c r="D14" s="92"/>
+      <c r="E14" s="93"/>
+      <c r="F14" s="94"/>
+      <c r="G14" s="90"/>
+      <c r="H14" s="95"/>
+      <c r="I14" s="91"/>
+      <c r="J14" s="96"/>
+      <c r="K14" s="97"/>
+      <c r="L14" s="97"/>
+      <c r="M14" s="97"/>
+      <c r="N14" s="97"/>
+      <c r="O14" s="97"/>
+      <c r="P14" s="98"/>
+      <c r="Q14" s="99"/>
+      <c r="R14" s="100"/>
+      <c r="S14" s="100"/>
+      <c r="T14" s="100"/>
+      <c r="U14" s="100"/>
+      <c r="V14" s="100"/>
+      <c r="W14" s="100"/>
+      <c r="X14" s="100"/>
+      <c r="Y14" s="100"/>
+      <c r="Z14" s="100"/>
+      <c r="AA14" s="100"/>
+      <c r="AB14" s="100"/>
+      <c r="AC14" s="100"/>
+      <c r="AD14" s="100"/>
+      <c r="AE14" s="101"/>
+      <c r="AF14" s="96"/>
+      <c r="AG14" s="97"/>
+      <c r="AH14" s="97"/>
+      <c r="AI14" s="98"/>
     </row>
     <row r="15" spans="1:40" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="13"/>
-      <c r="B15" s="143"/>
-      <c r="C15" s="117"/>
-      <c r="D15" s="118"/>
-      <c r="E15" s="119"/>
-      <c r="F15" s="120"/>
-      <c r="G15" s="143"/>
-      <c r="H15" s="122"/>
-      <c r="I15" s="117"/>
-      <c r="J15" s="144"/>
-      <c r="K15" s="124"/>
-      <c r="L15" s="124"/>
-      <c r="M15" s="124"/>
-      <c r="N15" s="124"/>
-      <c r="O15" s="124"/>
-      <c r="P15" s="125"/>
-      <c r="Q15" s="145"/>
-      <c r="R15" s="127"/>
-      <c r="S15" s="127"/>
-      <c r="T15" s="127"/>
-      <c r="U15" s="127"/>
-      <c r="V15" s="127"/>
-      <c r="W15" s="127"/>
-      <c r="X15" s="127"/>
-      <c r="Y15" s="127"/>
-      <c r="Z15" s="127"/>
-      <c r="AA15" s="127"/>
-      <c r="AB15" s="127"/>
-      <c r="AC15" s="127"/>
-      <c r="AD15" s="127"/>
-      <c r="AE15" s="128"/>
-      <c r="AF15" s="144"/>
-      <c r="AG15" s="124"/>
-      <c r="AH15" s="124"/>
-      <c r="AI15" s="125"/>
+      <c r="B15" s="90"/>
+      <c r="C15" s="91"/>
+      <c r="D15" s="92"/>
+      <c r="E15" s="93"/>
+      <c r="F15" s="94"/>
+      <c r="G15" s="90"/>
+      <c r="H15" s="95"/>
+      <c r="I15" s="91"/>
+      <c r="J15" s="96"/>
+      <c r="K15" s="97"/>
+      <c r="L15" s="97"/>
+      <c r="M15" s="97"/>
+      <c r="N15" s="97"/>
+      <c r="O15" s="97"/>
+      <c r="P15" s="98"/>
+      <c r="Q15" s="99"/>
+      <c r="R15" s="100"/>
+      <c r="S15" s="100"/>
+      <c r="T15" s="100"/>
+      <c r="U15" s="100"/>
+      <c r="V15" s="100"/>
+      <c r="W15" s="100"/>
+      <c r="X15" s="100"/>
+      <c r="Y15" s="100"/>
+      <c r="Z15" s="100"/>
+      <c r="AA15" s="100"/>
+      <c r="AB15" s="100"/>
+      <c r="AC15" s="100"/>
+      <c r="AD15" s="100"/>
+      <c r="AE15" s="101"/>
+      <c r="AF15" s="96"/>
+      <c r="AG15" s="97"/>
+      <c r="AH15" s="97"/>
+      <c r="AI15" s="98"/>
     </row>
     <row r="16" spans="1:40" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="13"/>
-      <c r="B16" s="143"/>
-      <c r="C16" s="117"/>
-      <c r="D16" s="118"/>
-      <c r="E16" s="119"/>
-      <c r="F16" s="120"/>
-      <c r="G16" s="143"/>
-      <c r="H16" s="122"/>
-      <c r="I16" s="117"/>
-      <c r="J16" s="144"/>
-      <c r="K16" s="124"/>
-      <c r="L16" s="124"/>
-      <c r="M16" s="124"/>
-      <c r="N16" s="124"/>
-      <c r="O16" s="124"/>
-      <c r="P16" s="125"/>
-      <c r="Q16" s="145"/>
-      <c r="R16" s="127"/>
-      <c r="S16" s="127"/>
-      <c r="T16" s="127"/>
-      <c r="U16" s="127"/>
-      <c r="V16" s="127"/>
-      <c r="W16" s="127"/>
-      <c r="X16" s="127"/>
-      <c r="Y16" s="127"/>
-      <c r="Z16" s="127"/>
-      <c r="AA16" s="127"/>
-      <c r="AB16" s="127"/>
-      <c r="AC16" s="127"/>
-      <c r="AD16" s="127"/>
-      <c r="AE16" s="128"/>
-      <c r="AF16" s="144"/>
-      <c r="AG16" s="124"/>
-      <c r="AH16" s="124"/>
-      <c r="AI16" s="125"/>
+      <c r="B16" s="90"/>
+      <c r="C16" s="91"/>
+      <c r="D16" s="92"/>
+      <c r="E16" s="93"/>
+      <c r="F16" s="94"/>
+      <c r="G16" s="90"/>
+      <c r="H16" s="95"/>
+      <c r="I16" s="91"/>
+      <c r="J16" s="96"/>
+      <c r="K16" s="97"/>
+      <c r="L16" s="97"/>
+      <c r="M16" s="97"/>
+      <c r="N16" s="97"/>
+      <c r="O16" s="97"/>
+      <c r="P16" s="98"/>
+      <c r="Q16" s="99"/>
+      <c r="R16" s="100"/>
+      <c r="S16" s="100"/>
+      <c r="T16" s="100"/>
+      <c r="U16" s="100"/>
+      <c r="V16" s="100"/>
+      <c r="W16" s="100"/>
+      <c r="X16" s="100"/>
+      <c r="Y16" s="100"/>
+      <c r="Z16" s="100"/>
+      <c r="AA16" s="100"/>
+      <c r="AB16" s="100"/>
+      <c r="AC16" s="100"/>
+      <c r="AD16" s="100"/>
+      <c r="AE16" s="101"/>
+      <c r="AF16" s="96"/>
+      <c r="AG16" s="97"/>
+      <c r="AH16" s="97"/>
+      <c r="AI16" s="98"/>
     </row>
     <row r="17" spans="1:35" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="13"/>
-      <c r="B17" s="143"/>
-      <c r="C17" s="117"/>
-      <c r="D17" s="118"/>
-      <c r="E17" s="119"/>
-      <c r="F17" s="120"/>
-      <c r="G17" s="143"/>
-      <c r="H17" s="122"/>
-      <c r="I17" s="117"/>
-      <c r="J17" s="144"/>
-      <c r="K17" s="124"/>
-      <c r="L17" s="124"/>
-      <c r="M17" s="124"/>
-      <c r="N17" s="124"/>
-      <c r="O17" s="124"/>
-      <c r="P17" s="125"/>
-      <c r="Q17" s="145"/>
-      <c r="R17" s="127"/>
-      <c r="S17" s="127"/>
-      <c r="T17" s="127"/>
-      <c r="U17" s="127"/>
-      <c r="V17" s="127"/>
-      <c r="W17" s="127"/>
-      <c r="X17" s="127"/>
-      <c r="Y17" s="127"/>
-      <c r="Z17" s="127"/>
-      <c r="AA17" s="127"/>
-      <c r="AB17" s="127"/>
-      <c r="AC17" s="127"/>
-      <c r="AD17" s="127"/>
-      <c r="AE17" s="128"/>
-      <c r="AF17" s="144"/>
-      <c r="AG17" s="124"/>
-      <c r="AH17" s="124"/>
-      <c r="AI17" s="125"/>
+      <c r="B17" s="90"/>
+      <c r="C17" s="91"/>
+      <c r="D17" s="92"/>
+      <c r="E17" s="93"/>
+      <c r="F17" s="94"/>
+      <c r="G17" s="90"/>
+      <c r="H17" s="95"/>
+      <c r="I17" s="91"/>
+      <c r="J17" s="96"/>
+      <c r="K17" s="97"/>
+      <c r="L17" s="97"/>
+      <c r="M17" s="97"/>
+      <c r="N17" s="97"/>
+      <c r="O17" s="97"/>
+      <c r="P17" s="98"/>
+      <c r="Q17" s="99"/>
+      <c r="R17" s="100"/>
+      <c r="S17" s="100"/>
+      <c r="T17" s="100"/>
+      <c r="U17" s="100"/>
+      <c r="V17" s="100"/>
+      <c r="W17" s="100"/>
+      <c r="X17" s="100"/>
+      <c r="Y17" s="100"/>
+      <c r="Z17" s="100"/>
+      <c r="AA17" s="100"/>
+      <c r="AB17" s="100"/>
+      <c r="AC17" s="100"/>
+      <c r="AD17" s="100"/>
+      <c r="AE17" s="101"/>
+      <c r="AF17" s="96"/>
+      <c r="AG17" s="97"/>
+      <c r="AH17" s="97"/>
+      <c r="AI17" s="98"/>
     </row>
     <row r="18" spans="1:35" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="13"/>
-      <c r="B18" s="143"/>
-      <c r="C18" s="117"/>
-      <c r="D18" s="118"/>
-      <c r="E18" s="119"/>
-      <c r="F18" s="120"/>
-      <c r="G18" s="143"/>
-      <c r="H18" s="122"/>
-      <c r="I18" s="117"/>
-      <c r="J18" s="144"/>
-      <c r="K18" s="124"/>
-      <c r="L18" s="124"/>
-      <c r="M18" s="124"/>
-      <c r="N18" s="124"/>
-      <c r="O18" s="124"/>
-      <c r="P18" s="125"/>
-      <c r="Q18" s="145"/>
-      <c r="R18" s="127"/>
-      <c r="S18" s="127"/>
-      <c r="T18" s="127"/>
-      <c r="U18" s="127"/>
-      <c r="V18" s="127"/>
-      <c r="W18" s="127"/>
-      <c r="X18" s="127"/>
-      <c r="Y18" s="127"/>
-      <c r="Z18" s="127"/>
-      <c r="AA18" s="127"/>
-      <c r="AB18" s="127"/>
-      <c r="AC18" s="127"/>
-      <c r="AD18" s="127"/>
-      <c r="AE18" s="128"/>
-      <c r="AF18" s="144"/>
-      <c r="AG18" s="124"/>
-      <c r="AH18" s="124"/>
-      <c r="AI18" s="125"/>
+      <c r="B18" s="90"/>
+      <c r="C18" s="91"/>
+      <c r="D18" s="92"/>
+      <c r="E18" s="93"/>
+      <c r="F18" s="94"/>
+      <c r="G18" s="90"/>
+      <c r="H18" s="95"/>
+      <c r="I18" s="91"/>
+      <c r="J18" s="96"/>
+      <c r="K18" s="97"/>
+      <c r="L18" s="97"/>
+      <c r="M18" s="97"/>
+      <c r="N18" s="97"/>
+      <c r="O18" s="97"/>
+      <c r="P18" s="98"/>
+      <c r="Q18" s="99"/>
+      <c r="R18" s="100"/>
+      <c r="S18" s="100"/>
+      <c r="T18" s="100"/>
+      <c r="U18" s="100"/>
+      <c r="V18" s="100"/>
+      <c r="W18" s="100"/>
+      <c r="X18" s="100"/>
+      <c r="Y18" s="100"/>
+      <c r="Z18" s="100"/>
+      <c r="AA18" s="100"/>
+      <c r="AB18" s="100"/>
+      <c r="AC18" s="100"/>
+      <c r="AD18" s="100"/>
+      <c r="AE18" s="101"/>
+      <c r="AF18" s="96"/>
+      <c r="AG18" s="97"/>
+      <c r="AH18" s="97"/>
+      <c r="AI18" s="98"/>
     </row>
     <row r="19" spans="1:35" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="13"/>
-      <c r="B19" s="143"/>
-      <c r="C19" s="117"/>
-      <c r="D19" s="118"/>
-      <c r="E19" s="119"/>
-      <c r="F19" s="120"/>
-      <c r="G19" s="143"/>
-      <c r="H19" s="122"/>
-      <c r="I19" s="117"/>
-      <c r="J19" s="144"/>
-      <c r="K19" s="124"/>
-      <c r="L19" s="124"/>
-      <c r="M19" s="124"/>
-      <c r="N19" s="124"/>
-      <c r="O19" s="124"/>
-      <c r="P19" s="125"/>
-      <c r="Q19" s="145"/>
-      <c r="R19" s="127"/>
-      <c r="S19" s="127"/>
-      <c r="T19" s="127"/>
-      <c r="U19" s="127"/>
-      <c r="V19" s="127"/>
-      <c r="W19" s="127"/>
-      <c r="X19" s="127"/>
-      <c r="Y19" s="127"/>
-      <c r="Z19" s="127"/>
-      <c r="AA19" s="127"/>
-      <c r="AB19" s="127"/>
-      <c r="AC19" s="127"/>
-      <c r="AD19" s="127"/>
-      <c r="AE19" s="128"/>
-      <c r="AF19" s="144"/>
-      <c r="AG19" s="124"/>
-      <c r="AH19" s="124"/>
-      <c r="AI19" s="125"/>
+      <c r="B19" s="90"/>
+      <c r="C19" s="91"/>
+      <c r="D19" s="92"/>
+      <c r="E19" s="93"/>
+      <c r="F19" s="94"/>
+      <c r="G19" s="90"/>
+      <c r="H19" s="95"/>
+      <c r="I19" s="91"/>
+      <c r="J19" s="96"/>
+      <c r="K19" s="97"/>
+      <c r="L19" s="97"/>
+      <c r="M19" s="97"/>
+      <c r="N19" s="97"/>
+      <c r="O19" s="97"/>
+      <c r="P19" s="98"/>
+      <c r="Q19" s="99"/>
+      <c r="R19" s="100"/>
+      <c r="S19" s="100"/>
+      <c r="T19" s="100"/>
+      <c r="U19" s="100"/>
+      <c r="V19" s="100"/>
+      <c r="W19" s="100"/>
+      <c r="X19" s="100"/>
+      <c r="Y19" s="100"/>
+      <c r="Z19" s="100"/>
+      <c r="AA19" s="100"/>
+      <c r="AB19" s="100"/>
+      <c r="AC19" s="100"/>
+      <c r="AD19" s="100"/>
+      <c r="AE19" s="101"/>
+      <c r="AF19" s="96"/>
+      <c r="AG19" s="97"/>
+      <c r="AH19" s="97"/>
+      <c r="AI19" s="98"/>
     </row>
     <row r="20" spans="1:35" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="13"/>
-      <c r="B20" s="143"/>
-      <c r="C20" s="117"/>
-      <c r="D20" s="118"/>
-      <c r="E20" s="119"/>
-      <c r="F20" s="120"/>
-      <c r="G20" s="143"/>
-      <c r="H20" s="122"/>
-      <c r="I20" s="117"/>
-      <c r="J20" s="144"/>
-      <c r="K20" s="124"/>
-      <c r="L20" s="124"/>
-      <c r="M20" s="124"/>
-      <c r="N20" s="124"/>
-      <c r="O20" s="124"/>
-      <c r="P20" s="125"/>
-      <c r="Q20" s="145"/>
-      <c r="R20" s="127"/>
-      <c r="S20" s="127"/>
-      <c r="T20" s="127"/>
-      <c r="U20" s="127"/>
-      <c r="V20" s="127"/>
-      <c r="W20" s="127"/>
-      <c r="X20" s="127"/>
-      <c r="Y20" s="127"/>
-      <c r="Z20" s="127"/>
-      <c r="AA20" s="127"/>
-      <c r="AB20" s="127"/>
-      <c r="AC20" s="127"/>
-      <c r="AD20" s="127"/>
-      <c r="AE20" s="128"/>
-      <c r="AF20" s="144"/>
-      <c r="AG20" s="124"/>
-      <c r="AH20" s="124"/>
-      <c r="AI20" s="125"/>
+      <c r="B20" s="90"/>
+      <c r="C20" s="91"/>
+      <c r="D20" s="92"/>
+      <c r="E20" s="93"/>
+      <c r="F20" s="94"/>
+      <c r="G20" s="90"/>
+      <c r="H20" s="95"/>
+      <c r="I20" s="91"/>
+      <c r="J20" s="96"/>
+      <c r="K20" s="97"/>
+      <c r="L20" s="97"/>
+      <c r="M20" s="97"/>
+      <c r="N20" s="97"/>
+      <c r="O20" s="97"/>
+      <c r="P20" s="98"/>
+      <c r="Q20" s="99"/>
+      <c r="R20" s="100"/>
+      <c r="S20" s="100"/>
+      <c r="T20" s="100"/>
+      <c r="U20" s="100"/>
+      <c r="V20" s="100"/>
+      <c r="W20" s="100"/>
+      <c r="X20" s="100"/>
+      <c r="Y20" s="100"/>
+      <c r="Z20" s="100"/>
+      <c r="AA20" s="100"/>
+      <c r="AB20" s="100"/>
+      <c r="AC20" s="100"/>
+      <c r="AD20" s="100"/>
+      <c r="AE20" s="101"/>
+      <c r="AF20" s="96"/>
+      <c r="AG20" s="97"/>
+      <c r="AH20" s="97"/>
+      <c r="AI20" s="98"/>
     </row>
     <row r="21" spans="1:35" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="13"/>
-      <c r="B21" s="143"/>
-      <c r="C21" s="117"/>
-      <c r="D21" s="118"/>
-      <c r="E21" s="119"/>
-      <c r="F21" s="120"/>
-      <c r="G21" s="143"/>
-      <c r="H21" s="122"/>
-      <c r="I21" s="117"/>
-      <c r="J21" s="144"/>
-      <c r="K21" s="124"/>
-      <c r="L21" s="124"/>
-      <c r="M21" s="124"/>
-      <c r="N21" s="124"/>
-      <c r="O21" s="124"/>
-      <c r="P21" s="125"/>
-      <c r="Q21" s="145"/>
-      <c r="R21" s="127"/>
-      <c r="S21" s="127"/>
-      <c r="T21" s="127"/>
-      <c r="U21" s="127"/>
-      <c r="V21" s="127"/>
-      <c r="W21" s="127"/>
-      <c r="X21" s="127"/>
-      <c r="Y21" s="127"/>
-      <c r="Z21" s="127"/>
-      <c r="AA21" s="127"/>
-      <c r="AB21" s="127"/>
-      <c r="AC21" s="127"/>
-      <c r="AD21" s="127"/>
-      <c r="AE21" s="128"/>
-      <c r="AF21" s="144"/>
-      <c r="AG21" s="124"/>
-      <c r="AH21" s="124"/>
-      <c r="AI21" s="125"/>
+      <c r="B21" s="90"/>
+      <c r="C21" s="91"/>
+      <c r="D21" s="92"/>
+      <c r="E21" s="93"/>
+      <c r="F21" s="94"/>
+      <c r="G21" s="90"/>
+      <c r="H21" s="95"/>
+      <c r="I21" s="91"/>
+      <c r="J21" s="96"/>
+      <c r="K21" s="97"/>
+      <c r="L21" s="97"/>
+      <c r="M21" s="97"/>
+      <c r="N21" s="97"/>
+      <c r="O21" s="97"/>
+      <c r="P21" s="98"/>
+      <c r="Q21" s="99"/>
+      <c r="R21" s="100"/>
+      <c r="S21" s="100"/>
+      <c r="T21" s="100"/>
+      <c r="U21" s="100"/>
+      <c r="V21" s="100"/>
+      <c r="W21" s="100"/>
+      <c r="X21" s="100"/>
+      <c r="Y21" s="100"/>
+      <c r="Z21" s="100"/>
+      <c r="AA21" s="100"/>
+      <c r="AB21" s="100"/>
+      <c r="AC21" s="100"/>
+      <c r="AD21" s="100"/>
+      <c r="AE21" s="101"/>
+      <c r="AF21" s="96"/>
+      <c r="AG21" s="97"/>
+      <c r="AH21" s="97"/>
+      <c r="AI21" s="98"/>
     </row>
     <row r="22" spans="1:35" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="13"/>
-      <c r="B22" s="143"/>
-      <c r="C22" s="117"/>
-      <c r="D22" s="118"/>
-      <c r="E22" s="119"/>
-      <c r="F22" s="120"/>
-      <c r="G22" s="143"/>
-      <c r="H22" s="122"/>
-      <c r="I22" s="117"/>
-      <c r="J22" s="144"/>
-      <c r="K22" s="124"/>
-      <c r="L22" s="124"/>
-      <c r="M22" s="124"/>
-      <c r="N22" s="124"/>
-      <c r="O22" s="124"/>
-      <c r="P22" s="125"/>
-      <c r="Q22" s="145"/>
-      <c r="R22" s="127"/>
-      <c r="S22" s="127"/>
-      <c r="T22" s="127"/>
-      <c r="U22" s="127"/>
-      <c r="V22" s="127"/>
-      <c r="W22" s="127"/>
-      <c r="X22" s="127"/>
-      <c r="Y22" s="127"/>
-      <c r="Z22" s="127"/>
-      <c r="AA22" s="127"/>
-      <c r="AB22" s="127"/>
-      <c r="AC22" s="127"/>
-      <c r="AD22" s="127"/>
-      <c r="AE22" s="128"/>
-      <c r="AF22" s="144"/>
-      <c r="AG22" s="124"/>
-      <c r="AH22" s="124"/>
-      <c r="AI22" s="125"/>
+      <c r="B22" s="90"/>
+      <c r="C22" s="91"/>
+      <c r="D22" s="92"/>
+      <c r="E22" s="93"/>
+      <c r="F22" s="94"/>
+      <c r="G22" s="90"/>
+      <c r="H22" s="95"/>
+      <c r="I22" s="91"/>
+      <c r="J22" s="96"/>
+      <c r="K22" s="97"/>
+      <c r="L22" s="97"/>
+      <c r="M22" s="97"/>
+      <c r="N22" s="97"/>
+      <c r="O22" s="97"/>
+      <c r="P22" s="98"/>
+      <c r="Q22" s="99"/>
+      <c r="R22" s="100"/>
+      <c r="S22" s="100"/>
+      <c r="T22" s="100"/>
+      <c r="U22" s="100"/>
+      <c r="V22" s="100"/>
+      <c r="W22" s="100"/>
+      <c r="X22" s="100"/>
+      <c r="Y22" s="100"/>
+      <c r="Z22" s="100"/>
+      <c r="AA22" s="100"/>
+      <c r="AB22" s="100"/>
+      <c r="AC22" s="100"/>
+      <c r="AD22" s="100"/>
+      <c r="AE22" s="101"/>
+      <c r="AF22" s="96"/>
+      <c r="AG22" s="97"/>
+      <c r="AH22" s="97"/>
+      <c r="AI22" s="98"/>
     </row>
     <row r="23" spans="1:35" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="13"/>
-      <c r="B23" s="143"/>
-      <c r="C23" s="117"/>
-      <c r="D23" s="118"/>
-      <c r="E23" s="119"/>
-      <c r="F23" s="120"/>
-      <c r="G23" s="143"/>
-      <c r="H23" s="122"/>
-      <c r="I23" s="117"/>
-      <c r="J23" s="144"/>
-      <c r="K23" s="124"/>
-      <c r="L23" s="124"/>
-      <c r="M23" s="124"/>
-      <c r="N23" s="124"/>
-      <c r="O23" s="124"/>
-      <c r="P23" s="125"/>
-      <c r="Q23" s="145"/>
-      <c r="R23" s="127"/>
-      <c r="S23" s="127"/>
-      <c r="T23" s="127"/>
-      <c r="U23" s="127"/>
-      <c r="V23" s="127"/>
-      <c r="W23" s="127"/>
-      <c r="X23" s="127"/>
-      <c r="Y23" s="127"/>
-      <c r="Z23" s="127"/>
-      <c r="AA23" s="127"/>
-      <c r="AB23" s="127"/>
-      <c r="AC23" s="127"/>
-      <c r="AD23" s="127"/>
-      <c r="AE23" s="128"/>
-      <c r="AF23" s="144"/>
-      <c r="AG23" s="124"/>
-      <c r="AH23" s="124"/>
-      <c r="AI23" s="125"/>
+      <c r="B23" s="90"/>
+      <c r="C23" s="91"/>
+      <c r="D23" s="92"/>
+      <c r="E23" s="93"/>
+      <c r="F23" s="94"/>
+      <c r="G23" s="90"/>
+      <c r="H23" s="95"/>
+      <c r="I23" s="91"/>
+      <c r="J23" s="96"/>
+      <c r="K23" s="97"/>
+      <c r="L23" s="97"/>
+      <c r="M23" s="97"/>
+      <c r="N23" s="97"/>
+      <c r="O23" s="97"/>
+      <c r="P23" s="98"/>
+      <c r="Q23" s="99"/>
+      <c r="R23" s="100"/>
+      <c r="S23" s="100"/>
+      <c r="T23" s="100"/>
+      <c r="U23" s="100"/>
+      <c r="V23" s="100"/>
+      <c r="W23" s="100"/>
+      <c r="X23" s="100"/>
+      <c r="Y23" s="100"/>
+      <c r="Z23" s="100"/>
+      <c r="AA23" s="100"/>
+      <c r="AB23" s="100"/>
+      <c r="AC23" s="100"/>
+      <c r="AD23" s="100"/>
+      <c r="AE23" s="101"/>
+      <c r="AF23" s="96"/>
+      <c r="AG23" s="97"/>
+      <c r="AH23" s="97"/>
+      <c r="AI23" s="98"/>
     </row>
     <row r="24" spans="1:35" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="13"/>
-      <c r="B24" s="143"/>
-      <c r="C24" s="117"/>
-      <c r="D24" s="118"/>
-      <c r="E24" s="119"/>
-      <c r="F24" s="120"/>
-      <c r="G24" s="143"/>
-      <c r="H24" s="122"/>
-      <c r="I24" s="117"/>
-      <c r="J24" s="144"/>
-      <c r="K24" s="124"/>
-      <c r="L24" s="124"/>
-      <c r="M24" s="124"/>
-      <c r="N24" s="124"/>
-      <c r="O24" s="124"/>
-      <c r="P24" s="125"/>
-      <c r="Q24" s="145"/>
-      <c r="R24" s="127"/>
-      <c r="S24" s="127"/>
-      <c r="T24" s="127"/>
-      <c r="U24" s="127"/>
-      <c r="V24" s="127"/>
-      <c r="W24" s="127"/>
-      <c r="X24" s="127"/>
-      <c r="Y24" s="127"/>
-      <c r="Z24" s="127"/>
-      <c r="AA24" s="127"/>
-      <c r="AB24" s="127"/>
-      <c r="AC24" s="127"/>
-      <c r="AD24" s="127"/>
-      <c r="AE24" s="128"/>
-      <c r="AF24" s="144"/>
-      <c r="AG24" s="124"/>
-      <c r="AH24" s="124"/>
-      <c r="AI24" s="125"/>
+      <c r="B24" s="90"/>
+      <c r="C24" s="91"/>
+      <c r="D24" s="92"/>
+      <c r="E24" s="93"/>
+      <c r="F24" s="94"/>
+      <c r="G24" s="90"/>
+      <c r="H24" s="95"/>
+      <c r="I24" s="91"/>
+      <c r="J24" s="96"/>
+      <c r="K24" s="97"/>
+      <c r="L24" s="97"/>
+      <c r="M24" s="97"/>
+      <c r="N24" s="97"/>
+      <c r="O24" s="97"/>
+      <c r="P24" s="98"/>
+      <c r="Q24" s="99"/>
+      <c r="R24" s="100"/>
+      <c r="S24" s="100"/>
+      <c r="T24" s="100"/>
+      <c r="U24" s="100"/>
+      <c r="V24" s="100"/>
+      <c r="W24" s="100"/>
+      <c r="X24" s="100"/>
+      <c r="Y24" s="100"/>
+      <c r="Z24" s="100"/>
+      <c r="AA24" s="100"/>
+      <c r="AB24" s="100"/>
+      <c r="AC24" s="100"/>
+      <c r="AD24" s="100"/>
+      <c r="AE24" s="101"/>
+      <c r="AF24" s="96"/>
+      <c r="AG24" s="97"/>
+      <c r="AH24" s="97"/>
+      <c r="AI24" s="98"/>
     </row>
     <row r="25" spans="1:35" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="13"/>
-      <c r="B25" s="143"/>
-      <c r="C25" s="117"/>
-      <c r="D25" s="118"/>
-      <c r="E25" s="119"/>
-      <c r="F25" s="120"/>
-      <c r="G25" s="143"/>
-      <c r="H25" s="122"/>
-      <c r="I25" s="117"/>
-      <c r="J25" s="144"/>
-      <c r="K25" s="124"/>
-      <c r="L25" s="124"/>
-      <c r="M25" s="124"/>
-      <c r="N25" s="124"/>
-      <c r="O25" s="124"/>
-      <c r="P25" s="125"/>
-      <c r="Q25" s="145"/>
-      <c r="R25" s="127"/>
-      <c r="S25" s="127"/>
-      <c r="T25" s="127"/>
-      <c r="U25" s="127"/>
-      <c r="V25" s="127"/>
-      <c r="W25" s="127"/>
-      <c r="X25" s="127"/>
-      <c r="Y25" s="127"/>
-      <c r="Z25" s="127"/>
-      <c r="AA25" s="127"/>
-      <c r="AB25" s="127"/>
-      <c r="AC25" s="127"/>
-      <c r="AD25" s="127"/>
-      <c r="AE25" s="128"/>
-      <c r="AF25" s="144"/>
-      <c r="AG25" s="124"/>
-      <c r="AH25" s="124"/>
-      <c r="AI25" s="125"/>
+      <c r="B25" s="90"/>
+      <c r="C25" s="91"/>
+      <c r="D25" s="92"/>
+      <c r="E25" s="93"/>
+      <c r="F25" s="94"/>
+      <c r="G25" s="90"/>
+      <c r="H25" s="95"/>
+      <c r="I25" s="91"/>
+      <c r="J25" s="96"/>
+      <c r="K25" s="97"/>
+      <c r="L25" s="97"/>
+      <c r="M25" s="97"/>
+      <c r="N25" s="97"/>
+      <c r="O25" s="97"/>
+      <c r="P25" s="98"/>
+      <c r="Q25" s="99"/>
+      <c r="R25" s="100"/>
+      <c r="S25" s="100"/>
+      <c r="T25" s="100"/>
+      <c r="U25" s="100"/>
+      <c r="V25" s="100"/>
+      <c r="W25" s="100"/>
+      <c r="X25" s="100"/>
+      <c r="Y25" s="100"/>
+      <c r="Z25" s="100"/>
+      <c r="AA25" s="100"/>
+      <c r="AB25" s="100"/>
+      <c r="AC25" s="100"/>
+      <c r="AD25" s="100"/>
+      <c r="AE25" s="101"/>
+      <c r="AF25" s="96"/>
+      <c r="AG25" s="97"/>
+      <c r="AH25" s="97"/>
+      <c r="AI25" s="98"/>
     </row>
     <row r="26" spans="1:35" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="13"/>
-      <c r="B26" s="143"/>
-      <c r="C26" s="117"/>
-      <c r="D26" s="118"/>
-      <c r="E26" s="119"/>
-      <c r="F26" s="120"/>
-      <c r="G26" s="143"/>
-      <c r="H26" s="122"/>
-      <c r="I26" s="117"/>
-      <c r="J26" s="144"/>
-      <c r="K26" s="124"/>
-      <c r="L26" s="124"/>
-      <c r="M26" s="124"/>
-      <c r="N26" s="124"/>
-      <c r="O26" s="124"/>
-      <c r="P26" s="125"/>
-      <c r="Q26" s="145"/>
-      <c r="R26" s="127"/>
-      <c r="S26" s="127"/>
-      <c r="T26" s="127"/>
-      <c r="U26" s="127"/>
-      <c r="V26" s="127"/>
-      <c r="W26" s="127"/>
-      <c r="X26" s="127"/>
-      <c r="Y26" s="127"/>
-      <c r="Z26" s="127"/>
-      <c r="AA26" s="127"/>
-      <c r="AB26" s="127"/>
-      <c r="AC26" s="127"/>
-      <c r="AD26" s="127"/>
-      <c r="AE26" s="128"/>
-      <c r="AF26" s="144"/>
-      <c r="AG26" s="124"/>
-      <c r="AH26" s="124"/>
-      <c r="AI26" s="125"/>
+      <c r="B26" s="90"/>
+      <c r="C26" s="91"/>
+      <c r="D26" s="92"/>
+      <c r="E26" s="93"/>
+      <c r="F26" s="94"/>
+      <c r="G26" s="90"/>
+      <c r="H26" s="95"/>
+      <c r="I26" s="91"/>
+      <c r="J26" s="96"/>
+      <c r="K26" s="97"/>
+      <c r="L26" s="97"/>
+      <c r="M26" s="97"/>
+      <c r="N26" s="97"/>
+      <c r="O26" s="97"/>
+      <c r="P26" s="98"/>
+      <c r="Q26" s="99"/>
+      <c r="R26" s="100"/>
+      <c r="S26" s="100"/>
+      <c r="T26" s="100"/>
+      <c r="U26" s="100"/>
+      <c r="V26" s="100"/>
+      <c r="W26" s="100"/>
+      <c r="X26" s="100"/>
+      <c r="Y26" s="100"/>
+      <c r="Z26" s="100"/>
+      <c r="AA26" s="100"/>
+      <c r="AB26" s="100"/>
+      <c r="AC26" s="100"/>
+      <c r="AD26" s="100"/>
+      <c r="AE26" s="101"/>
+      <c r="AF26" s="96"/>
+      <c r="AG26" s="97"/>
+      <c r="AH26" s="97"/>
+      <c r="AI26" s="98"/>
     </row>
     <row r="27" spans="1:35" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="13"/>
-      <c r="B27" s="143"/>
-      <c r="C27" s="117"/>
-      <c r="D27" s="118"/>
-      <c r="E27" s="119"/>
-      <c r="F27" s="120"/>
-      <c r="G27" s="143"/>
-      <c r="H27" s="122"/>
-      <c r="I27" s="117"/>
-      <c r="J27" s="144"/>
-      <c r="K27" s="124"/>
-      <c r="L27" s="124"/>
-      <c r="M27" s="124"/>
-      <c r="N27" s="124"/>
-      <c r="O27" s="124"/>
-      <c r="P27" s="125"/>
-      <c r="Q27" s="145"/>
-      <c r="R27" s="127"/>
-      <c r="S27" s="127"/>
-      <c r="T27" s="127"/>
-      <c r="U27" s="127"/>
-      <c r="V27" s="127"/>
-      <c r="W27" s="127"/>
-      <c r="X27" s="127"/>
-      <c r="Y27" s="127"/>
-      <c r="Z27" s="127"/>
-      <c r="AA27" s="127"/>
-      <c r="AB27" s="127"/>
-      <c r="AC27" s="127"/>
-      <c r="AD27" s="127"/>
-      <c r="AE27" s="128"/>
-      <c r="AF27" s="144"/>
-      <c r="AG27" s="124"/>
-      <c r="AH27" s="124"/>
-      <c r="AI27" s="125"/>
+      <c r="B27" s="90"/>
+      <c r="C27" s="91"/>
+      <c r="D27" s="92"/>
+      <c r="E27" s="93"/>
+      <c r="F27" s="94"/>
+      <c r="G27" s="90"/>
+      <c r="H27" s="95"/>
+      <c r="I27" s="91"/>
+      <c r="J27" s="96"/>
+      <c r="K27" s="97"/>
+      <c r="L27" s="97"/>
+      <c r="M27" s="97"/>
+      <c r="N27" s="97"/>
+      <c r="O27" s="97"/>
+      <c r="P27" s="98"/>
+      <c r="Q27" s="99"/>
+      <c r="R27" s="100"/>
+      <c r="S27" s="100"/>
+      <c r="T27" s="100"/>
+      <c r="U27" s="100"/>
+      <c r="V27" s="100"/>
+      <c r="W27" s="100"/>
+      <c r="X27" s="100"/>
+      <c r="Y27" s="100"/>
+      <c r="Z27" s="100"/>
+      <c r="AA27" s="100"/>
+      <c r="AB27" s="100"/>
+      <c r="AC27" s="100"/>
+      <c r="AD27" s="100"/>
+      <c r="AE27" s="101"/>
+      <c r="AF27" s="96"/>
+      <c r="AG27" s="97"/>
+      <c r="AH27" s="97"/>
+      <c r="AI27" s="98"/>
     </row>
     <row r="28" spans="1:35" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="13"/>
-      <c r="B28" s="143"/>
-      <c r="C28" s="117"/>
-      <c r="D28" s="118"/>
-      <c r="E28" s="119"/>
-      <c r="F28" s="120"/>
-      <c r="G28" s="143"/>
-      <c r="H28" s="122"/>
-      <c r="I28" s="117"/>
-      <c r="J28" s="144"/>
-      <c r="K28" s="124"/>
-      <c r="L28" s="124"/>
-      <c r="M28" s="124"/>
-      <c r="N28" s="124"/>
-      <c r="O28" s="124"/>
-      <c r="P28" s="125"/>
-      <c r="Q28" s="145"/>
-      <c r="R28" s="127"/>
-      <c r="S28" s="127"/>
-      <c r="T28" s="127"/>
-      <c r="U28" s="127"/>
-      <c r="V28" s="127"/>
-      <c r="W28" s="127"/>
-      <c r="X28" s="127"/>
-      <c r="Y28" s="127"/>
-      <c r="Z28" s="127"/>
-      <c r="AA28" s="127"/>
-      <c r="AB28" s="127"/>
-      <c r="AC28" s="127"/>
-      <c r="AD28" s="127"/>
-      <c r="AE28" s="128"/>
-      <c r="AF28" s="144"/>
-      <c r="AG28" s="124"/>
-      <c r="AH28" s="124"/>
-      <c r="AI28" s="125"/>
+      <c r="B28" s="90"/>
+      <c r="C28" s="91"/>
+      <c r="D28" s="92"/>
+      <c r="E28" s="93"/>
+      <c r="F28" s="94"/>
+      <c r="G28" s="90"/>
+      <c r="H28" s="95"/>
+      <c r="I28" s="91"/>
+      <c r="J28" s="96"/>
+      <c r="K28" s="97"/>
+      <c r="L28" s="97"/>
+      <c r="M28" s="97"/>
+      <c r="N28" s="97"/>
+      <c r="O28" s="97"/>
+      <c r="P28" s="98"/>
+      <c r="Q28" s="99"/>
+      <c r="R28" s="100"/>
+      <c r="S28" s="100"/>
+      <c r="T28" s="100"/>
+      <c r="U28" s="100"/>
+      <c r="V28" s="100"/>
+      <c r="W28" s="100"/>
+      <c r="X28" s="100"/>
+      <c r="Y28" s="100"/>
+      <c r="Z28" s="100"/>
+      <c r="AA28" s="100"/>
+      <c r="AB28" s="100"/>
+      <c r="AC28" s="100"/>
+      <c r="AD28" s="100"/>
+      <c r="AE28" s="101"/>
+      <c r="AF28" s="96"/>
+      <c r="AG28" s="97"/>
+      <c r="AH28" s="97"/>
+      <c r="AI28" s="98"/>
     </row>
     <row r="29" spans="1:35" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="13"/>
-      <c r="B29" s="143"/>
-      <c r="C29" s="117"/>
-      <c r="D29" s="118"/>
-      <c r="E29" s="119"/>
-      <c r="F29" s="120"/>
-      <c r="G29" s="143"/>
-      <c r="H29" s="122"/>
-      <c r="I29" s="117"/>
-      <c r="J29" s="144"/>
-      <c r="K29" s="124"/>
-      <c r="L29" s="124"/>
-      <c r="M29" s="124"/>
-      <c r="N29" s="124"/>
-      <c r="O29" s="124"/>
-      <c r="P29" s="125"/>
-      <c r="Q29" s="145"/>
-      <c r="R29" s="127"/>
-      <c r="S29" s="127"/>
-      <c r="T29" s="127"/>
-      <c r="U29" s="127"/>
-      <c r="V29" s="127"/>
-      <c r="W29" s="127"/>
-      <c r="X29" s="127"/>
-      <c r="Y29" s="127"/>
-      <c r="Z29" s="127"/>
-      <c r="AA29" s="127"/>
-      <c r="AB29" s="127"/>
-      <c r="AC29" s="127"/>
-      <c r="AD29" s="127"/>
-      <c r="AE29" s="128"/>
-      <c r="AF29" s="144"/>
-      <c r="AG29" s="124"/>
-      <c r="AH29" s="124"/>
-      <c r="AI29" s="125"/>
+      <c r="B29" s="90"/>
+      <c r="C29" s="91"/>
+      <c r="D29" s="92"/>
+      <c r="E29" s="93"/>
+      <c r="F29" s="94"/>
+      <c r="G29" s="90"/>
+      <c r="H29" s="95"/>
+      <c r="I29" s="91"/>
+      <c r="J29" s="96"/>
+      <c r="K29" s="97"/>
+      <c r="L29" s="97"/>
+      <c r="M29" s="97"/>
+      <c r="N29" s="97"/>
+      <c r="O29" s="97"/>
+      <c r="P29" s="98"/>
+      <c r="Q29" s="99"/>
+      <c r="R29" s="100"/>
+      <c r="S29" s="100"/>
+      <c r="T29" s="100"/>
+      <c r="U29" s="100"/>
+      <c r="V29" s="100"/>
+      <c r="W29" s="100"/>
+      <c r="X29" s="100"/>
+      <c r="Y29" s="100"/>
+      <c r="Z29" s="100"/>
+      <c r="AA29" s="100"/>
+      <c r="AB29" s="100"/>
+      <c r="AC29" s="100"/>
+      <c r="AD29" s="100"/>
+      <c r="AE29" s="101"/>
+      <c r="AF29" s="96"/>
+      <c r="AG29" s="97"/>
+      <c r="AH29" s="97"/>
+      <c r="AI29" s="98"/>
     </row>
     <row r="30" spans="1:35" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="13"/>
-      <c r="B30" s="143"/>
-      <c r="C30" s="117"/>
-      <c r="D30" s="118"/>
-      <c r="E30" s="119"/>
-      <c r="F30" s="120"/>
-      <c r="G30" s="143"/>
-      <c r="H30" s="122"/>
-      <c r="I30" s="117"/>
-      <c r="J30" s="144"/>
-      <c r="K30" s="124"/>
-      <c r="L30" s="124"/>
-      <c r="M30" s="124"/>
-      <c r="N30" s="124"/>
-      <c r="O30" s="124"/>
-      <c r="P30" s="125"/>
-      <c r="Q30" s="145"/>
-      <c r="R30" s="127"/>
-      <c r="S30" s="127"/>
-      <c r="T30" s="127"/>
-      <c r="U30" s="127"/>
-      <c r="V30" s="127"/>
-      <c r="W30" s="127"/>
-      <c r="X30" s="127"/>
-      <c r="Y30" s="127"/>
-      <c r="Z30" s="127"/>
-      <c r="AA30" s="127"/>
-      <c r="AB30" s="127"/>
-      <c r="AC30" s="127"/>
-      <c r="AD30" s="127"/>
-      <c r="AE30" s="128"/>
-      <c r="AF30" s="144"/>
-      <c r="AG30" s="124"/>
-      <c r="AH30" s="124"/>
-      <c r="AI30" s="125"/>
+      <c r="B30" s="90"/>
+      <c r="C30" s="91"/>
+      <c r="D30" s="92"/>
+      <c r="E30" s="93"/>
+      <c r="F30" s="94"/>
+      <c r="G30" s="90"/>
+      <c r="H30" s="95"/>
+      <c r="I30" s="91"/>
+      <c r="J30" s="96"/>
+      <c r="K30" s="97"/>
+      <c r="L30" s="97"/>
+      <c r="M30" s="97"/>
+      <c r="N30" s="97"/>
+      <c r="O30" s="97"/>
+      <c r="P30" s="98"/>
+      <c r="Q30" s="99"/>
+      <c r="R30" s="100"/>
+      <c r="S30" s="100"/>
+      <c r="T30" s="100"/>
+      <c r="U30" s="100"/>
+      <c r="V30" s="100"/>
+      <c r="W30" s="100"/>
+      <c r="X30" s="100"/>
+      <c r="Y30" s="100"/>
+      <c r="Z30" s="100"/>
+      <c r="AA30" s="100"/>
+      <c r="AB30" s="100"/>
+      <c r="AC30" s="100"/>
+      <c r="AD30" s="100"/>
+      <c r="AE30" s="101"/>
+      <c r="AF30" s="96"/>
+      <c r="AG30" s="97"/>
+      <c r="AH30" s="97"/>
+      <c r="AI30" s="98"/>
     </row>
     <row r="31" spans="1:35" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="13"/>
-      <c r="B31" s="143"/>
-      <c r="C31" s="117"/>
-      <c r="D31" s="118"/>
-      <c r="E31" s="119"/>
-      <c r="F31" s="120"/>
-      <c r="G31" s="143"/>
-      <c r="H31" s="122"/>
-      <c r="I31" s="117"/>
-      <c r="J31" s="144"/>
-      <c r="K31" s="124"/>
-      <c r="L31" s="124"/>
-      <c r="M31" s="124"/>
-      <c r="N31" s="124"/>
-      <c r="O31" s="124"/>
-      <c r="P31" s="125"/>
-      <c r="Q31" s="145"/>
-      <c r="R31" s="127"/>
-      <c r="S31" s="127"/>
-      <c r="T31" s="127"/>
-      <c r="U31" s="127"/>
-      <c r="V31" s="127"/>
-      <c r="W31" s="127"/>
-      <c r="X31" s="127"/>
-      <c r="Y31" s="127"/>
-      <c r="Z31" s="127"/>
-      <c r="AA31" s="127"/>
-      <c r="AB31" s="127"/>
-      <c r="AC31" s="127"/>
-      <c r="AD31" s="127"/>
-      <c r="AE31" s="128"/>
-      <c r="AF31" s="144"/>
-      <c r="AG31" s="124"/>
-      <c r="AH31" s="124"/>
-      <c r="AI31" s="125"/>
+      <c r="B31" s="90"/>
+      <c r="C31" s="91"/>
+      <c r="D31" s="92"/>
+      <c r="E31" s="93"/>
+      <c r="F31" s="94"/>
+      <c r="G31" s="90"/>
+      <c r="H31" s="95"/>
+      <c r="I31" s="91"/>
+      <c r="J31" s="96"/>
+      <c r="K31" s="97"/>
+      <c r="L31" s="97"/>
+      <c r="M31" s="97"/>
+      <c r="N31" s="97"/>
+      <c r="O31" s="97"/>
+      <c r="P31" s="98"/>
+      <c r="Q31" s="99"/>
+      <c r="R31" s="100"/>
+      <c r="S31" s="100"/>
+      <c r="T31" s="100"/>
+      <c r="U31" s="100"/>
+      <c r="V31" s="100"/>
+      <c r="W31" s="100"/>
+      <c r="X31" s="100"/>
+      <c r="Y31" s="100"/>
+      <c r="Z31" s="100"/>
+      <c r="AA31" s="100"/>
+      <c r="AB31" s="100"/>
+      <c r="AC31" s="100"/>
+      <c r="AD31" s="100"/>
+      <c r="AE31" s="101"/>
+      <c r="AF31" s="96"/>
+      <c r="AG31" s="97"/>
+      <c r="AH31" s="97"/>
+      <c r="AI31" s="98"/>
     </row>
     <row r="32" spans="1:35" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="13"/>
-      <c r="B32" s="143"/>
-      <c r="C32" s="117"/>
-      <c r="D32" s="118"/>
-      <c r="E32" s="119"/>
-      <c r="F32" s="120"/>
-      <c r="G32" s="143"/>
-      <c r="H32" s="122"/>
-      <c r="I32" s="117"/>
-      <c r="J32" s="144"/>
-      <c r="K32" s="146"/>
-      <c r="L32" s="124"/>
-      <c r="M32" s="124"/>
-      <c r="N32" s="124"/>
-      <c r="O32" s="124"/>
-      <c r="P32" s="125"/>
-      <c r="Q32" s="145"/>
-      <c r="R32" s="127"/>
-      <c r="S32" s="127"/>
-      <c r="T32" s="127"/>
-      <c r="U32" s="127"/>
-      <c r="V32" s="127"/>
-      <c r="W32" s="127"/>
-      <c r="X32" s="127"/>
-      <c r="Y32" s="127"/>
-      <c r="Z32" s="127"/>
-      <c r="AA32" s="127"/>
-      <c r="AB32" s="127"/>
-      <c r="AC32" s="127"/>
-      <c r="AD32" s="127"/>
-      <c r="AE32" s="128"/>
-      <c r="AF32" s="144"/>
-      <c r="AG32" s="124"/>
-      <c r="AH32" s="124"/>
-      <c r="AI32" s="125"/>
+      <c r="B32" s="90"/>
+      <c r="C32" s="91"/>
+      <c r="D32" s="92"/>
+      <c r="E32" s="93"/>
+      <c r="F32" s="94"/>
+      <c r="G32" s="90"/>
+      <c r="H32" s="95"/>
+      <c r="I32" s="91"/>
+      <c r="J32" s="96"/>
+      <c r="K32" s="102"/>
+      <c r="L32" s="97"/>
+      <c r="M32" s="97"/>
+      <c r="N32" s="97"/>
+      <c r="O32" s="97"/>
+      <c r="P32" s="98"/>
+      <c r="Q32" s="99"/>
+      <c r="R32" s="100"/>
+      <c r="S32" s="100"/>
+      <c r="T32" s="100"/>
+      <c r="U32" s="100"/>
+      <c r="V32" s="100"/>
+      <c r="W32" s="100"/>
+      <c r="X32" s="100"/>
+      <c r="Y32" s="100"/>
+      <c r="Z32" s="100"/>
+      <c r="AA32" s="100"/>
+      <c r="AB32" s="100"/>
+      <c r="AC32" s="100"/>
+      <c r="AD32" s="100"/>
+      <c r="AE32" s="101"/>
+      <c r="AF32" s="96"/>
+      <c r="AG32" s="97"/>
+      <c r="AH32" s="97"/>
+      <c r="AI32" s="98"/>
     </row>
     <row r="33" spans="1:35" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="13"/>
-      <c r="B33" s="143"/>
-      <c r="C33" s="117"/>
-      <c r="D33" s="118"/>
-      <c r="E33" s="119"/>
-      <c r="F33" s="120"/>
-      <c r="G33" s="143"/>
-      <c r="H33" s="122"/>
-      <c r="I33" s="117"/>
-      <c r="J33" s="144"/>
-      <c r="K33" s="124"/>
-      <c r="L33" s="124"/>
-      <c r="M33" s="124"/>
-      <c r="N33" s="124"/>
-      <c r="O33" s="124"/>
-      <c r="P33" s="125"/>
-      <c r="Q33" s="145"/>
-      <c r="R33" s="127"/>
-      <c r="S33" s="127"/>
-      <c r="T33" s="127"/>
-      <c r="U33" s="127"/>
-      <c r="V33" s="127"/>
-      <c r="W33" s="127"/>
-      <c r="X33" s="127"/>
-      <c r="Y33" s="127"/>
-      <c r="Z33" s="127"/>
-      <c r="AA33" s="127"/>
-      <c r="AB33" s="127"/>
-      <c r="AC33" s="127"/>
-      <c r="AD33" s="127"/>
-      <c r="AE33" s="128"/>
-      <c r="AF33" s="144"/>
-      <c r="AG33" s="124"/>
-      <c r="AH33" s="124"/>
-      <c r="AI33" s="125"/>
+      <c r="B33" s="90"/>
+      <c r="C33" s="91"/>
+      <c r="D33" s="92"/>
+      <c r="E33" s="93"/>
+      <c r="F33" s="94"/>
+      <c r="G33" s="90"/>
+      <c r="H33" s="95"/>
+      <c r="I33" s="91"/>
+      <c r="J33" s="96"/>
+      <c r="K33" s="97"/>
+      <c r="L33" s="97"/>
+      <c r="M33" s="97"/>
+      <c r="N33" s="97"/>
+      <c r="O33" s="97"/>
+      <c r="P33" s="98"/>
+      <c r="Q33" s="99"/>
+      <c r="R33" s="100"/>
+      <c r="S33" s="100"/>
+      <c r="T33" s="100"/>
+      <c r="U33" s="100"/>
+      <c r="V33" s="100"/>
+      <c r="W33" s="100"/>
+      <c r="X33" s="100"/>
+      <c r="Y33" s="100"/>
+      <c r="Z33" s="100"/>
+      <c r="AA33" s="100"/>
+      <c r="AB33" s="100"/>
+      <c r="AC33" s="100"/>
+      <c r="AD33" s="100"/>
+      <c r="AE33" s="101"/>
+      <c r="AF33" s="96"/>
+      <c r="AG33" s="97"/>
+      <c r="AH33" s="97"/>
+      <c r="AI33" s="98"/>
     </row>
     <row r="34" spans="1:35" ht="14.25" x14ac:dyDescent="0.15">
       <c r="K34" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="179">
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="J33:P33"/>
-    <mergeCell ref="Q33:AE33"/>
-    <mergeCell ref="AF33:AI33"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="J32:P32"/>
-    <mergeCell ref="Q32:AE32"/>
-    <mergeCell ref="AF32:AI32"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:P31"/>
-    <mergeCell ref="Q31:AE31"/>
-    <mergeCell ref="AF31:AI31"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:P30"/>
-    <mergeCell ref="Q30:AE30"/>
-    <mergeCell ref="AF30:AI30"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:P29"/>
-    <mergeCell ref="Q29:AE29"/>
-    <mergeCell ref="AF29:AI29"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:P28"/>
-    <mergeCell ref="Q28:AE28"/>
-    <mergeCell ref="AF28:AI28"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:P27"/>
-    <mergeCell ref="Q27:AE27"/>
-    <mergeCell ref="AF27:AI27"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="J26:P26"/>
-    <mergeCell ref="Q26:AE26"/>
-    <mergeCell ref="AF26:AI26"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:P25"/>
-    <mergeCell ref="Q25:AE25"/>
-    <mergeCell ref="AF25:AI25"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:P24"/>
-    <mergeCell ref="Q24:AE24"/>
-    <mergeCell ref="AF24:AI24"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:P23"/>
-    <mergeCell ref="Q23:AE23"/>
-    <mergeCell ref="AF23:AI23"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:P22"/>
-    <mergeCell ref="Q22:AE22"/>
-    <mergeCell ref="AF22:AI22"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:P21"/>
-    <mergeCell ref="Q21:AE21"/>
-    <mergeCell ref="AF21:AI21"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:P20"/>
-    <mergeCell ref="Q20:AE20"/>
-    <mergeCell ref="AF20:AI20"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:P19"/>
-    <mergeCell ref="Q19:AE19"/>
-    <mergeCell ref="AF19:AI19"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="J18:P18"/>
-    <mergeCell ref="Q18:AE18"/>
-    <mergeCell ref="AF18:AI18"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:P17"/>
-    <mergeCell ref="Q17:AE17"/>
-    <mergeCell ref="AF17:AI17"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:P16"/>
-    <mergeCell ref="Q16:AE16"/>
-    <mergeCell ref="AF16:AI16"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:P15"/>
-    <mergeCell ref="Q15:AE15"/>
-    <mergeCell ref="AF15:AI15"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="J14:P14"/>
-    <mergeCell ref="Q14:AE14"/>
-    <mergeCell ref="AF14:AI14"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="J13:P13"/>
-    <mergeCell ref="Q13:AE13"/>
-    <mergeCell ref="AF13:AI13"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="J12:P12"/>
-    <mergeCell ref="Q12:AE12"/>
-    <mergeCell ref="AF12:AI12"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="J11:P11"/>
-    <mergeCell ref="Q11:AE11"/>
-    <mergeCell ref="AF11:AI11"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="J10:P10"/>
-    <mergeCell ref="Q10:AE10"/>
-    <mergeCell ref="AF10:AI10"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="J9:P9"/>
-    <mergeCell ref="Q9:AE9"/>
-    <mergeCell ref="AF9:AI9"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="J8:P8"/>
-    <mergeCell ref="Q8:AE8"/>
-    <mergeCell ref="AF8:AI8"/>
     <mergeCell ref="AG3:AI3"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="D7:F7"/>
@@ -15612,6 +15712,162 @@
     <mergeCell ref="E3:N3"/>
     <mergeCell ref="AA3:AB3"/>
     <mergeCell ref="AC3:AF3"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="J9:P9"/>
+    <mergeCell ref="Q9:AE9"/>
+    <mergeCell ref="AF9:AI9"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="J8:P8"/>
+    <mergeCell ref="Q8:AE8"/>
+    <mergeCell ref="AF8:AI8"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="J11:P11"/>
+    <mergeCell ref="Q11:AE11"/>
+    <mergeCell ref="AF11:AI11"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="J10:P10"/>
+    <mergeCell ref="Q10:AE10"/>
+    <mergeCell ref="AF10:AI10"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="J13:P13"/>
+    <mergeCell ref="Q13:AE13"/>
+    <mergeCell ref="AF13:AI13"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="J12:P12"/>
+    <mergeCell ref="Q12:AE12"/>
+    <mergeCell ref="AF12:AI12"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:P15"/>
+    <mergeCell ref="Q15:AE15"/>
+    <mergeCell ref="AF15:AI15"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="J14:P14"/>
+    <mergeCell ref="Q14:AE14"/>
+    <mergeCell ref="AF14:AI14"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:P17"/>
+    <mergeCell ref="Q17:AE17"/>
+    <mergeCell ref="AF17:AI17"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:P16"/>
+    <mergeCell ref="Q16:AE16"/>
+    <mergeCell ref="AF16:AI16"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:P19"/>
+    <mergeCell ref="Q19:AE19"/>
+    <mergeCell ref="AF19:AI19"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="J18:P18"/>
+    <mergeCell ref="Q18:AE18"/>
+    <mergeCell ref="AF18:AI18"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:P21"/>
+    <mergeCell ref="Q21:AE21"/>
+    <mergeCell ref="AF21:AI21"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:P20"/>
+    <mergeCell ref="Q20:AE20"/>
+    <mergeCell ref="AF20:AI20"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:P23"/>
+    <mergeCell ref="Q23:AE23"/>
+    <mergeCell ref="AF23:AI23"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:P22"/>
+    <mergeCell ref="Q22:AE22"/>
+    <mergeCell ref="AF22:AI22"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:P25"/>
+    <mergeCell ref="Q25:AE25"/>
+    <mergeCell ref="AF25:AI25"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:P24"/>
+    <mergeCell ref="Q24:AE24"/>
+    <mergeCell ref="AF24:AI24"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:P27"/>
+    <mergeCell ref="Q27:AE27"/>
+    <mergeCell ref="AF27:AI27"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="J26:P26"/>
+    <mergeCell ref="Q26:AE26"/>
+    <mergeCell ref="AF26:AI26"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:P29"/>
+    <mergeCell ref="Q29:AE29"/>
+    <mergeCell ref="AF29:AI29"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:P28"/>
+    <mergeCell ref="Q28:AE28"/>
+    <mergeCell ref="AF28:AI28"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:P31"/>
+    <mergeCell ref="Q31:AE31"/>
+    <mergeCell ref="AF31:AI31"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:P30"/>
+    <mergeCell ref="Q30:AE30"/>
+    <mergeCell ref="AF30:AI30"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="J33:P33"/>
+    <mergeCell ref="Q33:AE33"/>
+    <mergeCell ref="AF33:AI33"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="J32:P32"/>
+    <mergeCell ref="Q32:AE32"/>
+    <mergeCell ref="AF32:AI32"/>
   </mergeCells>
   <phoneticPr fontId="10"/>
   <printOptions horizontalCentered="1"/>
@@ -15626,7 +15882,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AL48"/>
+  <dimension ref="A1:AL49"/>
   <sheetFormatPr defaultColWidth="4.83203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="16" width="4.83203125" style="33" customWidth="1"/>
@@ -15763,163 +16019,163 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="84" t="s">
+      <c r="A1" s="131" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="85"/>
-      <c r="D1" s="86"/>
-      <c r="E1" s="87" t="str">
+      <c r="B1" s="132"/>
+      <c r="C1" s="132"/>
+      <c r="D1" s="133"/>
+      <c r="E1" s="134" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E1")&lt;&gt;"",INDIRECT("変更履歴!E1"),"")</f>
         <v/>
       </c>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
-      <c r="H1" s="88"/>
-      <c r="I1" s="88"/>
-      <c r="J1" s="88"/>
-      <c r="K1" s="88"/>
-      <c r="L1" s="88"/>
-      <c r="M1" s="88"/>
-      <c r="N1" s="89"/>
-      <c r="O1" s="95" t="s">
+      <c r="F1" s="135"/>
+      <c r="G1" s="135"/>
+      <c r="H1" s="135"/>
+      <c r="I1" s="135"/>
+      <c r="J1" s="135"/>
+      <c r="K1" s="135"/>
+      <c r="L1" s="135"/>
+      <c r="M1" s="135"/>
+      <c r="N1" s="136"/>
+      <c r="O1" s="142" t="s">
         <v>11</v>
       </c>
-      <c r="P1" s="96"/>
-      <c r="Q1" s="96"/>
-      <c r="R1" s="97"/>
-      <c r="S1" s="152" t="str">
+      <c r="P1" s="143"/>
+      <c r="Q1" s="143"/>
+      <c r="R1" s="144"/>
+      <c r="S1" s="163" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!S1")&lt;&gt;"",INDIRECT("変更履歴!S1"),"")</f>
         <v>Nablarch開発標準設計書一覧</v>
       </c>
-      <c r="T1" s="105"/>
-      <c r="U1" s="105"/>
-      <c r="V1" s="105"/>
-      <c r="W1" s="105"/>
-      <c r="X1" s="105"/>
-      <c r="Y1" s="105"/>
-      <c r="Z1" s="106"/>
-      <c r="AA1" s="150" t="s">
+      <c r="T1" s="152"/>
+      <c r="U1" s="152"/>
+      <c r="V1" s="152"/>
+      <c r="W1" s="152"/>
+      <c r="X1" s="152"/>
+      <c r="Y1" s="152"/>
+      <c r="Z1" s="153"/>
+      <c r="AA1" s="164" t="s">
         <v>12</v>
       </c>
-      <c r="AB1" s="151"/>
-      <c r="AC1" s="113" t="str">
+      <c r="AB1" s="165"/>
+      <c r="AC1" s="160" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC1")&lt;&gt;"",INDIRECT("変更履歴!AC1"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="114"/>
-      <c r="AE1" s="114"/>
-      <c r="AF1" s="115"/>
-      <c r="AG1" s="147">
+      <c r="AD1" s="161"/>
+      <c r="AE1" s="161"/>
+      <c r="AF1" s="162"/>
+      <c r="AG1" s="166">
         <f ca="1">IF(INDIRECT("変更履歴!AG1")&lt;&gt;"",INDIRECT("変更履歴!AG1"),"")</f>
         <v>43336</v>
       </c>
-      <c r="AH1" s="148"/>
-      <c r="AI1" s="149"/>
+      <c r="AH1" s="167"/>
+      <c r="AI1" s="168"/>
       <c r="AJ1" s="1"/>
       <c r="AK1" s="1"/>
       <c r="AL1" s="2"/>
     </row>
     <row r="2" spans="1:38" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="84" t="s">
+      <c r="A2" s="131" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="85"/>
-      <c r="C2" s="85"/>
-      <c r="D2" s="86"/>
-      <c r="E2" s="87" t="str">
+      <c r="B2" s="132"/>
+      <c r="C2" s="132"/>
+      <c r="D2" s="133"/>
+      <c r="E2" s="134" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E2")&lt;&gt;"",INDIRECT("変更履歴!E2"),"")</f>
         <v/>
       </c>
-      <c r="F2" s="88"/>
-      <c r="G2" s="88"/>
-      <c r="H2" s="88"/>
-      <c r="I2" s="88"/>
-      <c r="J2" s="88"/>
-      <c r="K2" s="88"/>
-      <c r="L2" s="88"/>
-      <c r="M2" s="88"/>
-      <c r="N2" s="89"/>
-      <c r="O2" s="98"/>
-      <c r="P2" s="99"/>
-      <c r="Q2" s="99"/>
-      <c r="R2" s="100"/>
-      <c r="S2" s="107"/>
-      <c r="T2" s="108"/>
-      <c r="U2" s="108"/>
-      <c r="V2" s="108"/>
-      <c r="W2" s="108"/>
-      <c r="X2" s="108"/>
-      <c r="Y2" s="108"/>
-      <c r="Z2" s="109"/>
-      <c r="AA2" s="150" t="s">
+      <c r="F2" s="135"/>
+      <c r="G2" s="135"/>
+      <c r="H2" s="135"/>
+      <c r="I2" s="135"/>
+      <c r="J2" s="135"/>
+      <c r="K2" s="135"/>
+      <c r="L2" s="135"/>
+      <c r="M2" s="135"/>
+      <c r="N2" s="136"/>
+      <c r="O2" s="145"/>
+      <c r="P2" s="146"/>
+      <c r="Q2" s="146"/>
+      <c r="R2" s="147"/>
+      <c r="S2" s="154"/>
+      <c r="T2" s="155"/>
+      <c r="U2" s="155"/>
+      <c r="V2" s="155"/>
+      <c r="W2" s="155"/>
+      <c r="X2" s="155"/>
+      <c r="Y2" s="155"/>
+      <c r="Z2" s="156"/>
+      <c r="AA2" s="164" t="s">
         <v>13</v>
       </c>
-      <c r="AB2" s="151"/>
-      <c r="AC2" s="113" t="str">
+      <c r="AB2" s="165"/>
+      <c r="AC2" s="160" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC2")&lt;&gt;"",INDIRECT("変更履歴!AC2"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD2" s="114"/>
-      <c r="AE2" s="114"/>
-      <c r="AF2" s="115"/>
-      <c r="AG2" s="147">
+      <c r="AD2" s="161"/>
+      <c r="AE2" s="161"/>
+      <c r="AF2" s="162"/>
+      <c r="AG2" s="166">
         <f ca="1">IF(INDIRECT("変更履歴!AG2")&lt;&gt;"",INDIRECT("変更履歴!AG2"),"")</f>
-        <v>44848</v>
-      </c>
-      <c r="AH2" s="148"/>
-      <c r="AI2" s="149"/>
+        <v>45565</v>
+      </c>
+      <c r="AH2" s="167"/>
+      <c r="AI2" s="168"/>
       <c r="AJ2" s="1"/>
       <c r="AK2" s="1"/>
       <c r="AL2" s="1"/>
     </row>
     <row r="3" spans="1:38" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="84" t="s">
+      <c r="A3" s="131" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="85"/>
-      <c r="C3" s="85"/>
-      <c r="D3" s="86"/>
-      <c r="E3" s="87" t="str">
+      <c r="B3" s="132"/>
+      <c r="C3" s="132"/>
+      <c r="D3" s="133"/>
+      <c r="E3" s="134" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E3")&lt;&gt;"",INDIRECT("変更履歴!E3"),"")</f>
         <v/>
       </c>
-      <c r="F3" s="88"/>
-      <c r="G3" s="88"/>
-      <c r="H3" s="88"/>
-      <c r="I3" s="88"/>
-      <c r="J3" s="88"/>
-      <c r="K3" s="88"/>
-      <c r="L3" s="88"/>
-      <c r="M3" s="88"/>
-      <c r="N3" s="89"/>
-      <c r="O3" s="101"/>
-      <c r="P3" s="102"/>
-      <c r="Q3" s="102"/>
-      <c r="R3" s="103"/>
-      <c r="S3" s="110"/>
-      <c r="T3" s="111"/>
-      <c r="U3" s="111"/>
-      <c r="V3" s="111"/>
-      <c r="W3" s="111"/>
-      <c r="X3" s="111"/>
-      <c r="Y3" s="111"/>
-      <c r="Z3" s="112"/>
-      <c r="AA3" s="150"/>
-      <c r="AB3" s="151"/>
-      <c r="AC3" s="113" t="str">
+      <c r="F3" s="135"/>
+      <c r="G3" s="135"/>
+      <c r="H3" s="135"/>
+      <c r="I3" s="135"/>
+      <c r="J3" s="135"/>
+      <c r="K3" s="135"/>
+      <c r="L3" s="135"/>
+      <c r="M3" s="135"/>
+      <c r="N3" s="136"/>
+      <c r="O3" s="148"/>
+      <c r="P3" s="149"/>
+      <c r="Q3" s="149"/>
+      <c r="R3" s="150"/>
+      <c r="S3" s="157"/>
+      <c r="T3" s="158"/>
+      <c r="U3" s="158"/>
+      <c r="V3" s="158"/>
+      <c r="W3" s="158"/>
+      <c r="X3" s="158"/>
+      <c r="Y3" s="158"/>
+      <c r="Z3" s="159"/>
+      <c r="AA3" s="164"/>
+      <c r="AB3" s="165"/>
+      <c r="AC3" s="160" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC3")&lt;&gt;"",INDIRECT("変更履歴!AC3"),"")</f>
         <v/>
       </c>
-      <c r="AD3" s="114"/>
-      <c r="AE3" s="114"/>
-      <c r="AF3" s="115"/>
-      <c r="AG3" s="147" t="str">
+      <c r="AD3" s="161"/>
+      <c r="AE3" s="161"/>
+      <c r="AF3" s="162"/>
+      <c r="AG3" s="166" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AG3")&lt;&gt;"",INDIRECT("変更履歴!AG3"),"")</f>
         <v/>
       </c>
-      <c r="AH3" s="148"/>
-      <c r="AI3" s="149"/>
+      <c r="AH3" s="167"/>
+      <c r="AI3" s="168"/>
       <c r="AJ3" s="1"/>
       <c r="AK3" s="1"/>
       <c r="AL3" s="1"/>
@@ -15959,33 +16215,32 @@
     </row>
     <row r="9" spans="1:38" s="39" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B9" s="38"/>
-      <c r="D9" s="38"/>
+      <c r="D9" s="38" t="s">
+        <v>249</v>
+      </c>
       <c r="P9" s="40"/>
       <c r="R9" s="40"/>
       <c r="AH9" s="42"/>
     </row>
     <row r="10" spans="1:38" s="39" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C10" s="38" t="s">
-        <v>41</v>
-      </c>
+      <c r="B10" s="38"/>
+      <c r="D10" s="38"/>
       <c r="P10" s="40"/>
       <c r="R10" s="40"/>
-      <c r="AG10" s="40"/>
       <c r="AH10" s="42"/>
     </row>
     <row r="11" spans="1:38" s="39" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D11" s="38" t="s">
-        <v>42</v>
+      <c r="C11" s="38" t="s">
+        <v>41</v>
       </c>
       <c r="P11" s="40"/>
       <c r="R11" s="40"/>
-      <c r="V11" s="38"/>
       <c r="AG11" s="40"/>
       <c r="AH11" s="42"/>
     </row>
     <row r="12" spans="1:38" s="39" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D12" s="38" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="P12" s="40"/>
       <c r="R12" s="40"/>
@@ -15994,8 +16249,9 @@
       <c r="AH12" s="42"/>
     </row>
     <row r="13" spans="1:38" s="39" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D13" s="38"/>
-      <c r="N13" s="38"/>
+      <c r="D13" s="38" t="s">
+        <v>43</v>
+      </c>
       <c r="P13" s="40"/>
       <c r="R13" s="40"/>
       <c r="V13" s="38"/>
@@ -16003,33 +16259,37 @@
       <c r="AH13" s="42"/>
     </row>
     <row r="14" spans="1:38" s="39" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C14" s="38" t="s">
-        <v>46</v>
-      </c>
       <c r="D14" s="38"/>
-      <c r="Q14" s="43"/>
+      <c r="N14" s="38"/>
+      <c r="P14" s="40"/>
+      <c r="R14" s="40"/>
+      <c r="V14" s="38"/>
       <c r="AG14" s="40"/>
       <c r="AH14" s="42"/>
     </row>
     <row r="15" spans="1:38" s="39" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C15" s="38" t="s">
+        <v>46</v>
+      </c>
+      <c r="D15" s="38"/>
       <c r="Q15" s="43"/>
-      <c r="V15" s="38"/>
       <c r="AG15" s="40"/>
       <c r="AH15" s="42"/>
     </row>
     <row r="16" spans="1:38" s="39" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B16" s="43"/>
-      <c r="P16" s="40"/>
+      <c r="Q16" s="43"/>
+      <c r="V16" s="38"/>
       <c r="AG16" s="40"/>
       <c r="AH16" s="42"/>
     </row>
     <row r="17" spans="2:34" s="39" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="D17" s="38"/>
+      <c r="B17" s="43"/>
       <c r="P17" s="40"/>
       <c r="AG17" s="40"/>
       <c r="AH17" s="42"/>
     </row>
     <row r="18" spans="2:34" s="39" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D18" s="38"/>
       <c r="P18" s="40"/>
       <c r="AG18" s="40"/>
       <c r="AH18" s="42"/>
@@ -16050,12 +16310,12 @@
       <c r="AH21" s="42"/>
     </row>
     <row r="22" spans="2:34" s="39" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B22" s="43"/>
       <c r="P22" s="40"/>
       <c r="AG22" s="40"/>
       <c r="AH22" s="42"/>
     </row>
     <row r="23" spans="2:34" s="39" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B23" s="43"/>
       <c r="P23" s="40"/>
       <c r="AG23" s="40"/>
       <c r="AH23" s="42"/>
@@ -16091,95 +16351,108 @@
       <c r="AH29" s="42"/>
     </row>
     <row r="30" spans="2:34" s="39" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C30" s="40"/>
       <c r="P30" s="40"/>
-      <c r="Q30" s="42"/>
-      <c r="S30" s="44"/>
       <c r="AG30" s="40"/>
       <c r="AH30" s="42"/>
     </row>
     <row r="31" spans="2:34" s="39" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="K31" s="45"/>
-      <c r="P31" s="46"/>
+      <c r="C31" s="40"/>
+      <c r="P31" s="40"/>
       <c r="Q31" s="42"/>
       <c r="S31" s="44"/>
       <c r="AG31" s="40"/>
       <c r="AH31" s="42"/>
     </row>
     <row r="32" spans="2:34" s="39" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="K32" s="45"/>
       <c r="P32" s="46"/>
       <c r="Q32" s="42"/>
+      <c r="S32" s="44"/>
       <c r="AG32" s="40"/>
       <c r="AH32" s="42"/>
     </row>
     <row r="33" spans="11:34" s="39" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="K33" s="45"/>
       <c r="P33" s="46"/>
       <c r="Q33" s="42"/>
-      <c r="S33" s="44"/>
       <c r="AG33" s="40"/>
       <c r="AH33" s="42"/>
     </row>
     <row r="34" spans="11:34" s="39" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="K34" s="45"/>
       <c r="P34" s="46"/>
       <c r="Q34" s="42"/>
-      <c r="U34" s="47"/>
+      <c r="S34" s="44"/>
       <c r="AG34" s="40"/>
       <c r="AH34" s="42"/>
     </row>
     <row r="35" spans="11:34" s="39" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="P35" s="46"/>
       <c r="Q35" s="42"/>
+      <c r="U35" s="47"/>
+      <c r="AG35" s="40"/>
       <c r="AH35" s="42"/>
     </row>
-    <row r="36" spans="11:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="P36" s="34"/>
-      <c r="U36" s="36"/>
-      <c r="AG36" s="37"/>
+    <row r="36" spans="11:34" s="39" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P36" s="46"/>
+      <c r="Q36" s="42"/>
+      <c r="AH36" s="42"/>
     </row>
     <row r="37" spans="11:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P37" s="34"/>
       <c r="U37" s="36"/>
-      <c r="AF37" s="37"/>
-      <c r="AG37" s="34"/>
+      <c r="AG37" s="37"/>
     </row>
     <row r="38" spans="11:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="T38" s="36"/>
+      <c r="U38" s="36"/>
       <c r="AF38" s="37"/>
-      <c r="AG38" s="37"/>
+      <c r="AG38" s="34"/>
     </row>
     <row r="39" spans="11:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="AG39" s="34"/>
+      <c r="T39" s="36"/>
+      <c r="AF39" s="37"/>
+      <c r="AG39" s="37"/>
     </row>
     <row r="40" spans="11:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="AG40" s="34"/>
     </row>
     <row r="41" spans="11:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="AF41" s="37"/>
       <c r="AG41" s="34"/>
     </row>
     <row r="42" spans="11:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="AF42" s="37"/>
-      <c r="AG42" s="37"/>
+      <c r="AG42" s="34"/>
     </row>
     <row r="43" spans="11:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="AF43" s="37"/>
       <c r="AG43" s="37"/>
     </row>
     <row r="44" spans="11:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AF44" s="37"/>
       <c r="AG44" s="37"/>
     </row>
     <row r="45" spans="11:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="AF45" s="37"/>
       <c r="AG45" s="37"/>
     </row>
     <row r="46" spans="11:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AF46" s="37"/>
       <c r="AG46" s="37"/>
     </row>
-    <row r="48" spans="11:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="AG48" s="37"/>
+    <row r="47" spans="11:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AG47" s="37"/>
+    </row>
+    <row r="49" spans="33:33" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AG49" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="AG1:AI1"/>
+    <mergeCell ref="AC1:AF1"/>
+    <mergeCell ref="AC2:AF2"/>
+    <mergeCell ref="AG2:AI2"/>
+    <mergeCell ref="E3:N3"/>
+    <mergeCell ref="AA3:AB3"/>
+    <mergeCell ref="AC3:AF3"/>
+    <mergeCell ref="AG3:AI3"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="E1:N1"/>
     <mergeCell ref="O1:R3"/>
@@ -16189,14 +16462,6 @@
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="E2:N2"/>
     <mergeCell ref="AA2:AB2"/>
-    <mergeCell ref="AG1:AI1"/>
-    <mergeCell ref="AC1:AF1"/>
-    <mergeCell ref="AC2:AF2"/>
-    <mergeCell ref="AG2:AI2"/>
-    <mergeCell ref="E3:N3"/>
-    <mergeCell ref="AA3:AB3"/>
-    <mergeCell ref="AC3:AF3"/>
-    <mergeCell ref="AG3:AI3"/>
   </mergeCells>
   <phoneticPr fontId="10"/>
   <printOptions horizontalCentered="1"/>
@@ -16211,7 +16476,7 @@
   <sheetPr codeName="Sheet6">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AX11"/>
+  <dimension ref="A1:AX35"/>
   <sheetFormatPr defaultColWidth="4.83203125" defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="31" width="4.83203125" style="10" customWidth="1"/>
@@ -16219,59 +16484,59 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:50" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="84" t="s">
+      <c r="A1" s="131" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="85"/>
-      <c r="D1" s="86"/>
-      <c r="E1" s="87" t="str">
+      <c r="B1" s="132"/>
+      <c r="C1" s="132"/>
+      <c r="D1" s="133"/>
+      <c r="E1" s="134" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E1")&lt;&gt;"",INDIRECT("変更履歴!E1"),"")</f>
         <v/>
       </c>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
-      <c r="H1" s="88"/>
-      <c r="I1" s="88"/>
-      <c r="J1" s="88"/>
-      <c r="K1" s="88"/>
-      <c r="L1" s="88"/>
-      <c r="M1" s="88"/>
-      <c r="N1" s="89"/>
-      <c r="O1" s="162" t="s">
+      <c r="F1" s="135"/>
+      <c r="G1" s="135"/>
+      <c r="H1" s="135"/>
+      <c r="I1" s="135"/>
+      <c r="J1" s="135"/>
+      <c r="K1" s="135"/>
+      <c r="L1" s="135"/>
+      <c r="M1" s="135"/>
+      <c r="N1" s="136"/>
+      <c r="O1" s="169" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="163"/>
-      <c r="Q1" s="163"/>
-      <c r="R1" s="164"/>
-      <c r="S1" s="153" t="str">
+      <c r="P1" s="170"/>
+      <c r="Q1" s="170"/>
+      <c r="R1" s="171"/>
+      <c r="S1" s="178" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!S1")&lt;&gt;"",INDIRECT("変更履歴!S1"),"")</f>
         <v>Nablarch開発標準設計書一覧</v>
       </c>
-      <c r="T1" s="154"/>
-      <c r="U1" s="154"/>
-      <c r="V1" s="154"/>
-      <c r="W1" s="154"/>
-      <c r="X1" s="154"/>
-      <c r="Y1" s="154"/>
-      <c r="Z1" s="155"/>
-      <c r="AA1" s="84" t="s">
+      <c r="T1" s="179"/>
+      <c r="U1" s="179"/>
+      <c r="V1" s="179"/>
+      <c r="W1" s="179"/>
+      <c r="X1" s="179"/>
+      <c r="Y1" s="179"/>
+      <c r="Z1" s="180"/>
+      <c r="AA1" s="131" t="s">
         <v>3</v>
       </c>
-      <c r="AB1" s="86"/>
-      <c r="AC1" s="113" t="str">
+      <c r="AB1" s="133"/>
+      <c r="AC1" s="160" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC1")&lt;&gt;"",INDIRECT("変更履歴!AC1"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="114"/>
-      <c r="AE1" s="114"/>
-      <c r="AF1" s="115"/>
-      <c r="AG1" s="147">
+      <c r="AD1" s="161"/>
+      <c r="AE1" s="161"/>
+      <c r="AF1" s="162"/>
+      <c r="AG1" s="166">
         <f ca="1">IF(INDIRECT("変更履歴!AG1")&lt;&gt;"",INDIRECT("変更履歴!AG1"),"")</f>
         <v>43336</v>
       </c>
-      <c r="AH1" s="148"/>
-      <c r="AI1" s="149"/>
+      <c r="AH1" s="167"/>
+      <c r="AI1" s="168"/>
       <c r="AJ1" s="6"/>
       <c r="AN1" s="7"/>
       <c r="AO1" s="6"/>
@@ -16285,54 +16550,54 @@
       <c r="AW1" s="6"/>
     </row>
     <row r="2" spans="1:50" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="84" t="s">
+      <c r="A2" s="131" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="85"/>
-      <c r="C2" s="85"/>
-      <c r="D2" s="86"/>
-      <c r="E2" s="87" t="str">
+      <c r="B2" s="132"/>
+      <c r="C2" s="132"/>
+      <c r="D2" s="133"/>
+      <c r="E2" s="134" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E2")&lt;&gt;"",INDIRECT("変更履歴!E2"),"")</f>
         <v/>
       </c>
-      <c r="F2" s="88"/>
-      <c r="G2" s="88"/>
-      <c r="H2" s="88"/>
-      <c r="I2" s="88"/>
-      <c r="J2" s="88"/>
-      <c r="K2" s="88"/>
-      <c r="L2" s="88"/>
-      <c r="M2" s="88"/>
-      <c r="N2" s="89"/>
-      <c r="O2" s="165"/>
-      <c r="P2" s="166"/>
-      <c r="Q2" s="166"/>
-      <c r="R2" s="167"/>
-      <c r="S2" s="156"/>
-      <c r="T2" s="157"/>
-      <c r="U2" s="157"/>
-      <c r="V2" s="157"/>
-      <c r="W2" s="157"/>
-      <c r="X2" s="157"/>
-      <c r="Y2" s="157"/>
-      <c r="Z2" s="158"/>
-      <c r="AA2" s="84" t="s">
+      <c r="F2" s="135"/>
+      <c r="G2" s="135"/>
+      <c r="H2" s="135"/>
+      <c r="I2" s="135"/>
+      <c r="J2" s="135"/>
+      <c r="K2" s="135"/>
+      <c r="L2" s="135"/>
+      <c r="M2" s="135"/>
+      <c r="N2" s="136"/>
+      <c r="O2" s="172"/>
+      <c r="P2" s="173"/>
+      <c r="Q2" s="173"/>
+      <c r="R2" s="174"/>
+      <c r="S2" s="181"/>
+      <c r="T2" s="182"/>
+      <c r="U2" s="182"/>
+      <c r="V2" s="182"/>
+      <c r="W2" s="182"/>
+      <c r="X2" s="182"/>
+      <c r="Y2" s="182"/>
+      <c r="Z2" s="183"/>
+      <c r="AA2" s="131" t="s">
         <v>4</v>
       </c>
-      <c r="AB2" s="86"/>
-      <c r="AC2" s="113" t="str">
+      <c r="AB2" s="133"/>
+      <c r="AC2" s="160" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC2")&lt;&gt;"",INDIRECT("変更履歴!AC2"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD2" s="114"/>
-      <c r="AE2" s="114"/>
-      <c r="AF2" s="115"/>
-      <c r="AG2" s="147">
+      <c r="AD2" s="161"/>
+      <c r="AE2" s="161"/>
+      <c r="AF2" s="162"/>
+      <c r="AG2" s="166">
         <f ca="1">IF(INDIRECT("変更履歴!AG2")&lt;&gt;"",INDIRECT("変更履歴!AG2"),"")</f>
-        <v>44848</v>
-      </c>
-      <c r="AH2" s="148"/>
-      <c r="AI2" s="149"/>
+        <v>45565</v>
+      </c>
+      <c r="AH2" s="167"/>
+      <c r="AI2" s="168"/>
       <c r="AJ2" s="6"/>
       <c r="AN2" s="7"/>
       <c r="AO2" s="6"/>
@@ -16346,52 +16611,52 @@
       <c r="AW2" s="6"/>
     </row>
     <row r="3" spans="1:50" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="84" t="s">
+      <c r="A3" s="131" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="85"/>
-      <c r="C3" s="85"/>
-      <c r="D3" s="86"/>
-      <c r="E3" s="87" t="str">
+      <c r="B3" s="132"/>
+      <c r="C3" s="132"/>
+      <c r="D3" s="133"/>
+      <c r="E3" s="134" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E3")&lt;&gt;"",INDIRECT("変更履歴!E3"),"")</f>
         <v/>
       </c>
-      <c r="F3" s="88"/>
-      <c r="G3" s="88"/>
-      <c r="H3" s="88"/>
-      <c r="I3" s="88"/>
-      <c r="J3" s="88"/>
-      <c r="K3" s="88"/>
-      <c r="L3" s="88"/>
-      <c r="M3" s="88"/>
-      <c r="N3" s="89"/>
-      <c r="O3" s="168"/>
-      <c r="P3" s="169"/>
-      <c r="Q3" s="169"/>
-      <c r="R3" s="170"/>
-      <c r="S3" s="159"/>
-      <c r="T3" s="160"/>
-      <c r="U3" s="160"/>
-      <c r="V3" s="160"/>
-      <c r="W3" s="160"/>
-      <c r="X3" s="160"/>
-      <c r="Y3" s="160"/>
-      <c r="Z3" s="161"/>
-      <c r="AA3" s="84"/>
-      <c r="AB3" s="86"/>
-      <c r="AC3" s="113" t="str">
+      <c r="F3" s="135"/>
+      <c r="G3" s="135"/>
+      <c r="H3" s="135"/>
+      <c r="I3" s="135"/>
+      <c r="J3" s="135"/>
+      <c r="K3" s="135"/>
+      <c r="L3" s="135"/>
+      <c r="M3" s="135"/>
+      <c r="N3" s="136"/>
+      <c r="O3" s="175"/>
+      <c r="P3" s="176"/>
+      <c r="Q3" s="176"/>
+      <c r="R3" s="177"/>
+      <c r="S3" s="184"/>
+      <c r="T3" s="185"/>
+      <c r="U3" s="185"/>
+      <c r="V3" s="185"/>
+      <c r="W3" s="185"/>
+      <c r="X3" s="185"/>
+      <c r="Y3" s="185"/>
+      <c r="Z3" s="186"/>
+      <c r="AA3" s="131"/>
+      <c r="AB3" s="133"/>
+      <c r="AC3" s="160" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC3")&lt;&gt;"",INDIRECT("変更履歴!AC3"),"")</f>
         <v/>
       </c>
-      <c r="AD3" s="114"/>
-      <c r="AE3" s="114"/>
-      <c r="AF3" s="115"/>
-      <c r="AG3" s="147" t="str">
+      <c r="AD3" s="161"/>
+      <c r="AE3" s="161"/>
+      <c r="AF3" s="162"/>
+      <c r="AG3" s="166" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AG3")&lt;&gt;"",INDIRECT("変更履歴!AG3"),"")</f>
         <v/>
       </c>
-      <c r="AH3" s="148"/>
-      <c r="AI3" s="149"/>
+      <c r="AH3" s="167"/>
+      <c r="AI3" s="168"/>
       <c r="AJ3" s="9"/>
       <c r="AK3" s="1"/>
       <c r="AL3" s="1"/>
@@ -16473,22 +16738,547 @@
       <c r="AW9" s="6"/>
       <c r="AX9" s="6"/>
     </row>
-    <row r="10" spans="1:50" x14ac:dyDescent="0.15">
-      <c r="D10" s="38"/>
-    </row>
-    <row r="11" spans="1:50" x14ac:dyDescent="0.15">
-      <c r="C11" s="38"/>
-      <c r="D11"/>
+    <row r="10" spans="1:50" s="77" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C10" s="87" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="11" spans="1:50" s="77" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="12" spans="1:50" s="77" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="D12" s="77" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="13" spans="1:50" s="77" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="14" spans="1:50" s="77" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="D14" s="78" t="s">
+        <v>208</v>
+      </c>
+      <c r="E14" s="79" t="s">
+        <v>209</v>
+      </c>
+      <c r="F14" s="80"/>
+      <c r="G14" s="80"/>
+      <c r="H14" s="80"/>
+      <c r="I14" s="79" t="s">
+        <v>210</v>
+      </c>
+      <c r="J14" s="81"/>
+      <c r="K14" s="80"/>
+      <c r="L14" s="80"/>
+      <c r="M14" s="80"/>
+      <c r="N14" s="80"/>
+      <c r="O14" s="80"/>
+      <c r="P14" s="80"/>
+      <c r="Q14" s="80"/>
+      <c r="R14" s="80"/>
+      <c r="S14" s="80"/>
+      <c r="T14" s="81"/>
+      <c r="U14" s="82"/>
+    </row>
+    <row r="15" spans="1:50" s="77" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="D15" s="83">
+        <v>1</v>
+      </c>
+      <c r="E15" s="83" t="s">
+        <v>211</v>
+      </c>
+      <c r="F15" s="84"/>
+      <c r="G15" s="84"/>
+      <c r="H15" s="84"/>
+      <c r="I15" s="85" t="s">
+        <v>212</v>
+      </c>
+      <c r="J15" s="86"/>
+      <c r="K15" s="84"/>
+      <c r="L15" s="84"/>
+      <c r="M15" s="84"/>
+      <c r="N15" s="84"/>
+      <c r="O15" s="84"/>
+      <c r="P15" s="84"/>
+      <c r="Q15" s="84"/>
+      <c r="R15" s="84"/>
+      <c r="S15" s="84"/>
+      <c r="T15" s="86"/>
+      <c r="U15" s="82"/>
+    </row>
+    <row r="16" spans="1:50" s="77" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="D16" s="83">
+        <v>2</v>
+      </c>
+      <c r="E16" s="83" t="s">
+        <v>213</v>
+      </c>
+      <c r="F16" s="84"/>
+      <c r="G16" s="84"/>
+      <c r="H16" s="84"/>
+      <c r="I16" s="85" t="s">
+        <v>214</v>
+      </c>
+      <c r="J16" s="86"/>
+      <c r="K16" s="84"/>
+      <c r="L16" s="84"/>
+      <c r="M16" s="84"/>
+      <c r="N16" s="84"/>
+      <c r="O16" s="84"/>
+      <c r="P16" s="84"/>
+      <c r="Q16" s="84"/>
+      <c r="R16" s="84"/>
+      <c r="S16" s="84"/>
+      <c r="T16" s="86"/>
+      <c r="U16" s="82"/>
+    </row>
+    <row r="17" spans="4:21" s="77" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="D17" s="83">
+        <v>3</v>
+      </c>
+      <c r="E17" s="83" t="s">
+        <v>215</v>
+      </c>
+      <c r="F17" s="84"/>
+      <c r="G17" s="84"/>
+      <c r="H17" s="84"/>
+      <c r="I17" s="85" t="s">
+        <v>216</v>
+      </c>
+      <c r="J17" s="86"/>
+      <c r="K17" s="84"/>
+      <c r="L17" s="84"/>
+      <c r="M17" s="84"/>
+      <c r="N17" s="84"/>
+      <c r="O17" s="84"/>
+      <c r="P17" s="84"/>
+      <c r="Q17" s="84"/>
+      <c r="R17" s="84"/>
+      <c r="S17" s="84"/>
+      <c r="T17" s="86"/>
+      <c r="U17" s="82"/>
+    </row>
+    <row r="18" spans="4:21" s="77" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="D18" s="83">
+        <v>4</v>
+      </c>
+      <c r="E18" s="83" t="s">
+        <v>217</v>
+      </c>
+      <c r="F18" s="84"/>
+      <c r="G18" s="84"/>
+      <c r="H18" s="84"/>
+      <c r="I18" s="85" t="s">
+        <v>218</v>
+      </c>
+      <c r="J18" s="86"/>
+      <c r="K18" s="84"/>
+      <c r="L18" s="84"/>
+      <c r="M18" s="84"/>
+      <c r="N18" s="84"/>
+      <c r="O18" s="84"/>
+      <c r="P18" s="84"/>
+      <c r="Q18" s="84"/>
+      <c r="R18" s="84"/>
+      <c r="S18" s="84"/>
+      <c r="T18" s="86"/>
+      <c r="U18" s="82"/>
+    </row>
+    <row r="19" spans="4:21" s="77" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="D19" s="83">
+        <v>5</v>
+      </c>
+      <c r="E19" s="83" t="s">
+        <v>219</v>
+      </c>
+      <c r="F19" s="84"/>
+      <c r="G19" s="84"/>
+      <c r="H19" s="84"/>
+      <c r="I19" s="85" t="s">
+        <v>220</v>
+      </c>
+      <c r="J19" s="86"/>
+      <c r="K19" s="84"/>
+      <c r="L19" s="84"/>
+      <c r="M19" s="84"/>
+      <c r="N19" s="84"/>
+      <c r="O19" s="84"/>
+      <c r="P19" s="84"/>
+      <c r="Q19" s="84"/>
+      <c r="R19" s="84"/>
+      <c r="S19" s="84"/>
+      <c r="T19" s="86"/>
+      <c r="U19" s="82"/>
+    </row>
+    <row r="20" spans="4:21" s="77" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="D20" s="83">
+        <v>6</v>
+      </c>
+      <c r="E20" s="83" t="s">
+        <v>221</v>
+      </c>
+      <c r="F20" s="84"/>
+      <c r="G20" s="84"/>
+      <c r="H20" s="84"/>
+      <c r="I20" s="85" t="s">
+        <v>222</v>
+      </c>
+      <c r="J20" s="86"/>
+      <c r="K20" s="84"/>
+      <c r="L20" s="84"/>
+      <c r="M20" s="84"/>
+      <c r="N20" s="84"/>
+      <c r="O20" s="84"/>
+      <c r="P20" s="84"/>
+      <c r="Q20" s="84"/>
+      <c r="R20" s="84"/>
+      <c r="S20" s="84"/>
+      <c r="T20" s="86"/>
+      <c r="U20" s="82"/>
+    </row>
+    <row r="21" spans="4:21" s="77" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="D21" s="83">
+        <v>7</v>
+      </c>
+      <c r="E21" s="88" t="s">
+        <v>250</v>
+      </c>
+      <c r="F21" s="84"/>
+      <c r="G21" s="84"/>
+      <c r="H21" s="84"/>
+      <c r="I21" s="85" t="s">
+        <v>223</v>
+      </c>
+      <c r="J21" s="86"/>
+      <c r="K21" s="84"/>
+      <c r="L21" s="84"/>
+      <c r="M21" s="84"/>
+      <c r="N21" s="84"/>
+      <c r="O21" s="84"/>
+      <c r="P21" s="84"/>
+      <c r="Q21" s="84"/>
+      <c r="R21" s="84"/>
+      <c r="S21" s="84"/>
+      <c r="T21" s="86"/>
+      <c r="U21" s="82"/>
+    </row>
+    <row r="22" spans="4:21" s="77" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="D22" s="83">
+        <v>8</v>
+      </c>
+      <c r="E22" s="83" t="s">
+        <v>224</v>
+      </c>
+      <c r="F22" s="84"/>
+      <c r="G22" s="84"/>
+      <c r="H22" s="84"/>
+      <c r="I22" s="85" t="s">
+        <v>225</v>
+      </c>
+      <c r="J22" s="86"/>
+      <c r="K22" s="84"/>
+      <c r="L22" s="84"/>
+      <c r="M22" s="84"/>
+      <c r="N22" s="84"/>
+      <c r="O22" s="84"/>
+      <c r="P22" s="84"/>
+      <c r="Q22" s="84"/>
+      <c r="R22" s="84"/>
+      <c r="S22" s="84"/>
+      <c r="T22" s="86"/>
+      <c r="U22" s="82"/>
+    </row>
+    <row r="23" spans="4:21" s="77" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="D23" s="83">
+        <v>9</v>
+      </c>
+      <c r="E23" s="83" t="s">
+        <v>226</v>
+      </c>
+      <c r="F23" s="84"/>
+      <c r="G23" s="84"/>
+      <c r="H23" s="84"/>
+      <c r="I23" s="85" t="s">
+        <v>227</v>
+      </c>
+      <c r="J23" s="86"/>
+      <c r="K23" s="84"/>
+      <c r="L23" s="84"/>
+      <c r="M23" s="84"/>
+      <c r="N23" s="84"/>
+      <c r="O23" s="84"/>
+      <c r="P23" s="84"/>
+      <c r="Q23" s="84"/>
+      <c r="R23" s="84"/>
+      <c r="S23" s="84"/>
+      <c r="T23" s="86"/>
+      <c r="U23" s="82"/>
+    </row>
+    <row r="24" spans="4:21" s="77" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="D24" s="83">
+        <v>10</v>
+      </c>
+      <c r="E24" s="83" t="s">
+        <v>228</v>
+      </c>
+      <c r="F24" s="84"/>
+      <c r="G24" s="84"/>
+      <c r="H24" s="84"/>
+      <c r="I24" s="85" t="s">
+        <v>229</v>
+      </c>
+      <c r="J24" s="86"/>
+      <c r="K24" s="84"/>
+      <c r="L24" s="84"/>
+      <c r="M24" s="84"/>
+      <c r="N24" s="84"/>
+      <c r="O24" s="84"/>
+      <c r="P24" s="84"/>
+      <c r="Q24" s="84"/>
+      <c r="R24" s="84"/>
+      <c r="S24" s="84"/>
+      <c r="T24" s="86"/>
+      <c r="U24" s="82"/>
+    </row>
+    <row r="25" spans="4:21" s="77" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="D25" s="83">
+        <v>11</v>
+      </c>
+      <c r="E25" s="83" t="s">
+        <v>230</v>
+      </c>
+      <c r="F25" s="84"/>
+      <c r="G25" s="84"/>
+      <c r="H25" s="84"/>
+      <c r="I25" s="85" t="s">
+        <v>231</v>
+      </c>
+      <c r="J25" s="86"/>
+      <c r="K25" s="84"/>
+      <c r="L25" s="84"/>
+      <c r="M25" s="84"/>
+      <c r="N25" s="84"/>
+      <c r="O25" s="84"/>
+      <c r="P25" s="84"/>
+      <c r="Q25" s="84"/>
+      <c r="R25" s="84"/>
+      <c r="S25" s="84"/>
+      <c r="T25" s="86"/>
+      <c r="U25" s="82"/>
+    </row>
+    <row r="26" spans="4:21" s="77" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="D26" s="83">
+        <v>12</v>
+      </c>
+      <c r="E26" s="83" t="s">
+        <v>232</v>
+      </c>
+      <c r="F26" s="84"/>
+      <c r="G26" s="84"/>
+      <c r="H26" s="84"/>
+      <c r="I26" s="85" t="s">
+        <v>233</v>
+      </c>
+      <c r="J26" s="86"/>
+      <c r="K26" s="84"/>
+      <c r="L26" s="84"/>
+      <c r="M26" s="84"/>
+      <c r="N26" s="84"/>
+      <c r="O26" s="84"/>
+      <c r="P26" s="84"/>
+      <c r="Q26" s="84"/>
+      <c r="R26" s="84"/>
+      <c r="S26" s="84"/>
+      <c r="T26" s="86"/>
+      <c r="U26" s="82"/>
+    </row>
+    <row r="27" spans="4:21" s="77" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="D27" s="83">
+        <v>13</v>
+      </c>
+      <c r="E27" s="83" t="s">
+        <v>234</v>
+      </c>
+      <c r="F27" s="84"/>
+      <c r="G27" s="84"/>
+      <c r="H27" s="84"/>
+      <c r="I27" s="85" t="s">
+        <v>235</v>
+      </c>
+      <c r="J27" s="86"/>
+      <c r="K27" s="84"/>
+      <c r="L27" s="84"/>
+      <c r="M27" s="84"/>
+      <c r="N27" s="84"/>
+      <c r="O27" s="84"/>
+      <c r="P27" s="84"/>
+      <c r="Q27" s="84"/>
+      <c r="R27" s="84"/>
+      <c r="S27" s="84"/>
+      <c r="T27" s="86"/>
+      <c r="U27" s="82"/>
+    </row>
+    <row r="28" spans="4:21" s="77" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="D28" s="83">
+        <v>14</v>
+      </c>
+      <c r="E28" s="83" t="s">
+        <v>236</v>
+      </c>
+      <c r="F28" s="84"/>
+      <c r="G28" s="84"/>
+      <c r="H28" s="84"/>
+      <c r="I28" s="85" t="s">
+        <v>237</v>
+      </c>
+      <c r="J28" s="86"/>
+      <c r="K28" s="84"/>
+      <c r="L28" s="84"/>
+      <c r="M28" s="84"/>
+      <c r="N28" s="84"/>
+      <c r="O28" s="84"/>
+      <c r="P28" s="84"/>
+      <c r="Q28" s="84"/>
+      <c r="R28" s="84"/>
+      <c r="S28" s="84"/>
+      <c r="T28" s="86"/>
+      <c r="U28" s="82"/>
+    </row>
+    <row r="29" spans="4:21" s="77" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="D29" s="83">
+        <v>15</v>
+      </c>
+      <c r="E29" s="83" t="s">
+        <v>238</v>
+      </c>
+      <c r="F29" s="84"/>
+      <c r="G29" s="84"/>
+      <c r="H29" s="84"/>
+      <c r="I29" s="85" t="s">
+        <v>239</v>
+      </c>
+      <c r="J29" s="86"/>
+      <c r="K29" s="84"/>
+      <c r="L29" s="84"/>
+      <c r="M29" s="84"/>
+      <c r="N29" s="84"/>
+      <c r="O29" s="84"/>
+      <c r="P29" s="84"/>
+      <c r="Q29" s="84"/>
+      <c r="R29" s="84"/>
+      <c r="S29" s="84"/>
+      <c r="T29" s="86"/>
+      <c r="U29" s="82"/>
+    </row>
+    <row r="30" spans="4:21" s="77" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="D30" s="83">
+        <v>16</v>
+      </c>
+      <c r="E30" s="83" t="s">
+        <v>240</v>
+      </c>
+      <c r="F30" s="84"/>
+      <c r="G30" s="84"/>
+      <c r="H30" s="84"/>
+      <c r="I30" s="85" t="s">
+        <v>241</v>
+      </c>
+      <c r="J30" s="86"/>
+      <c r="K30" s="84"/>
+      <c r="L30" s="84"/>
+      <c r="M30" s="84"/>
+      <c r="N30" s="84"/>
+      <c r="O30" s="84"/>
+      <c r="P30" s="84"/>
+      <c r="Q30" s="84"/>
+      <c r="R30" s="84"/>
+      <c r="S30" s="84"/>
+      <c r="T30" s="86"/>
+      <c r="U30" s="82"/>
+    </row>
+    <row r="31" spans="4:21" s="77" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="D31" s="83">
+        <v>17</v>
+      </c>
+      <c r="E31" s="83" t="s">
+        <v>242</v>
+      </c>
+      <c r="F31" s="84"/>
+      <c r="G31" s="84"/>
+      <c r="H31" s="84"/>
+      <c r="I31" s="85" t="s">
+        <v>243</v>
+      </c>
+      <c r="J31" s="86"/>
+      <c r="K31" s="84"/>
+      <c r="L31" s="84"/>
+      <c r="M31" s="84"/>
+      <c r="N31" s="84"/>
+      <c r="O31" s="84"/>
+      <c r="P31" s="84"/>
+      <c r="Q31" s="84"/>
+      <c r="R31" s="84"/>
+      <c r="S31" s="84"/>
+      <c r="T31" s="86"/>
+      <c r="U31" s="82"/>
+    </row>
+    <row r="32" spans="4:21" s="77" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="D32" s="83">
+        <v>18</v>
+      </c>
+      <c r="E32" s="83" t="s">
+        <v>244</v>
+      </c>
+      <c r="F32" s="84"/>
+      <c r="G32" s="84"/>
+      <c r="H32" s="84"/>
+      <c r="I32" s="85" t="s">
+        <v>245</v>
+      </c>
+      <c r="J32" s="86"/>
+      <c r="K32" s="84"/>
+      <c r="L32" s="84"/>
+      <c r="M32" s="84"/>
+      <c r="N32" s="84"/>
+      <c r="O32" s="84"/>
+      <c r="P32" s="84"/>
+      <c r="Q32" s="84"/>
+      <c r="R32" s="84"/>
+      <c r="S32" s="84"/>
+      <c r="T32" s="86"/>
+      <c r="U32" s="82"/>
+    </row>
+    <row r="33" spans="3:21" s="77" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="D33" s="83">
+        <v>19</v>
+      </c>
+      <c r="E33" s="83" t="s">
+        <v>246</v>
+      </c>
+      <c r="F33" s="84"/>
+      <c r="G33" s="84"/>
+      <c r="H33" s="84"/>
+      <c r="I33" s="85" t="s">
+        <v>247</v>
+      </c>
+      <c r="J33" s="86"/>
+      <c r="K33" s="84"/>
+      <c r="L33" s="84"/>
+      <c r="M33" s="84"/>
+      <c r="N33" s="84"/>
+      <c r="O33" s="84"/>
+      <c r="P33" s="84"/>
+      <c r="Q33" s="84"/>
+      <c r="R33" s="84"/>
+      <c r="S33" s="84"/>
+      <c r="T33" s="86"/>
+      <c r="U33" s="82"/>
+    </row>
+    <row r="34" spans="3:21" x14ac:dyDescent="0.15">
+      <c r="D34" s="38"/>
+    </row>
+    <row r="35" spans="3:21" x14ac:dyDescent="0.15">
+      <c r="C35" s="38"/>
+      <c r="D35"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="O1:R3"/>
-    <mergeCell ref="AA1:AB1"/>
-    <mergeCell ref="AA2:AB2"/>
-    <mergeCell ref="AA3:AB3"/>
     <mergeCell ref="AC3:AF3"/>
     <mergeCell ref="AG3:AI3"/>
     <mergeCell ref="E1:N1"/>
@@ -16499,11 +17289,39 @@
     <mergeCell ref="AC2:AF2"/>
     <mergeCell ref="AG2:AI2"/>
     <mergeCell ref="S1:Z3"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="O1:R3"/>
+    <mergeCell ref="AA1:AB1"/>
+    <mergeCell ref="AA2:AB2"/>
+    <mergeCell ref="AA3:AB3"/>
   </mergeCells>
   <phoneticPr fontId="10"/>
+  <hyperlinks>
+    <hyperlink ref="AB15" r:id="rId1" display="https://jakarta.ee/specifications/faces/" xr:uid="{A1CDF289-622B-415E-8DD7-79777CFD0F39}"/>
+    <hyperlink ref="AB16" r:id="rId2" display="https://jakarta.ee/specifications/authentication/" xr:uid="{49DDB29E-F977-4C84-B300-6B23000B25EC}"/>
+    <hyperlink ref="AB17" r:id="rId3" display="https://jakarta.ee/specifications/authorization/" xr:uid="{DF7FB6E4-BF79-4A82-A090-FB95A4DAEAA6}"/>
+    <hyperlink ref="AB18" r:id="rId4" display="https://jakarta.ee/specifications/messaging/" xr:uid="{D0B46F37-30B7-4F77-B1AE-19183BF86502}"/>
+    <hyperlink ref="AB19" r:id="rId5" display="https://jakarta.ee/specifications/persistence/" xr:uid="{9952206C-D127-4359-8EE3-DF51D8556240}"/>
+    <hyperlink ref="AB20" r:id="rId6" display="https://jakarta.ee/specifications/transactions/" xr:uid="{B7B333C1-7295-4D94-AAF5-67C2325FECD9}"/>
+    <hyperlink ref="AB21" r:id="rId7" display="https://jakarta.ee/specifications/batch/" xr:uid="{991A5834-A442-48FE-81E7-507ECD0B0FB2}"/>
+    <hyperlink ref="AB22" r:id="rId8" display="https://jakarta.ee/specifications/connectors/" xr:uid="{7633A53E-0FD7-4BAF-BA63-F434475351EF}"/>
+    <hyperlink ref="AB23" r:id="rId9" display="https://jakarta.ee/specifications/activation/" xr:uid="{91D54A17-C7C5-463A-BBCC-358D190D657F}"/>
+    <hyperlink ref="AB24" r:id="rId10" display="https://jakarta.ee/specifications/expression-language/" xr:uid="{6BB03A96-1BD2-46EF-9371-967C104EE2D5}"/>
+    <hyperlink ref="AB25" r:id="rId11" display="https://jakarta.ee/specifications/enterprise-beans/" xr:uid="{9703855A-D5F6-432D-BDCC-3086906EDB56}"/>
+    <hyperlink ref="AB26" r:id="rId12" display="https://jakarta.ee/specifications/xml-binding/" xr:uid="{66461F33-B064-49A5-9DA7-59758E41EC0A}"/>
+    <hyperlink ref="AB27" r:id="rId13" display="https://jakarta.ee/specifications/jsonb/" xr:uid="{9F173BD6-5F61-42ED-A3CE-23E9E226803E}"/>
+    <hyperlink ref="AB28" r:id="rId14" display="https://jakarta.ee/specifications/jsonp/" xr:uid="{AE9A363A-7A11-42A7-9F11-2B6EBB5B6892}"/>
+    <hyperlink ref="AB29" r:id="rId15" display="https://jakarta.ee/specifications/pages/" xr:uid="{BE4F1F25-AA14-4A4B-8152-A5631DE0939B}"/>
+    <hyperlink ref="AB30" r:id="rId16" display="https://jakarta.ee/specifications/xml-web-services/" xr:uid="{BA5BD9E6-2B5C-44F6-9B0C-7F2C127128C4}"/>
+    <hyperlink ref="AB31" r:id="rId17" display="https://jakarta.ee/specifications/restful-ws/" xr:uid="{F1C36587-F45F-4061-8AE5-FE737F71444C}"/>
+    <hyperlink ref="AB32" r:id="rId18" display="https://jakarta.ee/specifications/tags/" xr:uid="{46186705-1011-4047-B8BB-9F40E9200823}"/>
+    <hyperlink ref="AB33" r:id="rId19" display="https://jakarta.ee/specifications/cdi/" xr:uid="{E0FD9CCA-67BD-49E1-B6F2-68A671C7ADD3}"/>
+  </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
-  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" useFirstPageNumber="1" r:id="rId1"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" useFirstPageNumber="1" r:id="rId20"/>
   <headerFooter alignWithMargins="0">
     <oddFooter>&amp;C- &amp;P -</oddFooter>
   </headerFooter>
@@ -16523,59 +17341,59 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:49" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="84" t="s">
+      <c r="A1" s="131" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="85"/>
-      <c r="D1" s="86"/>
-      <c r="E1" s="87" t="str">
+      <c r="B1" s="132"/>
+      <c r="C1" s="132"/>
+      <c r="D1" s="133"/>
+      <c r="E1" s="134" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E1")&lt;&gt;"",INDIRECT("変更履歴!E1"),"")</f>
         <v/>
       </c>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
-      <c r="H1" s="88"/>
-      <c r="I1" s="88"/>
-      <c r="J1" s="88"/>
-      <c r="K1" s="88"/>
-      <c r="L1" s="88"/>
-      <c r="M1" s="88"/>
-      <c r="N1" s="89"/>
-      <c r="O1" s="162" t="s">
+      <c r="F1" s="135"/>
+      <c r="G1" s="135"/>
+      <c r="H1" s="135"/>
+      <c r="I1" s="135"/>
+      <c r="J1" s="135"/>
+      <c r="K1" s="135"/>
+      <c r="L1" s="135"/>
+      <c r="M1" s="135"/>
+      <c r="N1" s="136"/>
+      <c r="O1" s="169" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="163"/>
-      <c r="Q1" s="163"/>
-      <c r="R1" s="164"/>
-      <c r="S1" s="153" t="str">
+      <c r="P1" s="170"/>
+      <c r="Q1" s="170"/>
+      <c r="R1" s="171"/>
+      <c r="S1" s="178" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!S1")&lt;&gt;"",INDIRECT("変更履歴!S1"),"")</f>
         <v>Nablarch開発標準設計書一覧</v>
       </c>
-      <c r="T1" s="154"/>
-      <c r="U1" s="154"/>
-      <c r="V1" s="154"/>
-      <c r="W1" s="154"/>
-      <c r="X1" s="154"/>
-      <c r="Y1" s="154"/>
-      <c r="Z1" s="155"/>
-      <c r="AA1" s="84" t="s">
+      <c r="T1" s="179"/>
+      <c r="U1" s="179"/>
+      <c r="V1" s="179"/>
+      <c r="W1" s="179"/>
+      <c r="X1" s="179"/>
+      <c r="Y1" s="179"/>
+      <c r="Z1" s="180"/>
+      <c r="AA1" s="131" t="s">
         <v>3</v>
       </c>
-      <c r="AB1" s="86"/>
-      <c r="AC1" s="113" t="str">
+      <c r="AB1" s="133"/>
+      <c r="AC1" s="160" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC1")&lt;&gt;"",INDIRECT("変更履歴!AC1"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="114"/>
-      <c r="AE1" s="114"/>
-      <c r="AF1" s="115"/>
-      <c r="AG1" s="147">
+      <c r="AD1" s="161"/>
+      <c r="AE1" s="161"/>
+      <c r="AF1" s="162"/>
+      <c r="AG1" s="166">
         <f ca="1">IF(INDIRECT("変更履歴!AG1")&lt;&gt;"",INDIRECT("変更履歴!AG1"),"")</f>
         <v>43336</v>
       </c>
-      <c r="AH1" s="148"/>
-      <c r="AI1" s="149"/>
+      <c r="AH1" s="167"/>
+      <c r="AI1" s="168"/>
       <c r="AJ1" s="6"/>
       <c r="AN1" s="7"/>
       <c r="AO1" s="6"/>
@@ -16589,54 +17407,54 @@
       <c r="AW1" s="6"/>
     </row>
     <row r="2" spans="1:49" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="84" t="s">
+      <c r="A2" s="131" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="85"/>
-      <c r="C2" s="85"/>
-      <c r="D2" s="86"/>
-      <c r="E2" s="87" t="str">
+      <c r="B2" s="132"/>
+      <c r="C2" s="132"/>
+      <c r="D2" s="133"/>
+      <c r="E2" s="134" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E2")&lt;&gt;"",INDIRECT("変更履歴!E2"),"")</f>
         <v/>
       </c>
-      <c r="F2" s="88"/>
-      <c r="G2" s="88"/>
-      <c r="H2" s="88"/>
-      <c r="I2" s="88"/>
-      <c r="J2" s="88"/>
-      <c r="K2" s="88"/>
-      <c r="L2" s="88"/>
-      <c r="M2" s="88"/>
-      <c r="N2" s="89"/>
-      <c r="O2" s="165"/>
-      <c r="P2" s="166"/>
-      <c r="Q2" s="166"/>
-      <c r="R2" s="167"/>
-      <c r="S2" s="156"/>
-      <c r="T2" s="157"/>
-      <c r="U2" s="157"/>
-      <c r="V2" s="157"/>
-      <c r="W2" s="157"/>
-      <c r="X2" s="157"/>
-      <c r="Y2" s="157"/>
-      <c r="Z2" s="158"/>
-      <c r="AA2" s="84" t="s">
+      <c r="F2" s="135"/>
+      <c r="G2" s="135"/>
+      <c r="H2" s="135"/>
+      <c r="I2" s="135"/>
+      <c r="J2" s="135"/>
+      <c r="K2" s="135"/>
+      <c r="L2" s="135"/>
+      <c r="M2" s="135"/>
+      <c r="N2" s="136"/>
+      <c r="O2" s="172"/>
+      <c r="P2" s="173"/>
+      <c r="Q2" s="173"/>
+      <c r="R2" s="174"/>
+      <c r="S2" s="181"/>
+      <c r="T2" s="182"/>
+      <c r="U2" s="182"/>
+      <c r="V2" s="182"/>
+      <c r="W2" s="182"/>
+      <c r="X2" s="182"/>
+      <c r="Y2" s="182"/>
+      <c r="Z2" s="183"/>
+      <c r="AA2" s="131" t="s">
         <v>4</v>
       </c>
-      <c r="AB2" s="86"/>
-      <c r="AC2" s="113" t="str">
+      <c r="AB2" s="133"/>
+      <c r="AC2" s="160" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC2")&lt;&gt;"",INDIRECT("変更履歴!AC2"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD2" s="114"/>
-      <c r="AE2" s="114"/>
-      <c r="AF2" s="115"/>
-      <c r="AG2" s="147">
+      <c r="AD2" s="161"/>
+      <c r="AE2" s="161"/>
+      <c r="AF2" s="162"/>
+      <c r="AG2" s="166">
         <f ca="1">IF(INDIRECT("変更履歴!AG2")&lt;&gt;"",INDIRECT("変更履歴!AG2"),"")</f>
-        <v>44848</v>
-      </c>
-      <c r="AH2" s="148"/>
-      <c r="AI2" s="149"/>
+        <v>45565</v>
+      </c>
+      <c r="AH2" s="167"/>
+      <c r="AI2" s="168"/>
       <c r="AJ2" s="6"/>
       <c r="AN2" s="7"/>
       <c r="AO2" s="6"/>
@@ -16650,52 +17468,52 @@
       <c r="AW2" s="6"/>
     </row>
     <row r="3" spans="1:49" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="84" t="s">
+      <c r="A3" s="131" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="85"/>
-      <c r="C3" s="85"/>
-      <c r="D3" s="86"/>
-      <c r="E3" s="87" t="str">
+      <c r="B3" s="132"/>
+      <c r="C3" s="132"/>
+      <c r="D3" s="133"/>
+      <c r="E3" s="134" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E3")&lt;&gt;"",INDIRECT("変更履歴!E3"),"")</f>
         <v/>
       </c>
-      <c r="F3" s="88"/>
-      <c r="G3" s="88"/>
-      <c r="H3" s="88"/>
-      <c r="I3" s="88"/>
-      <c r="J3" s="88"/>
-      <c r="K3" s="88"/>
-      <c r="L3" s="88"/>
-      <c r="M3" s="88"/>
-      <c r="N3" s="89"/>
-      <c r="O3" s="168"/>
-      <c r="P3" s="169"/>
-      <c r="Q3" s="169"/>
-      <c r="R3" s="170"/>
-      <c r="S3" s="159"/>
-      <c r="T3" s="160"/>
-      <c r="U3" s="160"/>
-      <c r="V3" s="160"/>
-      <c r="W3" s="160"/>
-      <c r="X3" s="160"/>
-      <c r="Y3" s="160"/>
-      <c r="Z3" s="161"/>
-      <c r="AA3" s="84"/>
-      <c r="AB3" s="86"/>
-      <c r="AC3" s="113" t="str">
+      <c r="F3" s="135"/>
+      <c r="G3" s="135"/>
+      <c r="H3" s="135"/>
+      <c r="I3" s="135"/>
+      <c r="J3" s="135"/>
+      <c r="K3" s="135"/>
+      <c r="L3" s="135"/>
+      <c r="M3" s="135"/>
+      <c r="N3" s="136"/>
+      <c r="O3" s="175"/>
+      <c r="P3" s="176"/>
+      <c r="Q3" s="176"/>
+      <c r="R3" s="177"/>
+      <c r="S3" s="184"/>
+      <c r="T3" s="185"/>
+      <c r="U3" s="185"/>
+      <c r="V3" s="185"/>
+      <c r="W3" s="185"/>
+      <c r="X3" s="185"/>
+      <c r="Y3" s="185"/>
+      <c r="Z3" s="186"/>
+      <c r="AA3" s="131"/>
+      <c r="AB3" s="133"/>
+      <c r="AC3" s="160" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC3")&lt;&gt;"",INDIRECT("変更履歴!AC3"),"")</f>
         <v/>
       </c>
-      <c r="AD3" s="114"/>
-      <c r="AE3" s="114"/>
-      <c r="AF3" s="115"/>
-      <c r="AG3" s="147" t="str">
+      <c r="AD3" s="161"/>
+      <c r="AE3" s="161"/>
+      <c r="AF3" s="162"/>
+      <c r="AG3" s="166" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AG3")&lt;&gt;"",INDIRECT("変更履歴!AG3"),"")</f>
         <v/>
       </c>
-      <c r="AH3" s="148"/>
-      <c r="AI3" s="149"/>
+      <c r="AH3" s="167"/>
+      <c r="AI3" s="168"/>
       <c r="AJ3" s="9"/>
       <c r="AK3" s="1"/>
       <c r="AL3" s="1"/>
@@ -16737,14 +17555,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="AG1:AI1"/>
-    <mergeCell ref="AC1:AF1"/>
-    <mergeCell ref="AC2:AF2"/>
-    <mergeCell ref="AG2:AI2"/>
-    <mergeCell ref="E3:N3"/>
-    <mergeCell ref="AA3:AB3"/>
-    <mergeCell ref="AC3:AF3"/>
-    <mergeCell ref="AG3:AI3"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="E1:N1"/>
     <mergeCell ref="O1:R3"/>
@@ -16754,6 +17564,14 @@
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="E2:N2"/>
     <mergeCell ref="AA2:AB2"/>
+    <mergeCell ref="AG1:AI1"/>
+    <mergeCell ref="AC1:AF1"/>
+    <mergeCell ref="AC2:AF2"/>
+    <mergeCell ref="AG2:AI2"/>
+    <mergeCell ref="E3:N3"/>
+    <mergeCell ref="AA3:AB3"/>
+    <mergeCell ref="AC3:AF3"/>
+    <mergeCell ref="AG3:AI3"/>
   </mergeCells>
   <phoneticPr fontId="10"/>
   <printOptions horizontalCentered="1"/>
@@ -16783,59 +17601,59 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="84" t="s">
+      <c r="A1" s="131" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="85"/>
-      <c r="D1" s="86"/>
-      <c r="E1" s="87" t="str">
+      <c r="B1" s="132"/>
+      <c r="C1" s="132"/>
+      <c r="D1" s="133"/>
+      <c r="E1" s="134" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E1")&lt;&gt;"",INDIRECT("変更履歴!E1"),"")</f>
         <v/>
       </c>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
-      <c r="H1" s="88"/>
-      <c r="I1" s="88"/>
-      <c r="J1" s="88"/>
-      <c r="K1" s="88"/>
-      <c r="L1" s="88"/>
-      <c r="M1" s="88"/>
-      <c r="N1" s="89"/>
-      <c r="O1" s="162" t="s">
+      <c r="F1" s="135"/>
+      <c r="G1" s="135"/>
+      <c r="H1" s="135"/>
+      <c r="I1" s="135"/>
+      <c r="J1" s="135"/>
+      <c r="K1" s="135"/>
+      <c r="L1" s="135"/>
+      <c r="M1" s="135"/>
+      <c r="N1" s="136"/>
+      <c r="O1" s="169" t="s">
         <v>73</v>
       </c>
-      <c r="P1" s="163"/>
-      <c r="Q1" s="163"/>
-      <c r="R1" s="164"/>
-      <c r="S1" s="153" t="str">
+      <c r="P1" s="170"/>
+      <c r="Q1" s="170"/>
+      <c r="R1" s="171"/>
+      <c r="S1" s="178" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!S1")&lt;&gt;"",INDIRECT("変更履歴!S1"),"")</f>
         <v>Nablarch開発標準設計書一覧</v>
       </c>
-      <c r="T1" s="154"/>
-      <c r="U1" s="154"/>
-      <c r="V1" s="154"/>
-      <c r="W1" s="154"/>
-      <c r="X1" s="154"/>
-      <c r="Y1" s="154"/>
-      <c r="Z1" s="155"/>
-      <c r="AA1" s="84" t="s">
+      <c r="T1" s="179"/>
+      <c r="U1" s="179"/>
+      <c r="V1" s="179"/>
+      <c r="W1" s="179"/>
+      <c r="X1" s="179"/>
+      <c r="Y1" s="179"/>
+      <c r="Z1" s="180"/>
+      <c r="AA1" s="131" t="s">
         <v>3</v>
       </c>
-      <c r="AB1" s="86"/>
-      <c r="AC1" s="113" t="str">
+      <c r="AB1" s="133"/>
+      <c r="AC1" s="160" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC1")&lt;&gt;"",INDIRECT("変更履歴!AC1"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="114"/>
-      <c r="AE1" s="114"/>
-      <c r="AF1" s="115"/>
-      <c r="AG1" s="147">
+      <c r="AD1" s="161"/>
+      <c r="AE1" s="161"/>
+      <c r="AF1" s="162"/>
+      <c r="AG1" s="166">
         <f ca="1">IF(INDIRECT("変更履歴!AG1")&lt;&gt;"",INDIRECT("変更履歴!AG1"),"")</f>
         <v>43336</v>
       </c>
-      <c r="AH1" s="148"/>
-      <c r="AI1" s="149"/>
+      <c r="AH1" s="167"/>
+      <c r="AI1" s="168"/>
       <c r="AJ1" s="6"/>
       <c r="AM1" s="6"/>
       <c r="AN1" s="6"/>
@@ -16843,54 +17661,54 @@
       <c r="AP1" s="6"/>
     </row>
     <row r="2" spans="1:42" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="84" t="s">
+      <c r="A2" s="131" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="85"/>
-      <c r="C2" s="85"/>
-      <c r="D2" s="86"/>
-      <c r="E2" s="87" t="str">
+      <c r="B2" s="132"/>
+      <c r="C2" s="132"/>
+      <c r="D2" s="133"/>
+      <c r="E2" s="134" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E2")&lt;&gt;"",INDIRECT("変更履歴!E2"),"")</f>
         <v/>
       </c>
-      <c r="F2" s="88"/>
-      <c r="G2" s="88"/>
-      <c r="H2" s="88"/>
-      <c r="I2" s="88"/>
-      <c r="J2" s="88"/>
-      <c r="K2" s="88"/>
-      <c r="L2" s="88"/>
-      <c r="M2" s="88"/>
-      <c r="N2" s="89"/>
-      <c r="O2" s="165"/>
-      <c r="P2" s="166"/>
-      <c r="Q2" s="166"/>
-      <c r="R2" s="167"/>
-      <c r="S2" s="156"/>
-      <c r="T2" s="157"/>
-      <c r="U2" s="157"/>
-      <c r="V2" s="157"/>
-      <c r="W2" s="157"/>
-      <c r="X2" s="157"/>
-      <c r="Y2" s="157"/>
-      <c r="Z2" s="158"/>
-      <c r="AA2" s="84" t="s">
+      <c r="F2" s="135"/>
+      <c r="G2" s="135"/>
+      <c r="H2" s="135"/>
+      <c r="I2" s="135"/>
+      <c r="J2" s="135"/>
+      <c r="K2" s="135"/>
+      <c r="L2" s="135"/>
+      <c r="M2" s="135"/>
+      <c r="N2" s="136"/>
+      <c r="O2" s="172"/>
+      <c r="P2" s="173"/>
+      <c r="Q2" s="173"/>
+      <c r="R2" s="174"/>
+      <c r="S2" s="181"/>
+      <c r="T2" s="182"/>
+      <c r="U2" s="182"/>
+      <c r="V2" s="182"/>
+      <c r="W2" s="182"/>
+      <c r="X2" s="182"/>
+      <c r="Y2" s="182"/>
+      <c r="Z2" s="183"/>
+      <c r="AA2" s="131" t="s">
         <v>4</v>
       </c>
-      <c r="AB2" s="86"/>
-      <c r="AC2" s="113" t="str">
+      <c r="AB2" s="133"/>
+      <c r="AC2" s="160" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC2")&lt;&gt;"",INDIRECT("変更履歴!AC2"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD2" s="114"/>
-      <c r="AE2" s="114"/>
-      <c r="AF2" s="115"/>
-      <c r="AG2" s="147">
+      <c r="AD2" s="161"/>
+      <c r="AE2" s="161"/>
+      <c r="AF2" s="162"/>
+      <c r="AG2" s="166">
         <f ca="1">IF(INDIRECT("変更履歴!AG2")&lt;&gt;"",INDIRECT("変更履歴!AG2"),"")</f>
-        <v>44848</v>
-      </c>
-      <c r="AH2" s="148"/>
-      <c r="AI2" s="149"/>
+        <v>45565</v>
+      </c>
+      <c r="AH2" s="167"/>
+      <c r="AI2" s="168"/>
       <c r="AJ2" s="6"/>
       <c r="AM2" s="6"/>
       <c r="AN2" s="6"/>
@@ -16898,52 +17716,52 @@
       <c r="AP2" s="6"/>
     </row>
     <row r="3" spans="1:42" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="84" t="s">
+      <c r="A3" s="131" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="85"/>
-      <c r="C3" s="85"/>
-      <c r="D3" s="86"/>
-      <c r="E3" s="87" t="str">
+      <c r="B3" s="132"/>
+      <c r="C3" s="132"/>
+      <c r="D3" s="133"/>
+      <c r="E3" s="134" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E3")&lt;&gt;"",INDIRECT("変更履歴!E3"),"")</f>
         <v/>
       </c>
-      <c r="F3" s="88"/>
-      <c r="G3" s="88"/>
-      <c r="H3" s="88"/>
-      <c r="I3" s="88"/>
-      <c r="J3" s="88"/>
-      <c r="K3" s="88"/>
-      <c r="L3" s="88"/>
-      <c r="M3" s="88"/>
-      <c r="N3" s="89"/>
-      <c r="O3" s="168"/>
-      <c r="P3" s="169"/>
-      <c r="Q3" s="169"/>
-      <c r="R3" s="170"/>
-      <c r="S3" s="159"/>
-      <c r="T3" s="160"/>
-      <c r="U3" s="160"/>
-      <c r="V3" s="160"/>
-      <c r="W3" s="160"/>
-      <c r="X3" s="160"/>
-      <c r="Y3" s="160"/>
-      <c r="Z3" s="161"/>
-      <c r="AA3" s="84"/>
-      <c r="AB3" s="86"/>
-      <c r="AC3" s="113" t="str">
+      <c r="F3" s="135"/>
+      <c r="G3" s="135"/>
+      <c r="H3" s="135"/>
+      <c r="I3" s="135"/>
+      <c r="J3" s="135"/>
+      <c r="K3" s="135"/>
+      <c r="L3" s="135"/>
+      <c r="M3" s="135"/>
+      <c r="N3" s="136"/>
+      <c r="O3" s="175"/>
+      <c r="P3" s="176"/>
+      <c r="Q3" s="176"/>
+      <c r="R3" s="177"/>
+      <c r="S3" s="184"/>
+      <c r="T3" s="185"/>
+      <c r="U3" s="185"/>
+      <c r="V3" s="185"/>
+      <c r="W3" s="185"/>
+      <c r="X3" s="185"/>
+      <c r="Y3" s="185"/>
+      <c r="Z3" s="186"/>
+      <c r="AA3" s="131"/>
+      <c r="AB3" s="133"/>
+      <c r="AC3" s="160" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC3")&lt;&gt;"",INDIRECT("変更履歴!AC3"),"")</f>
         <v/>
       </c>
-      <c r="AD3" s="114"/>
-      <c r="AE3" s="114"/>
-      <c r="AF3" s="115"/>
-      <c r="AG3" s="147" t="str">
+      <c r="AD3" s="161"/>
+      <c r="AE3" s="161"/>
+      <c r="AF3" s="162"/>
+      <c r="AG3" s="166" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AG3")&lt;&gt;"",INDIRECT("変更履歴!AG3"),"")</f>
         <v/>
       </c>
-      <c r="AH3" s="148"/>
-      <c r="AI3" s="149"/>
+      <c r="AH3" s="167"/>
+      <c r="AI3" s="168"/>
       <c r="AJ3" s="9"/>
       <c r="AK3" s="1"/>
       <c r="AL3" s="1"/>
@@ -20121,7 +20939,7 @@
     <row r="69" spans="2:42" x14ac:dyDescent="0.15">
       <c r="B69" s="71"/>
       <c r="C69" s="69"/>
-      <c r="D69" s="171" t="s">
+      <c r="D69" s="76" t="s">
         <v>202</v>
       </c>
       <c r="E69" s="67"/>
@@ -20176,7 +20994,7 @@
     <row r="70" spans="2:42" x14ac:dyDescent="0.15">
       <c r="B70" s="71"/>
       <c r="C70" s="69"/>
-      <c r="D70" s="171" t="s">
+      <c r="D70" s="76" t="s">
         <v>203</v>
       </c>
       <c r="E70" s="67"/>
@@ -20231,7 +21049,7 @@
     <row r="71" spans="2:42" x14ac:dyDescent="0.15">
       <c r="B71" s="71"/>
       <c r="C71" s="69"/>
-      <c r="D71" s="171" t="s">
+      <c r="D71" s="76" t="s">
         <v>204</v>
       </c>
       <c r="E71" s="67"/>
@@ -20286,7 +21104,7 @@
     <row r="72" spans="2:42" x14ac:dyDescent="0.15">
       <c r="B72" s="72"/>
       <c r="C72" s="65"/>
-      <c r="D72" s="171" t="s">
+      <c r="D72" s="76" t="s">
         <v>205</v>
       </c>
       <c r="E72" s="67"/>
@@ -20340,6 +21158,14 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="AG1:AI1"/>
+    <mergeCell ref="AC1:AF1"/>
+    <mergeCell ref="AC2:AF2"/>
+    <mergeCell ref="AG2:AI2"/>
+    <mergeCell ref="E3:N3"/>
+    <mergeCell ref="AA3:AB3"/>
+    <mergeCell ref="AC3:AF3"/>
+    <mergeCell ref="AG3:AI3"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="E1:N1"/>
     <mergeCell ref="O1:R3"/>
@@ -20349,14 +21175,6 @@
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="E2:N2"/>
     <mergeCell ref="AA2:AB2"/>
-    <mergeCell ref="AG1:AI1"/>
-    <mergeCell ref="AC1:AF1"/>
-    <mergeCell ref="AC2:AF2"/>
-    <mergeCell ref="AG2:AI2"/>
-    <mergeCell ref="E3:N3"/>
-    <mergeCell ref="AA3:AB3"/>
-    <mergeCell ref="AC3:AF3"/>
-    <mergeCell ref="AG3:AI3"/>
   </mergeCells>
   <phoneticPr fontId="10"/>
   <printOptions horizontalCentered="1"/>
@@ -20384,59 +21202,59 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:49" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="84" t="s">
+      <c r="A1" s="131" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="85"/>
-      <c r="D1" s="86"/>
-      <c r="E1" s="87" t="str">
+      <c r="B1" s="132"/>
+      <c r="C1" s="132"/>
+      <c r="D1" s="133"/>
+      <c r="E1" s="134" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E1")&lt;&gt;"",INDIRECT("変更履歴!E1"),"")</f>
         <v/>
       </c>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
-      <c r="H1" s="88"/>
-      <c r="I1" s="88"/>
-      <c r="J1" s="88"/>
-      <c r="K1" s="88"/>
-      <c r="L1" s="88"/>
-      <c r="M1" s="88"/>
-      <c r="N1" s="89"/>
-      <c r="O1" s="162" t="s">
+      <c r="F1" s="135"/>
+      <c r="G1" s="135"/>
+      <c r="H1" s="135"/>
+      <c r="I1" s="135"/>
+      <c r="J1" s="135"/>
+      <c r="K1" s="135"/>
+      <c r="L1" s="135"/>
+      <c r="M1" s="135"/>
+      <c r="N1" s="136"/>
+      <c r="O1" s="169" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="163"/>
-      <c r="Q1" s="163"/>
-      <c r="R1" s="164"/>
-      <c r="S1" s="153" t="str">
+      <c r="P1" s="170"/>
+      <c r="Q1" s="170"/>
+      <c r="R1" s="171"/>
+      <c r="S1" s="178" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!S1")&lt;&gt;"",INDIRECT("変更履歴!S1"),"")</f>
         <v>Nablarch開発標準設計書一覧</v>
       </c>
-      <c r="T1" s="154"/>
-      <c r="U1" s="154"/>
-      <c r="V1" s="154"/>
-      <c r="W1" s="154"/>
-      <c r="X1" s="154"/>
-      <c r="Y1" s="154"/>
-      <c r="Z1" s="155"/>
-      <c r="AA1" s="84" t="s">
+      <c r="T1" s="179"/>
+      <c r="U1" s="179"/>
+      <c r="V1" s="179"/>
+      <c r="W1" s="179"/>
+      <c r="X1" s="179"/>
+      <c r="Y1" s="179"/>
+      <c r="Z1" s="180"/>
+      <c r="AA1" s="131" t="s">
         <v>3</v>
       </c>
-      <c r="AB1" s="86"/>
-      <c r="AC1" s="113" t="str">
+      <c r="AB1" s="133"/>
+      <c r="AC1" s="160" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC1")&lt;&gt;"",INDIRECT("変更履歴!AC1"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="114"/>
-      <c r="AE1" s="114"/>
-      <c r="AF1" s="115"/>
-      <c r="AG1" s="147">
+      <c r="AD1" s="161"/>
+      <c r="AE1" s="161"/>
+      <c r="AF1" s="162"/>
+      <c r="AG1" s="166">
         <f ca="1">IF(INDIRECT("変更履歴!AG1")&lt;&gt;"",INDIRECT("変更履歴!AG1"),"")</f>
         <v>43336</v>
       </c>
-      <c r="AH1" s="148"/>
-      <c r="AI1" s="149"/>
+      <c r="AH1" s="167"/>
+      <c r="AI1" s="168"/>
       <c r="AJ1" s="6"/>
       <c r="AN1" s="7"/>
       <c r="AO1" s="6"/>
@@ -20450,54 +21268,54 @@
       <c r="AW1" s="6"/>
     </row>
     <row r="2" spans="1:49" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="84" t="s">
+      <c r="A2" s="131" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="85"/>
-      <c r="C2" s="85"/>
-      <c r="D2" s="86"/>
-      <c r="E2" s="87" t="str">
+      <c r="B2" s="132"/>
+      <c r="C2" s="132"/>
+      <c r="D2" s="133"/>
+      <c r="E2" s="134" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E2")&lt;&gt;"",INDIRECT("変更履歴!E2"),"")</f>
         <v/>
       </c>
-      <c r="F2" s="88"/>
-      <c r="G2" s="88"/>
-      <c r="H2" s="88"/>
-      <c r="I2" s="88"/>
-      <c r="J2" s="88"/>
-      <c r="K2" s="88"/>
-      <c r="L2" s="88"/>
-      <c r="M2" s="88"/>
-      <c r="N2" s="89"/>
-      <c r="O2" s="165"/>
-      <c r="P2" s="166"/>
-      <c r="Q2" s="166"/>
-      <c r="R2" s="167"/>
-      <c r="S2" s="156"/>
-      <c r="T2" s="157"/>
-      <c r="U2" s="157"/>
-      <c r="V2" s="157"/>
-      <c r="W2" s="157"/>
-      <c r="X2" s="157"/>
-      <c r="Y2" s="157"/>
-      <c r="Z2" s="158"/>
-      <c r="AA2" s="84" t="s">
+      <c r="F2" s="135"/>
+      <c r="G2" s="135"/>
+      <c r="H2" s="135"/>
+      <c r="I2" s="135"/>
+      <c r="J2" s="135"/>
+      <c r="K2" s="135"/>
+      <c r="L2" s="135"/>
+      <c r="M2" s="135"/>
+      <c r="N2" s="136"/>
+      <c r="O2" s="172"/>
+      <c r="P2" s="173"/>
+      <c r="Q2" s="173"/>
+      <c r="R2" s="174"/>
+      <c r="S2" s="181"/>
+      <c r="T2" s="182"/>
+      <c r="U2" s="182"/>
+      <c r="V2" s="182"/>
+      <c r="W2" s="182"/>
+      <c r="X2" s="182"/>
+      <c r="Y2" s="182"/>
+      <c r="Z2" s="183"/>
+      <c r="AA2" s="131" t="s">
         <v>4</v>
       </c>
-      <c r="AB2" s="86"/>
-      <c r="AC2" s="113" t="str">
+      <c r="AB2" s="133"/>
+      <c r="AC2" s="160" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC2")&lt;&gt;"",INDIRECT("変更履歴!AC2"),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD2" s="114"/>
-      <c r="AE2" s="114"/>
-      <c r="AF2" s="115"/>
-      <c r="AG2" s="147">
+      <c r="AD2" s="161"/>
+      <c r="AE2" s="161"/>
+      <c r="AF2" s="162"/>
+      <c r="AG2" s="166">
         <f ca="1">IF(INDIRECT("変更履歴!AG2")&lt;&gt;"",INDIRECT("変更履歴!AG2"),"")</f>
-        <v>44848</v>
-      </c>
-      <c r="AH2" s="148"/>
-      <c r="AI2" s="149"/>
+        <v>45565</v>
+      </c>
+      <c r="AH2" s="167"/>
+      <c r="AI2" s="168"/>
       <c r="AJ2" s="6"/>
       <c r="AN2" s="7"/>
       <c r="AO2" s="6"/>
@@ -20511,52 +21329,52 @@
       <c r="AW2" s="6"/>
     </row>
     <row r="3" spans="1:49" s="3" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="84" t="s">
+      <c r="A3" s="131" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="85"/>
-      <c r="C3" s="85"/>
-      <c r="D3" s="86"/>
-      <c r="E3" s="87" t="str">
+      <c r="B3" s="132"/>
+      <c r="C3" s="132"/>
+      <c r="D3" s="133"/>
+      <c r="E3" s="134" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!E3")&lt;&gt;"",INDIRECT("変更履歴!E3"),"")</f>
         <v/>
       </c>
-      <c r="F3" s="88"/>
-      <c r="G3" s="88"/>
-      <c r="H3" s="88"/>
-      <c r="I3" s="88"/>
-      <c r="J3" s="88"/>
-      <c r="K3" s="88"/>
-      <c r="L3" s="88"/>
-      <c r="M3" s="88"/>
-      <c r="N3" s="89"/>
-      <c r="O3" s="168"/>
-      <c r="P3" s="169"/>
-      <c r="Q3" s="169"/>
-      <c r="R3" s="170"/>
-      <c r="S3" s="159"/>
-      <c r="T3" s="160"/>
-      <c r="U3" s="160"/>
-      <c r="V3" s="160"/>
-      <c r="W3" s="160"/>
-      <c r="X3" s="160"/>
-      <c r="Y3" s="160"/>
-      <c r="Z3" s="161"/>
-      <c r="AA3" s="84"/>
-      <c r="AB3" s="86"/>
-      <c r="AC3" s="113" t="str">
+      <c r="F3" s="135"/>
+      <c r="G3" s="135"/>
+      <c r="H3" s="135"/>
+      <c r="I3" s="135"/>
+      <c r="J3" s="135"/>
+      <c r="K3" s="135"/>
+      <c r="L3" s="135"/>
+      <c r="M3" s="135"/>
+      <c r="N3" s="136"/>
+      <c r="O3" s="175"/>
+      <c r="P3" s="176"/>
+      <c r="Q3" s="176"/>
+      <c r="R3" s="177"/>
+      <c r="S3" s="184"/>
+      <c r="T3" s="185"/>
+      <c r="U3" s="185"/>
+      <c r="V3" s="185"/>
+      <c r="W3" s="185"/>
+      <c r="X3" s="185"/>
+      <c r="Y3" s="185"/>
+      <c r="Z3" s="186"/>
+      <c r="AA3" s="131"/>
+      <c r="AB3" s="133"/>
+      <c r="AC3" s="160" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AC3")&lt;&gt;"",INDIRECT("変更履歴!AC3"),"")</f>
         <v/>
       </c>
-      <c r="AD3" s="114"/>
-      <c r="AE3" s="114"/>
-      <c r="AF3" s="115"/>
-      <c r="AG3" s="147" t="str">
+      <c r="AD3" s="161"/>
+      <c r="AE3" s="161"/>
+      <c r="AF3" s="162"/>
+      <c r="AG3" s="166" t="str">
         <f ca="1">IF(INDIRECT("変更履歴!AG3")&lt;&gt;"",INDIRECT("変更履歴!AG3"),"")</f>
         <v/>
       </c>
-      <c r="AH3" s="148"/>
-      <c r="AI3" s="149"/>
+      <c r="AH3" s="167"/>
+      <c r="AI3" s="168"/>
       <c r="AJ3" s="9"/>
       <c r="AK3" s="1"/>
       <c r="AL3" s="1"/>
@@ -20728,6 +21546,14 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="AG1:AI1"/>
+    <mergeCell ref="AC1:AF1"/>
+    <mergeCell ref="AC2:AF2"/>
+    <mergeCell ref="AG2:AI2"/>
+    <mergeCell ref="E3:N3"/>
+    <mergeCell ref="AA3:AB3"/>
+    <mergeCell ref="AC3:AF3"/>
+    <mergeCell ref="AG3:AI3"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="E1:N1"/>
     <mergeCell ref="O1:R3"/>
@@ -20737,14 +21563,6 @@
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="E2:N2"/>
     <mergeCell ref="AA2:AB2"/>
-    <mergeCell ref="AG1:AI1"/>
-    <mergeCell ref="AC1:AF1"/>
-    <mergeCell ref="AC2:AF2"/>
-    <mergeCell ref="AG2:AI2"/>
-    <mergeCell ref="E3:N3"/>
-    <mergeCell ref="AA3:AB3"/>
-    <mergeCell ref="AC3:AF3"/>
-    <mergeCell ref="AG3:AI3"/>
   </mergeCells>
   <phoneticPr fontId="10"/>
   <printOptions horizontalCentered="1"/>
